--- a/Översikt ESLÖV.xlsx
+++ b/Översikt ESLÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45307</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45615</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44960</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>44846</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>45817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>46244</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 14395-2026</t>
+          <t>A 23773-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46100</v>
+        <v>45793</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1336,38 +1336,38 @@
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14395-2026 artfynd.xlsx", "A 14395-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 23773-2025 artfynd.xlsx", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14395-2026 karta.png", "A 14395-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 23773-2025 karta.png", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14395-2026 georefererad karta.tif", "A 14395-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 23773-2025 georefererad karta.tif", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14395-2026 FSC-klagomål.docx", "A 14395-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 23773-2025 FSC-klagomål.docx", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14395-2026 FSC-klagomål mail.docx", "A 14395-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 23773-2025 FSC-klagomål mail.docx", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14395-2026 tillsynsbegäran.docx", "A 14395-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 23773-2025 tillsynsbegäran.docx", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14395-2026 tillsynsbegäran mail.docx", "A 14395-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 23773-2025 tillsynsbegäran mail.docx", "A 23773-2025")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 9487-2023</t>
+          <t>A 14395-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44981</v>
+        <v>46100</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.9</v>
+        <v>4.9</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1406,13 +1406,13 @@
         <v>1</v>
       </c>
       <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
         <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1424,162 +1424,162 @@
         <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>2</v>
       </c>
       <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Kransrams</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14395-2026 artfynd.xlsx", "A 14395-2026")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14395-2026 karta.png", "A 14395-2026")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14395-2026 georefererad karta.tif", "A 14395-2026")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14395-2026 FSC-klagomål.docx", "A 14395-2026")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14395-2026 FSC-klagomål mail.docx", "A 14395-2026")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14395-2026 tillsynsbegäran.docx", "A 14395-2026")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14395-2026 tillsynsbegäran mail.docx", "A 14395-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 9487-2023</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>44981</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ESLÖV</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>2</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Älg
 Kambräken</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 9487-2023 artfynd.xlsx", "A 9487-2023")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 9487-2023 karta.png", "A 9487-2023")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 9487-2023 georefererad karta.tif", "A 9487-2023")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 9487-2023 FSC-klagomål.docx", "A 9487-2023")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 9487-2023 FSC-klagomål mail.docx", "A 9487-2023")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 9487-2023 tillsynsbegäran.docx", "A 9487-2023")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 9487-2023 tillsynsbegäran mail.docx", "A 9487-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 23773-2025</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45793</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>ESLÖV</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>4</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Kransrams</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 23773-2025 artfynd.xlsx", "A 23773-2025")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 23773-2025 karta.png", "A 23773-2025")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 23773-2025 georefererad karta.tif", "A 23773-2025")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 23773-2025 FSC-klagomål.docx", "A 23773-2025")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 23773-2025 FSC-klagomål mail.docx", "A 23773-2025")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 23773-2025 tillsynsbegäran.docx", "A 23773-2025")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 23773-2025 tillsynsbegäran mail.docx", "A 23773-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 14013-2026</t>
+          <t>A 24809-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46098</v>
+        <v>45799</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1608,13 +1608,8 @@
           <t>ESLÖV</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>8.800000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1650,50 +1645,50 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14013-2026 artfynd.xlsx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 24809-2025 artfynd.xlsx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14013-2026 karta.png", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 24809-2025 karta.png", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14013-2026 georefererad karta.tif", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 24809-2025 georefererad karta.tif", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14013-2026 FSC-klagomål.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 24809-2025 FSC-klagomål.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14013-2026 FSC-klagomål mail.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 24809-2025 FSC-klagomål mail.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14013-2026 tillsynsbegäran.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 24809-2025 tillsynsbegäran.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14013-2026 tillsynsbegäran mail.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 24809-2025 tillsynsbegäran mail.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 14013-2026 prioriterade fågelarter.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 24809-2025 prioriterade fågelarter.docx", "A 24809-2025")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 61035-2024</t>
+          <t>A 14013-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1707,10 +1702,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45645</v>
+        <v>46098</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1722,17 +1717,22 @@
           <t>ESLÖV</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1747,7 +1747,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1756,49 +1756,53 @@
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 61035-2024 artfynd.xlsx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14013-2026 artfynd.xlsx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 61035-2024 karta.png", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14013-2026 karta.png", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 61035-2024 georefererad karta.tif", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14013-2026 georefererad karta.tif", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 61035-2024 FSC-klagomål.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14013-2026 FSC-klagomål.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 61035-2024 FSC-klagomål mail.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14013-2026 FSC-klagomål mail.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 61035-2024 tillsynsbegäran.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14013-2026 tillsynsbegäran.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 61035-2024 tillsynsbegäran mail.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14013-2026 tillsynsbegäran mail.docx", "A 14013-2026")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 14013-2026 prioriterade fågelarter.docx", "A 14013-2026")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 1510-2024</t>
+          <t>A 61035-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1812,10 +1816,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45306</v>
+        <v>45645</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1828,17 +1832,17 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.7</v>
+        <v>7.6</v>
       </c>
       <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
@@ -1849,7 +1853,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
@@ -1861,53 +1865,49 @@
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Svart stork</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 1510-2024 artfynd.xlsx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 61035-2024 artfynd.xlsx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 1510-2024 karta.png", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 61035-2024 karta.png", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 1510-2024 georefererad karta.tif", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 61035-2024 georefererad karta.tif", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 1510-2024 FSC-klagomål.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 61035-2024 FSC-klagomål.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 1510-2024 FSC-klagomål mail.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 61035-2024 FSC-klagomål mail.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 1510-2024 tillsynsbegäran.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 61035-2024 tillsynsbegäran.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 1510-2024 tillsynsbegäran mail.docx", "A 1510-2024")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 1510-2024 prioriterade fågelarter.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 61035-2024 tillsynsbegäran mail.docx", "A 61035-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 52652-2023</t>
+          <t>A 1510-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45225</v>
+        <v>45306</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1949,22 +1949,22 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
         <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1977,42 +1977,46 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Grönfläckig padda</t>
+          <t>Svart stork</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 52652-2023 artfynd.xlsx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 1510-2024 artfynd.xlsx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 52652-2023 karta.png", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 1510-2024 karta.png", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 52652-2023 georefererad karta.tif", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 1510-2024 georefererad karta.tif", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 52652-2023 FSC-klagomål.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 1510-2024 FSC-klagomål.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 52652-2023 FSC-klagomål mail.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 1510-2024 FSC-klagomål mail.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 52652-2023 tillsynsbegäran.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 1510-2024 tillsynsbegäran.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 52652-2023 tillsynsbegäran mail.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 1510-2024 tillsynsbegäran mail.docx", "A 1510-2024")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 1510-2024 prioriterade fågelarter.docx", "A 1510-2024")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 18713-2024</t>
+          <t>A 52652-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2026,10 +2030,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45426</v>
+        <v>45225</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2042,7 +2046,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2082,42 +2086,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Gråtrut</t>
+          <t>Grönfläckig padda</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 18713-2024 artfynd.xlsx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 52652-2023 artfynd.xlsx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 18713-2024 karta.png", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 52652-2023 karta.png", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 18713-2024 georefererad karta.tif", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 52652-2023 georefererad karta.tif", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 18713-2024 FSC-klagomål.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 52652-2023 FSC-klagomål.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 18713-2024 FSC-klagomål mail.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 52652-2023 FSC-klagomål mail.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 18713-2024 tillsynsbegäran.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 52652-2023 tillsynsbegäran.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 18713-2024 tillsynsbegäran mail.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 52652-2023 tillsynsbegäran mail.docx", "A 52652-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 24809-2025</t>
+          <t>A 18713-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2131,10 +2135,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45799</v>
+        <v>45426</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2147,7 +2151,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.4</v>
+        <v>4.1</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2159,7 +2163,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2171,10 +2175,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2187,39 +2191,35 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gråtrut</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 24809-2025 artfynd.xlsx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 18713-2024 artfynd.xlsx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 24809-2025 karta.png", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 18713-2024 karta.png", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 24809-2025 georefererad karta.tif", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 18713-2024 georefererad karta.tif", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 24809-2025 FSC-klagomål.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 18713-2024 FSC-klagomål.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 24809-2025 FSC-klagomål mail.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 18713-2024 FSC-klagomål mail.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 24809-2025 tillsynsbegäran.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 18713-2024 tillsynsbegäran.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 24809-2025 tillsynsbegäran mail.docx", "A 24809-2025")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 24809-2025 prioriterade fågelarter.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 18713-2024 tillsynsbegäran mail.docx", "A 18713-2024")</f>
         <v/>
       </c>
     </row>
@@ -2243,7 +2243,7 @@
         <v>44553</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>44690</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 12079-2024</t>
+          <t>A 32984-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2386,10 +2386,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45377</v>
+        <v>45517</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>6.9</v>
+        <v>2.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2445,7 +2445,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 15467-2025</t>
+          <t>A 16792-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45747</v>
+        <v>45411</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2518,7 +2518,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 11221-2024</t>
+          <t>A 47870-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45371</v>
+        <v>45932</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.3</v>
+        <v>6.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 15533-2024</t>
+          <t>A 28088-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2605,10 +2605,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45401</v>
+        <v>45817</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>7.5</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2664,7 +2664,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 5869-2023</t>
+          <t>A 16733-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2674,14 +2674,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44958</v>
+        <v>45030</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 9482-2023</t>
+          <t>A 58721-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2751,10 +2751,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44981</v>
+        <v>45986</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.7</v>
+        <v>2.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2810,7 +2810,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 25385-2023</t>
+          <t>A 47356-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45089</v>
+        <v>45930</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2883,7 +2883,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 43808-2024</t>
+          <t>A 9849-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2893,14 +2893,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45571</v>
+        <v>46072</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2956,7 +2956,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 11204-2023</t>
+          <t>A 5812-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2970,10 +2970,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44992</v>
+        <v>44596</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3029,7 +3029,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 9849-2026</t>
+          <t>A 14386-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3043,10 +3043,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46072</v>
+        <v>46100</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.5</v>
+        <v>12.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3102,7 +3102,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 25508-2023</t>
+          <t>A 35996-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45089</v>
+        <v>45863</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3175,7 +3175,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 9686-2023</t>
+          <t>A 35997-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44984</v>
+        <v>45863</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 47356-2025</t>
+          <t>A 15467-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45930</v>
+        <v>45747</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3321,7 +3321,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 14386-2026</t>
+          <t>A 18281-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3335,10 +3335,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46100</v>
+        <v>46125</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>12.4</v>
+        <v>0.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3394,7 +3394,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 7409-2025</t>
+          <t>A 5869-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3404,14 +3404,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45705</v>
+        <v>44958</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3467,7 +3467,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 35996-2025</t>
+          <t>A 7409-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3481,10 +3481,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45863</v>
+        <v>45705</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3540,7 +3540,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 35997-2025</t>
+          <t>A 9686-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3554,10 +3554,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45863</v>
+        <v>44984</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3613,7 +3613,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 36761-2022</t>
+          <t>A 7016-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3627,10 +3627,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44805</v>
+        <v>45701</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3642,8 +3642,13 @@
           <t>ESLÖV</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>4.8</v>
+        <v>2.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3686,7 +3691,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 18281-2026</t>
+          <t>A 24115-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3700,10 +3705,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46125</v>
+        <v>44725</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3716,7 +3721,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.8</v>
+        <v>4.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3776,7 +3781,7 @@
         <v>45089</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3832,7 +3837,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 47870-2025</t>
+          <t>A 22134-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3846,10 +3851,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45932</v>
+        <v>46153</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3862,7 +3867,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>6.8</v>
+        <v>2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3905,7 +3910,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 10940-2024</t>
+          <t>A 18503-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3919,10 +3924,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45370</v>
+        <v>46127</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3935,7 +3940,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.5</v>
+        <v>4.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3978,7 +3983,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 58721-2025</t>
+          <t>A 10819-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3992,10 +3997,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45986</v>
+        <v>46078</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4008,7 +4013,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.2</v>
+        <v>4.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4051,7 +4056,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 7016-2025</t>
+          <t>A 1574-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4065,10 +4070,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45701</v>
+        <v>45306</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4080,13 +4085,8 @@
           <t>ESLÖV</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4129,7 +4129,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 22134-2026</t>
+          <t>A 25730-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4143,10 +4143,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46153</v>
+        <v>46178</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4202,7 +4202,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 18503-2026</t>
+          <t>A 26165-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4216,10 +4216,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46127</v>
+        <v>46181</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4.9</v>
+        <v>2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4275,7 +4275,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 10819-2026</t>
+          <t>A 26169-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4289,10 +4289,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46078</v>
+        <v>46181</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4.9</v>
+        <v>3.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4348,7 +4348,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 1574-2024</t>
+          <t>A 26497-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4362,10 +4362,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45306</v>
+        <v>46183</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.6</v>
+        <v>1.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4421,7 +4421,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 16670-2025</t>
+          <t>A 27439-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4435,10 +4435,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45754</v>
+        <v>46189</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4494,7 +4494,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 34468-2023</t>
+          <t>A 27428-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45139</v>
+        <v>46189</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>5.5</v>
+        <v>3.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4567,7 +4567,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 25730-2026</t>
+          <t>A 27435-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46178</v>
+        <v>46189</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4640,7 +4640,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 26165-2026</t>
+          <t>A 12079-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4654,10 +4654,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46181</v>
+        <v>45377</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2</v>
+        <v>6.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4713,7 +4713,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 26169-2026</t>
+          <t>A 11204-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4727,10 +4727,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46181</v>
+        <v>44992</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4786,7 +4786,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 26497-2026</t>
+          <t>A 9482-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46183</v>
+        <v>44981</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4859,7 +4859,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 27428-2026</t>
+          <t>A 15533-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46189</v>
+        <v>45401</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.4</v>
+        <v>7.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4932,7 +4932,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 27439-2026</t>
+          <t>A 62496-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4946,10 +4946,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46189</v>
+        <v>45268</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5005,7 +5005,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 62496-2023</t>
+          <t>A 25385-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5019,10 +5019,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45268</v>
+        <v>45089</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5078,7 +5078,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 27435-2026</t>
+          <t>A 34170-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5092,10 +5092,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46189</v>
+        <v>45138</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.9</v>
+        <v>5.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5151,7 +5151,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 34170-2023</t>
+          <t>A 15357-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45138</v>
+        <v>45019</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>5.8</v>
+        <v>1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5224,7 +5224,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 24115-2022</t>
+          <t>A 36761-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5238,10 +5238,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44725</v>
+        <v>44805</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5297,7 +5297,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 9484-2023</t>
+          <t>A 34468-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44981</v>
+        <v>45139</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.4</v>
+        <v>5.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5370,7 +5370,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 16733-2023</t>
+          <t>A 10940-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5384,10 +5384,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45030</v>
+        <v>45370</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5443,7 +5443,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 44496-2023</t>
+          <t>A 11221-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5457,10 +5457,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45189</v>
+        <v>45371</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5516,7 +5516,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 34466-2023</t>
+          <t>A 43808-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5526,14 +5526,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45139</v>
+        <v>45571</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4.3</v>
+        <v>1.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5589,7 +5589,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 33865-2024</t>
+          <t>A 9484-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5603,10 +5603,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45520</v>
+        <v>44981</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5662,7 +5662,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 5812-2022</t>
+          <t>A 44496-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5676,10 +5676,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44596</v>
+        <v>45189</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 38173-2023</t>
+          <t>A 33865-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5749,10 +5749,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45161</v>
+        <v>45520</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5808,7 +5808,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 15357-2023</t>
+          <t>A 16670-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5822,10 +5822,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45019</v>
+        <v>45754</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5881,7 +5881,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 49137-2024</t>
+          <t>A 34466-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5895,10 +5895,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45594</v>
+        <v>45139</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.4</v>
+        <v>4.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5954,7 +5954,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 32984-2024</t>
+          <t>A 38173-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5968,10 +5968,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45517</v>
+        <v>45161</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6027,7 +6027,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 16792-2024</t>
+          <t>A 25508-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6041,10 +6041,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45411</v>
+        <v>45089</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6100,7 +6100,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 28088-2025</t>
+          <t>A 49137-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6114,10 +6114,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45817</v>
+        <v>45594</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>

--- a/Översikt ESLÖV.xlsx
+++ b/Översikt ESLÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45307</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45615</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44960</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>44846</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>45817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>46244</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 23773-2025</t>
+          <t>A 14395-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45793</v>
+        <v>46100</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1336,38 +1336,38 @@
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 23773-2025 artfynd.xlsx", "A 23773-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14395-2026 artfynd.xlsx", "A 14395-2026")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 23773-2025 karta.png", "A 23773-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14395-2026 karta.png", "A 14395-2026")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 23773-2025 georefererad karta.tif", "A 23773-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14395-2026 georefererad karta.tif", "A 14395-2026")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 23773-2025 FSC-klagomål.docx", "A 23773-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14395-2026 FSC-klagomål.docx", "A 14395-2026")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 23773-2025 FSC-klagomål mail.docx", "A 23773-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14395-2026 FSC-klagomål mail.docx", "A 14395-2026")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 23773-2025 tillsynsbegäran.docx", "A 23773-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14395-2026 tillsynsbegäran.docx", "A 14395-2026")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 23773-2025 tillsynsbegäran mail.docx", "A 23773-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14395-2026 tillsynsbegäran mail.docx", "A 14395-2026")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 14395-2026</t>
+          <t>A 9487-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46100</v>
+        <v>44981</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.9</v>
+        <v>1.9</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1406,13 +1406,13 @@
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1424,162 +1424,162 @@
         <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>2</v>
       </c>
       <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Älg
+Kambräken</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 9487-2023 artfynd.xlsx", "A 9487-2023")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 9487-2023 karta.png", "A 9487-2023")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 9487-2023 georefererad karta.tif", "A 9487-2023")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 9487-2023 FSC-klagomål.docx", "A 9487-2023")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 9487-2023 FSC-klagomål mail.docx", "A 9487-2023")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 9487-2023 tillsynsbegäran.docx", "A 9487-2023")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 9487-2023 tillsynsbegäran mail.docx", "A 9487-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 23773-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45793</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ESLÖV</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="n">
         <v>4</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Ask
 Kransrams</t>
         </is>
       </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14395-2026 artfynd.xlsx", "A 14395-2026")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14395-2026 karta.png", "A 14395-2026")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14395-2026 georefererad karta.tif", "A 14395-2026")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14395-2026 FSC-klagomål.docx", "A 14395-2026")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14395-2026 FSC-klagomål mail.docx", "A 14395-2026")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14395-2026 tillsynsbegäran.docx", "A 14395-2026")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14395-2026 tillsynsbegäran mail.docx", "A 14395-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 9487-2023</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>44981</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>ESLÖV</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Älg
-Kambräken</t>
-        </is>
-      </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 9487-2023 artfynd.xlsx", "A 9487-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 23773-2025 artfynd.xlsx", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 9487-2023 karta.png", "A 9487-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 23773-2025 karta.png", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 9487-2023 georefererad karta.tif", "A 9487-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 23773-2025 georefererad karta.tif", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 9487-2023 FSC-klagomål.docx", "A 9487-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 23773-2025 FSC-klagomål.docx", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 9487-2023 FSC-klagomål mail.docx", "A 9487-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 23773-2025 FSC-klagomål mail.docx", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 9487-2023 tillsynsbegäran.docx", "A 9487-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 23773-2025 tillsynsbegäran.docx", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 9487-2023 tillsynsbegäran mail.docx", "A 9487-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 23773-2025 tillsynsbegäran mail.docx", "A 23773-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 24809-2025</t>
+          <t>A 14013-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45799</v>
+        <v>46098</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1608,8 +1608,13 @@
           <t>ESLÖV</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>1.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1645,50 +1650,50 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 24809-2025 artfynd.xlsx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14013-2026 artfynd.xlsx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 24809-2025 karta.png", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14013-2026 karta.png", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 24809-2025 georefererad karta.tif", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14013-2026 georefererad karta.tif", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 24809-2025 FSC-klagomål.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14013-2026 FSC-klagomål.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 24809-2025 FSC-klagomål mail.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14013-2026 FSC-klagomål mail.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 24809-2025 tillsynsbegäran.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14013-2026 tillsynsbegäran.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 24809-2025 tillsynsbegäran mail.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14013-2026 tillsynsbegäran mail.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 24809-2025 prioriterade fågelarter.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 14013-2026 prioriterade fågelarter.docx", "A 14013-2026")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 14013-2026</t>
+          <t>A 61035-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1702,10 +1707,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46098</v>
+        <v>45645</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1717,23 +1722,18 @@
           <t>ESLÖV</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
         <v>1</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
@@ -1747,7 +1747,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1756,53 +1756,49 @@
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14013-2026 artfynd.xlsx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 61035-2024 artfynd.xlsx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14013-2026 karta.png", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 61035-2024 karta.png", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14013-2026 georefererad karta.tif", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 61035-2024 georefererad karta.tif", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14013-2026 FSC-klagomål.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 61035-2024 FSC-klagomål.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14013-2026 FSC-klagomål mail.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 61035-2024 FSC-klagomål mail.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14013-2026 tillsynsbegäran.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 61035-2024 tillsynsbegäran.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14013-2026 tillsynsbegäran mail.docx", "A 14013-2026")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 14013-2026 prioriterade fågelarter.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 61035-2024 tillsynsbegäran mail.docx", "A 61035-2024")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 61035-2024</t>
+          <t>A 1510-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1816,10 +1812,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45645</v>
+        <v>45306</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1832,28 +1828,28 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>7.6</v>
+        <v>3.7</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
         <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
@@ -1865,49 +1861,53 @@
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Svart stork</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 61035-2024 artfynd.xlsx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 1510-2024 artfynd.xlsx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 61035-2024 karta.png", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 1510-2024 karta.png", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 61035-2024 georefererad karta.tif", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 1510-2024 georefererad karta.tif", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 61035-2024 FSC-klagomål.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 1510-2024 FSC-klagomål.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 61035-2024 FSC-klagomål mail.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 1510-2024 FSC-klagomål mail.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 61035-2024 tillsynsbegäran.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 1510-2024 tillsynsbegäran.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 61035-2024 tillsynsbegäran mail.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 1510-2024 tillsynsbegäran mail.docx", "A 1510-2024")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 1510-2024 prioriterade fågelarter.docx", "A 1510-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 1510-2024</t>
+          <t>A 52652-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45306</v>
+        <v>45225</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1949,7 +1949,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1958,13 +1958,13 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1977,46 +1977,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Svart stork</t>
+          <t>Grönfläckig padda</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 1510-2024 artfynd.xlsx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 52652-2023 artfynd.xlsx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 1510-2024 karta.png", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 52652-2023 karta.png", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 1510-2024 georefererad karta.tif", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 52652-2023 georefererad karta.tif", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 1510-2024 FSC-klagomål.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 52652-2023 FSC-klagomål.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 1510-2024 FSC-klagomål mail.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 52652-2023 FSC-klagomål mail.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 1510-2024 tillsynsbegäran.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 52652-2023 tillsynsbegäran.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 1510-2024 tillsynsbegäran mail.docx", "A 1510-2024")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 1510-2024 prioriterade fågelarter.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 52652-2023 tillsynsbegäran mail.docx", "A 52652-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 52652-2023</t>
+          <t>A 18713-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2030,10 +2026,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45225</v>
+        <v>45426</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2046,7 +2042,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2086,42 +2082,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Grönfläckig padda</t>
+          <t>Gråtrut</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 52652-2023 artfynd.xlsx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 18713-2024 artfynd.xlsx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 52652-2023 karta.png", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 18713-2024 karta.png", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 52652-2023 georefererad karta.tif", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 18713-2024 georefererad karta.tif", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 52652-2023 FSC-klagomål.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 18713-2024 FSC-klagomål.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 52652-2023 FSC-klagomål mail.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 18713-2024 FSC-klagomål mail.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 52652-2023 tillsynsbegäran.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 18713-2024 tillsynsbegäran.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 52652-2023 tillsynsbegäran mail.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 18713-2024 tillsynsbegäran mail.docx", "A 18713-2024")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 18713-2024</t>
+          <t>A 24809-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2135,10 +2131,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45426</v>
+        <v>45799</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2151,7 +2147,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.1</v>
+        <v>1.4</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2163,7 +2159,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2175,10 +2171,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2191,35 +2187,39 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Gråtrut</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 18713-2024 artfynd.xlsx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 24809-2025 artfynd.xlsx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 18713-2024 karta.png", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 24809-2025 karta.png", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 18713-2024 georefererad karta.tif", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 24809-2025 georefererad karta.tif", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 18713-2024 FSC-klagomål.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 24809-2025 FSC-klagomål.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 18713-2024 FSC-klagomål mail.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 24809-2025 FSC-klagomål mail.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 18713-2024 tillsynsbegäran.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 24809-2025 tillsynsbegäran.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 18713-2024 tillsynsbegäran mail.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 24809-2025 tillsynsbegäran mail.docx", "A 24809-2025")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 24809-2025 prioriterade fågelarter.docx", "A 24809-2025")</f>
         <v/>
       </c>
     </row>
@@ -2243,7 +2243,7 @@
         <v>44553</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>44690</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 32984-2024</t>
+          <t>A 12079-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2386,10 +2386,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45517</v>
+        <v>45377</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.9</v>
+        <v>6.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2445,7 +2445,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 16792-2024</t>
+          <t>A 15533-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45411</v>
+        <v>45401</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.9</v>
+        <v>7.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2518,7 +2518,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 47870-2025</t>
+          <t>A 11221-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45932</v>
+        <v>45371</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>6.8</v>
+        <v>0.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 28088-2025</t>
+          <t>A 15467-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2605,10 +2605,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45817</v>
+        <v>45747</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2664,7 +2664,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 16733-2023</t>
+          <t>A 16670-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2678,10 +2678,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45030</v>
+        <v>45754</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 58721-2025</t>
+          <t>A 34468-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2751,10 +2751,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45986</v>
+        <v>45139</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.2</v>
+        <v>5.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2810,7 +2810,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 47356-2025</t>
+          <t>A 5869-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2820,14 +2820,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45930</v>
+        <v>44958</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2883,7 +2883,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 9849-2026</t>
+          <t>A 62496-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2897,10 +2897,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46072</v>
+        <v>45268</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2956,7 +2956,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 5812-2022</t>
+          <t>A 9482-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2970,10 +2970,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44596</v>
+        <v>44981</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3029,7 +3029,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 14386-2026</t>
+          <t>A 25385-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3043,10 +3043,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46100</v>
+        <v>45089</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>12.4</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3102,7 +3102,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 35996-2025</t>
+          <t>A 14386-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45863</v>
+        <v>46100</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.8</v>
+        <v>12.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3175,7 +3175,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 35997-2025</t>
+          <t>A 43808-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3185,14 +3185,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45863</v>
+        <v>45571</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 15467-2025</t>
+          <t>A 18281-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45747</v>
+        <v>46125</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3321,7 +3321,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 18281-2026</t>
+          <t>A 47356-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3335,10 +3335,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46125</v>
+        <v>45930</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3394,7 +3394,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 5869-2023</t>
+          <t>A 34170-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3404,14 +3404,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44958</v>
+        <v>45138</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3</v>
+        <v>5.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3467,7 +3467,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 7409-2025</t>
+          <t>A 11204-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3481,10 +3481,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45705</v>
+        <v>44992</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3540,7 +3540,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 9686-2023</t>
+          <t>A 35996-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3554,10 +3554,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44984</v>
+        <v>45863</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 7016-2025</t>
+          <t>A 35997-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3627,10 +3627,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45701</v>
+        <v>45863</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3642,13 +3642,8 @@
           <t>ESLÖV</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3691,7 +3686,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 24115-2022</t>
+          <t>A 25508-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3705,10 +3700,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44725</v>
+        <v>45089</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3721,7 +3716,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.4</v>
+        <v>0.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3764,7 +3759,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 25388-2023</t>
+          <t>A 9686-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3778,10 +3773,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45089</v>
+        <v>44984</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3794,7 +3789,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3837,7 +3832,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 22134-2026</t>
+          <t>A 24115-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3851,10 +3846,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46153</v>
+        <v>44725</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3867,7 +3862,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>4.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3910,7 +3905,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 18503-2026</t>
+          <t>A 7409-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3924,10 +3919,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46127</v>
+        <v>45705</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3940,7 +3935,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>4.9</v>
+        <v>1.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3983,7 +3978,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 10819-2026</t>
+          <t>A 22134-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3997,10 +3992,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46078</v>
+        <v>46153</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4013,7 +4008,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>4.9</v>
+        <v>2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4056,7 +4051,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 1574-2024</t>
+          <t>A 18503-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4070,10 +4065,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45306</v>
+        <v>46127</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4086,7 +4081,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4129,7 +4124,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 25730-2026</t>
+          <t>A 47870-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4143,10 +4138,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46178</v>
+        <v>45932</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4159,7 +4154,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.4</v>
+        <v>6.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4202,7 +4197,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 26165-2026</t>
+          <t>A 36761-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4216,10 +4211,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46181</v>
+        <v>44805</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4232,7 +4227,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2</v>
+        <v>4.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4275,7 +4270,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 26169-2026</t>
+          <t>A 10819-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4289,10 +4284,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46181</v>
+        <v>46078</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4305,7 +4300,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4348,7 +4343,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 26497-2026</t>
+          <t>A 1574-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4362,10 +4357,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46183</v>
+        <v>45306</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4378,7 +4373,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.4</v>
+        <v>3.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4421,7 +4416,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 27439-2026</t>
+          <t>A 25388-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4435,10 +4430,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46189</v>
+        <v>45089</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4451,7 +4446,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4494,7 +4489,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 27428-2026</t>
+          <t>A 58721-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4508,10 +4503,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46189</v>
+        <v>45986</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4524,7 +4519,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4567,7 +4562,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 27435-2026</t>
+          <t>A 25730-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4581,10 +4576,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46189</v>
+        <v>46178</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4597,7 +4592,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4640,7 +4635,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 12079-2024</t>
+          <t>A 26165-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4654,10 +4649,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45377</v>
+        <v>46181</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4670,7 +4665,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>6.9</v>
+        <v>2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4713,7 +4708,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 11204-2023</t>
+          <t>A 26169-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4727,10 +4722,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44992</v>
+        <v>46181</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4743,7 +4738,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4786,7 +4781,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 9482-2023</t>
+          <t>A 26497-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4800,10 +4795,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44981</v>
+        <v>46183</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4816,7 +4811,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4859,7 +4854,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 15533-2024</t>
+          <t>A 10940-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4873,10 +4868,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45401</v>
+        <v>45370</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4889,7 +4884,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>7.5</v>
+        <v>0.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4932,7 +4927,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 62496-2023</t>
+          <t>A 9849-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4946,10 +4941,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45268</v>
+        <v>46072</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4962,7 +4957,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5005,7 +5000,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 25385-2023</t>
+          <t>A 27428-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5019,10 +5014,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45089</v>
+        <v>46189</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5035,7 +5030,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5078,7 +5073,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 34170-2023</t>
+          <t>A 27439-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5092,10 +5087,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45138</v>
+        <v>46189</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5108,7 +5103,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>5.8</v>
+        <v>1.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5151,7 +5146,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 15357-2023</t>
+          <t>A 27435-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5165,10 +5160,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45019</v>
+        <v>46189</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5181,7 +5176,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5224,7 +5219,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 36761-2022</t>
+          <t>A 9484-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5238,10 +5233,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44805</v>
+        <v>44981</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5254,7 +5249,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4.8</v>
+        <v>1.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5297,7 +5292,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 34468-2023</t>
+          <t>A 16733-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5311,10 +5306,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45139</v>
+        <v>45030</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5327,7 +5322,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>5.5</v>
+        <v>2.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5370,7 +5365,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 10940-2024</t>
+          <t>A 44496-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5384,10 +5379,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45370</v>
+        <v>45189</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5443,7 +5438,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 11221-2024</t>
+          <t>A 7016-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5457,10 +5452,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45371</v>
+        <v>45701</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5472,8 +5467,13 @@
           <t>ESLÖV</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>0.3</v>
+        <v>2.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5516,7 +5516,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 43808-2024</t>
+          <t>A 34466-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5526,14 +5526,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45571</v>
+        <v>45139</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.5</v>
+        <v>4.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5589,7 +5589,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 9484-2023</t>
+          <t>A 33865-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5603,10 +5603,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44981</v>
+        <v>45520</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5662,7 +5662,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 44496-2023</t>
+          <t>A 5812-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5676,10 +5676,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45189</v>
+        <v>44596</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 33865-2024</t>
+          <t>A 38173-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5749,10 +5749,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45520</v>
+        <v>45161</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5808,7 +5808,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 16670-2025</t>
+          <t>A 15357-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5822,10 +5822,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45754</v>
+        <v>45019</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5881,7 +5881,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 34466-2023</t>
+          <t>A 49137-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5895,10 +5895,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45139</v>
+        <v>45594</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>4.3</v>
+        <v>2.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5954,7 +5954,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 38173-2023</t>
+          <t>A 32984-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5968,10 +5968,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45161</v>
+        <v>45517</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6027,7 +6027,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 25508-2023</t>
+          <t>A 16792-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6041,10 +6041,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45089</v>
+        <v>45411</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6100,7 +6100,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 49137-2024</t>
+          <t>A 28088-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6114,10 +6114,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45594</v>
+        <v>45817</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>

--- a/Översikt ESLÖV.xlsx
+++ b/Översikt ESLÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45307</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45615</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44960</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>44846</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>45817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>46244</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>46100</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>44981</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>45793</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 14013-2026</t>
+          <t>A 24809-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46098</v>
+        <v>45799</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1608,13 +1608,8 @@
           <t>ESLÖV</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>8.800000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1650,50 +1645,50 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14013-2026 artfynd.xlsx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 24809-2025 artfynd.xlsx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14013-2026 karta.png", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 24809-2025 karta.png", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14013-2026 georefererad karta.tif", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 24809-2025 georefererad karta.tif", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14013-2026 FSC-klagomål.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 24809-2025 FSC-klagomål.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14013-2026 FSC-klagomål mail.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 24809-2025 FSC-klagomål mail.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14013-2026 tillsynsbegäran.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 24809-2025 tillsynsbegäran.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14013-2026 tillsynsbegäran mail.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 24809-2025 tillsynsbegäran mail.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 14013-2026 prioriterade fågelarter.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 24809-2025 prioriterade fågelarter.docx", "A 24809-2025")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 61035-2024</t>
+          <t>A 14013-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1707,10 +1702,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45645</v>
+        <v>46098</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1722,17 +1717,22 @@
           <t>ESLÖV</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1747,7 +1747,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1756,49 +1756,53 @@
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 61035-2024 artfynd.xlsx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14013-2026 artfynd.xlsx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 61035-2024 karta.png", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14013-2026 karta.png", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 61035-2024 georefererad karta.tif", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14013-2026 georefererad karta.tif", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 61035-2024 FSC-klagomål.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14013-2026 FSC-klagomål.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 61035-2024 FSC-klagomål mail.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14013-2026 FSC-klagomål mail.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 61035-2024 tillsynsbegäran.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14013-2026 tillsynsbegäran.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 61035-2024 tillsynsbegäran mail.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14013-2026 tillsynsbegäran mail.docx", "A 14013-2026")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 14013-2026 prioriterade fågelarter.docx", "A 14013-2026")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 1510-2024</t>
+          <t>A 61035-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1812,10 +1816,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45306</v>
+        <v>45645</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1828,17 +1832,17 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.7</v>
+        <v>7.6</v>
       </c>
       <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
@@ -1849,7 +1853,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
@@ -1861,53 +1865,49 @@
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Svart stork</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 1510-2024 artfynd.xlsx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 61035-2024 artfynd.xlsx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 1510-2024 karta.png", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 61035-2024 karta.png", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 1510-2024 georefererad karta.tif", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 61035-2024 georefererad karta.tif", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 1510-2024 FSC-klagomål.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 61035-2024 FSC-klagomål.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 1510-2024 FSC-klagomål mail.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 61035-2024 FSC-klagomål mail.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 1510-2024 tillsynsbegäran.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 61035-2024 tillsynsbegäran.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 1510-2024 tillsynsbegäran mail.docx", "A 1510-2024")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 1510-2024 prioriterade fågelarter.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 61035-2024 tillsynsbegäran mail.docx", "A 61035-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 52652-2023</t>
+          <t>A 1510-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45225</v>
+        <v>45306</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1949,22 +1949,22 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
         <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1977,42 +1977,46 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Grönfläckig padda</t>
+          <t>Svart stork</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 52652-2023 artfynd.xlsx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 1510-2024 artfynd.xlsx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 52652-2023 karta.png", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 1510-2024 karta.png", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 52652-2023 georefererad karta.tif", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 1510-2024 georefererad karta.tif", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 52652-2023 FSC-klagomål.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 1510-2024 FSC-klagomål.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 52652-2023 FSC-klagomål mail.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 1510-2024 FSC-klagomål mail.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 52652-2023 tillsynsbegäran.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 1510-2024 tillsynsbegäran.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 52652-2023 tillsynsbegäran mail.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 1510-2024 tillsynsbegäran mail.docx", "A 1510-2024")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 1510-2024 prioriterade fågelarter.docx", "A 1510-2024")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 18713-2024</t>
+          <t>A 52652-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2026,10 +2030,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45426</v>
+        <v>45225</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2042,7 +2046,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2082,42 +2086,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Gråtrut</t>
+          <t>Grönfläckig padda</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 18713-2024 artfynd.xlsx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 52652-2023 artfynd.xlsx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 18713-2024 karta.png", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 52652-2023 karta.png", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 18713-2024 georefererad karta.tif", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 52652-2023 georefererad karta.tif", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 18713-2024 FSC-klagomål.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 52652-2023 FSC-klagomål.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 18713-2024 FSC-klagomål mail.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 52652-2023 FSC-klagomål mail.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 18713-2024 tillsynsbegäran.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 52652-2023 tillsynsbegäran.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 18713-2024 tillsynsbegäran mail.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 52652-2023 tillsynsbegäran mail.docx", "A 52652-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 24809-2025</t>
+          <t>A 18713-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2131,10 +2135,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45799</v>
+        <v>45426</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2147,7 +2151,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.4</v>
+        <v>4.1</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2159,7 +2163,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2171,10 +2175,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2187,39 +2191,35 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gråtrut</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 24809-2025 artfynd.xlsx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 18713-2024 artfynd.xlsx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 24809-2025 karta.png", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 18713-2024 karta.png", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 24809-2025 georefererad karta.tif", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 18713-2024 georefererad karta.tif", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 24809-2025 FSC-klagomål.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 18713-2024 FSC-klagomål.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 24809-2025 FSC-klagomål mail.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 18713-2024 FSC-klagomål mail.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 24809-2025 tillsynsbegäran.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 18713-2024 tillsynsbegäran.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 24809-2025 tillsynsbegäran mail.docx", "A 24809-2025")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 24809-2025 prioriterade fågelarter.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 18713-2024 tillsynsbegäran mail.docx", "A 18713-2024")</f>
         <v/>
       </c>
     </row>
@@ -2243,7 +2243,7 @@
         <v>44553</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>44690</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 12079-2024</t>
+          <t>A 16792-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2386,10 +2386,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45377</v>
+        <v>45411</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>6.9</v>
+        <v>0.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2445,7 +2445,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 15533-2024</t>
+          <t>A 47870-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45401</v>
+        <v>45932</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2518,7 +2518,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 11221-2024</t>
+          <t>A 28088-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45371</v>
+        <v>45817</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 15467-2025</t>
+          <t>A 16733-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2605,10 +2605,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45747</v>
+        <v>45030</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2664,7 +2664,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 16670-2025</t>
+          <t>A 5812-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2678,10 +2678,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45754</v>
+        <v>44596</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 34468-2023</t>
+          <t>A 47356-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2751,10 +2751,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45139</v>
+        <v>45930</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>5.5</v>
+        <v>0.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2810,7 +2810,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 5869-2023</t>
+          <t>A 35996-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2820,14 +2820,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44958</v>
+        <v>45863</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2883,7 +2883,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 62496-2023</t>
+          <t>A 58721-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2897,10 +2897,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45268</v>
+        <v>45986</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2956,7 +2956,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 9482-2023</t>
+          <t>A 35997-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2970,10 +2970,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44981</v>
+        <v>45863</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3029,7 +3029,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 25385-2023</t>
+          <t>A 15467-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3043,10 +3043,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45089</v>
+        <v>45747</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3102,7 +3102,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 14386-2026</t>
+          <t>A 5869-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3112,14 +3112,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46100</v>
+        <v>44958</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>12.4</v>
+        <v>3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3175,7 +3175,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 43808-2024</t>
+          <t>A 7409-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3185,14 +3185,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45571</v>
+        <v>45705</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 18281-2026</t>
+          <t>A 9686-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46125</v>
+        <v>44984</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 47356-2025</t>
+          <t>A 7016-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3335,10 +3335,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45930</v>
+        <v>45701</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3350,8 +3350,13 @@
           <t>ESLÖV</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3394,7 +3399,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 34170-2023</t>
+          <t>A 9849-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3408,10 +3413,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45138</v>
+        <v>46072</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3424,7 +3429,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>5.8</v>
+        <v>2.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3467,7 +3472,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 11204-2023</t>
+          <t>A 24115-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3481,10 +3486,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44992</v>
+        <v>44725</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3497,7 +3502,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.7</v>
+        <v>4.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3540,7 +3545,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 35996-2025</t>
+          <t>A 14386-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3554,10 +3559,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45863</v>
+        <v>46100</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3570,7 +3575,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.8</v>
+        <v>12.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3613,7 +3618,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 35997-2025</t>
+          <t>A 25388-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3627,10 +3632,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45863</v>
+        <v>45089</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3643,7 +3648,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3686,7 +3691,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 25508-2023</t>
+          <t>A 18281-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3700,10 +3705,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45089</v>
+        <v>46125</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3716,7 +3721,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3759,7 +3764,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 9686-2023</t>
+          <t>A 12079-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3773,10 +3778,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44984</v>
+        <v>45377</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3789,7 +3794,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.8</v>
+        <v>6.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3832,7 +3837,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 24115-2022</t>
+          <t>A 11204-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3846,10 +3851,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44725</v>
+        <v>44992</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3862,7 +3867,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4.4</v>
+        <v>0.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3905,7 +3910,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 7409-2025</t>
+          <t>A 9482-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3919,10 +3924,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45705</v>
+        <v>44981</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3935,7 +3940,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3978,7 +3983,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 22134-2026</t>
+          <t>A 15533-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3992,10 +3997,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46153</v>
+        <v>45401</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4008,7 +4013,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>7.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4051,7 +4056,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 18503-2026</t>
+          <t>A 62496-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4065,10 +4070,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46127</v>
+        <v>45268</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4081,7 +4086,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>4.9</v>
+        <v>2.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4124,7 +4129,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 47870-2025</t>
+          <t>A 25385-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4138,10 +4143,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45932</v>
+        <v>45089</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4154,7 +4159,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>6.8</v>
+        <v>0.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4197,7 +4202,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 36761-2022</t>
+          <t>A 34170-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4211,10 +4216,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44805</v>
+        <v>45138</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4227,7 +4232,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4270,7 +4275,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 10819-2026</t>
+          <t>A 22134-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4284,10 +4289,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46078</v>
+        <v>46153</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4300,7 +4305,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4.9</v>
+        <v>2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4343,7 +4348,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 1574-2024</t>
+          <t>A 15357-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4357,10 +4362,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45306</v>
+        <v>45019</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4373,7 +4378,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4416,7 +4421,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 25388-2023</t>
+          <t>A 36761-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4430,10 +4435,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45089</v>
+        <v>44805</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4446,7 +4451,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4489,7 +4494,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 58721-2025</t>
+          <t>A 18503-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4503,10 +4508,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45986</v>
+        <v>46127</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4519,7 +4524,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.2</v>
+        <v>4.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4562,7 +4567,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 25730-2026</t>
+          <t>A 10819-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4576,10 +4581,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46178</v>
+        <v>46078</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4592,7 +4597,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.4</v>
+        <v>4.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4635,7 +4640,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 26165-2026</t>
+          <t>A 34468-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4649,10 +4654,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46181</v>
+        <v>45139</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4665,7 +4670,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4708,7 +4713,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 26169-2026</t>
+          <t>A 1574-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4722,10 +4727,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46181</v>
+        <v>45306</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4738,7 +4743,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4781,7 +4786,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 26497-2026</t>
+          <t>A 25730-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4795,10 +4800,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46183</v>
+        <v>46178</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4854,7 +4859,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 10940-2024</t>
+          <t>A 26165-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4868,10 +4873,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45370</v>
+        <v>46181</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4884,7 +4889,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4927,7 +4932,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 9849-2026</t>
+          <t>A 26169-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4941,10 +4946,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46072</v>
+        <v>46181</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4957,7 +4962,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5000,7 +5005,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 27428-2026</t>
+          <t>A 26497-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5014,10 +5019,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46189</v>
+        <v>46183</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5030,7 +5035,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5090,7 +5095,7 @@
         <v>46189</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5146,7 +5151,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 27435-2026</t>
+          <t>A 27428-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5163,7 +5168,7 @@
         <v>46189</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5176,7 +5181,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5219,7 +5224,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 9484-2023</t>
+          <t>A 27435-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5233,10 +5238,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44981</v>
+        <v>46189</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5249,7 +5254,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5292,7 +5297,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 16733-2023</t>
+          <t>A 10940-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5306,10 +5311,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45030</v>
+        <v>45370</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5322,7 +5327,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5365,7 +5370,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 44496-2023</t>
+          <t>A 11221-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5379,10 +5384,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45189</v>
+        <v>45371</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5395,7 +5400,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5438,7 +5443,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 7016-2025</t>
+          <t>A 43808-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5448,14 +5453,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45701</v>
+        <v>45571</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5467,13 +5472,8 @@
           <t>ESLÖV</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5516,7 +5516,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 34466-2023</t>
+          <t>A 9484-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5530,10 +5530,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45139</v>
+        <v>44981</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4.3</v>
+        <v>1.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5589,7 +5589,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 33865-2024</t>
+          <t>A 44496-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5603,10 +5603,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45520</v>
+        <v>45189</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5662,7 +5662,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 5812-2022</t>
+          <t>A 33865-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5676,10 +5676,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44596</v>
+        <v>45520</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5735,7 +5735,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 38173-2023</t>
+          <t>A 16670-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5749,10 +5749,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45161</v>
+        <v>45754</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5808,7 +5808,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 15357-2023</t>
+          <t>A 34466-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5822,10 +5822,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45019</v>
+        <v>45139</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>4.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5881,7 +5881,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 49137-2024</t>
+          <t>A 38173-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5895,10 +5895,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45594</v>
+        <v>45161</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5954,7 +5954,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 32984-2024</t>
+          <t>A 25508-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5968,10 +5968,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45517</v>
+        <v>45089</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.9</v>
+        <v>0.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6027,7 +6027,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 16792-2024</t>
+          <t>A 49137-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6041,10 +6041,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45411</v>
+        <v>45594</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6100,7 +6100,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 28088-2025</t>
+          <t>A 32984-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6114,10 +6114,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45817</v>
+        <v>45517</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>

--- a/Översikt ESLÖV.xlsx
+++ b/Översikt ESLÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45307</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45615</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44960</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>44846</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>45817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>46244</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>46100</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>44981</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>45793</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 24809-2025</t>
+          <t>A 14013-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45799</v>
+        <v>46098</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1608,8 +1608,13 @@
           <t>ESLÖV</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>1.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1645,50 +1650,50 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 24809-2025 artfynd.xlsx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14013-2026 artfynd.xlsx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 24809-2025 karta.png", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14013-2026 karta.png", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 24809-2025 georefererad karta.tif", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14013-2026 georefererad karta.tif", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 24809-2025 FSC-klagomål.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14013-2026 FSC-klagomål.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 24809-2025 FSC-klagomål mail.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14013-2026 FSC-klagomål mail.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 24809-2025 tillsynsbegäran.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14013-2026 tillsynsbegäran.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 24809-2025 tillsynsbegäran mail.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14013-2026 tillsynsbegäran mail.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 24809-2025 prioriterade fågelarter.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 14013-2026 prioriterade fågelarter.docx", "A 14013-2026")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 14013-2026</t>
+          <t>A 61035-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1702,10 +1707,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46098</v>
+        <v>45645</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1717,23 +1722,18 @@
           <t>ESLÖV</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
         <v>1</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
@@ -1747,7 +1747,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1756,53 +1756,49 @@
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14013-2026 artfynd.xlsx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 61035-2024 artfynd.xlsx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14013-2026 karta.png", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 61035-2024 karta.png", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14013-2026 georefererad karta.tif", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 61035-2024 georefererad karta.tif", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14013-2026 FSC-klagomål.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 61035-2024 FSC-klagomål.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14013-2026 FSC-klagomål mail.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 61035-2024 FSC-klagomål mail.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14013-2026 tillsynsbegäran.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 61035-2024 tillsynsbegäran.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14013-2026 tillsynsbegäran mail.docx", "A 14013-2026")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 14013-2026 prioriterade fågelarter.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 61035-2024 tillsynsbegäran mail.docx", "A 61035-2024")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 61035-2024</t>
+          <t>A 1510-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1816,10 +1812,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45645</v>
+        <v>45306</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1832,28 +1828,28 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>7.6</v>
+        <v>3.7</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
         <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
@@ -1865,49 +1861,53 @@
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Svart stork</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 61035-2024 artfynd.xlsx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 1510-2024 artfynd.xlsx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 61035-2024 karta.png", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 1510-2024 karta.png", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 61035-2024 georefererad karta.tif", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 1510-2024 georefererad karta.tif", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 61035-2024 FSC-klagomål.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 1510-2024 FSC-klagomål.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 61035-2024 FSC-klagomål mail.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 1510-2024 FSC-klagomål mail.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 61035-2024 tillsynsbegäran.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 1510-2024 tillsynsbegäran.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 61035-2024 tillsynsbegäran mail.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 1510-2024 tillsynsbegäran mail.docx", "A 1510-2024")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 1510-2024 prioriterade fågelarter.docx", "A 1510-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 1510-2024</t>
+          <t>A 52652-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45306</v>
+        <v>45225</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1949,7 +1949,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1958,13 +1958,13 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1977,46 +1977,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Svart stork</t>
+          <t>Grönfläckig padda</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 1510-2024 artfynd.xlsx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 52652-2023 artfynd.xlsx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 1510-2024 karta.png", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 52652-2023 karta.png", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 1510-2024 georefererad karta.tif", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 52652-2023 georefererad karta.tif", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 1510-2024 FSC-klagomål.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 52652-2023 FSC-klagomål.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 1510-2024 FSC-klagomål mail.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 52652-2023 FSC-klagomål mail.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 1510-2024 tillsynsbegäran.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 52652-2023 tillsynsbegäran.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 1510-2024 tillsynsbegäran mail.docx", "A 1510-2024")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 1510-2024 prioriterade fågelarter.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 52652-2023 tillsynsbegäran mail.docx", "A 52652-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 52652-2023</t>
+          <t>A 18713-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2030,10 +2026,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45225</v>
+        <v>45426</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2046,7 +2042,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2086,42 +2082,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Grönfläckig padda</t>
+          <t>Gråtrut</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 52652-2023 artfynd.xlsx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 18713-2024 artfynd.xlsx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 52652-2023 karta.png", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 18713-2024 karta.png", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 52652-2023 georefererad karta.tif", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 18713-2024 georefererad karta.tif", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 52652-2023 FSC-klagomål.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 18713-2024 FSC-klagomål.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 52652-2023 FSC-klagomål mail.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 18713-2024 FSC-klagomål mail.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 52652-2023 tillsynsbegäran.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 18713-2024 tillsynsbegäran.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 52652-2023 tillsynsbegäran mail.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 18713-2024 tillsynsbegäran mail.docx", "A 18713-2024")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 18713-2024</t>
+          <t>A 24809-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2135,10 +2131,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45426</v>
+        <v>45799</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2151,7 +2147,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.1</v>
+        <v>1.4</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2163,7 +2159,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2175,10 +2171,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2191,35 +2187,39 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Gråtrut</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 18713-2024 artfynd.xlsx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 24809-2025 artfynd.xlsx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 18713-2024 karta.png", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 24809-2025 karta.png", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 18713-2024 georefererad karta.tif", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 24809-2025 georefererad karta.tif", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 18713-2024 FSC-klagomål.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 24809-2025 FSC-klagomål.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 18713-2024 FSC-klagomål mail.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 24809-2025 FSC-klagomål mail.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 18713-2024 tillsynsbegäran.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 24809-2025 tillsynsbegäran.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 18713-2024 tillsynsbegäran mail.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 24809-2025 tillsynsbegäran mail.docx", "A 24809-2025")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 24809-2025 prioriterade fågelarter.docx", "A 24809-2025")</f>
         <v/>
       </c>
     </row>
@@ -2243,7 +2243,7 @@
         <v>44553</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>44690</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 16792-2024</t>
+          <t>A 12079-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2386,10 +2386,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45411</v>
+        <v>45377</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.9</v>
+        <v>6.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2445,7 +2445,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 47870-2025</t>
+          <t>A 15533-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45932</v>
+        <v>45401</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2518,7 +2518,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 28088-2025</t>
+          <t>A 11221-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45817</v>
+        <v>45371</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 16733-2023</t>
+          <t>A 15467-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2605,10 +2605,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45030</v>
+        <v>45747</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2664,7 +2664,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 5812-2022</t>
+          <t>A 5869-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2674,14 +2674,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44596</v>
+        <v>44958</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 47356-2025</t>
+          <t>A 25385-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2751,10 +2751,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45930</v>
+        <v>45089</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2810,7 +2810,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 35996-2025</t>
+          <t>A 9482-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45863</v>
+        <v>44981</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2883,7 +2883,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 58721-2025</t>
+          <t>A 43808-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2893,14 +2893,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45986</v>
+        <v>45571</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2956,7 +2956,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 35997-2025</t>
+          <t>A 9849-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2970,10 +2970,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45863</v>
+        <v>46072</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3029,7 +3029,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 15467-2025</t>
+          <t>A 11204-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3043,10 +3043,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45747</v>
+        <v>44992</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3102,7 +3102,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 5869-2023</t>
+          <t>A 14386-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3112,14 +3112,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44958</v>
+        <v>46100</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3</v>
+        <v>12.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3175,7 +3175,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 7409-2025</t>
+          <t>A 25508-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45705</v>
+        <v>45089</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3265,7 +3265,7 @@
         <v>44984</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 7016-2025</t>
+          <t>A 18281-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3335,10 +3335,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45701</v>
+        <v>46125</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3350,13 +3350,8 @@
           <t>ESLÖV</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3399,7 +3394,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 9849-2026</t>
+          <t>A 7409-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3413,10 +3408,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46072</v>
+        <v>45705</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3429,7 +3424,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3472,7 +3467,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 24115-2022</t>
+          <t>A 36761-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3486,10 +3481,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44725</v>
+        <v>44805</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3502,7 +3497,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3545,7 +3540,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 14386-2026</t>
+          <t>A 25388-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3559,10 +3554,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46100</v>
+        <v>45089</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3575,7 +3570,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>12.4</v>
+        <v>0.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3618,7 +3613,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 25388-2023</t>
+          <t>A 47356-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3632,10 +3627,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45089</v>
+        <v>45930</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3648,7 +3643,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3691,7 +3686,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 18281-2026</t>
+          <t>A 22134-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3705,10 +3700,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46125</v>
+        <v>46153</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3721,7 +3716,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3764,7 +3759,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 12079-2024</t>
+          <t>A 10940-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3778,10 +3773,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45377</v>
+        <v>45370</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3794,7 +3789,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>6.9</v>
+        <v>0.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3837,7 +3832,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 11204-2023</t>
+          <t>A 18503-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3851,10 +3846,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44992</v>
+        <v>46127</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3867,7 +3862,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.7</v>
+        <v>4.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3910,7 +3905,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 9482-2023</t>
+          <t>A 10819-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3924,10 +3919,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44981</v>
+        <v>46078</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3940,7 +3935,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3983,7 +3978,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 15533-2024</t>
+          <t>A 1574-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3997,10 +3992,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45401</v>
+        <v>45306</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4013,7 +4008,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>7.5</v>
+        <v>3.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4056,7 +4051,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 62496-2023</t>
+          <t>A 25730-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4070,10 +4065,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45268</v>
+        <v>46178</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4086,7 +4081,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4129,7 +4124,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 25385-2023</t>
+          <t>A 26165-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4143,10 +4138,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45089</v>
+        <v>46181</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4159,7 +4154,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4202,7 +4197,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 34170-2023</t>
+          <t>A 26169-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4216,10 +4211,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45138</v>
+        <v>46181</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4232,7 +4227,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>5.8</v>
+        <v>3.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4275,7 +4270,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 22134-2026</t>
+          <t>A 26497-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4289,10 +4284,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46153</v>
+        <v>46183</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4305,7 +4300,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4348,7 +4343,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 15357-2023</t>
+          <t>A 35996-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4362,10 +4357,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45019</v>
+        <v>45863</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4378,7 +4373,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4421,7 +4416,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 36761-2022</t>
+          <t>A 27428-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4435,10 +4430,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44805</v>
+        <v>46189</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4451,7 +4446,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4494,7 +4489,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 18503-2026</t>
+          <t>A 35997-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4508,10 +4503,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46127</v>
+        <v>45863</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4524,7 +4519,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>4.9</v>
+        <v>0.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4567,7 +4562,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 10819-2026</t>
+          <t>A 27439-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4581,10 +4576,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46078</v>
+        <v>46189</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4597,7 +4592,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>4.9</v>
+        <v>1.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4640,7 +4635,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 34468-2023</t>
+          <t>A 27435-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4654,10 +4649,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45139</v>
+        <v>46189</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4670,7 +4665,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>5.5</v>
+        <v>0.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4713,7 +4708,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 1574-2024</t>
+          <t>A 7016-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4727,10 +4722,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45306</v>
+        <v>45701</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4742,8 +4737,13 @@
           <t>ESLÖV</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4786,7 +4786,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 25730-2026</t>
+          <t>A 16670-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46178</v>
+        <v>45754</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4859,7 +4859,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 26165-2026</t>
+          <t>A 34468-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46181</v>
+        <v>45139</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4932,7 +4932,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 26169-2026</t>
+          <t>A 62496-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4946,10 +4946,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46181</v>
+        <v>45268</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5005,7 +5005,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 26497-2026</t>
+          <t>A 34170-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5019,10 +5019,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46183</v>
+        <v>45138</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.4</v>
+        <v>5.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5078,7 +5078,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 27439-2026</t>
+          <t>A 47870-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5092,10 +5092,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46189</v>
+        <v>45932</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.6</v>
+        <v>6.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5151,7 +5151,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 27428-2026</t>
+          <t>A 24115-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46189</v>
+        <v>44725</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5224,7 +5224,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 27435-2026</t>
+          <t>A 9484-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5238,10 +5238,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46189</v>
+        <v>44981</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5297,7 +5297,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 10940-2024</t>
+          <t>A 16733-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45370</v>
+        <v>45030</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5370,7 +5370,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 11221-2024</t>
+          <t>A 58721-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5384,10 +5384,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45371</v>
+        <v>45986</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.3</v>
+        <v>2.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5443,7 +5443,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 43808-2024</t>
+          <t>A 44496-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5453,14 +5453,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45571</v>
+        <v>45189</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5516,7 +5516,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 9484-2023</t>
+          <t>A 34466-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5530,10 +5530,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44981</v>
+        <v>45139</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.4</v>
+        <v>4.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5589,7 +5589,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 44496-2023</t>
+          <t>A 33865-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5603,10 +5603,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45189</v>
+        <v>45520</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5662,7 +5662,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 33865-2024</t>
+          <t>A 5812-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5676,10 +5676,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45520</v>
+        <v>44596</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5735,7 +5735,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 16670-2025</t>
+          <t>A 38173-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5749,10 +5749,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45754</v>
+        <v>45161</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5808,7 +5808,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 34466-2023</t>
+          <t>A 15357-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5822,10 +5822,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45139</v>
+        <v>45019</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>4.3</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5881,7 +5881,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 38173-2023</t>
+          <t>A 49137-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5895,10 +5895,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45161</v>
+        <v>45594</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5954,7 +5954,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 25508-2023</t>
+          <t>A 32984-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5968,10 +5968,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45089</v>
+        <v>45517</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6027,7 +6027,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 49137-2024</t>
+          <t>A 16792-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6041,10 +6041,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45594</v>
+        <v>45411</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6100,7 +6100,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 32984-2024</t>
+          <t>A 28088-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6114,10 +6114,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45517</v>
+        <v>45817</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>

--- a/Översikt ESLÖV.xlsx
+++ b/Översikt ESLÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45307</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45615</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44960</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>44846</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>45817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>46244</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>46100</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>44981</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>45793</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 14013-2026</t>
+          <t>A 61035-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46098</v>
+        <v>45645</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1608,23 +1608,18 @@
           <t>ESLÖV</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>1</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
@@ -1638,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1647,53 +1642,49 @@
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14013-2026 artfynd.xlsx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 61035-2024 artfynd.xlsx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14013-2026 karta.png", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 61035-2024 karta.png", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14013-2026 georefererad karta.tif", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 61035-2024 georefererad karta.tif", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14013-2026 FSC-klagomål.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 61035-2024 FSC-klagomål.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14013-2026 FSC-klagomål mail.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 61035-2024 FSC-klagomål mail.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14013-2026 tillsynsbegäran.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 61035-2024 tillsynsbegäran.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14013-2026 tillsynsbegäran mail.docx", "A 14013-2026")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 14013-2026 prioriterade fågelarter.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 61035-2024 tillsynsbegäran mail.docx", "A 61035-2024")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 61035-2024</t>
+          <t>A 14013-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1707,10 +1698,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45645</v>
+        <v>46098</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1722,17 +1713,22 @@
           <t>ESLÖV</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1747,7 +1743,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1756,42 +1752,46 @@
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 61035-2024 artfynd.xlsx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14013-2026 artfynd.xlsx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 61035-2024 karta.png", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14013-2026 karta.png", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 61035-2024 georefererad karta.tif", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14013-2026 georefererad karta.tif", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 61035-2024 FSC-klagomål.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14013-2026 FSC-klagomål.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 61035-2024 FSC-klagomål mail.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14013-2026 FSC-klagomål mail.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 61035-2024 tillsynsbegäran.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14013-2026 tillsynsbegäran.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 61035-2024 tillsynsbegäran mail.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14013-2026 tillsynsbegäran mail.docx", "A 14013-2026")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 14013-2026 prioriterade fågelarter.docx", "A 14013-2026")</f>
         <v/>
       </c>
     </row>
@@ -1815,7 +1815,7 @@
         <v>45306</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>45225</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>45426</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>45799</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>44553</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>44690</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 12079-2024</t>
+          <t>A 16733-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2386,10 +2386,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45377</v>
+        <v>45030</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>6.9</v>
+        <v>2.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2445,7 +2445,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 15533-2024</t>
+          <t>A 5812-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45401</v>
+        <v>44596</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>7.5</v>
+        <v>0.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2518,7 +2518,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 11221-2024</t>
+          <t>A 15467-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45371</v>
+        <v>45747</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 15467-2025</t>
+          <t>A 5869-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2601,14 +2601,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45747</v>
+        <v>44958</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2664,7 +2664,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 5869-2023</t>
+          <t>A 7409-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2674,14 +2674,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44958</v>
+        <v>45705</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 25385-2023</t>
+          <t>A 9686-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2751,10 +2751,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45089</v>
+        <v>44984</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2810,7 +2810,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 9482-2023</t>
+          <t>A 7016-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44981</v>
+        <v>45701</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2839,8 +2839,13 @@
           <t>ESLÖV</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2883,7 +2888,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 43808-2024</t>
+          <t>A 24115-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2893,14 +2898,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45571</v>
+        <v>44725</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2913,7 +2918,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.5</v>
+        <v>4.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2956,7 +2961,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 9849-2026</t>
+          <t>A 47356-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2970,10 +2975,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46072</v>
+        <v>45930</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2986,7 +2991,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3029,7 +3034,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 11204-2023</t>
+          <t>A 25388-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3043,10 +3048,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44992</v>
+        <v>45089</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3059,7 +3064,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3102,7 +3107,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 14386-2026</t>
+          <t>A 12079-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3116,10 +3121,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46100</v>
+        <v>45377</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3132,7 +3137,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>12.4</v>
+        <v>6.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3175,7 +3180,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 25508-2023</t>
+          <t>A 35996-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3189,10 +3194,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45089</v>
+        <v>45863</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3205,7 +3210,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3248,7 +3253,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 9686-2023</t>
+          <t>A 35997-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3262,10 +3267,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44984</v>
+        <v>45863</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3278,7 +3283,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3321,7 +3326,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 18281-2026</t>
+          <t>A 22134-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3335,10 +3340,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46125</v>
+        <v>46153</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3351,7 +3356,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3394,7 +3399,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 7409-2025</t>
+          <t>A 11204-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3408,10 +3413,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45705</v>
+        <v>44992</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3424,7 +3429,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3467,7 +3472,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 36761-2022</t>
+          <t>A 9482-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3481,10 +3486,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44805</v>
+        <v>44981</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3497,7 +3502,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3540,7 +3545,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 25388-2023</t>
+          <t>A 15533-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3554,10 +3559,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45089</v>
+        <v>45401</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3570,7 +3575,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.5</v>
+        <v>7.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3613,7 +3618,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 47356-2025</t>
+          <t>A 62496-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3627,10 +3632,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45930</v>
+        <v>45268</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3643,7 +3648,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3686,7 +3691,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 22134-2026</t>
+          <t>A 18503-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3700,10 +3705,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46153</v>
+        <v>46127</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3716,7 +3721,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>4.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3759,7 +3764,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 10940-2024</t>
+          <t>A 25385-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3773,10 +3778,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45370</v>
+        <v>45089</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3789,7 +3794,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3832,7 +3837,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 18503-2026</t>
+          <t>A 34170-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3846,10 +3851,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46127</v>
+        <v>45138</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3862,7 +3867,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3922,7 +3927,7 @@
         <v>46078</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3978,7 +3983,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 1574-2024</t>
+          <t>A 15357-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3992,10 +3997,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45306</v>
+        <v>45019</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4008,7 +4013,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4051,7 +4056,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 25730-2026</t>
+          <t>A 36761-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4065,10 +4070,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46178</v>
+        <v>44805</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4081,7 +4086,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.4</v>
+        <v>4.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4124,7 +4129,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 26165-2026</t>
+          <t>A 47870-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4138,10 +4143,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46181</v>
+        <v>45932</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4154,7 +4159,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>6.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4197,7 +4202,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 26169-2026</t>
+          <t>A 1574-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4211,10 +4216,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46181</v>
+        <v>45306</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4227,7 +4232,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4270,7 +4275,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 26497-2026</t>
+          <t>A 34468-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4284,10 +4289,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46183</v>
+        <v>45139</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4300,7 +4305,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.4</v>
+        <v>5.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4343,7 +4348,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 35996-2025</t>
+          <t>A 25730-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4357,10 +4362,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45863</v>
+        <v>46178</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4373,7 +4378,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4416,7 +4421,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 27428-2026</t>
+          <t>A 26165-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4430,10 +4435,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46189</v>
+        <v>46181</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4446,7 +4451,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4489,7 +4494,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 35997-2025</t>
+          <t>A 26169-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4503,10 +4508,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45863</v>
+        <v>46181</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4519,7 +4524,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4562,7 +4567,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 27439-2026</t>
+          <t>A 9849-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4576,10 +4581,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46189</v>
+        <v>46072</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4592,7 +4597,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4635,7 +4640,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 27435-2026</t>
+          <t>A 26497-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4649,10 +4654,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46189</v>
+        <v>46183</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4665,7 +4670,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4708,7 +4713,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 7016-2025</t>
+          <t>A 27439-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4722,10 +4727,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45701</v>
+        <v>46189</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4737,13 +4742,8 @@
           <t>ESLÖV</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4786,7 +4786,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 16670-2025</t>
+          <t>A 27428-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45754</v>
+        <v>46189</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4859,7 +4859,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 34468-2023</t>
+          <t>A 27435-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45139</v>
+        <v>46189</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>5.5</v>
+        <v>0.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4932,7 +4932,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 62496-2023</t>
+          <t>A 14386-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4946,10 +4946,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45268</v>
+        <v>46100</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.6</v>
+        <v>12.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5005,7 +5005,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 34170-2023</t>
+          <t>A 18281-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5019,10 +5019,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45138</v>
+        <v>46125</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>5.8</v>
+        <v>0.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5078,7 +5078,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 47870-2025</t>
+          <t>A 10940-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5092,10 +5092,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45932</v>
+        <v>45370</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>6.8</v>
+        <v>0.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5151,7 +5151,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 24115-2022</t>
+          <t>A 11221-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44725</v>
+        <v>45371</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>4.4</v>
+        <v>0.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5224,7 +5224,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 9484-2023</t>
+          <t>A 43808-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5234,14 +5234,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44981</v>
+        <v>45571</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5297,7 +5297,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 16733-2023</t>
+          <t>A 9484-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45030</v>
+        <v>44981</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5370,7 +5370,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 58721-2025</t>
+          <t>A 44496-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5384,10 +5384,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45986</v>
+        <v>45189</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5443,7 +5443,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 44496-2023</t>
+          <t>A 33865-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5457,10 +5457,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45189</v>
+        <v>45520</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5516,7 +5516,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 34466-2023</t>
+          <t>A 16670-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5530,10 +5530,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45139</v>
+        <v>45754</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4.3</v>
+        <v>1.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5589,7 +5589,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 33865-2024</t>
+          <t>A 34466-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5603,10 +5603,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45520</v>
+        <v>45139</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.3</v>
+        <v>4.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5662,7 +5662,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 5812-2022</t>
+          <t>A 38173-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5676,10 +5676,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44596</v>
+        <v>45161</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5735,7 +5735,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 38173-2023</t>
+          <t>A 25508-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5749,10 +5749,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45161</v>
+        <v>45089</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.8</v>
+        <v>0.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5808,7 +5808,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 15357-2023</t>
+          <t>A 49137-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5822,10 +5822,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45019</v>
+        <v>45594</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5881,7 +5881,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 49137-2024</t>
+          <t>A 32984-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5895,10 +5895,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45594</v>
+        <v>45517</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5954,7 +5954,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 32984-2024</t>
+          <t>A 58721-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5968,10 +5968,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45517</v>
+        <v>45986</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6044,7 +6044,7 @@
         <v>45411</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
         <v>45817</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>

--- a/Översikt ESLÖV.xlsx
+++ b/Översikt ESLÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45307</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45615</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44960</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>44846</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>45817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>46244</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>46100</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>44981</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>45793</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>45645</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>46098</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>45306</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>45225</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>45426</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>45799</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>44553</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>44690</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>45030</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>44596</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>45747</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>44958</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>45705</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>44984</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>45701</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>44725</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>45930</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>45089</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>45377</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>45863</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>45863</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>46153</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>44992</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         <v>44981</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>45401</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>45268</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>46127</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
         <v>45089</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>45138</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         <v>46078</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         <v>45019</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>44805</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>45932</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         <v>45306</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         <v>45139</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         <v>46178</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>46181</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         <v>46181</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>46072</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>46183</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>46189</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>46189</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         <v>46189</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         <v>46100</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         <v>46125</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>45370</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>45371</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>45571</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>44981</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>45189</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         <v>45520</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>45754</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>45139</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>45161</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>45089</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>45594</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>45517</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>45986</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>45411</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
         <v>45817</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>

--- a/Översikt ESLÖV.xlsx
+++ b/Översikt ESLÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45307</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45615</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44960</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>44846</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>45817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>46244</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>46100</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>44981</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>45793</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>45645</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>46098</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>45306</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>45225</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>45426</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>45799</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>44553</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>44690</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>45030</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>44596</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>45747</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>44958</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>45705</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>44984</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>45701</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 24115-2022</t>
+          <t>A 47356-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2902,10 +2902,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44725</v>
+        <v>45930</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4.4</v>
+        <v>0.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2961,7 +2961,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 47356-2025</t>
+          <t>A 24115-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2975,10 +2975,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45930</v>
+        <v>44725</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.6</v>
+        <v>4.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3034,7 +3034,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 25388-2023</t>
+          <t>A 22134-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3048,10 +3048,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45089</v>
+        <v>46153</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3107,7 +3107,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 12079-2024</t>
+          <t>A 35996-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3121,10 +3121,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45377</v>
+        <v>45863</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>6.9</v>
+        <v>0.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3180,7 +3180,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 35996-2025</t>
+          <t>A 35997-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3197,7 +3197,7 @@
         <v>45863</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3253,7 +3253,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 35997-2025</t>
+          <t>A 18503-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3267,10 +3267,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45863</v>
+        <v>46127</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.9</v>
+        <v>4.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3326,7 +3326,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 22134-2026</t>
+          <t>A 25388-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3340,10 +3340,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46153</v>
+        <v>45089</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3399,7 +3399,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 11204-2023</t>
+          <t>A 10819-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3413,10 +3413,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44992</v>
+        <v>46078</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.7</v>
+        <v>4.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3472,7 +3472,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 9482-2023</t>
+          <t>A 12079-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3486,10 +3486,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44981</v>
+        <v>45377</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.7</v>
+        <v>6.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 15533-2024</t>
+          <t>A 1574-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45401</v>
+        <v>45306</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>7.5</v>
+        <v>3.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3618,7 +3618,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 62496-2023</t>
+          <t>A 11204-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3632,10 +3632,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45268</v>
+        <v>44992</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3691,7 +3691,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 18503-2026</t>
+          <t>A 25730-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3705,10 +3705,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46127</v>
+        <v>46178</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.9</v>
+        <v>1.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3764,7 +3764,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 25385-2023</t>
+          <t>A 26165-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3778,10 +3778,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45089</v>
+        <v>46181</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3837,7 +3837,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 34170-2023</t>
+          <t>A 47870-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3851,10 +3851,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45138</v>
+        <v>45932</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3910,7 +3910,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 10819-2026</t>
+          <t>A 9482-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3924,10 +3924,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46078</v>
+        <v>44981</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3983,7 +3983,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 15357-2023</t>
+          <t>A 26169-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45019</v>
+        <v>46181</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4056,7 +4056,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 36761-2022</t>
+          <t>A 15533-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4070,10 +4070,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44805</v>
+        <v>45401</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>4.8</v>
+        <v>7.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4129,7 +4129,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 47870-2025</t>
+          <t>A 26497-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4143,10 +4143,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45932</v>
+        <v>46183</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>6.8</v>
+        <v>1.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4202,7 +4202,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 1574-2024</t>
+          <t>A 62496-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4216,10 +4216,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45306</v>
+        <v>45268</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4275,7 +4275,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 34468-2023</t>
+          <t>A 27439-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4289,10 +4289,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45139</v>
+        <v>46189</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>5.5</v>
+        <v>1.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4348,7 +4348,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 25730-2026</t>
+          <t>A 27428-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4362,10 +4362,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46178</v>
+        <v>46189</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4421,7 +4421,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 26165-2026</t>
+          <t>A 27435-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4435,10 +4435,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46181</v>
+        <v>46189</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4494,7 +4494,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 26169-2026</t>
+          <t>A 25385-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46181</v>
+        <v>45089</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4567,7 +4567,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 9849-2026</t>
+          <t>A 34170-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46072</v>
+        <v>45138</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.5</v>
+        <v>5.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4640,7 +4640,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 26497-2026</t>
+          <t>A 9849-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4654,10 +4654,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46183</v>
+        <v>46072</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4713,7 +4713,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 27439-2026</t>
+          <t>A 15357-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4727,10 +4727,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46189</v>
+        <v>45019</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4786,7 +4786,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 27428-2026</t>
+          <t>A 36761-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46189</v>
+        <v>44805</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4859,7 +4859,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 27435-2026</t>
+          <t>A 14386-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46189</v>
+        <v>46100</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.9</v>
+        <v>12.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4932,7 +4932,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 14386-2026</t>
+          <t>A 34468-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4946,10 +4946,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46100</v>
+        <v>45139</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>12.4</v>
+        <v>5.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5022,7 +5022,7 @@
         <v>46125</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>45370</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>45371</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>45571</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>44981</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>45189</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         <v>45520</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>45754</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>45139</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>45161</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 25508-2023</t>
+          <t>A 58721-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5749,10 +5749,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45089</v>
+        <v>45986</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.4</v>
+        <v>2.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5808,7 +5808,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 49137-2024</t>
+          <t>A 25508-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5822,10 +5822,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45594</v>
+        <v>45089</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5881,7 +5881,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 32984-2024</t>
+          <t>A 49137-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5895,10 +5895,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45517</v>
+        <v>45594</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5954,7 +5954,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 58721-2025</t>
+          <t>A 32984-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5968,10 +5968,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45986</v>
+        <v>45517</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6044,7 +6044,7 @@
         <v>45411</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
         <v>45817</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>

--- a/Översikt ESLÖV.xlsx
+++ b/Översikt ESLÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45307</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45615</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44960</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>44846</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>45817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>46244</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 14395-2026</t>
+          <t>A 23773-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46100</v>
+        <v>45793</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1336,38 +1336,38 @@
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14395-2026 artfynd.xlsx", "A 14395-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 23773-2025 artfynd.xlsx", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14395-2026 karta.png", "A 14395-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 23773-2025 karta.png", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14395-2026 georefererad karta.tif", "A 14395-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 23773-2025 georefererad karta.tif", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14395-2026 FSC-klagomål.docx", "A 14395-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 23773-2025 FSC-klagomål.docx", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14395-2026 FSC-klagomål mail.docx", "A 14395-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 23773-2025 FSC-klagomål mail.docx", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14395-2026 tillsynsbegäran.docx", "A 14395-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 23773-2025 tillsynsbegäran.docx", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14395-2026 tillsynsbegäran mail.docx", "A 14395-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 23773-2025 tillsynsbegäran mail.docx", "A 23773-2025")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 9487-2023</t>
+          <t>A 14395-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44981</v>
+        <v>46100</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.9</v>
+        <v>4.9</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1406,13 +1406,13 @@
         <v>1</v>
       </c>
       <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
         <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1424,162 +1424,162 @@
         <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>2</v>
       </c>
       <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Kransrams</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14395-2026 artfynd.xlsx", "A 14395-2026")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14395-2026 karta.png", "A 14395-2026")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14395-2026 georefererad karta.tif", "A 14395-2026")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14395-2026 FSC-klagomål.docx", "A 14395-2026")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14395-2026 FSC-klagomål mail.docx", "A 14395-2026")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14395-2026 tillsynsbegäran.docx", "A 14395-2026")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14395-2026 tillsynsbegäran mail.docx", "A 14395-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 9487-2023</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>44981</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ESLÖV</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>2</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Älg
 Kambräken</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 9487-2023 artfynd.xlsx", "A 9487-2023")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 9487-2023 karta.png", "A 9487-2023")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 9487-2023 georefererad karta.tif", "A 9487-2023")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 9487-2023 FSC-klagomål.docx", "A 9487-2023")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 9487-2023 FSC-klagomål mail.docx", "A 9487-2023")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 9487-2023 tillsynsbegäran.docx", "A 9487-2023")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 9487-2023 tillsynsbegäran mail.docx", "A 9487-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 23773-2025</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45793</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>ESLÖV</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>4</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Kransrams</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 23773-2025 artfynd.xlsx", "A 23773-2025")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 23773-2025 karta.png", "A 23773-2025")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 23773-2025 georefererad karta.tif", "A 23773-2025")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 23773-2025 FSC-klagomål.docx", "A 23773-2025")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 23773-2025 FSC-klagomål mail.docx", "A 23773-2025")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 23773-2025 tillsynsbegäran.docx", "A 23773-2025")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 23773-2025 tillsynsbegäran mail.docx", "A 23773-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 61035-2024</t>
+          <t>A 52652-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45645</v>
+        <v>45225</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1609,19 +1609,19 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>7.6</v>
+        <v>2.9</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
         <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1636,55 +1636,55 @@
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Grönfläckig padda</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 61035-2024 artfynd.xlsx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 52652-2023 artfynd.xlsx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 61035-2024 karta.png", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 52652-2023 karta.png", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 61035-2024 georefererad karta.tif", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 52652-2023 georefererad karta.tif", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 61035-2024 FSC-klagomål.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 52652-2023 FSC-klagomål.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 61035-2024 FSC-klagomål mail.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 52652-2023 FSC-klagomål mail.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 61035-2024 tillsynsbegäran.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 52652-2023 tillsynsbegäran.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 61035-2024 tillsynsbegäran mail.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 52652-2023 tillsynsbegäran mail.docx", "A 52652-2023")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 14013-2026</t>
+          <t>A 18713-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46098</v>
+        <v>45426</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1713,13 +1713,8 @@
           <t>ESLÖV</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>8.800000000000001</v>
+        <v>4.1</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1731,7 +1726,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1743,10 +1738,10 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1755,50 +1750,46 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Gråtrut</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14013-2026 artfynd.xlsx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 18713-2024 artfynd.xlsx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14013-2026 karta.png", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 18713-2024 karta.png", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14013-2026 georefererad karta.tif", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 18713-2024 georefererad karta.tif", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14013-2026 FSC-klagomål.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 18713-2024 FSC-klagomål.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14013-2026 FSC-klagomål mail.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 18713-2024 FSC-klagomål mail.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14013-2026 tillsynsbegäran.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 18713-2024 tillsynsbegäran.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14013-2026 tillsynsbegäran mail.docx", "A 14013-2026")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 14013-2026 prioriterade fågelarter.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 18713-2024 tillsynsbegäran mail.docx", "A 18713-2024")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 1510-2024</t>
+          <t>A 24809-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1812,10 +1803,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45306</v>
+        <v>45799</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1828,7 +1819,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1849,10 +1840,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1868,46 +1859,46 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Svart stork</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 1510-2024 artfynd.xlsx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 24809-2025 artfynd.xlsx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 1510-2024 karta.png", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 24809-2025 karta.png", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 1510-2024 georefererad karta.tif", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 24809-2025 georefererad karta.tif", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 1510-2024 FSC-klagomål.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 24809-2025 FSC-klagomål.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 1510-2024 FSC-klagomål mail.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 24809-2025 FSC-klagomål mail.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 1510-2024 tillsynsbegäran.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 24809-2025 tillsynsbegäran.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 1510-2024 tillsynsbegäran mail.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 24809-2025 tillsynsbegäran mail.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 1510-2024 prioriterade fågelarter.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 24809-2025 prioriterade fågelarter.docx", "A 24809-2025")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 52652-2023</t>
+          <t>A 14013-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1921,10 +1912,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45225</v>
+        <v>46098</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1936,8 +1927,13 @@
           <t>ESLÖV</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>2.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1949,7 +1945,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1961,10 +1957,10 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1973,46 +1969,50 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Grönfläckig padda</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 52652-2023 artfynd.xlsx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14013-2026 artfynd.xlsx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 52652-2023 karta.png", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14013-2026 karta.png", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 52652-2023 georefererad karta.tif", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14013-2026 georefererad karta.tif", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 52652-2023 FSC-klagomål.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14013-2026 FSC-klagomål.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 52652-2023 FSC-klagomål mail.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14013-2026 FSC-klagomål mail.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 52652-2023 tillsynsbegäran.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14013-2026 tillsynsbegäran.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 52652-2023 tillsynsbegäran mail.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14013-2026 tillsynsbegäran mail.docx", "A 14013-2026")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 14013-2026 prioriterade fågelarter.docx", "A 14013-2026")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 18713-2024</t>
+          <t>A 1510-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45426</v>
+        <v>45306</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2054,22 +2054,22 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
         <v>1</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2082,42 +2082,46 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Gråtrut</t>
+          <t>Svart stork</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 18713-2024 artfynd.xlsx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 1510-2024 artfynd.xlsx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 18713-2024 karta.png", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 1510-2024 karta.png", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 18713-2024 georefererad karta.tif", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 1510-2024 georefererad karta.tif", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 18713-2024 FSC-klagomål.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 1510-2024 FSC-klagomål.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 18713-2024 FSC-klagomål mail.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 1510-2024 FSC-klagomål mail.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 18713-2024 tillsynsbegäran.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 1510-2024 tillsynsbegäran.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 18713-2024 tillsynsbegäran mail.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 1510-2024 tillsynsbegäran mail.docx", "A 1510-2024")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 1510-2024 prioriterade fågelarter.docx", "A 1510-2024")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 24809-2025</t>
+          <t>A 61035-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2131,10 +2135,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45799</v>
+        <v>45645</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2147,17 +2151,17 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.4</v>
+        <v>7.6</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
@@ -2171,7 +2175,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2180,46 +2184,42 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 24809-2025 artfynd.xlsx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 61035-2024 artfynd.xlsx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 24809-2025 karta.png", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 61035-2024 karta.png", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 24809-2025 georefererad karta.tif", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 61035-2024 georefererad karta.tif", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 24809-2025 FSC-klagomål.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 61035-2024 FSC-klagomål.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 24809-2025 FSC-klagomål mail.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 61035-2024 FSC-klagomål mail.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 24809-2025 tillsynsbegäran.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 61035-2024 tillsynsbegäran.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 24809-2025 tillsynsbegäran mail.docx", "A 24809-2025")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 24809-2025 prioriterade fågelarter.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 61035-2024 tillsynsbegäran mail.docx", "A 61035-2024")</f>
         <v/>
       </c>
     </row>
@@ -2243,7 +2243,7 @@
         <v>44553</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>44690</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 16733-2023</t>
+          <t>A 49137-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2386,10 +2386,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45030</v>
+        <v>45594</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2445,7 +2445,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 5812-2022</t>
+          <t>A 7409-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44596</v>
+        <v>45705</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2518,7 +2518,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 15467-2025</t>
+          <t>A 12079-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45747</v>
+        <v>45377</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.4</v>
+        <v>6.9</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 5869-2023</t>
+          <t>A 32984-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2601,14 +2601,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44958</v>
+        <v>45517</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2664,7 +2664,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 7409-2025</t>
+          <t>A 15533-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2678,10 +2678,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45705</v>
+        <v>45401</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 9686-2023</t>
+          <t>A 11221-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2751,10 +2751,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44984</v>
+        <v>45371</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2810,7 +2810,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 7016-2025</t>
+          <t>A 15467-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45701</v>
+        <v>45747</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2839,13 +2839,8 @@
           <t>ESLÖV</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2888,7 +2883,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 47356-2025</t>
+          <t>A 36761-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2902,10 +2897,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45930</v>
+        <v>44805</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2918,7 +2913,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.6</v>
+        <v>4.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2961,7 +2956,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 24115-2022</t>
+          <t>A 25388-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2975,10 +2970,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44725</v>
+        <v>45089</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2991,7 +2986,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>4.4</v>
+        <v>0.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3034,7 +3029,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 22134-2026</t>
+          <t>A 5869-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3044,14 +3039,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46153</v>
+        <v>44958</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3064,7 +3059,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3107,7 +3102,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 35996-2025</t>
+          <t>A 10940-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3121,10 +3116,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45863</v>
+        <v>45370</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3137,7 +3132,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3180,7 +3175,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 35997-2025</t>
+          <t>A 16792-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3194,10 +3189,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45863</v>
+        <v>45411</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3253,7 +3248,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 18503-2026</t>
+          <t>A 9482-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3267,10 +3262,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46127</v>
+        <v>44981</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3283,7 +3278,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3326,7 +3321,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 25388-2023</t>
+          <t>A 25385-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3343,7 +3338,7 @@
         <v>45089</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3356,7 +3351,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3399,7 +3394,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 10819-2026</t>
+          <t>A 43808-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3409,14 +3404,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46078</v>
+        <v>45571</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3429,7 +3424,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.9</v>
+        <v>1.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3472,7 +3467,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 12079-2024</t>
+          <t>A 47356-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3486,10 +3481,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45377</v>
+        <v>45930</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3502,7 +3497,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>6.9</v>
+        <v>0.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3545,7 +3540,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 1574-2024</t>
+          <t>A 7016-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3559,10 +3554,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45306</v>
+        <v>45701</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3574,8 +3569,13 @@
           <t>ESLÖV</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3618,7 +3618,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 11204-2023</t>
+          <t>A 28088-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3632,10 +3632,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44992</v>
+        <v>45817</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3691,7 +3691,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 25730-2026</t>
+          <t>A 35996-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3705,10 +3705,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46178</v>
+        <v>45863</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3764,7 +3764,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 26165-2026</t>
+          <t>A 35997-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3778,10 +3778,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46181</v>
+        <v>45863</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3837,7 +3837,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 47870-2025</t>
+          <t>A 11204-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3851,10 +3851,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45932</v>
+        <v>44992</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>6.8</v>
+        <v>0.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3910,7 +3910,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 9482-2023</t>
+          <t>A 25508-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3924,10 +3924,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44981</v>
+        <v>45089</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.7</v>
+        <v>0.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3983,7 +3983,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 26169-2026</t>
+          <t>A 9686-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46181</v>
+        <v>44984</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.5</v>
+        <v>0.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4056,7 +4056,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 15533-2024</t>
+          <t>A 16670-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4070,10 +4070,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45401</v>
+        <v>45754</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>7.5</v>
+        <v>1.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4129,7 +4129,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 26497-2026</t>
+          <t>A 34468-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4143,10 +4143,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46183</v>
+        <v>45139</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.4</v>
+        <v>5.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4202,7 +4202,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 62496-2023</t>
+          <t>A 47870-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4216,10 +4216,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45268</v>
+        <v>45932</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.6</v>
+        <v>6.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4275,7 +4275,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 27439-2026</t>
+          <t>A 62496-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4289,10 +4289,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46189</v>
+        <v>45268</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4348,7 +4348,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 27428-2026</t>
+          <t>A 34170-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4362,10 +4362,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46189</v>
+        <v>45138</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.4</v>
+        <v>5.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4421,7 +4421,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 27435-2026</t>
+          <t>A 9849-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4435,10 +4435,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46189</v>
+        <v>46072</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4494,7 +4494,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 25385-2023</t>
+          <t>A 58721-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45089</v>
+        <v>45986</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4567,7 +4567,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 34170-2023</t>
+          <t>A 24115-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45138</v>
+        <v>44725</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4640,7 +4640,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 9849-2026</t>
+          <t>A 14386-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4654,10 +4654,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46072</v>
+        <v>46100</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.5</v>
+        <v>12.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4713,7 +4713,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 15357-2023</t>
+          <t>A 9484-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4727,10 +4727,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45019</v>
+        <v>44981</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4786,7 +4786,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 36761-2022</t>
+          <t>A 16733-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44805</v>
+        <v>45030</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>4.8</v>
+        <v>2.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4859,7 +4859,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 14386-2026</t>
+          <t>A 18281-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46100</v>
+        <v>46125</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>12.4</v>
+        <v>0.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4932,7 +4932,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 34468-2023</t>
+          <t>A 44496-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4946,10 +4946,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45139</v>
+        <v>45189</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>5.5</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5005,7 +5005,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 18281-2026</t>
+          <t>A 34466-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5019,10 +5019,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46125</v>
+        <v>45139</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.8</v>
+        <v>4.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5078,7 +5078,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 10940-2024</t>
+          <t>A 33865-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5092,10 +5092,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45370</v>
+        <v>45520</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5151,7 +5151,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 11221-2024</t>
+          <t>A 5812-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45371</v>
+        <v>44596</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5224,7 +5224,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 43808-2024</t>
+          <t>A 38173-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5234,14 +5234,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45571</v>
+        <v>45161</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5297,7 +5297,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 9484-2023</t>
+          <t>A 15357-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44981</v>
+        <v>45019</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5370,7 +5370,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 44496-2023</t>
+          <t>A 22134-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5384,10 +5384,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45189</v>
+        <v>46153</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5443,7 +5443,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 33865-2024</t>
+          <t>A 18503-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5457,10 +5457,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45520</v>
+        <v>46127</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.3</v>
+        <v>4.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5516,7 +5516,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 16670-2025</t>
+          <t>A 10819-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5530,10 +5530,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45754</v>
+        <v>46078</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.5</v>
+        <v>4.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5589,7 +5589,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 34466-2023</t>
+          <t>A 1574-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5603,10 +5603,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45139</v>
+        <v>45306</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5662,7 +5662,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 38173-2023</t>
+          <t>A 25730-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5676,10 +5676,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45161</v>
+        <v>46178</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5735,7 +5735,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 58721-2025</t>
+          <t>A 26165-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5749,10 +5749,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45986</v>
+        <v>46181</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5808,7 +5808,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 25508-2023</t>
+          <t>A 26169-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5822,10 +5822,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45089</v>
+        <v>46181</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.4</v>
+        <v>3.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5881,7 +5881,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 49137-2024</t>
+          <t>A 26497-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5895,10 +5895,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45594</v>
+        <v>46183</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5954,7 +5954,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 32984-2024</t>
+          <t>A 27428-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5968,10 +5968,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45517</v>
+        <v>46189</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6027,7 +6027,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 16792-2024</t>
+          <t>A 27439-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6041,10 +6041,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45411</v>
+        <v>46189</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6100,7 +6100,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 28088-2025</t>
+          <t>A 27435-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6114,10 +6114,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45817</v>
+        <v>46189</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>

--- a/Översikt ESLÖV.xlsx
+++ b/Översikt ESLÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45307</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45615</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44960</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>44846</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>45817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>46244</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 23773-2025</t>
+          <t>A 14395-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45793</v>
+        <v>46100</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1336,38 +1336,38 @@
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 23773-2025 artfynd.xlsx", "A 23773-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14395-2026 artfynd.xlsx", "A 14395-2026")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 23773-2025 karta.png", "A 23773-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14395-2026 karta.png", "A 14395-2026")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 23773-2025 georefererad karta.tif", "A 23773-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14395-2026 georefererad karta.tif", "A 14395-2026")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 23773-2025 FSC-klagomål.docx", "A 23773-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14395-2026 FSC-klagomål.docx", "A 14395-2026")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 23773-2025 FSC-klagomål mail.docx", "A 23773-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14395-2026 FSC-klagomål mail.docx", "A 14395-2026")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 23773-2025 tillsynsbegäran.docx", "A 23773-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14395-2026 tillsynsbegäran.docx", "A 14395-2026")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 23773-2025 tillsynsbegäran mail.docx", "A 23773-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14395-2026 tillsynsbegäran mail.docx", "A 14395-2026")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 14395-2026</t>
+          <t>A 9487-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46100</v>
+        <v>44981</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.9</v>
+        <v>1.9</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1406,13 +1406,13 @@
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1424,162 +1424,162 @@
         <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>2</v>
       </c>
       <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Älg
+Kambräken</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 9487-2023 artfynd.xlsx", "A 9487-2023")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 9487-2023 karta.png", "A 9487-2023")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 9487-2023 georefererad karta.tif", "A 9487-2023")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 9487-2023 FSC-klagomål.docx", "A 9487-2023")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 9487-2023 FSC-klagomål mail.docx", "A 9487-2023")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 9487-2023 tillsynsbegäran.docx", "A 9487-2023")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 9487-2023 tillsynsbegäran mail.docx", "A 9487-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 23773-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45793</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ESLÖV</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="n">
         <v>4</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Ask
 Kransrams</t>
         </is>
       </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14395-2026 artfynd.xlsx", "A 14395-2026")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14395-2026 karta.png", "A 14395-2026")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14395-2026 georefererad karta.tif", "A 14395-2026")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14395-2026 FSC-klagomål.docx", "A 14395-2026")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14395-2026 FSC-klagomål mail.docx", "A 14395-2026")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14395-2026 tillsynsbegäran.docx", "A 14395-2026")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14395-2026 tillsynsbegäran mail.docx", "A 14395-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 9487-2023</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>44981</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>ESLÖV</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Älg
-Kambräken</t>
-        </is>
-      </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 9487-2023 artfynd.xlsx", "A 9487-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 23773-2025 artfynd.xlsx", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 9487-2023 karta.png", "A 9487-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 23773-2025 karta.png", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 9487-2023 georefererad karta.tif", "A 9487-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 23773-2025 georefererad karta.tif", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 9487-2023 FSC-klagomål.docx", "A 9487-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 23773-2025 FSC-klagomål.docx", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 9487-2023 FSC-klagomål mail.docx", "A 9487-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 23773-2025 FSC-klagomål mail.docx", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 9487-2023 tillsynsbegäran.docx", "A 9487-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 23773-2025 tillsynsbegäran.docx", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 9487-2023 tillsynsbegäran mail.docx", "A 9487-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 23773-2025 tillsynsbegäran mail.docx", "A 23773-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 52652-2023</t>
+          <t>A 61035-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45225</v>
+        <v>45645</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1609,19 +1609,19 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.9</v>
+        <v>7.6</v>
       </c>
       <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>1</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1636,55 +1636,55 @@
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Grönfläckig padda</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 52652-2023 artfynd.xlsx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 61035-2024 artfynd.xlsx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 52652-2023 karta.png", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 61035-2024 karta.png", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 52652-2023 georefererad karta.tif", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 61035-2024 georefererad karta.tif", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 52652-2023 FSC-klagomål.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 61035-2024 FSC-klagomål.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 52652-2023 FSC-klagomål mail.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 61035-2024 FSC-klagomål mail.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 52652-2023 tillsynsbegäran.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 61035-2024 tillsynsbegäran.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 52652-2023 tillsynsbegäran mail.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 61035-2024 tillsynsbegäran mail.docx", "A 61035-2024")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 18713-2024</t>
+          <t>A 14013-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45426</v>
+        <v>46098</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1713,8 +1713,13 @@
           <t>ESLÖV</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>4.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1726,7 +1731,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1738,10 +1743,10 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1750,46 +1755,50 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Gråtrut</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 18713-2024 artfynd.xlsx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14013-2026 artfynd.xlsx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 18713-2024 karta.png", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14013-2026 karta.png", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 18713-2024 georefererad karta.tif", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14013-2026 georefererad karta.tif", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 18713-2024 FSC-klagomål.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14013-2026 FSC-klagomål.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 18713-2024 FSC-klagomål mail.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14013-2026 FSC-klagomål mail.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 18713-2024 tillsynsbegäran.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14013-2026 tillsynsbegäran.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 18713-2024 tillsynsbegäran mail.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14013-2026 tillsynsbegäran mail.docx", "A 14013-2026")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 14013-2026 prioriterade fågelarter.docx", "A 14013-2026")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 24809-2025</t>
+          <t>A 1510-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1803,10 +1812,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45799</v>
+        <v>45306</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1819,7 +1828,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1840,10 +1849,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1859,46 +1868,46 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svart stork</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 24809-2025 artfynd.xlsx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 1510-2024 artfynd.xlsx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 24809-2025 karta.png", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 1510-2024 karta.png", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 24809-2025 georefererad karta.tif", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 1510-2024 georefererad karta.tif", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 24809-2025 FSC-klagomål.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 1510-2024 FSC-klagomål.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 24809-2025 FSC-klagomål mail.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 1510-2024 FSC-klagomål mail.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 24809-2025 tillsynsbegäran.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 1510-2024 tillsynsbegäran.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 24809-2025 tillsynsbegäran mail.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 1510-2024 tillsynsbegäran mail.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 24809-2025 prioriterade fågelarter.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 1510-2024 prioriterade fågelarter.docx", "A 1510-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 14013-2026</t>
+          <t>A 52652-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1912,10 +1921,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46098</v>
+        <v>45225</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1927,13 +1936,8 @@
           <t>ESLÖV</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>8.800000000000001</v>
+        <v>2.9</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1945,7 +1949,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1957,10 +1961,10 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1969,50 +1973,46 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Grönfläckig padda</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14013-2026 artfynd.xlsx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 52652-2023 artfynd.xlsx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14013-2026 karta.png", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 52652-2023 karta.png", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14013-2026 georefererad karta.tif", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 52652-2023 georefererad karta.tif", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14013-2026 FSC-klagomål.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 52652-2023 FSC-klagomål.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14013-2026 FSC-klagomål mail.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 52652-2023 FSC-klagomål mail.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14013-2026 tillsynsbegäran.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 52652-2023 tillsynsbegäran.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14013-2026 tillsynsbegäran mail.docx", "A 14013-2026")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 14013-2026 prioriterade fågelarter.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 52652-2023 tillsynsbegäran mail.docx", "A 52652-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 1510-2024</t>
+          <t>A 18713-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45306</v>
+        <v>45426</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2054,7 +2054,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2063,13 +2063,13 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2082,46 +2082,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Svart stork</t>
+          <t>Gråtrut</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 1510-2024 artfynd.xlsx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 18713-2024 artfynd.xlsx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 1510-2024 karta.png", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 18713-2024 karta.png", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 1510-2024 georefererad karta.tif", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 18713-2024 georefererad karta.tif", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 1510-2024 FSC-klagomål.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 18713-2024 FSC-klagomål.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 1510-2024 FSC-klagomål mail.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 18713-2024 FSC-klagomål mail.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 1510-2024 tillsynsbegäran.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 18713-2024 tillsynsbegäran.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 1510-2024 tillsynsbegäran mail.docx", "A 1510-2024")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 1510-2024 prioriterade fågelarter.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 18713-2024 tillsynsbegäran mail.docx", "A 18713-2024")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 61035-2024</t>
+          <t>A 24809-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2135,10 +2131,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45645</v>
+        <v>45799</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2151,16 +2147,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>7.6</v>
+        <v>1.4</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2175,7 +2171,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2184,42 +2180,46 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 61035-2024 artfynd.xlsx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 24809-2025 artfynd.xlsx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 61035-2024 karta.png", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 24809-2025 karta.png", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 61035-2024 georefererad karta.tif", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 24809-2025 georefererad karta.tif", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 61035-2024 FSC-klagomål.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 24809-2025 FSC-klagomål.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 61035-2024 FSC-klagomål mail.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 24809-2025 FSC-klagomål mail.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 61035-2024 tillsynsbegäran.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 24809-2025 tillsynsbegäran.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 61035-2024 tillsynsbegäran mail.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 24809-2025 tillsynsbegäran mail.docx", "A 24809-2025")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 24809-2025 prioriterade fågelarter.docx", "A 24809-2025")</f>
         <v/>
       </c>
     </row>
@@ -2243,7 +2243,7 @@
         <v>44553</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>44690</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 49137-2024</t>
+          <t>A 16733-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2386,10 +2386,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45594</v>
+        <v>45030</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2445,7 +2445,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 7409-2025</t>
+          <t>A 5812-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45705</v>
+        <v>44596</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2518,7 +2518,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 12079-2024</t>
+          <t>A 15467-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45377</v>
+        <v>45747</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>6.9</v>
+        <v>1.4</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 32984-2024</t>
+          <t>A 5869-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2601,14 +2601,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45517</v>
+        <v>44958</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2664,7 +2664,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 15533-2024</t>
+          <t>A 7409-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2678,10 +2678,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45401</v>
+        <v>45705</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>7.5</v>
+        <v>1.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 11221-2024</t>
+          <t>A 9686-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2751,10 +2751,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45371</v>
+        <v>44984</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2810,7 +2810,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 15467-2025</t>
+          <t>A 7016-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45747</v>
+        <v>45701</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2839,8 +2839,13 @@
           <t>ESLÖV</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2883,7 +2888,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 36761-2022</t>
+          <t>A 47356-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2897,10 +2902,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44805</v>
+        <v>45930</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2913,7 +2918,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2956,7 +2961,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 25388-2023</t>
+          <t>A 24115-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2970,10 +2975,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45089</v>
+        <v>44725</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2986,7 +2991,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.5</v>
+        <v>4.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3029,7 +3034,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 5869-2023</t>
+          <t>A 35996-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3039,14 +3044,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44958</v>
+        <v>45863</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3059,7 +3064,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3102,7 +3107,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 10940-2024</t>
+          <t>A 35997-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3116,10 +3121,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45370</v>
+        <v>45863</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3132,7 +3137,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3175,7 +3180,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 16792-2024</t>
+          <t>A 25388-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3189,10 +3194,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45411</v>
+        <v>45089</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3205,7 +3210,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3248,7 +3253,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 9482-2023</t>
+          <t>A 12079-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3262,10 +3267,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44981</v>
+        <v>45377</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3278,7 +3283,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.7</v>
+        <v>6.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3321,7 +3326,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 25385-2023</t>
+          <t>A 11204-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3335,10 +3340,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45089</v>
+        <v>44992</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3394,7 +3399,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 43808-2024</t>
+          <t>A 22134-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3404,14 +3409,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45571</v>
+        <v>46153</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3424,7 +3429,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3467,7 +3472,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 47356-2025</t>
+          <t>A 9482-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3481,10 +3486,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45930</v>
+        <v>44981</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3497,7 +3502,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.6</v>
+        <v>3.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3540,7 +3545,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 7016-2025</t>
+          <t>A 15533-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3554,10 +3559,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45701</v>
+        <v>45401</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3569,13 +3574,8 @@
           <t>ESLÖV</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>2.3</v>
+        <v>7.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3618,7 +3618,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 28088-2025</t>
+          <t>A 47870-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3632,10 +3632,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45817</v>
+        <v>45932</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>6.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3691,7 +3691,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 35996-2025</t>
+          <t>A 62496-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3705,10 +3705,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45863</v>
+        <v>45268</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3764,7 +3764,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 35997-2025</t>
+          <t>A 18503-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3778,10 +3778,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45863</v>
+        <v>46127</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.9</v>
+        <v>4.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3837,7 +3837,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 11204-2023</t>
+          <t>A 25385-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3851,10 +3851,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44992</v>
+        <v>45089</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 25508-2023</t>
+          <t>A 10819-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3924,10 +3924,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45089</v>
+        <v>46078</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.4</v>
+        <v>4.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3983,7 +3983,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 9686-2023</t>
+          <t>A 34170-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44984</v>
+        <v>45138</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.8</v>
+        <v>5.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4056,7 +4056,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 16670-2025</t>
+          <t>A 15357-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4070,10 +4070,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45754</v>
+        <v>45019</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4129,7 +4129,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 34468-2023</t>
+          <t>A 36761-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4143,10 +4143,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45139</v>
+        <v>44805</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4202,7 +4202,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 47870-2025</t>
+          <t>A 1574-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4216,10 +4216,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45932</v>
+        <v>45306</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>6.8</v>
+        <v>3.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4275,7 +4275,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 62496-2023</t>
+          <t>A 9849-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4289,10 +4289,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45268</v>
+        <v>46072</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4348,7 +4348,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 34170-2023</t>
+          <t>A 14386-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4362,10 +4362,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45138</v>
+        <v>46100</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>5.8</v>
+        <v>12.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4421,7 +4421,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 9849-2026</t>
+          <t>A 25730-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4435,10 +4435,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46072</v>
+        <v>46178</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4494,7 +4494,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 58721-2025</t>
+          <t>A 26165-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45986</v>
+        <v>46181</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4567,7 +4567,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 24115-2022</t>
+          <t>A 34468-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44725</v>
+        <v>45139</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4640,7 +4640,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 14386-2026</t>
+          <t>A 26169-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4654,10 +4654,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46100</v>
+        <v>46181</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>12.4</v>
+        <v>3.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4713,7 +4713,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 9484-2023</t>
+          <t>A 26497-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4727,10 +4727,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44981</v>
+        <v>46183</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 16733-2023</t>
+          <t>A 27439-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45030</v>
+        <v>46189</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4859,7 +4859,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 18281-2026</t>
+          <t>A 27428-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46125</v>
+        <v>46189</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4932,7 +4932,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 44496-2023</t>
+          <t>A 27435-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4946,10 +4946,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45189</v>
+        <v>46189</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5005,7 +5005,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 34466-2023</t>
+          <t>A 18281-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5019,10 +5019,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45139</v>
+        <v>46125</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4.3</v>
+        <v>0.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5078,7 +5078,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 33865-2024</t>
+          <t>A 10940-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5092,10 +5092,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45520</v>
+        <v>45370</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5151,7 +5151,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 5812-2022</t>
+          <t>A 11221-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44596</v>
+        <v>45371</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5224,7 +5224,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 38173-2023</t>
+          <t>A 43808-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5234,14 +5234,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45161</v>
+        <v>45571</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5297,7 +5297,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 15357-2023</t>
+          <t>A 9484-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45019</v>
+        <v>44981</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5370,7 +5370,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 22134-2026</t>
+          <t>A 44496-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5384,10 +5384,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46153</v>
+        <v>45189</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5443,7 +5443,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 18503-2026</t>
+          <t>A 33865-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5457,10 +5457,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46127</v>
+        <v>45520</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4.9</v>
+        <v>1.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5516,7 +5516,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 10819-2026</t>
+          <t>A 16670-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5530,10 +5530,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46078</v>
+        <v>45754</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4.9</v>
+        <v>1.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5589,7 +5589,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 1574-2024</t>
+          <t>A 34466-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5603,10 +5603,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45306</v>
+        <v>45139</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5662,7 +5662,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 25730-2026</t>
+          <t>A 38173-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5676,10 +5676,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46178</v>
+        <v>45161</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5735,7 +5735,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 26165-2026</t>
+          <t>A 25508-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5749,10 +5749,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46181</v>
+        <v>45089</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5808,7 +5808,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 26169-2026</t>
+          <t>A 49137-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5822,10 +5822,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46181</v>
+        <v>45594</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5881,7 +5881,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 26497-2026</t>
+          <t>A 32984-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5895,10 +5895,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46183</v>
+        <v>45517</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5954,7 +5954,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 27428-2026</t>
+          <t>A 58721-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5968,10 +5968,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46189</v>
+        <v>45986</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6027,7 +6027,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 27439-2026</t>
+          <t>A 16792-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6041,10 +6041,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46189</v>
+        <v>45411</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6100,7 +6100,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 27435-2026</t>
+          <t>A 28088-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6114,10 +6114,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46189</v>
+        <v>45817</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>

--- a/Översikt ESLÖV.xlsx
+++ b/Översikt ESLÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45307</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45615</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44960</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>44846</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>45817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>46244</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 14395-2026</t>
+          <t>A 23773-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46100</v>
+        <v>45793</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1336,38 +1336,38 @@
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14395-2026 artfynd.xlsx", "A 14395-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 23773-2025 artfynd.xlsx", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14395-2026 karta.png", "A 14395-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 23773-2025 karta.png", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14395-2026 georefererad karta.tif", "A 14395-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 23773-2025 georefererad karta.tif", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14395-2026 FSC-klagomål.docx", "A 14395-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 23773-2025 FSC-klagomål.docx", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14395-2026 FSC-klagomål mail.docx", "A 14395-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 23773-2025 FSC-klagomål mail.docx", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14395-2026 tillsynsbegäran.docx", "A 14395-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 23773-2025 tillsynsbegäran.docx", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14395-2026 tillsynsbegäran mail.docx", "A 14395-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 23773-2025 tillsynsbegäran mail.docx", "A 23773-2025")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 9487-2023</t>
+          <t>A 14395-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44981</v>
+        <v>46100</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.9</v>
+        <v>4.9</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1406,13 +1406,13 @@
         <v>1</v>
       </c>
       <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
         <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1424,162 +1424,162 @@
         <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>2</v>
       </c>
       <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Kransrams</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14395-2026 artfynd.xlsx", "A 14395-2026")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14395-2026 karta.png", "A 14395-2026")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14395-2026 georefererad karta.tif", "A 14395-2026")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14395-2026 FSC-klagomål.docx", "A 14395-2026")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14395-2026 FSC-klagomål mail.docx", "A 14395-2026")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14395-2026 tillsynsbegäran.docx", "A 14395-2026")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14395-2026 tillsynsbegäran mail.docx", "A 14395-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 9487-2023</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>44981</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ESLÖV</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>2</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Älg
 Kambräken</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 9487-2023 artfynd.xlsx", "A 9487-2023")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 9487-2023 karta.png", "A 9487-2023")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 9487-2023 georefererad karta.tif", "A 9487-2023")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 9487-2023 FSC-klagomål.docx", "A 9487-2023")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 9487-2023 FSC-klagomål mail.docx", "A 9487-2023")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 9487-2023 tillsynsbegäran.docx", "A 9487-2023")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 9487-2023 tillsynsbegäran mail.docx", "A 9487-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 23773-2025</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45793</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>ESLÖV</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>4</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Kransrams</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 23773-2025 artfynd.xlsx", "A 23773-2025")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 23773-2025 karta.png", "A 23773-2025")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 23773-2025 georefererad karta.tif", "A 23773-2025")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 23773-2025 FSC-klagomål.docx", "A 23773-2025")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 23773-2025 FSC-klagomål mail.docx", "A 23773-2025")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 23773-2025 tillsynsbegäran.docx", "A 23773-2025")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 23773-2025 tillsynsbegäran mail.docx", "A 23773-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 61035-2024</t>
+          <t>A 24809-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45645</v>
+        <v>45799</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1609,16 +1609,16 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>7.6</v>
+        <v>1.4</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1642,42 +1642,46 @@
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 61035-2024 artfynd.xlsx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 24809-2025 artfynd.xlsx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 61035-2024 karta.png", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 24809-2025 karta.png", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 61035-2024 georefererad karta.tif", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 24809-2025 georefererad karta.tif", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 61035-2024 FSC-klagomål.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 24809-2025 FSC-klagomål.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 61035-2024 FSC-klagomål mail.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 24809-2025 FSC-klagomål mail.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 61035-2024 tillsynsbegäran.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 24809-2025 tillsynsbegäran.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 61035-2024 tillsynsbegäran mail.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 24809-2025 tillsynsbegäran mail.docx", "A 24809-2025")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 24809-2025 prioriterade fågelarter.docx", "A 24809-2025")</f>
         <v/>
       </c>
     </row>
@@ -1701,7 +1705,7 @@
         <v>46098</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1798,7 +1802,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 1510-2024</t>
+          <t>A 61035-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1812,10 +1816,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45306</v>
+        <v>45645</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1828,17 +1832,17 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.7</v>
+        <v>7.6</v>
       </c>
       <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
@@ -1849,7 +1853,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
@@ -1861,53 +1865,49 @@
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Svart stork</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 1510-2024 artfynd.xlsx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 61035-2024 artfynd.xlsx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 1510-2024 karta.png", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 61035-2024 karta.png", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 1510-2024 georefererad karta.tif", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 61035-2024 georefererad karta.tif", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 1510-2024 FSC-klagomål.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 61035-2024 FSC-klagomål.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 1510-2024 FSC-klagomål mail.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 61035-2024 FSC-klagomål mail.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 1510-2024 tillsynsbegäran.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 61035-2024 tillsynsbegäran.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 1510-2024 tillsynsbegäran mail.docx", "A 1510-2024")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 1510-2024 prioriterade fågelarter.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 61035-2024 tillsynsbegäran mail.docx", "A 61035-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 52652-2023</t>
+          <t>A 1510-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45225</v>
+        <v>45306</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1949,22 +1949,22 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
         <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1977,42 +1977,46 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Grönfläckig padda</t>
+          <t>Svart stork</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 52652-2023 artfynd.xlsx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 1510-2024 artfynd.xlsx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 52652-2023 karta.png", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 1510-2024 karta.png", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 52652-2023 georefererad karta.tif", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 1510-2024 georefererad karta.tif", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 52652-2023 FSC-klagomål.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 1510-2024 FSC-klagomål.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 52652-2023 FSC-klagomål mail.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 1510-2024 FSC-klagomål mail.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 52652-2023 tillsynsbegäran.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 1510-2024 tillsynsbegäran.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 52652-2023 tillsynsbegäran mail.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 1510-2024 tillsynsbegäran mail.docx", "A 1510-2024")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 1510-2024 prioriterade fågelarter.docx", "A 1510-2024")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 18713-2024</t>
+          <t>A 52652-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2026,10 +2030,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45426</v>
+        <v>45225</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2042,7 +2046,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2082,42 +2086,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Gråtrut</t>
+          <t>Grönfläckig padda</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 18713-2024 artfynd.xlsx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 52652-2023 artfynd.xlsx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 18713-2024 karta.png", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 52652-2023 karta.png", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 18713-2024 georefererad karta.tif", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 52652-2023 georefererad karta.tif", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 18713-2024 FSC-klagomål.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 52652-2023 FSC-klagomål.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 18713-2024 FSC-klagomål mail.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 52652-2023 FSC-klagomål mail.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 18713-2024 tillsynsbegäran.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 52652-2023 tillsynsbegäran.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 18713-2024 tillsynsbegäran mail.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 52652-2023 tillsynsbegäran mail.docx", "A 52652-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 24809-2025</t>
+          <t>A 18713-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2131,10 +2135,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45799</v>
+        <v>45426</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2147,7 +2151,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.4</v>
+        <v>4.1</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2159,7 +2163,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2171,10 +2175,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2187,39 +2191,35 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gråtrut</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 24809-2025 artfynd.xlsx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 18713-2024 artfynd.xlsx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 24809-2025 karta.png", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 18713-2024 karta.png", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 24809-2025 georefererad karta.tif", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 18713-2024 georefererad karta.tif", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 24809-2025 FSC-klagomål.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 18713-2024 FSC-klagomål.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 24809-2025 FSC-klagomål mail.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 18713-2024 FSC-klagomål mail.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 24809-2025 tillsynsbegäran.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 18713-2024 tillsynsbegäran.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 24809-2025 tillsynsbegäran mail.docx", "A 24809-2025")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 24809-2025 prioriterade fågelarter.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 18713-2024 tillsynsbegäran mail.docx", "A 18713-2024")</f>
         <v/>
       </c>
     </row>
@@ -2243,7 +2243,7 @@
         <v>44553</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>44690</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 16733-2023</t>
+          <t>A 12079-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2386,10 +2386,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45030</v>
+        <v>45377</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.6</v>
+        <v>6.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2445,7 +2445,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 5812-2022</t>
+          <t>A 15533-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44596</v>
+        <v>45401</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.5</v>
+        <v>7.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2518,7 +2518,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 15467-2025</t>
+          <t>A 11221-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45747</v>
+        <v>45371</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.4</v>
+        <v>0.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 5869-2023</t>
+          <t>A 15467-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2601,14 +2601,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44958</v>
+        <v>45747</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2664,7 +2664,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 7409-2025</t>
+          <t>A 5869-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2674,14 +2674,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45705</v>
+        <v>44958</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 9686-2023</t>
+          <t>A 47870-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2751,10 +2751,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44984</v>
+        <v>45932</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.8</v>
+        <v>6.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2810,7 +2810,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 7016-2025</t>
+          <t>A 9482-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45701</v>
+        <v>44981</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2839,13 +2839,8 @@
           <t>ESLÖV</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2888,7 +2883,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 47356-2025</t>
+          <t>A 25385-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2902,10 +2897,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45930</v>
+        <v>45089</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2918,7 +2913,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2961,7 +2956,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 24115-2022</t>
+          <t>A 16792-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2975,10 +2970,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44725</v>
+        <v>45411</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2991,7 +2986,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>4.4</v>
+        <v>0.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3034,7 +3029,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 35996-2025</t>
+          <t>A 43808-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3044,14 +3039,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45863</v>
+        <v>45571</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3064,7 +3059,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3107,7 +3102,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 35997-2025</t>
+          <t>A 9849-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3121,10 +3116,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45863</v>
+        <v>46072</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3137,7 +3132,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3180,7 +3175,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 25388-2023</t>
+          <t>A 47356-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3194,10 +3189,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45089</v>
+        <v>45930</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3210,7 +3205,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3253,7 +3248,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 12079-2024</t>
+          <t>A 14386-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3267,10 +3262,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45377</v>
+        <v>46100</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3283,7 +3278,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>6.9</v>
+        <v>12.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3343,7 +3338,7 @@
         <v>44992</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3399,7 +3394,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 22134-2026</t>
+          <t>A 35996-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3413,10 +3408,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46153</v>
+        <v>45863</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3429,7 +3424,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3472,7 +3467,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 9482-2023</t>
+          <t>A 35997-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3486,10 +3481,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44981</v>
+        <v>45863</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3502,7 +3497,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3545,7 +3540,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 15533-2024</t>
+          <t>A 25508-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3559,10 +3554,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45401</v>
+        <v>45089</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3575,7 +3570,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>7.5</v>
+        <v>0.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3618,7 +3613,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 47870-2025</t>
+          <t>A 18281-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3632,10 +3627,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45932</v>
+        <v>46125</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3648,7 +3643,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>6.8</v>
+        <v>0.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3691,7 +3686,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 62496-2023</t>
+          <t>A 9686-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3705,10 +3700,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45268</v>
+        <v>44984</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3721,7 +3716,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3764,7 +3759,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 18503-2026</t>
+          <t>A 28088-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3778,10 +3773,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46127</v>
+        <v>45817</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3794,7 +3789,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>4.9</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3837,7 +3832,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 25385-2023</t>
+          <t>A 7409-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3851,10 +3846,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45089</v>
+        <v>45705</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3867,7 +3862,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3910,7 +3905,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 10819-2026</t>
+          <t>A 36761-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3924,10 +3919,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46078</v>
+        <v>44805</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3940,7 +3935,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3983,7 +3978,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 34170-2023</t>
+          <t>A 25388-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3997,10 +3992,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45138</v>
+        <v>45089</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4013,7 +4008,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>5.8</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4056,7 +4051,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 15357-2023</t>
+          <t>A 22134-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4070,10 +4065,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45019</v>
+        <v>46153</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4086,7 +4081,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4129,7 +4124,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 36761-2022</t>
+          <t>A 18503-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4143,10 +4138,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44805</v>
+        <v>46127</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4159,7 +4154,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4202,7 +4197,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 1574-2024</t>
+          <t>A 10940-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4216,10 +4211,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45306</v>
+        <v>45370</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4232,7 +4227,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.6</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4275,7 +4270,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 9849-2026</t>
+          <t>A 10819-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4289,10 +4284,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46072</v>
+        <v>46078</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4305,7 +4300,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.5</v>
+        <v>4.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4348,7 +4343,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 14386-2026</t>
+          <t>A 1574-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4362,10 +4357,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46100</v>
+        <v>45306</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4378,7 +4373,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>12.4</v>
+        <v>3.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4438,7 +4433,7 @@
         <v>46178</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4511,7 +4506,7 @@
         <v>46181</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4567,7 +4562,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 34468-2023</t>
+          <t>A 26169-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4581,10 +4576,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45139</v>
+        <v>46181</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4597,7 +4592,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4640,7 +4635,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 26169-2026</t>
+          <t>A 26497-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4654,10 +4649,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46181</v>
+        <v>46183</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4670,7 +4665,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4713,7 +4708,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 26497-2026</t>
+          <t>A 27428-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4727,10 +4722,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46183</v>
+        <v>46189</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4743,7 +4738,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4803,7 +4798,7 @@
         <v>46189</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4859,7 +4854,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 27428-2026</t>
+          <t>A 27435-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4876,7 +4871,7 @@
         <v>46189</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4889,7 +4884,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4932,7 +4927,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 27435-2026</t>
+          <t>A 7016-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4946,10 +4941,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46189</v>
+        <v>45701</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4961,8 +4956,13 @@
           <t>ESLÖV</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5005,7 +5005,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 18281-2026</t>
+          <t>A 16670-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5019,10 +5019,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46125</v>
+        <v>45754</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5078,7 +5078,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 10940-2024</t>
+          <t>A 34468-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5092,10 +5092,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45370</v>
+        <v>45139</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.5</v>
+        <v>5.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5151,7 +5151,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 11221-2024</t>
+          <t>A 62496-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45371</v>
+        <v>45268</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.3</v>
+        <v>2.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5224,7 +5224,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 43808-2024</t>
+          <t>A 34170-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5234,14 +5234,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45571</v>
+        <v>45138</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.5</v>
+        <v>5.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5297,7 +5297,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 9484-2023</t>
+          <t>A 24115-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44981</v>
+        <v>44725</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.4</v>
+        <v>4.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5370,7 +5370,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 44496-2023</t>
+          <t>A 58721-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5384,10 +5384,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45189</v>
+        <v>45986</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5443,7 +5443,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 33865-2024</t>
+          <t>A 9484-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5457,10 +5457,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45520</v>
+        <v>44981</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5516,7 +5516,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 16670-2025</t>
+          <t>A 16733-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5530,10 +5530,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45754</v>
+        <v>45030</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5589,7 +5589,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 34466-2023</t>
+          <t>A 44496-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5603,10 +5603,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45139</v>
+        <v>45189</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4.3</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5662,7 +5662,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 38173-2023</t>
+          <t>A 34466-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5676,10 +5676,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45161</v>
+        <v>45139</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.8</v>
+        <v>4.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5735,7 +5735,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 25508-2023</t>
+          <t>A 33865-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5749,10 +5749,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45089</v>
+        <v>45520</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5808,7 +5808,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 49137-2024</t>
+          <t>A 5812-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5822,10 +5822,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45594</v>
+        <v>44596</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5881,7 +5881,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 32984-2024</t>
+          <t>A 38173-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5895,10 +5895,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45517</v>
+        <v>45161</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5954,7 +5954,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 58721-2025</t>
+          <t>A 15357-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5968,10 +5968,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45986</v>
+        <v>45019</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6027,7 +6027,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 16792-2024</t>
+          <t>A 49137-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6041,10 +6041,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45411</v>
+        <v>45594</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6100,7 +6100,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 28088-2025</t>
+          <t>A 32984-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6114,10 +6114,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45817</v>
+        <v>45517</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>

--- a/Översikt ESLÖV.xlsx
+++ b/Översikt ESLÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45307</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45615</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44960</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>44846</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>45817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>46244</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>45793</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>46100</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>44981</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>45799</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>46098</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>45645</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>45306</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>45225</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>45426</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>44553</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>44690</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>45377</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>45401</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>45371</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>45747</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>44958</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>45932</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>44981</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>45089</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>45411</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>45571</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>46072</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>45930</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>46100</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         <v>44992</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         <v>45863</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>45863</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         <v>45089</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>46125</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>44984</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>45817</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>45705</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>44805</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         <v>45089</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>46153</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         <v>46127</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         <v>45370</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>46078</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         <v>45306</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
         <v>46178</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>46181</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
         <v>46181</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>46183</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>46189</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>46189</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>46189</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>45701</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         <v>45754</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>45139</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>45268</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>45138</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>44725</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>45986</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         <v>44981</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>45030</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>45189</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>45139</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>45520</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>44596</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>45161</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>45019</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>45594</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
         <v>45517</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>

--- a/Översikt ESLÖV.xlsx
+++ b/Översikt ESLÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45307</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45615</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44960</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>44846</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>45817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>46244</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>45793</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>46100</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>44981</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>45799</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>46098</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>45645</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>45306</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>45225</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>45426</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>44553</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>44690</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>45377</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>45401</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>45371</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>45747</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>44958</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>45932</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>44981</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>45089</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>45411</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>45571</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>46072</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>45930</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>46100</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         <v>44992</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         <v>45863</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>45863</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         <v>45089</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>46125</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>44984</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>45817</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>45705</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>44805</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         <v>45089</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>46153</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         <v>46127</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         <v>45370</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>46078</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         <v>45306</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
         <v>46178</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>46181</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
         <v>46181</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>46183</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>46189</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>46189</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>46189</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>45701</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         <v>45754</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>45139</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>45268</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>45138</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>44725</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>45986</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         <v>44981</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>45030</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>45189</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>45139</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>45520</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>44596</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>45161</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>45019</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>45594</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
         <v>45517</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>

--- a/Översikt ESLÖV.xlsx
+++ b/Översikt ESLÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45307</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45615</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44960</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>44846</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>45817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>46244</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>45793</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>46100</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>44981</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 24809-2025</t>
+          <t>A 1510-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45799</v>
+        <v>45306</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1630,10 +1630,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1649,46 +1649,46 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svart stork</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 24809-2025 artfynd.xlsx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 1510-2024 artfynd.xlsx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 24809-2025 karta.png", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 1510-2024 karta.png", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 24809-2025 georefererad karta.tif", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 1510-2024 georefererad karta.tif", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 24809-2025 FSC-klagomål.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 1510-2024 FSC-klagomål.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 24809-2025 FSC-klagomål mail.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 1510-2024 FSC-klagomål mail.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 24809-2025 tillsynsbegäran.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 1510-2024 tillsynsbegäran.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 24809-2025 tillsynsbegäran mail.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 1510-2024 tillsynsbegäran mail.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 24809-2025 prioriterade fågelarter.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 1510-2024 prioriterade fågelarter.docx", "A 1510-2024")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 14013-2026</t>
+          <t>A 52652-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1702,10 +1702,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46098</v>
+        <v>45225</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1717,13 +1717,8 @@
           <t>ESLÖV</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>8.800000000000001</v>
+        <v>2.9</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1735,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1747,10 +1742,10 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1759,50 +1754,46 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Grönfläckig padda</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14013-2026 artfynd.xlsx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 52652-2023 artfynd.xlsx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14013-2026 karta.png", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 52652-2023 karta.png", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14013-2026 georefererad karta.tif", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 52652-2023 georefererad karta.tif", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14013-2026 FSC-klagomål.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 52652-2023 FSC-klagomål.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14013-2026 FSC-klagomål mail.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 52652-2023 FSC-klagomål mail.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14013-2026 tillsynsbegäran.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 52652-2023 tillsynsbegäran.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14013-2026 tillsynsbegäran mail.docx", "A 14013-2026")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 14013-2026 prioriterade fågelarter.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 52652-2023 tillsynsbegäran mail.docx", "A 52652-2023")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 61035-2024</t>
+          <t>A 18713-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1816,10 +1807,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45645</v>
+        <v>45426</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1832,19 +1823,19 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>7.6</v>
+        <v>4.1</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
         <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1859,55 +1850,55 @@
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Gråtrut</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 61035-2024 artfynd.xlsx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 18713-2024 artfynd.xlsx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 61035-2024 karta.png", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 18713-2024 karta.png", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 61035-2024 georefererad karta.tif", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 18713-2024 georefererad karta.tif", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 61035-2024 FSC-klagomål.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 18713-2024 FSC-klagomål.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 61035-2024 FSC-klagomål mail.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 18713-2024 FSC-klagomål mail.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 61035-2024 tillsynsbegäran.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 18713-2024 tillsynsbegäran.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 61035-2024 tillsynsbegäran mail.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 18713-2024 tillsynsbegäran mail.docx", "A 18713-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 1510-2024</t>
+          <t>A 24809-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1921,10 +1912,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45306</v>
+        <v>45799</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1937,7 +1928,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1958,10 +1949,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1977,46 +1968,46 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Svart stork</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 1510-2024 artfynd.xlsx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 24809-2025 artfynd.xlsx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 1510-2024 karta.png", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 24809-2025 karta.png", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 1510-2024 georefererad karta.tif", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 24809-2025 georefererad karta.tif", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 1510-2024 FSC-klagomål.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 24809-2025 FSC-klagomål.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 1510-2024 FSC-klagomål mail.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 24809-2025 FSC-klagomål mail.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 1510-2024 tillsynsbegäran.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 24809-2025 tillsynsbegäran.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 1510-2024 tillsynsbegäran mail.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 24809-2025 tillsynsbegäran mail.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 1510-2024 prioriterade fågelarter.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 24809-2025 prioriterade fågelarter.docx", "A 24809-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 52652-2023</t>
+          <t>A 14013-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2030,10 +2021,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45225</v>
+        <v>46098</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2045,8 +2036,13 @@
           <t>ESLÖV</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>2.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2058,7 +2054,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2070,10 +2066,10 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2082,46 +2078,50 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Grönfläckig padda</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 52652-2023 artfynd.xlsx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14013-2026 artfynd.xlsx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 52652-2023 karta.png", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14013-2026 karta.png", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 52652-2023 georefererad karta.tif", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14013-2026 georefererad karta.tif", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 52652-2023 FSC-klagomål.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14013-2026 FSC-klagomål.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 52652-2023 FSC-klagomål mail.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14013-2026 FSC-klagomål mail.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 52652-2023 tillsynsbegäran.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14013-2026 tillsynsbegäran.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 52652-2023 tillsynsbegäran mail.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14013-2026 tillsynsbegäran mail.docx", "A 14013-2026")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 14013-2026 prioriterade fågelarter.docx", "A 14013-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 18713-2024</t>
+          <t>A 61035-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2135,10 +2135,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45426</v>
+        <v>45645</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2151,19 +2151,19 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.1</v>
+        <v>7.6</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2178,48 +2178,48 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Gråtrut</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 18713-2024 artfynd.xlsx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 61035-2024 artfynd.xlsx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 18713-2024 karta.png", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 61035-2024 karta.png", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 18713-2024 georefererad karta.tif", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 61035-2024 georefererad karta.tif", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 18713-2024 FSC-klagomål.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 61035-2024 FSC-klagomål.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 18713-2024 FSC-klagomål mail.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 61035-2024 FSC-klagomål mail.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 18713-2024 tillsynsbegäran.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 61035-2024 tillsynsbegäran.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 18713-2024 tillsynsbegäran mail.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 61035-2024 tillsynsbegäran mail.docx", "A 61035-2024")</f>
         <v/>
       </c>
     </row>
@@ -2243,7 +2243,7 @@
         <v>44553</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>44690</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 12079-2024</t>
+          <t>A 32984-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2386,10 +2386,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45377</v>
+        <v>45517</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>6.9</v>
+        <v>2.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2445,7 +2445,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 15533-2024</t>
+          <t>A 16792-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45401</v>
+        <v>45411</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>7.5</v>
+        <v>0.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2518,7 +2518,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 11221-2024</t>
+          <t>A 28088-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45371</v>
+        <v>45817</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 15467-2025</t>
+          <t>A 47356-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2605,10 +2605,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45747</v>
+        <v>45930</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2664,7 +2664,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 5869-2023</t>
+          <t>A 16733-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2674,14 +2674,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44958</v>
+        <v>45030</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2754,7 +2754,7 @@
         <v>45932</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 9482-2023</t>
+          <t>A 35996-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44981</v>
+        <v>45863</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.7</v>
+        <v>0.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2883,7 +2883,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 25385-2023</t>
+          <t>A 35997-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2897,10 +2897,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45089</v>
+        <v>45863</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2956,7 +2956,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 16792-2024</t>
+          <t>A 5812-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2970,10 +2970,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45411</v>
+        <v>44596</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3029,7 +3029,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 43808-2024</t>
+          <t>A 15467-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3039,14 +3039,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45571</v>
+        <v>45747</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3102,7 +3102,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 9849-2026</t>
+          <t>A 5869-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3112,14 +3112,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46072</v>
+        <v>44958</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3175,7 +3175,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 47356-2025</t>
+          <t>A 7409-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45930</v>
+        <v>45705</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 14386-2026</t>
+          <t>A 9686-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46100</v>
+        <v>44984</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>12.4</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3321,7 +3321,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 11204-2023</t>
+          <t>A 7016-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3335,10 +3335,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44992</v>
+        <v>45701</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3350,8 +3350,13 @@
           <t>ESLÖV</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3394,7 +3399,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 35996-2025</t>
+          <t>A 9849-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3408,10 +3413,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45863</v>
+        <v>46072</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3424,7 +3429,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3467,7 +3472,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 35997-2025</t>
+          <t>A 24115-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3481,10 +3486,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45863</v>
+        <v>44725</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3497,7 +3502,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>4.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3540,7 +3545,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 25508-2023</t>
+          <t>A 14386-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3554,10 +3559,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45089</v>
+        <v>46100</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3570,7 +3575,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.4</v>
+        <v>12.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3613,7 +3618,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 18281-2026</t>
+          <t>A 25388-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3627,10 +3632,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46125</v>
+        <v>45089</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3643,7 +3648,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3686,7 +3691,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 9686-2023</t>
+          <t>A 18281-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3700,10 +3705,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44984</v>
+        <v>46125</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3759,7 +3764,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 28088-2025</t>
+          <t>A 12079-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3773,10 +3778,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45817</v>
+        <v>45377</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3789,7 +3794,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>6.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3832,7 +3837,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 7409-2025</t>
+          <t>A 11204-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3846,10 +3851,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45705</v>
+        <v>44992</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3862,7 +3867,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3905,7 +3910,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 36761-2022</t>
+          <t>A 9482-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3919,10 +3924,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44805</v>
+        <v>44981</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3935,7 +3940,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3978,7 +3983,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 25388-2023</t>
+          <t>A 15533-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3992,10 +3997,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45089</v>
+        <v>45401</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4008,7 +4013,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>7.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4051,7 +4056,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 22134-2026</t>
+          <t>A 62496-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4065,10 +4070,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46153</v>
+        <v>45268</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4081,7 +4086,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4124,7 +4129,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 18503-2026</t>
+          <t>A 25385-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4138,10 +4143,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46127</v>
+        <v>45089</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4154,7 +4159,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>4.9</v>
+        <v>0.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4197,7 +4202,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 10940-2024</t>
+          <t>A 22134-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4211,10 +4216,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45370</v>
+        <v>46153</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4227,7 +4232,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4270,7 +4275,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 10819-2026</t>
+          <t>A 34170-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4284,10 +4289,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46078</v>
+        <v>45138</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4300,7 +4305,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4343,7 +4348,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 1574-2024</t>
+          <t>A 15357-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4357,10 +4362,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45306</v>
+        <v>45019</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4373,7 +4378,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4416,7 +4421,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 25730-2026</t>
+          <t>A 36761-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4430,10 +4435,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46178</v>
+        <v>44805</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4446,7 +4451,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.4</v>
+        <v>4.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4489,7 +4494,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 26165-2026</t>
+          <t>A 18503-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4503,10 +4508,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46181</v>
+        <v>46127</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4519,7 +4524,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2</v>
+        <v>4.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4562,7 +4567,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 26169-2026</t>
+          <t>A 10819-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4576,10 +4581,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46181</v>
+        <v>46078</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4592,7 +4597,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4635,7 +4640,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 26497-2026</t>
+          <t>A 34468-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4649,10 +4654,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46183</v>
+        <v>45139</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4665,7 +4670,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.4</v>
+        <v>5.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4708,7 +4713,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 27428-2026</t>
+          <t>A 1574-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4722,10 +4727,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46189</v>
+        <v>45306</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4738,7 +4743,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4781,7 +4786,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 27439-2026</t>
+          <t>A 25730-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4795,10 +4800,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46189</v>
+        <v>46178</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4811,7 +4816,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4854,7 +4859,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 27435-2026</t>
+          <t>A 26165-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4868,10 +4873,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46189</v>
+        <v>46181</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4884,7 +4889,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4927,7 +4932,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 7016-2025</t>
+          <t>A 26169-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4941,10 +4946,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45701</v>
+        <v>46181</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4956,13 +4961,8 @@
           <t>ESLÖV</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5005,7 +5005,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 16670-2025</t>
+          <t>A 26497-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5019,10 +5019,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45754</v>
+        <v>46183</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5078,7 +5078,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 34468-2023</t>
+          <t>A 27439-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5092,10 +5092,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45139</v>
+        <v>46189</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>5.5</v>
+        <v>1.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5151,7 +5151,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 62496-2023</t>
+          <t>A 27428-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45268</v>
+        <v>46189</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5224,7 +5224,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 34170-2023</t>
+          <t>A 27435-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5238,10 +5238,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45138</v>
+        <v>46189</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>5.8</v>
+        <v>0.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5297,7 +5297,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 24115-2022</t>
+          <t>A 10940-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44725</v>
+        <v>45370</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4.4</v>
+        <v>0.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5370,7 +5370,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 58721-2025</t>
+          <t>A 11221-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5384,10 +5384,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45986</v>
+        <v>45371</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.2</v>
+        <v>0.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5443,7 +5443,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 9484-2023</t>
+          <t>A 43808-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5453,14 +5453,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44981</v>
+        <v>45571</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5516,7 +5516,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 16733-2023</t>
+          <t>A 9484-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5530,10 +5530,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45030</v>
+        <v>44981</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5606,7 +5606,7 @@
         <v>45189</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 34466-2023</t>
+          <t>A 33865-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5676,10 +5676,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45139</v>
+        <v>45520</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4.3</v>
+        <v>1.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5735,7 +5735,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 33865-2024</t>
+          <t>A 16670-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5749,10 +5749,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45520</v>
+        <v>45754</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5808,7 +5808,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 5812-2022</t>
+          <t>A 34466-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5822,10 +5822,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44596</v>
+        <v>45139</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.5</v>
+        <v>4.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5898,7 +5898,7 @@
         <v>45161</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 15357-2023</t>
+          <t>A 25508-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5968,10 +5968,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45019</v>
+        <v>45089</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6044,7 +6044,7 @@
         <v>45594</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 32984-2024</t>
+          <t>A 58721-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6114,10 +6114,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45517</v>
+        <v>45986</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>

--- a/Översikt ESLÖV.xlsx
+++ b/Översikt ESLÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45307</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45615</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44960</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>44846</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>45817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>46244</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>45793</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>46100</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>44981</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 1510-2024</t>
+          <t>A 18713-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45306</v>
+        <v>45426</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1621,7 +1621,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1630,13 +1630,13 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1649,46 +1649,42 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Svart stork</t>
+          <t>Gråtrut</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 1510-2024 artfynd.xlsx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 18713-2024 artfynd.xlsx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 1510-2024 karta.png", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 18713-2024 karta.png", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 1510-2024 georefererad karta.tif", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 18713-2024 georefererad karta.tif", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 1510-2024 FSC-klagomål.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 18713-2024 FSC-klagomål.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 1510-2024 FSC-klagomål mail.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 18713-2024 FSC-klagomål mail.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 1510-2024 tillsynsbegäran.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 18713-2024 tillsynsbegäran.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 1510-2024 tillsynsbegäran mail.docx", "A 1510-2024")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 1510-2024 prioriterade fågelarter.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 18713-2024 tillsynsbegäran mail.docx", "A 18713-2024")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 52652-2023</t>
+          <t>A 24809-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1702,10 +1698,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45225</v>
+        <v>45799</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1718,7 +1714,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1730,7 +1726,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1742,10 +1738,10 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1758,42 +1754,46 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Grönfläckig padda</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 52652-2023 artfynd.xlsx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 24809-2025 artfynd.xlsx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 52652-2023 karta.png", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 24809-2025 karta.png", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 52652-2023 georefererad karta.tif", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 24809-2025 georefererad karta.tif", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 52652-2023 FSC-klagomål.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 24809-2025 FSC-klagomål.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 52652-2023 FSC-klagomål mail.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 24809-2025 FSC-klagomål mail.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 52652-2023 tillsynsbegäran.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 24809-2025 tillsynsbegäran.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 52652-2023 tillsynsbegäran mail.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 24809-2025 tillsynsbegäran mail.docx", "A 24809-2025")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 24809-2025 prioriterade fågelarter.docx", "A 24809-2025")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 18713-2024</t>
+          <t>A 14013-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1807,10 +1807,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45426</v>
+        <v>46098</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1822,8 +1822,13 @@
           <t>ESLÖV</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>4.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1835,7 +1840,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1847,10 +1852,10 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1859,46 +1864,50 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Gråtrut</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 18713-2024 artfynd.xlsx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14013-2026 artfynd.xlsx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 18713-2024 karta.png", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14013-2026 karta.png", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 18713-2024 georefererad karta.tif", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14013-2026 georefererad karta.tif", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 18713-2024 FSC-klagomål.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14013-2026 FSC-klagomål.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 18713-2024 FSC-klagomål mail.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14013-2026 FSC-klagomål mail.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 18713-2024 tillsynsbegäran.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14013-2026 tillsynsbegäran.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 18713-2024 tillsynsbegäran mail.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14013-2026 tillsynsbegäran mail.docx", "A 14013-2026")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 14013-2026 prioriterade fågelarter.docx", "A 14013-2026")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 24809-2025</t>
+          <t>A 61035-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1912,10 +1921,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45799</v>
+        <v>45645</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1928,17 +1937,17 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.4</v>
+        <v>7.6</v>
       </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
@@ -1952,7 +1961,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1961,53 +1970,49 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 24809-2025 artfynd.xlsx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 61035-2024 artfynd.xlsx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 24809-2025 karta.png", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 61035-2024 karta.png", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 24809-2025 georefererad karta.tif", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 61035-2024 georefererad karta.tif", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 24809-2025 FSC-klagomål.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 61035-2024 FSC-klagomål.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 24809-2025 FSC-klagomål mail.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 61035-2024 FSC-klagomål mail.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 24809-2025 tillsynsbegäran.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 61035-2024 tillsynsbegäran.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 24809-2025 tillsynsbegäran mail.docx", "A 24809-2025")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 24809-2025 prioriterade fågelarter.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 61035-2024 tillsynsbegäran mail.docx", "A 61035-2024")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 14013-2026</t>
+          <t>A 1510-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2021,10 +2026,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46098</v>
+        <v>45306</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2036,13 +2041,8 @@
           <t>ESLÖV</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>8.800000000000001</v>
+        <v>3.7</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2063,10 +2063,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2078,50 +2078,50 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Svart stork</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14013-2026 artfynd.xlsx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 1510-2024 artfynd.xlsx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14013-2026 karta.png", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 1510-2024 karta.png", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14013-2026 georefererad karta.tif", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 1510-2024 georefererad karta.tif", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14013-2026 FSC-klagomål.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 1510-2024 FSC-klagomål.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14013-2026 FSC-klagomål mail.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 1510-2024 FSC-klagomål mail.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14013-2026 tillsynsbegäran.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 1510-2024 tillsynsbegäran.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14013-2026 tillsynsbegäran mail.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 1510-2024 tillsynsbegäran mail.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 14013-2026 prioriterade fågelarter.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 1510-2024 prioriterade fågelarter.docx", "A 1510-2024")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 61035-2024</t>
+          <t>A 52652-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2135,10 +2135,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45645</v>
+        <v>45225</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2151,19 +2151,19 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>7.6</v>
+        <v>2.9</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2178,48 +2178,48 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Grönfläckig padda</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 61035-2024 artfynd.xlsx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 52652-2023 artfynd.xlsx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 61035-2024 karta.png", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 52652-2023 karta.png", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 61035-2024 georefererad karta.tif", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 52652-2023 georefererad karta.tif", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 61035-2024 FSC-klagomål.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 52652-2023 FSC-klagomål.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 61035-2024 FSC-klagomål mail.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 52652-2023 FSC-klagomål mail.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 61035-2024 tillsynsbegäran.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 52652-2023 tillsynsbegäran.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 61035-2024 tillsynsbegäran mail.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 52652-2023 tillsynsbegäran mail.docx", "A 52652-2023")</f>
         <v/>
       </c>
     </row>
@@ -2243,7 +2243,7 @@
         <v>44553</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>44690</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 32984-2024</t>
+          <t>A 12079-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2386,10 +2386,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45517</v>
+        <v>45377</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.9</v>
+        <v>6.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2445,7 +2445,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 16792-2024</t>
+          <t>A 15533-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45411</v>
+        <v>45401</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.9</v>
+        <v>7.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2518,7 +2518,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 28088-2025</t>
+          <t>A 11221-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45817</v>
+        <v>45371</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 47356-2025</t>
+          <t>A 15467-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2605,10 +2605,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45930</v>
+        <v>45747</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2664,7 +2664,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 16733-2023</t>
+          <t>A 5869-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2674,14 +2674,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45030</v>
+        <v>44958</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 47870-2025</t>
+          <t>A 32984-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2751,10 +2751,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45932</v>
+        <v>45517</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>6.8</v>
+        <v>2.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2810,7 +2810,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 35996-2025</t>
+          <t>A 47870-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45863</v>
+        <v>45932</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.8</v>
+        <v>6.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2883,7 +2883,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 35997-2025</t>
+          <t>A 16792-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2897,10 +2897,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45863</v>
+        <v>45411</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 5812-2022</t>
+          <t>A 9482-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2970,10 +2970,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44596</v>
+        <v>44981</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3029,7 +3029,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 15467-2025</t>
+          <t>A 25385-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3043,10 +3043,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45747</v>
+        <v>45089</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3102,7 +3102,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 5869-2023</t>
+          <t>A 43808-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44958</v>
+        <v>45571</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3175,7 +3175,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 7409-2025</t>
+          <t>A 28088-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45705</v>
+        <v>45817</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 9686-2023</t>
+          <t>A 47356-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44984</v>
+        <v>45930</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3321,7 +3321,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 7016-2025</t>
+          <t>A 11204-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3335,10 +3335,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45701</v>
+        <v>44992</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3350,13 +3350,8 @@
           <t>ESLÖV</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3399,7 +3394,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 9849-2026</t>
+          <t>A 35996-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3413,10 +3408,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46072</v>
+        <v>45863</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3429,7 +3424,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3472,7 +3467,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 24115-2022</t>
+          <t>A 35997-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3486,10 +3481,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44725</v>
+        <v>45863</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3502,7 +3497,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4.4</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3545,7 +3540,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 14386-2026</t>
+          <t>A 25508-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3559,10 +3554,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46100</v>
+        <v>45089</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3575,7 +3570,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>12.4</v>
+        <v>0.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3618,7 +3613,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 25388-2023</t>
+          <t>A 9686-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3632,10 +3627,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45089</v>
+        <v>44984</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3648,7 +3643,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3691,7 +3686,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 18281-2026</t>
+          <t>A 9849-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3705,10 +3700,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46125</v>
+        <v>46072</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3721,7 +3716,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3764,7 +3759,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 12079-2024</t>
+          <t>A 7409-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3778,10 +3773,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45377</v>
+        <v>45705</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3794,7 +3789,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>6.9</v>
+        <v>1.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3837,7 +3832,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 11204-2023</t>
+          <t>A 14386-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3851,10 +3846,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44992</v>
+        <v>46100</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3867,7 +3862,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.7</v>
+        <v>12.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3910,7 +3905,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 9482-2023</t>
+          <t>A 36761-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3924,10 +3919,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44981</v>
+        <v>44805</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3940,7 +3935,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3983,7 +3978,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 15533-2024</t>
+          <t>A 25388-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3997,10 +3992,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45401</v>
+        <v>45089</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4013,7 +4008,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>7.5</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4056,7 +4051,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 62496-2023</t>
+          <t>A 18281-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4070,10 +4065,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45268</v>
+        <v>46125</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4086,7 +4081,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4129,7 +4124,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 25385-2023</t>
+          <t>A 10940-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4143,10 +4138,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45089</v>
+        <v>45370</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4159,7 +4154,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4202,7 +4197,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 22134-2026</t>
+          <t>A 7016-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4216,10 +4211,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46153</v>
+        <v>45701</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4231,8 +4226,13 @@
           <t>ESLÖV</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4275,7 +4275,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 34170-2023</t>
+          <t>A 22134-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4289,10 +4289,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45138</v>
+        <v>46153</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>5.8</v>
+        <v>2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4348,7 +4348,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 15357-2023</t>
+          <t>A 18503-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4362,10 +4362,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45019</v>
+        <v>46127</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>4.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4421,7 +4421,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 36761-2022</t>
+          <t>A 10819-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4435,10 +4435,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44805</v>
+        <v>46078</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4494,7 +4494,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 18503-2026</t>
+          <t>A 1574-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46127</v>
+        <v>45306</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>4.9</v>
+        <v>3.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4567,7 +4567,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 10819-2026</t>
+          <t>A 16670-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46078</v>
+        <v>45754</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>4.9</v>
+        <v>1.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4657,7 +4657,7 @@
         <v>45139</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 1574-2024</t>
+          <t>A 25730-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4727,10 +4727,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45306</v>
+        <v>46178</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.6</v>
+        <v>1.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4786,7 +4786,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 25730-2026</t>
+          <t>A 26165-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4859,7 +4859,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 26165-2026</t>
+          <t>A 26169-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4876,7 +4876,7 @@
         <v>46181</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4932,7 +4932,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 26169-2026</t>
+          <t>A 26497-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4946,10 +4946,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46181</v>
+        <v>46183</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5005,7 +5005,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 26497-2026</t>
+          <t>A 27428-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5019,10 +5019,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46183</v>
+        <v>46189</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5095,7 +5095,7 @@
         <v>46189</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 27428-2026</t>
+          <t>A 27435-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5168,7 +5168,7 @@
         <v>46189</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5224,7 +5224,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 27435-2026</t>
+          <t>A 62496-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5238,10 +5238,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46189</v>
+        <v>45268</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5297,7 +5297,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 10940-2024</t>
+          <t>A 34170-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45370</v>
+        <v>45138</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>5.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5370,7 +5370,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 11221-2024</t>
+          <t>A 24115-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5384,10 +5384,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45371</v>
+        <v>44725</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.3</v>
+        <v>4.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5443,7 +5443,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 43808-2024</t>
+          <t>A 9484-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5453,14 +5453,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45571</v>
+        <v>44981</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5516,7 +5516,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 9484-2023</t>
+          <t>A 16733-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5530,10 +5530,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44981</v>
+        <v>45030</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5606,7 +5606,7 @@
         <v>45189</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 33865-2024</t>
+          <t>A 34466-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5676,10 +5676,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45520</v>
+        <v>45139</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.3</v>
+        <v>4.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5735,7 +5735,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 16670-2025</t>
+          <t>A 33865-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5749,10 +5749,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45754</v>
+        <v>45520</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5808,7 +5808,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 34466-2023</t>
+          <t>A 5812-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5822,10 +5822,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45139</v>
+        <v>44596</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>4.3</v>
+        <v>0.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5898,7 +5898,7 @@
         <v>45161</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 25508-2023</t>
+          <t>A 15357-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5968,10 +5968,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45089</v>
+        <v>45019</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6044,7 +6044,7 @@
         <v>45594</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
         <v>45986</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>

--- a/Översikt ESLÖV.xlsx
+++ b/Översikt ESLÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45307</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45615</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44960</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>44846</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>45817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>46244</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>45793</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 14395-2026</t>
+          <t>A 9487-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46100</v>
+        <v>44981</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.9</v>
+        <v>1.9</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1406,13 +1406,13 @@
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1424,162 +1424,162 @@
         <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>2</v>
       </c>
       <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Älg
+Kambräken</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 9487-2023 artfynd.xlsx", "A 9487-2023")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 9487-2023 karta.png", "A 9487-2023")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 9487-2023 georefererad karta.tif", "A 9487-2023")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 9487-2023 FSC-klagomål.docx", "A 9487-2023")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 9487-2023 FSC-klagomål mail.docx", "A 9487-2023")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 9487-2023 tillsynsbegäran.docx", "A 9487-2023")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 9487-2023 tillsynsbegäran mail.docx", "A 9487-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 14395-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46100</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ESLÖV</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="n">
         <v>4</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Ask
 Kransrams</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14395-2026 artfynd.xlsx", "A 14395-2026")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14395-2026 karta.png", "A 14395-2026")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14395-2026 georefererad karta.tif", "A 14395-2026")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14395-2026 FSC-klagomål.docx", "A 14395-2026")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14395-2026 FSC-klagomål mail.docx", "A 14395-2026")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14395-2026 tillsynsbegäran.docx", "A 14395-2026")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14395-2026 tillsynsbegäran mail.docx", "A 14395-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 9487-2023</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>44981</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>ESLÖV</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Älg
-Kambräken</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 9487-2023 artfynd.xlsx", "A 9487-2023")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 9487-2023 karta.png", "A 9487-2023")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 9487-2023 georefererad karta.tif", "A 9487-2023")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 9487-2023 FSC-klagomål.docx", "A 9487-2023")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 9487-2023 FSC-klagomål mail.docx", "A 9487-2023")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 9487-2023 tillsynsbegäran.docx", "A 9487-2023")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 9487-2023 tillsynsbegäran mail.docx", "A 9487-2023")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 18713-2024</t>
+          <t>A 1510-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45426</v>
+        <v>45306</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1621,22 +1621,22 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
         <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1649,42 +1649,46 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Gråtrut</t>
+          <t>Svart stork</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 18713-2024 artfynd.xlsx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 1510-2024 artfynd.xlsx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 18713-2024 karta.png", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 1510-2024 karta.png", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 18713-2024 georefererad karta.tif", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 1510-2024 georefererad karta.tif", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 18713-2024 FSC-klagomål.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 1510-2024 FSC-klagomål.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 18713-2024 FSC-klagomål mail.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 1510-2024 FSC-klagomål mail.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 18713-2024 tillsynsbegäran.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 1510-2024 tillsynsbegäran.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 18713-2024 tillsynsbegäran mail.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 1510-2024 tillsynsbegäran mail.docx", "A 1510-2024")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 1510-2024 prioriterade fågelarter.docx", "A 1510-2024")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 24809-2025</t>
+          <t>A 52652-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1698,10 +1702,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45799</v>
+        <v>45225</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1714,7 +1718,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1726,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1738,10 +1742,10 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1754,46 +1758,42 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönfläckig padda</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 24809-2025 artfynd.xlsx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 52652-2023 artfynd.xlsx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 24809-2025 karta.png", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 52652-2023 karta.png", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 24809-2025 georefererad karta.tif", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 52652-2023 georefererad karta.tif", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 24809-2025 FSC-klagomål.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 52652-2023 FSC-klagomål.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 24809-2025 FSC-klagomål mail.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 52652-2023 FSC-klagomål mail.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 24809-2025 tillsynsbegäran.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 52652-2023 tillsynsbegäran.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 24809-2025 tillsynsbegäran mail.docx", "A 24809-2025")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 24809-2025 prioriterade fågelarter.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 52652-2023 tillsynsbegäran mail.docx", "A 52652-2023")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 14013-2026</t>
+          <t>A 18713-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1807,10 +1807,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46098</v>
+        <v>45426</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1822,13 +1822,8 @@
           <t>ESLÖV</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>8.800000000000001</v>
+        <v>4.1</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1840,7 +1835,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1852,10 +1847,10 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1864,50 +1859,46 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Gråtrut</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14013-2026 artfynd.xlsx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 18713-2024 artfynd.xlsx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14013-2026 karta.png", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 18713-2024 karta.png", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14013-2026 georefererad karta.tif", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 18713-2024 georefererad karta.tif", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14013-2026 FSC-klagomål.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 18713-2024 FSC-klagomål.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14013-2026 FSC-klagomål mail.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 18713-2024 FSC-klagomål mail.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14013-2026 tillsynsbegäran.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 18713-2024 tillsynsbegäran.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14013-2026 tillsynsbegäran mail.docx", "A 14013-2026")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 14013-2026 prioriterade fågelarter.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 18713-2024 tillsynsbegäran mail.docx", "A 18713-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 61035-2024</t>
+          <t>A 24809-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1921,10 +1912,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45645</v>
+        <v>45799</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1937,16 +1928,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>7.6</v>
+        <v>1.4</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1961,7 +1952,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1970,49 +1961,53 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 61035-2024 artfynd.xlsx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 24809-2025 artfynd.xlsx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 61035-2024 karta.png", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 24809-2025 karta.png", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 61035-2024 georefererad karta.tif", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 24809-2025 georefererad karta.tif", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 61035-2024 FSC-klagomål.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 24809-2025 FSC-klagomål.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 61035-2024 FSC-klagomål mail.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 24809-2025 FSC-klagomål mail.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 61035-2024 tillsynsbegäran.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 24809-2025 tillsynsbegäran.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 61035-2024 tillsynsbegäran mail.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 24809-2025 tillsynsbegäran mail.docx", "A 24809-2025")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 24809-2025 prioriterade fågelarter.docx", "A 24809-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 1510-2024</t>
+          <t>A 14013-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2026,10 +2021,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45306</v>
+        <v>46098</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2041,8 +2036,13 @@
           <t>ESLÖV</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>3.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2063,10 +2063,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2078,50 +2078,50 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Svart stork</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 1510-2024 artfynd.xlsx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14013-2026 artfynd.xlsx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 1510-2024 karta.png", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14013-2026 karta.png", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 1510-2024 georefererad karta.tif", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14013-2026 georefererad karta.tif", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 1510-2024 FSC-klagomål.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14013-2026 FSC-klagomål.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 1510-2024 FSC-klagomål mail.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14013-2026 FSC-klagomål mail.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 1510-2024 tillsynsbegäran.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14013-2026 tillsynsbegäran.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 1510-2024 tillsynsbegäran mail.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14013-2026 tillsynsbegäran mail.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 1510-2024 prioriterade fågelarter.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 14013-2026 prioriterade fågelarter.docx", "A 14013-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 52652-2023</t>
+          <t>A 61035-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2135,10 +2135,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45225</v>
+        <v>45645</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2151,19 +2151,19 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.9</v>
+        <v>7.6</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2178,48 +2178,48 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Grönfläckig padda</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 52652-2023 artfynd.xlsx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 61035-2024 artfynd.xlsx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 52652-2023 karta.png", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 61035-2024 karta.png", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 52652-2023 georefererad karta.tif", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 61035-2024 georefererad karta.tif", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 52652-2023 FSC-klagomål.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 61035-2024 FSC-klagomål.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 52652-2023 FSC-klagomål mail.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 61035-2024 FSC-klagomål mail.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 52652-2023 tillsynsbegäran.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 61035-2024 tillsynsbegäran.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 52652-2023 tillsynsbegäran mail.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 61035-2024 tillsynsbegäran mail.docx", "A 61035-2024")</f>
         <v/>
       </c>
     </row>
@@ -2243,7 +2243,7 @@
         <v>44553</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>44690</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 12079-2024</t>
+          <t>A 5812-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2386,10 +2386,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45377</v>
+        <v>44596</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>6.9</v>
+        <v>0.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2445,7 +2445,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 15533-2024</t>
+          <t>A 44496-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45401</v>
+        <v>45189</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>7.5</v>
+        <v>0.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2518,7 +2518,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 11221-2024</t>
+          <t>A 33865-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45371</v>
+        <v>45520</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 15467-2025</t>
+          <t>A 25385-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2605,10 +2605,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45747</v>
+        <v>45089</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2664,7 +2664,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 5869-2023</t>
+          <t>A 16670-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2674,14 +2674,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44958</v>
+        <v>45754</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 32984-2024</t>
+          <t>A 34466-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2751,10 +2751,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45517</v>
+        <v>45139</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2810,7 +2810,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 47870-2025</t>
+          <t>A 38173-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45932</v>
+        <v>45161</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>6.8</v>
+        <v>2.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2883,7 +2883,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 16792-2024</t>
+          <t>A 34170-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2897,10 +2897,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45411</v>
+        <v>45138</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.9</v>
+        <v>5.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2956,7 +2956,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 9482-2023</t>
+          <t>A 15357-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2970,10 +2970,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44981</v>
+        <v>45019</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.7</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3029,7 +3029,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 25385-2023</t>
+          <t>A 36761-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3043,10 +3043,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45089</v>
+        <v>44805</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.7</v>
+        <v>4.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3102,7 +3102,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 43808-2024</t>
+          <t>A 15467-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3112,14 +3112,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45571</v>
+        <v>45747</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3175,7 +3175,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 28088-2025</t>
+          <t>A 5869-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3185,14 +3185,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45817</v>
+        <v>44958</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 47356-2025</t>
+          <t>A 7409-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45930</v>
+        <v>45705</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3321,7 +3321,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 11204-2023</t>
+          <t>A 9686-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3335,10 +3335,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44992</v>
+        <v>44984</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3394,7 +3394,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 35996-2025</t>
+          <t>A 7016-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3408,10 +3408,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45863</v>
+        <v>45701</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3423,8 +3423,13 @@
           <t>ESLÖV</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3467,7 +3472,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 35997-2025</t>
+          <t>A 34468-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3481,10 +3486,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45863</v>
+        <v>45139</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3497,7 +3502,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>5.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3557,7 +3562,7 @@
         <v>45089</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3613,7 +3618,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 9686-2023</t>
+          <t>A 24115-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3627,10 +3632,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44984</v>
+        <v>44725</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3643,7 +3648,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.8</v>
+        <v>4.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3686,7 +3691,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 9849-2026</t>
+          <t>A 49137-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3700,10 +3705,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46072</v>
+        <v>45594</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3716,7 +3721,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3759,7 +3764,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 7409-2025</t>
+          <t>A 32984-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3773,10 +3778,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45705</v>
+        <v>45517</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3789,7 +3794,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3832,7 +3837,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 14386-2026</t>
+          <t>A 25388-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3846,10 +3851,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46100</v>
+        <v>45089</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3862,7 +3867,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>12.4</v>
+        <v>0.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3905,7 +3910,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 36761-2022</t>
+          <t>A 16792-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3919,10 +3924,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44805</v>
+        <v>45411</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3935,7 +3940,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>4.8</v>
+        <v>0.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3978,7 +3983,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 25388-2023</t>
+          <t>A 12079-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3992,10 +3997,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45089</v>
+        <v>45377</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4008,7 +4013,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>6.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4051,7 +4056,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 18281-2026</t>
+          <t>A 28088-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4065,10 +4070,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46125</v>
+        <v>45817</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4081,7 +4086,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4124,7 +4129,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 10940-2024</t>
+          <t>A 11204-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4138,10 +4143,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45370</v>
+        <v>44992</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4154,7 +4159,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4197,7 +4202,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 7016-2025</t>
+          <t>A 10940-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4211,10 +4216,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45701</v>
+        <v>45370</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4226,13 +4231,8 @@
           <t>ESLÖV</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4275,7 +4275,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 22134-2026</t>
+          <t>A 11221-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4289,10 +4289,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46153</v>
+        <v>45371</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4348,7 +4348,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 18503-2026</t>
+          <t>A 16733-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4362,10 +4362,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46127</v>
+        <v>45030</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>4.9</v>
+        <v>2.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4421,7 +4421,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 10819-2026</t>
+          <t>A 43808-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4431,14 +4431,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46078</v>
+        <v>45571</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4.9</v>
+        <v>1.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4494,7 +4494,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 1574-2024</t>
+          <t>A 9484-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45306</v>
+        <v>44981</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.6</v>
+        <v>1.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4567,7 +4567,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 16670-2025</t>
+          <t>A 9482-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45754</v>
+        <v>44981</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4640,7 +4640,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 34468-2023</t>
+          <t>A 15533-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4654,10 +4654,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45139</v>
+        <v>45401</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4713,7 +4713,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 25730-2026</t>
+          <t>A 62496-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4727,10 +4727,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46178</v>
+        <v>45268</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4786,7 +4786,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 26165-2026</t>
+          <t>A 35996-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46181</v>
+        <v>45863</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4859,7 +4859,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 26169-2026</t>
+          <t>A 35997-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46181</v>
+        <v>45863</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.5</v>
+        <v>0.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4932,7 +4932,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 26497-2026</t>
+          <t>A 47356-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4946,10 +4946,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46183</v>
+        <v>45930</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5005,7 +5005,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 27428-2026</t>
+          <t>A 47870-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5019,10 +5019,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46189</v>
+        <v>45932</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.4</v>
+        <v>6.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5078,7 +5078,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 27439-2026</t>
+          <t>A 9849-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5092,10 +5092,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46189</v>
+        <v>46072</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5151,7 +5151,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 27435-2026</t>
+          <t>A 14386-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46189</v>
+        <v>46100</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.9</v>
+        <v>12.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5224,7 +5224,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 62496-2023</t>
+          <t>A 18281-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5238,10 +5238,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45268</v>
+        <v>46125</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5297,7 +5297,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 34170-2023</t>
+          <t>A 22134-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45138</v>
+        <v>46153</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>5.8</v>
+        <v>2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5370,7 +5370,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 24115-2022</t>
+          <t>A 18503-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5384,10 +5384,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44725</v>
+        <v>46127</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5443,7 +5443,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 9484-2023</t>
+          <t>A 10819-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5457,10 +5457,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44981</v>
+        <v>46078</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.4</v>
+        <v>4.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5516,7 +5516,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 16733-2023</t>
+          <t>A 1574-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5530,10 +5530,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45030</v>
+        <v>45306</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5589,7 +5589,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 44496-2023</t>
+          <t>A 25730-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5603,10 +5603,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45189</v>
+        <v>46178</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5662,7 +5662,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 34466-2023</t>
+          <t>A 26165-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5676,10 +5676,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45139</v>
+        <v>46181</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4.3</v>
+        <v>2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5735,7 +5735,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 33865-2024</t>
+          <t>A 26169-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5749,10 +5749,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45520</v>
+        <v>46181</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5808,7 +5808,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 5812-2022</t>
+          <t>A 26497-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5822,10 +5822,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44596</v>
+        <v>46183</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5881,7 +5881,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 38173-2023</t>
+          <t>A 27439-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5895,10 +5895,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45161</v>
+        <v>46189</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5954,7 +5954,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 15357-2023</t>
+          <t>A 27428-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5968,10 +5968,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45019</v>
+        <v>46189</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6027,7 +6027,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 49137-2024</t>
+          <t>A 27435-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6041,10 +6041,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45594</v>
+        <v>46189</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6117,7 +6117,7 @@
         <v>45986</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>

--- a/Översikt ESLÖV.xlsx
+++ b/Översikt ESLÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45307</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45615</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44960</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>44846</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>45817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>46244</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>45793</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 9487-2023</t>
+          <t>A 14395-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44981</v>
+        <v>46100</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.9</v>
+        <v>4.9</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1406,13 +1406,13 @@
         <v>1</v>
       </c>
       <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
         <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1424,162 +1424,162 @@
         <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>2</v>
       </c>
       <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Kransrams</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14395-2026 artfynd.xlsx", "A 14395-2026")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14395-2026 karta.png", "A 14395-2026")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14395-2026 georefererad karta.tif", "A 14395-2026")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14395-2026 FSC-klagomål.docx", "A 14395-2026")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14395-2026 FSC-klagomål mail.docx", "A 14395-2026")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14395-2026 tillsynsbegäran.docx", "A 14395-2026")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14395-2026 tillsynsbegäran mail.docx", "A 14395-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 9487-2023</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>44981</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ESLÖV</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>2</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Älg
 Kambräken</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 9487-2023 artfynd.xlsx", "A 9487-2023")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 9487-2023 karta.png", "A 9487-2023")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 9487-2023 georefererad karta.tif", "A 9487-2023")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 9487-2023 FSC-klagomål.docx", "A 9487-2023")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 9487-2023 FSC-klagomål mail.docx", "A 9487-2023")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 9487-2023 tillsynsbegäran.docx", "A 9487-2023")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 9487-2023 tillsynsbegäran mail.docx", "A 9487-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 14395-2026</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>46100</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>ESLÖV</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>4</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Kransrams</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14395-2026 artfynd.xlsx", "A 14395-2026")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14395-2026 karta.png", "A 14395-2026")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14395-2026 georefererad karta.tif", "A 14395-2026")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14395-2026 FSC-klagomål.docx", "A 14395-2026")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14395-2026 FSC-klagomål mail.docx", "A 14395-2026")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14395-2026 tillsynsbegäran.docx", "A 14395-2026")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14395-2026 tillsynsbegäran mail.docx", "A 14395-2026")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 1510-2024</t>
+          <t>A 18713-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45306</v>
+        <v>45426</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1621,7 +1621,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1630,13 +1630,13 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1649,46 +1649,42 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Svart stork</t>
+          <t>Gråtrut</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 1510-2024 artfynd.xlsx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 18713-2024 artfynd.xlsx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 1510-2024 karta.png", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 18713-2024 karta.png", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 1510-2024 georefererad karta.tif", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 18713-2024 georefererad karta.tif", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 1510-2024 FSC-klagomål.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 18713-2024 FSC-klagomål.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 1510-2024 FSC-klagomål mail.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 18713-2024 FSC-klagomål mail.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 1510-2024 tillsynsbegäran.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 18713-2024 tillsynsbegäran.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 1510-2024 tillsynsbegäran mail.docx", "A 1510-2024")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 1510-2024 prioriterade fågelarter.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 18713-2024 tillsynsbegäran mail.docx", "A 18713-2024")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 52652-2023</t>
+          <t>A 24809-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1702,10 +1698,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45225</v>
+        <v>45799</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1718,7 +1714,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1730,7 +1726,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1742,10 +1738,10 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1758,42 +1754,46 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Grönfläckig padda</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 52652-2023 artfynd.xlsx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 24809-2025 artfynd.xlsx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 52652-2023 karta.png", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 24809-2025 karta.png", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 52652-2023 georefererad karta.tif", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 24809-2025 georefererad karta.tif", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 52652-2023 FSC-klagomål.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 24809-2025 FSC-klagomål.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 52652-2023 FSC-klagomål mail.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 24809-2025 FSC-klagomål mail.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 52652-2023 tillsynsbegäran.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 24809-2025 tillsynsbegäran.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 52652-2023 tillsynsbegäran mail.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 24809-2025 tillsynsbegäran mail.docx", "A 24809-2025")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 24809-2025 prioriterade fågelarter.docx", "A 24809-2025")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 18713-2024</t>
+          <t>A 14013-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1807,10 +1807,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45426</v>
+        <v>46098</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1822,8 +1822,13 @@
           <t>ESLÖV</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>4.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1835,7 +1840,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1847,10 +1852,10 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1859,46 +1864,50 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Gråtrut</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 18713-2024 artfynd.xlsx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14013-2026 artfynd.xlsx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 18713-2024 karta.png", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14013-2026 karta.png", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 18713-2024 georefererad karta.tif", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14013-2026 georefererad karta.tif", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 18713-2024 FSC-klagomål.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14013-2026 FSC-klagomål.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 18713-2024 FSC-klagomål mail.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14013-2026 FSC-klagomål mail.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 18713-2024 tillsynsbegäran.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14013-2026 tillsynsbegäran.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 18713-2024 tillsynsbegäran mail.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14013-2026 tillsynsbegäran mail.docx", "A 14013-2026")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 14013-2026 prioriterade fågelarter.docx", "A 14013-2026")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 24809-2025</t>
+          <t>A 61035-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1912,10 +1921,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45799</v>
+        <v>45645</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1928,17 +1937,17 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.4</v>
+        <v>7.6</v>
       </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
@@ -1952,7 +1961,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1961,53 +1970,49 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 24809-2025 artfynd.xlsx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 61035-2024 artfynd.xlsx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 24809-2025 karta.png", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 61035-2024 karta.png", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 24809-2025 georefererad karta.tif", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 61035-2024 georefererad karta.tif", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 24809-2025 FSC-klagomål.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 61035-2024 FSC-klagomål.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 24809-2025 FSC-klagomål mail.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 61035-2024 FSC-klagomål mail.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 24809-2025 tillsynsbegäran.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 61035-2024 tillsynsbegäran.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 24809-2025 tillsynsbegäran mail.docx", "A 24809-2025")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 24809-2025 prioriterade fågelarter.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 61035-2024 tillsynsbegäran mail.docx", "A 61035-2024")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 14013-2026</t>
+          <t>A 1510-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2021,10 +2026,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46098</v>
+        <v>45306</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2036,13 +2041,8 @@
           <t>ESLÖV</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>8.800000000000001</v>
+        <v>3.7</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2063,10 +2063,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2078,50 +2078,50 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Svart stork</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14013-2026 artfynd.xlsx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 1510-2024 artfynd.xlsx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14013-2026 karta.png", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 1510-2024 karta.png", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14013-2026 georefererad karta.tif", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 1510-2024 georefererad karta.tif", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14013-2026 FSC-klagomål.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 1510-2024 FSC-klagomål.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14013-2026 FSC-klagomål mail.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 1510-2024 FSC-klagomål mail.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14013-2026 tillsynsbegäran.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 1510-2024 tillsynsbegäran.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14013-2026 tillsynsbegäran mail.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 1510-2024 tillsynsbegäran mail.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 14013-2026 prioriterade fågelarter.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 1510-2024 prioriterade fågelarter.docx", "A 1510-2024")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 61035-2024</t>
+          <t>A 52652-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2135,10 +2135,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45645</v>
+        <v>45225</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2151,19 +2151,19 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>7.6</v>
+        <v>2.9</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2178,48 +2178,48 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Grönfläckig padda</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 61035-2024 artfynd.xlsx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 52652-2023 artfynd.xlsx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 61035-2024 karta.png", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 52652-2023 karta.png", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 61035-2024 georefererad karta.tif", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 52652-2023 georefererad karta.tif", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 61035-2024 FSC-klagomål.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 52652-2023 FSC-klagomål.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 61035-2024 FSC-klagomål mail.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 52652-2023 FSC-klagomål mail.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 61035-2024 tillsynsbegäran.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 52652-2023 tillsynsbegäran.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 61035-2024 tillsynsbegäran mail.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 52652-2023 tillsynsbegäran mail.docx", "A 52652-2023")</f>
         <v/>
       </c>
     </row>
@@ -2243,7 +2243,7 @@
         <v>44553</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>44690</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 5812-2022</t>
+          <t>A 12079-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2386,10 +2386,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44596</v>
+        <v>45377</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.5</v>
+        <v>6.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2445,7 +2445,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 44496-2023</t>
+          <t>A 15533-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45189</v>
+        <v>45401</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.5</v>
+        <v>7.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2518,7 +2518,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 33865-2024</t>
+          <t>A 15467-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45520</v>
+        <v>45747</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 25385-2023</t>
+          <t>A 11221-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2605,10 +2605,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45089</v>
+        <v>45371</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2664,7 +2664,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 16670-2025</t>
+          <t>A 5869-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2674,14 +2674,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45754</v>
+        <v>44958</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 34466-2023</t>
+          <t>A 32984-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2751,10 +2751,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45139</v>
+        <v>45517</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>4.3</v>
+        <v>2.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2810,7 +2810,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 38173-2023</t>
+          <t>A 47870-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45161</v>
+        <v>45932</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.8</v>
+        <v>6.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2883,7 +2883,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 34170-2023</t>
+          <t>A 9482-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2897,10 +2897,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45138</v>
+        <v>44981</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>5.8</v>
+        <v>3.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2956,7 +2956,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 15357-2023</t>
+          <t>A 25385-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2970,10 +2970,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45019</v>
+        <v>45089</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3029,7 +3029,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 36761-2022</t>
+          <t>A 16792-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3043,10 +3043,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44805</v>
+        <v>45411</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4.8</v>
+        <v>0.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3102,7 +3102,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 15467-2025</t>
+          <t>A 43808-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3112,14 +3112,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45747</v>
+        <v>45571</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3175,7 +3175,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 5869-2023</t>
+          <t>A 9849-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3185,14 +3185,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44958</v>
+        <v>46072</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 7409-2025</t>
+          <t>A 47356-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45705</v>
+        <v>45930</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3321,7 +3321,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 9686-2023</t>
+          <t>A 14386-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3335,10 +3335,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44984</v>
+        <v>46100</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.8</v>
+        <v>12.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3394,7 +3394,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 7016-2025</t>
+          <t>A 35996-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3408,10 +3408,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45701</v>
+        <v>45863</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3423,13 +3423,8 @@
           <t>ESLÖV</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3472,7 +3467,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 34468-2023</t>
+          <t>A 35997-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3486,10 +3481,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45139</v>
+        <v>45863</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3502,7 +3497,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>5.5</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3545,7 +3540,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 25508-2023</t>
+          <t>A 11204-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3559,10 +3554,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45089</v>
+        <v>44992</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3575,7 +3570,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3618,7 +3613,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 24115-2022</t>
+          <t>A 28088-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3632,10 +3627,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44725</v>
+        <v>45817</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3648,7 +3643,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.4</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3691,7 +3686,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 49137-2024</t>
+          <t>A 18281-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3705,10 +3700,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45594</v>
+        <v>46125</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3721,7 +3716,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3764,7 +3759,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 32984-2024</t>
+          <t>A 25508-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3778,10 +3773,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45517</v>
+        <v>45089</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3794,7 +3789,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.9</v>
+        <v>0.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3837,7 +3832,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 25388-2023</t>
+          <t>A 9686-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3851,10 +3846,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45089</v>
+        <v>44984</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3867,7 +3862,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3910,7 +3905,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 16792-2024</t>
+          <t>A 7409-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3924,10 +3919,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45411</v>
+        <v>45705</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3940,7 +3935,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3983,7 +3978,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 12079-2024</t>
+          <t>A 36761-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3997,10 +3992,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45377</v>
+        <v>44805</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4013,7 +4008,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>6.9</v>
+        <v>4.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4056,7 +4051,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 28088-2025</t>
+          <t>A 25388-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4070,10 +4065,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45817</v>
+        <v>45089</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4086,7 +4081,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4129,7 +4124,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 11204-2023</t>
+          <t>A 22134-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4143,10 +4138,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44992</v>
+        <v>46153</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4159,7 +4154,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4219,7 +4214,7 @@
         <v>45370</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4275,7 +4270,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 11221-2024</t>
+          <t>A 18503-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4289,10 +4284,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45371</v>
+        <v>46127</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4305,7 +4300,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.3</v>
+        <v>4.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4348,7 +4343,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 16733-2023</t>
+          <t>A 10819-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4362,10 +4357,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45030</v>
+        <v>46078</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4378,7 +4373,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.6</v>
+        <v>4.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4421,7 +4416,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 43808-2024</t>
+          <t>A 1574-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4431,14 +4426,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45571</v>
+        <v>45306</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4451,7 +4446,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4494,7 +4489,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 9484-2023</t>
+          <t>A 25730-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4508,10 +4503,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44981</v>
+        <v>46178</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4567,7 +4562,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 9482-2023</t>
+          <t>A 7016-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4581,10 +4576,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44981</v>
+        <v>45701</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4596,8 +4591,13 @@
           <t>ESLÖV</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4640,7 +4640,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 15533-2024</t>
+          <t>A 26165-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4654,10 +4654,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45401</v>
+        <v>46181</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>7.5</v>
+        <v>2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4713,7 +4713,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 62496-2023</t>
+          <t>A 26169-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4727,10 +4727,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45268</v>
+        <v>46181</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4786,7 +4786,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 35996-2025</t>
+          <t>A 26497-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45863</v>
+        <v>46183</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4859,7 +4859,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 35997-2025</t>
+          <t>A 27428-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45863</v>
+        <v>46189</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4932,7 +4932,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 47356-2025</t>
+          <t>A 27439-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4946,10 +4946,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45930</v>
+        <v>46189</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5005,7 +5005,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 47870-2025</t>
+          <t>A 27435-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5019,10 +5019,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45932</v>
+        <v>46189</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>6.8</v>
+        <v>0.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5078,7 +5078,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 9849-2026</t>
+          <t>A 16670-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5092,10 +5092,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46072</v>
+        <v>45754</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5151,7 +5151,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 14386-2026</t>
+          <t>A 34468-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46100</v>
+        <v>45139</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>12.4</v>
+        <v>5.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5224,7 +5224,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 18281-2026</t>
+          <t>A 62496-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5238,10 +5238,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46125</v>
+        <v>45268</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5297,7 +5297,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 22134-2026</t>
+          <t>A 34170-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46153</v>
+        <v>45138</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2</v>
+        <v>5.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5370,7 +5370,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 18503-2026</t>
+          <t>A 24115-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5384,10 +5384,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46127</v>
+        <v>44725</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5443,7 +5443,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 10819-2026</t>
+          <t>A 9484-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5457,10 +5457,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46078</v>
+        <v>44981</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4.9</v>
+        <v>1.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5516,7 +5516,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 1574-2024</t>
+          <t>A 16733-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5530,10 +5530,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45306</v>
+        <v>45030</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5589,7 +5589,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 25730-2026</t>
+          <t>A 44496-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5603,10 +5603,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46178</v>
+        <v>45189</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5662,7 +5662,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 26165-2026</t>
+          <t>A 58721-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5676,10 +5676,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46181</v>
+        <v>45986</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5735,7 +5735,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 26169-2026</t>
+          <t>A 34466-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5749,10 +5749,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46181</v>
+        <v>45139</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5808,7 +5808,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 26497-2026</t>
+          <t>A 33865-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5822,10 +5822,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46183</v>
+        <v>45520</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5881,7 +5881,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 27439-2026</t>
+          <t>A 5812-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5895,10 +5895,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46189</v>
+        <v>44596</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5954,7 +5954,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 27428-2026</t>
+          <t>A 38173-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5968,10 +5968,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46189</v>
+        <v>45161</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6027,7 +6027,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 27435-2026</t>
+          <t>A 15357-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6041,10 +6041,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46189</v>
+        <v>45019</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6100,7 +6100,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 58721-2025</t>
+          <t>A 49137-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6114,10 +6114,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45986</v>
+        <v>45594</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>

--- a/Översikt ESLÖV.xlsx
+++ b/Översikt ESLÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45307</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45615</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44960</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>44846</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>45817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>46244</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>45793</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>46100</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>44981</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 18713-2024</t>
+          <t>A 1510-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45426</v>
+        <v>45306</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1621,22 +1621,22 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
         <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1649,42 +1649,46 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Gråtrut</t>
+          <t>Svart stork</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 18713-2024 artfynd.xlsx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 1510-2024 artfynd.xlsx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 18713-2024 karta.png", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 1510-2024 karta.png", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 18713-2024 georefererad karta.tif", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 1510-2024 georefererad karta.tif", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 18713-2024 FSC-klagomål.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 1510-2024 FSC-klagomål.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 18713-2024 FSC-klagomål mail.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 1510-2024 FSC-klagomål mail.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 18713-2024 tillsynsbegäran.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 1510-2024 tillsynsbegäran.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 18713-2024 tillsynsbegäran mail.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 1510-2024 tillsynsbegäran mail.docx", "A 1510-2024")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 1510-2024 prioriterade fågelarter.docx", "A 1510-2024")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 24809-2025</t>
+          <t>A 52652-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1698,10 +1702,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45799</v>
+        <v>45225</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1714,7 +1718,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1726,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1738,10 +1742,10 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1754,46 +1758,42 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönfläckig padda</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 24809-2025 artfynd.xlsx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 52652-2023 artfynd.xlsx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 24809-2025 karta.png", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 52652-2023 karta.png", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 24809-2025 georefererad karta.tif", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 52652-2023 georefererad karta.tif", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 24809-2025 FSC-klagomål.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 52652-2023 FSC-klagomål.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 24809-2025 FSC-klagomål mail.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 52652-2023 FSC-klagomål mail.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 24809-2025 tillsynsbegäran.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 52652-2023 tillsynsbegäran.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 24809-2025 tillsynsbegäran mail.docx", "A 24809-2025")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 24809-2025 prioriterade fågelarter.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 52652-2023 tillsynsbegäran mail.docx", "A 52652-2023")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 14013-2026</t>
+          <t>A 18713-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1807,10 +1807,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46098</v>
+        <v>45426</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1822,13 +1822,8 @@
           <t>ESLÖV</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>8.800000000000001</v>
+        <v>4.1</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1840,7 +1835,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1852,10 +1847,10 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1864,50 +1859,46 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Gråtrut</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14013-2026 artfynd.xlsx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 18713-2024 artfynd.xlsx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14013-2026 karta.png", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 18713-2024 karta.png", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14013-2026 georefererad karta.tif", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 18713-2024 georefererad karta.tif", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14013-2026 FSC-klagomål.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 18713-2024 FSC-klagomål.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14013-2026 FSC-klagomål mail.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 18713-2024 FSC-klagomål mail.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14013-2026 tillsynsbegäran.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 18713-2024 tillsynsbegäran.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14013-2026 tillsynsbegäran mail.docx", "A 14013-2026")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 14013-2026 prioriterade fågelarter.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 18713-2024 tillsynsbegäran mail.docx", "A 18713-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 61035-2024</t>
+          <t>A 24809-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1921,10 +1912,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45645</v>
+        <v>45799</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1937,16 +1928,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>7.6</v>
+        <v>1.4</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1961,7 +1952,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1970,49 +1961,53 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 61035-2024 artfynd.xlsx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 24809-2025 artfynd.xlsx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 61035-2024 karta.png", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 24809-2025 karta.png", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 61035-2024 georefererad karta.tif", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 24809-2025 georefererad karta.tif", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 61035-2024 FSC-klagomål.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 24809-2025 FSC-klagomål.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 61035-2024 FSC-klagomål mail.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 24809-2025 FSC-klagomål mail.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 61035-2024 tillsynsbegäran.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 24809-2025 tillsynsbegäran.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 61035-2024 tillsynsbegäran mail.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 24809-2025 tillsynsbegäran mail.docx", "A 24809-2025")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 24809-2025 prioriterade fågelarter.docx", "A 24809-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 1510-2024</t>
+          <t>A 14013-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2026,10 +2021,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45306</v>
+        <v>46098</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2041,8 +2036,13 @@
           <t>ESLÖV</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>3.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2063,10 +2063,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2078,50 +2078,50 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Svart stork</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 1510-2024 artfynd.xlsx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14013-2026 artfynd.xlsx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 1510-2024 karta.png", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14013-2026 karta.png", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 1510-2024 georefererad karta.tif", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14013-2026 georefererad karta.tif", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 1510-2024 FSC-klagomål.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14013-2026 FSC-klagomål.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 1510-2024 FSC-klagomål mail.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14013-2026 FSC-klagomål mail.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 1510-2024 tillsynsbegäran.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14013-2026 tillsynsbegäran.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 1510-2024 tillsynsbegäran mail.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14013-2026 tillsynsbegäran mail.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 1510-2024 prioriterade fågelarter.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 14013-2026 prioriterade fågelarter.docx", "A 14013-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 52652-2023</t>
+          <t>A 61035-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2135,10 +2135,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45225</v>
+        <v>45645</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2151,19 +2151,19 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.9</v>
+        <v>7.6</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2178,48 +2178,48 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Grönfläckig padda</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 52652-2023 artfynd.xlsx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 61035-2024 artfynd.xlsx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 52652-2023 karta.png", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 61035-2024 karta.png", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 52652-2023 georefererad karta.tif", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 61035-2024 georefererad karta.tif", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 52652-2023 FSC-klagomål.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 61035-2024 FSC-klagomål.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 52652-2023 FSC-klagomål mail.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 61035-2024 FSC-klagomål mail.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 52652-2023 tillsynsbegäran.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 61035-2024 tillsynsbegäran.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 52652-2023 tillsynsbegäran mail.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 61035-2024 tillsynsbegäran mail.docx", "A 61035-2024")</f>
         <v/>
       </c>
     </row>
@@ -2243,7 +2243,7 @@
         <v>44553</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>44690</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 12079-2024</t>
+          <t>A 47870-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2386,10 +2386,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45377</v>
+        <v>45932</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2445,7 +2445,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 15533-2024</t>
+          <t>A 32984-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45401</v>
+        <v>45517</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>7.5</v>
+        <v>2.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2518,7 +2518,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 15467-2025</t>
+          <t>A 16792-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45747</v>
+        <v>45411</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 11221-2024</t>
+          <t>A 16733-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2605,10 +2605,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45371</v>
+        <v>45030</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.3</v>
+        <v>2.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2664,7 +2664,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 5869-2023</t>
+          <t>A 47356-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2674,14 +2674,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44958</v>
+        <v>45930</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 32984-2024</t>
+          <t>A 9849-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2751,10 +2751,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45517</v>
+        <v>46072</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2810,7 +2810,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 47870-2025</t>
+          <t>A 5812-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45932</v>
+        <v>44596</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>6.8</v>
+        <v>0.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2883,7 +2883,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 9482-2023</t>
+          <t>A 35996-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2897,10 +2897,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44981</v>
+        <v>45863</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.7</v>
+        <v>0.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2956,7 +2956,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 25385-2023</t>
+          <t>A 35997-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2970,10 +2970,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45089</v>
+        <v>45863</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3029,7 +3029,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 16792-2024</t>
+          <t>A 14386-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3043,10 +3043,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45411</v>
+        <v>46100</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.9</v>
+        <v>12.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3102,7 +3102,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 43808-2024</t>
+          <t>A 28088-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3112,14 +3112,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45571</v>
+        <v>45817</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3175,7 +3175,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 9849-2026</t>
+          <t>A 15467-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46072</v>
+        <v>45747</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 47356-2025</t>
+          <t>A 5869-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3258,14 +3258,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45930</v>
+        <v>44958</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3321,7 +3321,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 14386-2026</t>
+          <t>A 18281-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3335,10 +3335,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46100</v>
+        <v>46125</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>12.4</v>
+        <v>0.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3394,7 +3394,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 35996-2025</t>
+          <t>A 7409-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3408,10 +3408,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45863</v>
+        <v>45705</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3467,7 +3467,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 35997-2025</t>
+          <t>A 9686-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3481,10 +3481,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45863</v>
+        <v>44984</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3540,7 +3540,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 11204-2023</t>
+          <t>A 7016-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3554,10 +3554,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44992</v>
+        <v>45701</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3569,8 +3569,13 @@
           <t>ESLÖV</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3613,7 +3618,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 28088-2025</t>
+          <t>A 24115-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3627,10 +3632,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45817</v>
+        <v>44725</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3643,7 +3648,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>4.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3686,7 +3691,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 18281-2026</t>
+          <t>A 25388-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3700,10 +3705,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46125</v>
+        <v>45089</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3716,7 +3721,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3759,7 +3764,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 25508-2023</t>
+          <t>A 12079-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3773,10 +3778,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45089</v>
+        <v>45377</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3789,7 +3794,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.4</v>
+        <v>6.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3832,7 +3837,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 9686-2023</t>
+          <t>A 11204-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3846,10 +3851,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44984</v>
+        <v>44992</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3862,7 +3867,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3905,7 +3910,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 7409-2025</t>
+          <t>A 22134-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3919,10 +3924,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45705</v>
+        <v>46153</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3935,7 +3940,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3978,7 +3983,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 36761-2022</t>
+          <t>A 18503-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3992,10 +3997,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44805</v>
+        <v>46127</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4008,7 +4013,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4051,7 +4056,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 25388-2023</t>
+          <t>A 9482-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4065,10 +4070,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45089</v>
+        <v>44981</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4081,7 +4086,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4124,7 +4129,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 22134-2026</t>
+          <t>A 15533-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4138,10 +4143,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46153</v>
+        <v>45401</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4154,7 +4159,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>7.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4197,7 +4202,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 10940-2024</t>
+          <t>A 10819-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4211,10 +4216,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45370</v>
+        <v>46078</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4227,7 +4232,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>4.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4270,7 +4275,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 18503-2026</t>
+          <t>A 1574-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4284,10 +4289,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46127</v>
+        <v>45306</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4300,7 +4305,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4.9</v>
+        <v>3.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4343,7 +4348,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 10819-2026</t>
+          <t>A 62496-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4357,10 +4362,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46078</v>
+        <v>45268</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4373,7 +4378,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>4.9</v>
+        <v>2.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4416,7 +4421,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 1574-2024</t>
+          <t>A 25730-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4430,10 +4435,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45306</v>
+        <v>46178</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4446,7 +4451,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.6</v>
+        <v>1.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4489,7 +4494,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 25730-2026</t>
+          <t>A 26165-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4503,10 +4508,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4519,7 +4524,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4562,7 +4567,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 7016-2025</t>
+          <t>A 26169-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4576,10 +4581,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45701</v>
+        <v>46181</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4591,13 +4596,8 @@
           <t>ESLÖV</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4640,7 +4640,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 26165-2026</t>
+          <t>A 25385-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4654,10 +4654,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46181</v>
+        <v>45089</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4713,7 +4713,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 26169-2026</t>
+          <t>A 26497-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4727,10 +4727,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46181</v>
+        <v>46183</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4786,7 +4786,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 26497-2026</t>
+          <t>A 27439-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46183</v>
+        <v>46189</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>46189</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 27439-2026</t>
+          <t>A 27435-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4949,7 +4949,7 @@
         <v>46189</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5005,7 +5005,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 27435-2026</t>
+          <t>A 34170-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5019,10 +5019,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46189</v>
+        <v>45138</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.9</v>
+        <v>5.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5078,7 +5078,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 16670-2025</t>
+          <t>A 15357-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5092,10 +5092,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45754</v>
+        <v>45019</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5151,7 +5151,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 34468-2023</t>
+          <t>A 36761-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45139</v>
+        <v>44805</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5224,7 +5224,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 62496-2023</t>
+          <t>A 34468-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5238,10 +5238,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45268</v>
+        <v>45139</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.6</v>
+        <v>5.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5297,7 +5297,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 34170-2023</t>
+          <t>A 58721-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45138</v>
+        <v>45986</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>5.8</v>
+        <v>2.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5370,7 +5370,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 24115-2022</t>
+          <t>A 10940-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5384,10 +5384,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44725</v>
+        <v>45370</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4.4</v>
+        <v>0.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5443,7 +5443,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 9484-2023</t>
+          <t>A 11221-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5457,10 +5457,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44981</v>
+        <v>45371</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.4</v>
+        <v>0.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5516,7 +5516,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 16733-2023</t>
+          <t>A 43808-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5526,14 +5526,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45030</v>
+        <v>45571</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5589,7 +5589,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 44496-2023</t>
+          <t>A 9484-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5603,10 +5603,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45189</v>
+        <v>44981</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5662,7 +5662,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 58721-2025</t>
+          <t>A 44496-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5676,10 +5676,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45986</v>
+        <v>45189</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5735,7 +5735,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 34466-2023</t>
+          <t>A 33865-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5749,10 +5749,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45139</v>
+        <v>45520</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4.3</v>
+        <v>1.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5808,7 +5808,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 33865-2024</t>
+          <t>A 16670-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5822,10 +5822,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45520</v>
+        <v>45754</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5881,7 +5881,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 5812-2022</t>
+          <t>A 34466-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5895,10 +5895,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44596</v>
+        <v>45139</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.5</v>
+        <v>4.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5971,7 +5971,7 @@
         <v>45161</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 15357-2023</t>
+          <t>A 25508-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6041,10 +6041,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45019</v>
+        <v>45089</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6117,7 +6117,7 @@
         <v>45594</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>

--- a/Översikt ESLÖV.xlsx
+++ b/Översikt ESLÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45307</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45615</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44960</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>44846</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>45817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>46244</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>45793</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>46100</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>44981</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>45306</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>45225</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>45426</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>45799</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>46098</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>45645</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>44553</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>44690</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>45932</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>45517</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>45411</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>45030</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>45930</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>46072</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>44596</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>45863</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>45863</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>46100</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>45817</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>45747</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>44958</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         <v>46125</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         <v>45705</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>44984</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         <v>45701</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>44725</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>45089</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
         <v>45377</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>44992</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         <v>46153</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         <v>46127</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>44981</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>45401</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         <v>46078</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         <v>45306</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         <v>45268</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>46178</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         <v>46181</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>46181</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>45089</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>46183</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>46189</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         <v>46189</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         <v>46189</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         <v>45138</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>45019</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>44805</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>45139</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>45986</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>45370</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         <v>45371</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>45571</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>44981</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>45189</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>45520</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>45754</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>45139</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>45161</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>45089</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
         <v>45594</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>

--- a/Översikt ESLÖV.xlsx
+++ b/Översikt ESLÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45307</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45615</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44960</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>44846</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>45817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>46244</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>45793</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>46100</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>44981</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>45306</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>45225</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>45426</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>45799</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>46098</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>45645</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>44553</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>44690</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>45932</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>45517</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>45411</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>45030</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>45930</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>46072</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>44596</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>45863</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>45863</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>46100</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>45817</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>45747</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>44958</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         <v>46125</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         <v>45705</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>44984</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         <v>45701</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>44725</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>45089</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
         <v>45377</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>44992</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         <v>46153</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         <v>46127</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>44981</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>45401</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         <v>46078</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         <v>45306</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         <v>45268</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>46178</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         <v>46181</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>46181</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>45089</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>46183</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>46189</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         <v>46189</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         <v>46189</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         <v>45138</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>45019</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>44805</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>45139</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>45986</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>45370</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         <v>45371</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>45571</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>44981</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>45189</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>45520</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>45754</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>45139</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>45161</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>45089</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
         <v>45594</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>

--- a/Översikt ESLÖV.xlsx
+++ b/Översikt ESLÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45307</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45615</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44960</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>44846</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>45817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>46244</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 23773-2025</t>
+          <t>A 14395-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45793</v>
+        <v>46100</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1336,38 +1336,38 @@
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 23773-2025 artfynd.xlsx", "A 23773-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14395-2026 artfynd.xlsx", "A 14395-2026")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 23773-2025 karta.png", "A 23773-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14395-2026 karta.png", "A 14395-2026")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 23773-2025 georefererad karta.tif", "A 23773-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14395-2026 georefererad karta.tif", "A 14395-2026")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 23773-2025 FSC-klagomål.docx", "A 23773-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14395-2026 FSC-klagomål.docx", "A 14395-2026")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 23773-2025 FSC-klagomål mail.docx", "A 23773-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14395-2026 FSC-klagomål mail.docx", "A 14395-2026")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 23773-2025 tillsynsbegäran.docx", "A 23773-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14395-2026 tillsynsbegäran.docx", "A 14395-2026")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 23773-2025 tillsynsbegäran mail.docx", "A 23773-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14395-2026 tillsynsbegäran mail.docx", "A 14395-2026")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 14395-2026</t>
+          <t>A 9487-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46100</v>
+        <v>44981</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.9</v>
+        <v>1.9</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1406,13 +1406,13 @@
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1424,162 +1424,162 @@
         <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>2</v>
       </c>
       <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Älg
+Kambräken</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 9487-2023 artfynd.xlsx", "A 9487-2023")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 9487-2023 karta.png", "A 9487-2023")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 9487-2023 georefererad karta.tif", "A 9487-2023")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 9487-2023 FSC-klagomål.docx", "A 9487-2023")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 9487-2023 FSC-klagomål mail.docx", "A 9487-2023")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 9487-2023 tillsynsbegäran.docx", "A 9487-2023")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 9487-2023 tillsynsbegäran mail.docx", "A 9487-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 23773-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45793</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ESLÖV</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="n">
         <v>4</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Ask
 Kransrams</t>
         </is>
       </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14395-2026 artfynd.xlsx", "A 14395-2026")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14395-2026 karta.png", "A 14395-2026")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14395-2026 georefererad karta.tif", "A 14395-2026")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14395-2026 FSC-klagomål.docx", "A 14395-2026")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14395-2026 FSC-klagomål mail.docx", "A 14395-2026")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14395-2026 tillsynsbegäran.docx", "A 14395-2026")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14395-2026 tillsynsbegäran mail.docx", "A 14395-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 9487-2023</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>44981</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>ESLÖV</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Älg
-Kambräken</t>
-        </is>
-      </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 9487-2023 artfynd.xlsx", "A 9487-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 23773-2025 artfynd.xlsx", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 9487-2023 karta.png", "A 9487-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 23773-2025 karta.png", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 9487-2023 georefererad karta.tif", "A 9487-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 23773-2025 georefererad karta.tif", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 9487-2023 FSC-klagomål.docx", "A 9487-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 23773-2025 FSC-klagomål.docx", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 9487-2023 FSC-klagomål mail.docx", "A 9487-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 23773-2025 FSC-klagomål mail.docx", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 9487-2023 tillsynsbegäran.docx", "A 9487-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 23773-2025 tillsynsbegäran.docx", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 9487-2023 tillsynsbegäran mail.docx", "A 9487-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 23773-2025 tillsynsbegäran mail.docx", "A 23773-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 1510-2024</t>
+          <t>A 14013-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45306</v>
+        <v>46098</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1608,8 +1608,13 @@
           <t>ESLÖV</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>3.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1630,10 +1635,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1645,50 +1650,50 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Svart stork</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 1510-2024 artfynd.xlsx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14013-2026 artfynd.xlsx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 1510-2024 karta.png", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14013-2026 karta.png", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 1510-2024 georefererad karta.tif", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14013-2026 georefererad karta.tif", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 1510-2024 FSC-klagomål.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14013-2026 FSC-klagomål.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 1510-2024 FSC-klagomål mail.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14013-2026 FSC-klagomål mail.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 1510-2024 tillsynsbegäran.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14013-2026 tillsynsbegäran.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 1510-2024 tillsynsbegäran mail.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14013-2026 tillsynsbegäran mail.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 1510-2024 prioriterade fågelarter.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 14013-2026 prioriterade fågelarter.docx", "A 14013-2026")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 52652-2023</t>
+          <t>A 61035-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1702,10 +1707,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45225</v>
+        <v>45645</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1718,19 +1723,19 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.9</v>
+        <v>7.6</v>
       </c>
       <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
         <v>1</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1745,55 +1750,55 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Grönfläckig padda</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 52652-2023 artfynd.xlsx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 61035-2024 artfynd.xlsx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 52652-2023 karta.png", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 61035-2024 karta.png", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 52652-2023 georefererad karta.tif", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 61035-2024 georefererad karta.tif", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 52652-2023 FSC-klagomål.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 61035-2024 FSC-klagomål.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 52652-2023 FSC-klagomål mail.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 61035-2024 FSC-klagomål mail.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 52652-2023 tillsynsbegäran.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 61035-2024 tillsynsbegäran.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 52652-2023 tillsynsbegäran mail.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 61035-2024 tillsynsbegäran mail.docx", "A 61035-2024")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 18713-2024</t>
+          <t>A 1510-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1807,10 +1812,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45426</v>
+        <v>45306</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1823,7 +1828,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1835,22 +1840,22 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
         <v>1</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1863,42 +1868,46 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Gråtrut</t>
+          <t>Svart stork</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 18713-2024 artfynd.xlsx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 1510-2024 artfynd.xlsx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 18713-2024 karta.png", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 1510-2024 karta.png", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 18713-2024 georefererad karta.tif", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 1510-2024 georefererad karta.tif", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 18713-2024 FSC-klagomål.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 1510-2024 FSC-klagomål.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 18713-2024 FSC-klagomål mail.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 1510-2024 FSC-klagomål mail.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 18713-2024 tillsynsbegäran.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 1510-2024 tillsynsbegäran.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 18713-2024 tillsynsbegäran mail.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 1510-2024 tillsynsbegäran mail.docx", "A 1510-2024")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 1510-2024 prioriterade fågelarter.docx", "A 1510-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 24809-2025</t>
+          <t>A 52652-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1912,10 +1921,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45799</v>
+        <v>45225</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1928,7 +1937,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1940,7 +1949,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1952,10 +1961,10 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1968,46 +1977,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönfläckig padda</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 24809-2025 artfynd.xlsx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 52652-2023 artfynd.xlsx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 24809-2025 karta.png", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 52652-2023 karta.png", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 24809-2025 georefererad karta.tif", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 52652-2023 georefererad karta.tif", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 24809-2025 FSC-klagomål.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 52652-2023 FSC-klagomål.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 24809-2025 FSC-klagomål mail.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 52652-2023 FSC-klagomål mail.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 24809-2025 tillsynsbegäran.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 52652-2023 tillsynsbegäran.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 24809-2025 tillsynsbegäran mail.docx", "A 24809-2025")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 24809-2025 prioriterade fågelarter.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 52652-2023 tillsynsbegäran mail.docx", "A 52652-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 14013-2026</t>
+          <t>A 18713-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2021,10 +2026,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46098</v>
+        <v>45426</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2036,13 +2041,8 @@
           <t>ESLÖV</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>8.800000000000001</v>
+        <v>4.1</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2054,7 +2054,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2066,10 +2066,10 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2078,50 +2078,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Gråtrut</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14013-2026 artfynd.xlsx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 18713-2024 artfynd.xlsx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14013-2026 karta.png", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 18713-2024 karta.png", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14013-2026 georefererad karta.tif", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 18713-2024 georefererad karta.tif", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14013-2026 FSC-klagomål.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 18713-2024 FSC-klagomål.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14013-2026 FSC-klagomål mail.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 18713-2024 FSC-klagomål mail.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14013-2026 tillsynsbegäran.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 18713-2024 tillsynsbegäran.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14013-2026 tillsynsbegäran mail.docx", "A 14013-2026")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 14013-2026 prioriterade fågelarter.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 18713-2024 tillsynsbegäran mail.docx", "A 18713-2024")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 61035-2024</t>
+          <t>A 24809-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2135,10 +2131,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45645</v>
+        <v>45799</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2151,16 +2147,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>7.6</v>
+        <v>1.4</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2175,7 +2171,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2184,42 +2180,46 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 61035-2024 artfynd.xlsx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 24809-2025 artfynd.xlsx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 61035-2024 karta.png", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 24809-2025 karta.png", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 61035-2024 georefererad karta.tif", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 24809-2025 georefererad karta.tif", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 61035-2024 FSC-klagomål.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 24809-2025 FSC-klagomål.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 61035-2024 FSC-klagomål mail.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 24809-2025 FSC-klagomål mail.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 61035-2024 tillsynsbegäran.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 24809-2025 tillsynsbegäran.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 61035-2024 tillsynsbegäran mail.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 24809-2025 tillsynsbegäran mail.docx", "A 24809-2025")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 24809-2025 prioriterade fågelarter.docx", "A 24809-2025")</f>
         <v/>
       </c>
     </row>
@@ -2243,7 +2243,7 @@
         <v>44553</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>44690</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 47870-2025</t>
+          <t>A 12079-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2386,10 +2386,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45932</v>
+        <v>45377</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2445,7 +2445,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 32984-2024</t>
+          <t>A 15533-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45517</v>
+        <v>45401</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.9</v>
+        <v>7.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2518,7 +2518,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 16792-2024</t>
+          <t>A 11221-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45411</v>
+        <v>45371</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 16733-2023</t>
+          <t>A 15467-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2605,10 +2605,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45030</v>
+        <v>45747</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2664,7 +2664,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 47356-2025</t>
+          <t>A 5869-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2674,14 +2674,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45930</v>
+        <v>44958</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 9849-2026</t>
+          <t>A 9482-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2751,10 +2751,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46072</v>
+        <v>44981</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2810,7 +2810,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 5812-2022</t>
+          <t>A 25385-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44596</v>
+        <v>45089</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2883,7 +2883,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 35996-2025</t>
+          <t>A 43808-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2893,14 +2893,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45863</v>
+        <v>45571</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2956,7 +2956,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 35997-2025</t>
+          <t>A 28088-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2970,10 +2970,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45863</v>
+        <v>45817</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3029,7 +3029,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 14386-2026</t>
+          <t>A 11204-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3043,10 +3043,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46100</v>
+        <v>44992</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>12.4</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3102,7 +3102,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 28088-2025</t>
+          <t>A 47356-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45817</v>
+        <v>45930</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3175,7 +3175,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 15467-2025</t>
+          <t>A 25508-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45747</v>
+        <v>45089</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 5869-2023</t>
+          <t>A 9686-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3258,14 +3258,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44958</v>
+        <v>44984</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3321,7 +3321,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 18281-2026</t>
+          <t>A 9849-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3335,10 +3335,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46125</v>
+        <v>46072</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3394,7 +3394,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 7409-2025</t>
+          <t>A 35996-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3408,10 +3408,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45705</v>
+        <v>45863</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3467,7 +3467,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 9686-2023</t>
+          <t>A 35997-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3481,10 +3481,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44984</v>
+        <v>45863</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3540,7 +3540,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 7016-2025</t>
+          <t>A 7409-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3554,10 +3554,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45701</v>
+        <v>45705</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3569,13 +3569,8 @@
           <t>ESLÖV</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3618,7 +3613,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 24115-2022</t>
+          <t>A 14386-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3632,10 +3627,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44725</v>
+        <v>46100</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3648,7 +3643,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.4</v>
+        <v>12.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3691,7 +3686,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 25388-2023</t>
+          <t>A 18281-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3705,10 +3700,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45089</v>
+        <v>46125</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3721,7 +3716,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3764,7 +3759,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 12079-2024</t>
+          <t>A 36761-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3778,10 +3773,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45377</v>
+        <v>44805</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3794,7 +3789,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>6.9</v>
+        <v>4.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3837,7 +3832,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 11204-2023</t>
+          <t>A 25388-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3851,10 +3846,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44992</v>
+        <v>45089</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3867,7 +3862,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3910,7 +3905,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 22134-2026</t>
+          <t>A 47870-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3924,10 +3919,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46153</v>
+        <v>45932</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3940,7 +3935,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>6.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3983,7 +3978,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 18503-2026</t>
+          <t>A 10940-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3997,10 +3992,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46127</v>
+        <v>45370</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4013,7 +4008,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>4.9</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4056,7 +4051,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 9482-2023</t>
+          <t>A 22134-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4070,10 +4065,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44981</v>
+        <v>46153</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4086,7 +4081,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4129,7 +4124,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 15533-2024</t>
+          <t>A 18503-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4143,10 +4138,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45401</v>
+        <v>46127</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4159,7 +4154,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>7.5</v>
+        <v>4.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4202,7 +4197,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 10819-2026</t>
+          <t>A 7016-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4216,10 +4211,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46078</v>
+        <v>45701</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4231,8 +4226,13 @@
           <t>ESLÖV</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>4.9</v>
+        <v>2.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4275,7 +4275,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 1574-2024</t>
+          <t>A 10819-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4289,10 +4289,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45306</v>
+        <v>46078</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4348,7 +4348,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 62496-2023</t>
+          <t>A 1574-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4362,10 +4362,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45268</v>
+        <v>45306</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4438,7 +4438,7 @@
         <v>46178</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         <v>46181</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>46181</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 25385-2023</t>
+          <t>A 26497-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4654,10 +4654,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45089</v>
+        <v>46183</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4713,7 +4713,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 26497-2026</t>
+          <t>A 16670-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4727,10 +4727,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46183</v>
+        <v>45754</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4786,7 +4786,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 27439-2026</t>
+          <t>A 27428-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4803,7 +4803,7 @@
         <v>46189</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4859,7 +4859,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 27428-2026</t>
+          <t>A 34468-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46189</v>
+        <v>45139</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4932,7 +4932,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 27435-2026</t>
+          <t>A 27439-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4949,7 +4949,7 @@
         <v>46189</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5005,7 +5005,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 34170-2023</t>
+          <t>A 27435-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5019,10 +5019,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45138</v>
+        <v>46189</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>5.8</v>
+        <v>0.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5078,7 +5078,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 15357-2023</t>
+          <t>A 62496-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5092,10 +5092,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45019</v>
+        <v>45268</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5151,7 +5151,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 36761-2022</t>
+          <t>A 34170-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44805</v>
+        <v>45138</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5224,7 +5224,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 34468-2023</t>
+          <t>A 24115-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5238,10 +5238,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45139</v>
+        <v>44725</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5297,7 +5297,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 58721-2025</t>
+          <t>A 9484-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45986</v>
+        <v>44981</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5370,7 +5370,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 10940-2024</t>
+          <t>A 16733-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5384,10 +5384,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45370</v>
+        <v>45030</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5443,7 +5443,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 11221-2024</t>
+          <t>A 44496-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5457,10 +5457,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45371</v>
+        <v>45189</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5516,7 +5516,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 43808-2024</t>
+          <t>A 34466-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5526,14 +5526,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45571</v>
+        <v>45139</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.5</v>
+        <v>4.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5589,7 +5589,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 9484-2023</t>
+          <t>A 33865-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5603,10 +5603,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44981</v>
+        <v>45520</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5662,7 +5662,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 44496-2023</t>
+          <t>A 5812-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5676,10 +5676,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45189</v>
+        <v>44596</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 33865-2024</t>
+          <t>A 38173-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5749,10 +5749,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45520</v>
+        <v>45161</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5808,7 +5808,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 16670-2025</t>
+          <t>A 15357-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5822,10 +5822,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45754</v>
+        <v>45019</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5881,7 +5881,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 34466-2023</t>
+          <t>A 58721-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5895,10 +5895,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45139</v>
+        <v>45986</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>4.3</v>
+        <v>2.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5954,7 +5954,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 38173-2023</t>
+          <t>A 49137-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5968,10 +5968,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45161</v>
+        <v>45594</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6027,7 +6027,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 25508-2023</t>
+          <t>A 32984-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6041,10 +6041,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45089</v>
+        <v>45517</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6100,7 +6100,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 49137-2024</t>
+          <t>A 16792-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6114,10 +6114,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45594</v>
+        <v>45411</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>

--- a/Översikt ESLÖV.xlsx
+++ b/Översikt ESLÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45307</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45615</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44960</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>44846</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>45817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>46244</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>46100</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>44981</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>45793</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 14013-2026</t>
+          <t>A 24809-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46098</v>
+        <v>45799</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1608,13 +1608,8 @@
           <t>ESLÖV</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>8.800000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1650,50 +1645,50 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14013-2026 artfynd.xlsx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 24809-2025 artfynd.xlsx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14013-2026 karta.png", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 24809-2025 karta.png", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14013-2026 georefererad karta.tif", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 24809-2025 georefererad karta.tif", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14013-2026 FSC-klagomål.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 24809-2025 FSC-klagomål.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14013-2026 FSC-klagomål mail.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 24809-2025 FSC-klagomål mail.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14013-2026 tillsynsbegäran.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 24809-2025 tillsynsbegäran.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14013-2026 tillsynsbegäran mail.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 24809-2025 tillsynsbegäran mail.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 14013-2026 prioriterade fågelarter.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 24809-2025 prioriterade fågelarter.docx", "A 24809-2025")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 61035-2024</t>
+          <t>A 14013-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1707,10 +1702,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45645</v>
+        <v>46098</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1722,17 +1717,22 @@
           <t>ESLÖV</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1747,7 +1747,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1756,49 +1756,53 @@
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 61035-2024 artfynd.xlsx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14013-2026 artfynd.xlsx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 61035-2024 karta.png", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14013-2026 karta.png", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 61035-2024 georefererad karta.tif", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14013-2026 georefererad karta.tif", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 61035-2024 FSC-klagomål.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14013-2026 FSC-klagomål.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 61035-2024 FSC-klagomål mail.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14013-2026 FSC-klagomål mail.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 61035-2024 tillsynsbegäran.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14013-2026 tillsynsbegäran.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 61035-2024 tillsynsbegäran mail.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14013-2026 tillsynsbegäran mail.docx", "A 14013-2026")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 14013-2026 prioriterade fågelarter.docx", "A 14013-2026")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 1510-2024</t>
+          <t>A 61035-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1812,10 +1816,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45306</v>
+        <v>45645</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1828,17 +1832,17 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.7</v>
+        <v>7.6</v>
       </c>
       <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
@@ -1849,7 +1853,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
@@ -1861,53 +1865,49 @@
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Svart stork</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 1510-2024 artfynd.xlsx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 61035-2024 artfynd.xlsx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 1510-2024 karta.png", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 61035-2024 karta.png", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 1510-2024 georefererad karta.tif", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 61035-2024 georefererad karta.tif", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 1510-2024 FSC-klagomål.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 61035-2024 FSC-klagomål.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 1510-2024 FSC-klagomål mail.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 61035-2024 FSC-klagomål mail.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 1510-2024 tillsynsbegäran.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 61035-2024 tillsynsbegäran.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 1510-2024 tillsynsbegäran mail.docx", "A 1510-2024")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 1510-2024 prioriterade fågelarter.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 61035-2024 tillsynsbegäran mail.docx", "A 61035-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 52652-2023</t>
+          <t>A 1510-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45225</v>
+        <v>45306</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1949,22 +1949,22 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
         <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1977,42 +1977,46 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Grönfläckig padda</t>
+          <t>Svart stork</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 52652-2023 artfynd.xlsx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 1510-2024 artfynd.xlsx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 52652-2023 karta.png", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 1510-2024 karta.png", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 52652-2023 georefererad karta.tif", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 1510-2024 georefererad karta.tif", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 52652-2023 FSC-klagomål.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 1510-2024 FSC-klagomål.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 52652-2023 FSC-klagomål mail.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 1510-2024 FSC-klagomål mail.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 52652-2023 tillsynsbegäran.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 1510-2024 tillsynsbegäran.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 52652-2023 tillsynsbegäran mail.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 1510-2024 tillsynsbegäran mail.docx", "A 1510-2024")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 1510-2024 prioriterade fågelarter.docx", "A 1510-2024")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 18713-2024</t>
+          <t>A 52652-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2026,10 +2030,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45426</v>
+        <v>45225</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2042,7 +2046,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2082,42 +2086,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Gråtrut</t>
+          <t>Grönfläckig padda</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 18713-2024 artfynd.xlsx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 52652-2023 artfynd.xlsx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 18713-2024 karta.png", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 52652-2023 karta.png", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 18713-2024 georefererad karta.tif", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 52652-2023 georefererad karta.tif", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 18713-2024 FSC-klagomål.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 52652-2023 FSC-klagomål.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 18713-2024 FSC-klagomål mail.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 52652-2023 FSC-klagomål mail.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 18713-2024 tillsynsbegäran.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 52652-2023 tillsynsbegäran.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 18713-2024 tillsynsbegäran mail.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 52652-2023 tillsynsbegäran mail.docx", "A 52652-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 24809-2025</t>
+          <t>A 18713-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2131,10 +2135,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45799</v>
+        <v>45426</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2147,7 +2151,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.4</v>
+        <v>4.1</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2159,7 +2163,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2171,10 +2175,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2187,39 +2191,35 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gråtrut</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 24809-2025 artfynd.xlsx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 18713-2024 artfynd.xlsx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 24809-2025 karta.png", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 18713-2024 karta.png", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 24809-2025 georefererad karta.tif", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 18713-2024 georefererad karta.tif", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 24809-2025 FSC-klagomål.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 18713-2024 FSC-klagomål.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 24809-2025 FSC-klagomål mail.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 18713-2024 FSC-klagomål mail.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 24809-2025 tillsynsbegäran.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 18713-2024 tillsynsbegäran.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 24809-2025 tillsynsbegäran mail.docx", "A 24809-2025")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 24809-2025 prioriterade fågelarter.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 18713-2024 tillsynsbegäran mail.docx", "A 18713-2024")</f>
         <v/>
       </c>
     </row>
@@ -2243,7 +2243,7 @@
         <v>44553</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>44690</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 12079-2024</t>
+          <t>A 47870-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2386,10 +2386,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45377</v>
+        <v>45932</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2445,7 +2445,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 15533-2024</t>
+          <t>A 16792-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45401</v>
+        <v>45411</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>7.5</v>
+        <v>0.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2518,7 +2518,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 11221-2024</t>
+          <t>A 16733-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45371</v>
+        <v>45030</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.3</v>
+        <v>2.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 15467-2025</t>
+          <t>A 28088-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2605,10 +2605,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45747</v>
+        <v>45817</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2664,7 +2664,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 5869-2023</t>
+          <t>A 5812-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2674,14 +2674,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44958</v>
+        <v>44596</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 9482-2023</t>
+          <t>A 9849-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2751,10 +2751,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44981</v>
+        <v>46072</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2810,7 +2810,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 25385-2023</t>
+          <t>A 47356-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45089</v>
+        <v>45930</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2883,7 +2883,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 43808-2024</t>
+          <t>A 14386-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2893,14 +2893,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45571</v>
+        <v>46100</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.5</v>
+        <v>12.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2956,7 +2956,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 28088-2025</t>
+          <t>A 15467-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2970,10 +2970,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45817</v>
+        <v>45747</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3029,7 +3029,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 11204-2023</t>
+          <t>A 5869-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3039,14 +3039,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44992</v>
+        <v>44958</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3102,7 +3102,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 47356-2025</t>
+          <t>A 35996-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45930</v>
+        <v>45863</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3175,7 +3175,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 25508-2023</t>
+          <t>A 35997-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45089</v>
+        <v>45863</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 9686-2023</t>
+          <t>A 18281-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44984</v>
+        <v>46125</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 9849-2026</t>
+          <t>A 7409-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3335,10 +3335,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46072</v>
+        <v>45705</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3394,7 +3394,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 35996-2025</t>
+          <t>A 9686-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3408,10 +3408,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45863</v>
+        <v>44984</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 35997-2025</t>
+          <t>A 7016-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3481,10 +3481,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45863</v>
+        <v>45701</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3496,8 +3496,13 @@
           <t>ESLÖV</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3540,7 +3545,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 7409-2025</t>
+          <t>A 22134-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3554,10 +3559,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45705</v>
+        <v>46153</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3570,7 +3575,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3613,7 +3618,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 14386-2026</t>
+          <t>A 24115-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3627,10 +3632,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46100</v>
+        <v>44725</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3643,7 +3648,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>12.4</v>
+        <v>4.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3686,7 +3691,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 18281-2026</t>
+          <t>A 18503-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3700,10 +3705,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3716,7 +3721,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.8</v>
+        <v>4.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3759,7 +3764,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 36761-2022</t>
+          <t>A 10819-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3773,10 +3778,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44805</v>
+        <v>46078</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3789,7 +3794,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3832,7 +3837,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 25388-2023</t>
+          <t>A 1574-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3846,10 +3851,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45089</v>
+        <v>45306</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3862,7 +3867,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.5</v>
+        <v>3.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3905,7 +3910,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 47870-2025</t>
+          <t>A 25730-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3919,10 +3924,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45932</v>
+        <v>46178</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3935,7 +3940,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>6.8</v>
+        <v>1.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3978,7 +3983,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 10940-2024</t>
+          <t>A 26165-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3992,10 +3997,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45370</v>
+        <v>46181</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4008,7 +4013,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4051,7 +4056,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 22134-2026</t>
+          <t>A 26169-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4065,10 +4070,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46153</v>
+        <v>46181</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4081,7 +4086,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4124,7 +4129,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 18503-2026</t>
+          <t>A 26497-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4138,10 +4143,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46127</v>
+        <v>46183</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4154,7 +4159,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>4.9</v>
+        <v>1.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4197,7 +4202,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 7016-2025</t>
+          <t>A 27439-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4211,10 +4216,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45701</v>
+        <v>46189</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4226,13 +4231,8 @@
           <t>ESLÖV</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4275,7 +4275,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 10819-2026</t>
+          <t>A 27428-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4289,10 +4289,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46078</v>
+        <v>46189</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4.9</v>
+        <v>3.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4348,7 +4348,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 1574-2024</t>
+          <t>A 27435-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4362,10 +4362,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45306</v>
+        <v>46189</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.6</v>
+        <v>0.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4421,7 +4421,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 25730-2026</t>
+          <t>A 25388-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4435,10 +4435,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46178</v>
+        <v>45089</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4494,7 +4494,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 26165-2026</t>
+          <t>A 12079-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46181</v>
+        <v>45377</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2</v>
+        <v>6.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4567,7 +4567,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 26169-2026</t>
+          <t>A 11204-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46181</v>
+        <v>44992</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4640,7 +4640,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 26497-2026</t>
+          <t>A 9482-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4654,10 +4654,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46183</v>
+        <v>44981</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4713,7 +4713,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 16670-2025</t>
+          <t>A 15533-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4727,10 +4727,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45754</v>
+        <v>45401</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4786,7 +4786,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 27428-2026</t>
+          <t>A 62496-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46189</v>
+        <v>45268</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4859,7 +4859,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 34468-2023</t>
+          <t>A 25385-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45139</v>
+        <v>45089</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>5.5</v>
+        <v>0.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4932,7 +4932,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 27439-2026</t>
+          <t>A 34170-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4946,10 +4946,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46189</v>
+        <v>45138</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.6</v>
+        <v>5.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5005,7 +5005,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 27435-2026</t>
+          <t>A 15357-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5019,10 +5019,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46189</v>
+        <v>45019</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5078,7 +5078,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 62496-2023</t>
+          <t>A 36761-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5092,10 +5092,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45268</v>
+        <v>44805</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.6</v>
+        <v>4.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5151,7 +5151,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 34170-2023</t>
+          <t>A 34468-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45138</v>
+        <v>45139</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5224,7 +5224,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 24115-2022</t>
+          <t>A 58721-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5238,10 +5238,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44725</v>
+        <v>45986</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5297,7 +5297,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 9484-2023</t>
+          <t>A 10940-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44981</v>
+        <v>45370</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5370,7 +5370,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 16733-2023</t>
+          <t>A 11221-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5384,10 +5384,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45030</v>
+        <v>45371</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.6</v>
+        <v>0.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5443,7 +5443,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 44496-2023</t>
+          <t>A 43808-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5453,14 +5453,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45189</v>
+        <v>45571</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5516,7 +5516,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 34466-2023</t>
+          <t>A 9484-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5530,10 +5530,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45139</v>
+        <v>44981</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4.3</v>
+        <v>1.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5589,7 +5589,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 33865-2024</t>
+          <t>A 44496-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5603,10 +5603,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45520</v>
+        <v>45189</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5662,7 +5662,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 5812-2022</t>
+          <t>A 33865-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5676,10 +5676,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44596</v>
+        <v>45520</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5735,7 +5735,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 38173-2023</t>
+          <t>A 16670-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5749,10 +5749,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45161</v>
+        <v>45754</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5808,7 +5808,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 15357-2023</t>
+          <t>A 34466-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5822,10 +5822,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45019</v>
+        <v>45139</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>4.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5881,7 +5881,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 58721-2025</t>
+          <t>A 38173-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5895,10 +5895,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45986</v>
+        <v>45161</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5954,7 +5954,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 49137-2024</t>
+          <t>A 25508-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5968,10 +5968,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45594</v>
+        <v>45089</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6027,7 +6027,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 32984-2024</t>
+          <t>A 49137-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6041,10 +6041,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45517</v>
+        <v>45594</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6100,7 +6100,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 16792-2024</t>
+          <t>A 32984-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6114,10 +6114,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45411</v>
+        <v>45517</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>

--- a/Översikt ESLÖV.xlsx
+++ b/Översikt ESLÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45307</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45615</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44960</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>44846</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>45817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>46244</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 14395-2026</t>
+          <t>A 23773-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46100</v>
+        <v>45793</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1336,38 +1336,38 @@
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14395-2026 artfynd.xlsx", "A 14395-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 23773-2025 artfynd.xlsx", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14395-2026 karta.png", "A 14395-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 23773-2025 karta.png", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14395-2026 georefererad karta.tif", "A 14395-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 23773-2025 georefererad karta.tif", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14395-2026 FSC-klagomål.docx", "A 14395-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 23773-2025 FSC-klagomål.docx", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14395-2026 FSC-klagomål mail.docx", "A 14395-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 23773-2025 FSC-klagomål mail.docx", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14395-2026 tillsynsbegäran.docx", "A 14395-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 23773-2025 tillsynsbegäran.docx", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14395-2026 tillsynsbegäran mail.docx", "A 14395-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 23773-2025 tillsynsbegäran mail.docx", "A 23773-2025")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 9487-2023</t>
+          <t>A 14395-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44981</v>
+        <v>46100</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.9</v>
+        <v>4.9</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1406,13 +1406,13 @@
         <v>1</v>
       </c>
       <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
         <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1424,162 +1424,162 @@
         <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>2</v>
       </c>
       <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Kransrams</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14395-2026 artfynd.xlsx", "A 14395-2026")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14395-2026 karta.png", "A 14395-2026")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14395-2026 georefererad karta.tif", "A 14395-2026")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14395-2026 FSC-klagomål.docx", "A 14395-2026")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14395-2026 FSC-klagomål mail.docx", "A 14395-2026")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14395-2026 tillsynsbegäran.docx", "A 14395-2026")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14395-2026 tillsynsbegäran mail.docx", "A 14395-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 9487-2023</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>44981</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ESLÖV</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>2</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Älg
 Kambräken</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 9487-2023 artfynd.xlsx", "A 9487-2023")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 9487-2023 karta.png", "A 9487-2023")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 9487-2023 georefererad karta.tif", "A 9487-2023")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 9487-2023 FSC-klagomål.docx", "A 9487-2023")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 9487-2023 FSC-klagomål mail.docx", "A 9487-2023")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 9487-2023 tillsynsbegäran.docx", "A 9487-2023")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 9487-2023 tillsynsbegäran mail.docx", "A 9487-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 23773-2025</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45793</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>ESLÖV</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>4</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Kransrams</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 23773-2025 artfynd.xlsx", "A 23773-2025")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 23773-2025 karta.png", "A 23773-2025")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 23773-2025 georefererad karta.tif", "A 23773-2025")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 23773-2025 FSC-klagomål.docx", "A 23773-2025")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 23773-2025 FSC-klagomål mail.docx", "A 23773-2025")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 23773-2025 tillsynsbegäran.docx", "A 23773-2025")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 23773-2025 tillsynsbegäran mail.docx", "A 23773-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 24809-2025</t>
+          <t>A 1510-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45799</v>
+        <v>45306</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1630,10 +1630,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1649,46 +1649,46 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svart stork</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 24809-2025 artfynd.xlsx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 1510-2024 artfynd.xlsx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 24809-2025 karta.png", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 1510-2024 karta.png", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 24809-2025 georefererad karta.tif", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 1510-2024 georefererad karta.tif", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 24809-2025 FSC-klagomål.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 1510-2024 FSC-klagomål.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 24809-2025 FSC-klagomål mail.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 1510-2024 FSC-klagomål mail.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 24809-2025 tillsynsbegäran.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 1510-2024 tillsynsbegäran.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 24809-2025 tillsynsbegäran mail.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 1510-2024 tillsynsbegäran mail.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 24809-2025 prioriterade fågelarter.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 1510-2024 prioriterade fågelarter.docx", "A 1510-2024")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 14013-2026</t>
+          <t>A 52652-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1702,10 +1702,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46098</v>
+        <v>45225</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1717,13 +1717,8 @@
           <t>ESLÖV</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>8.800000000000001</v>
+        <v>2.9</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1735,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1747,10 +1742,10 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1759,50 +1754,46 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Grönfläckig padda</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14013-2026 artfynd.xlsx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 52652-2023 artfynd.xlsx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14013-2026 karta.png", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 52652-2023 karta.png", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14013-2026 georefererad karta.tif", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 52652-2023 georefererad karta.tif", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14013-2026 FSC-klagomål.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 52652-2023 FSC-klagomål.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14013-2026 FSC-klagomål mail.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 52652-2023 FSC-klagomål mail.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14013-2026 tillsynsbegäran.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 52652-2023 tillsynsbegäran.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14013-2026 tillsynsbegäran mail.docx", "A 14013-2026")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 14013-2026 prioriterade fågelarter.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 52652-2023 tillsynsbegäran mail.docx", "A 52652-2023")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 61035-2024</t>
+          <t>A 18713-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1816,10 +1807,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45645</v>
+        <v>45426</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1832,19 +1823,19 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>7.6</v>
+        <v>4.1</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
         <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1859,55 +1850,55 @@
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Gråtrut</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 61035-2024 artfynd.xlsx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 18713-2024 artfynd.xlsx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 61035-2024 karta.png", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 18713-2024 karta.png", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 61035-2024 georefererad karta.tif", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 18713-2024 georefererad karta.tif", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 61035-2024 FSC-klagomål.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 18713-2024 FSC-klagomål.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 61035-2024 FSC-klagomål mail.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 18713-2024 FSC-klagomål mail.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 61035-2024 tillsynsbegäran.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 18713-2024 tillsynsbegäran.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 61035-2024 tillsynsbegäran mail.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 18713-2024 tillsynsbegäran mail.docx", "A 18713-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 1510-2024</t>
+          <t>A 24809-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1921,10 +1912,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45306</v>
+        <v>45799</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1937,7 +1928,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1958,10 +1949,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1977,46 +1968,46 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Svart stork</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 1510-2024 artfynd.xlsx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 24809-2025 artfynd.xlsx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 1510-2024 karta.png", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 24809-2025 karta.png", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 1510-2024 georefererad karta.tif", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 24809-2025 georefererad karta.tif", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 1510-2024 FSC-klagomål.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 24809-2025 FSC-klagomål.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 1510-2024 FSC-klagomål mail.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 24809-2025 FSC-klagomål mail.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 1510-2024 tillsynsbegäran.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 24809-2025 tillsynsbegäran.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 1510-2024 tillsynsbegäran mail.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 24809-2025 tillsynsbegäran mail.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 1510-2024 prioriterade fågelarter.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 24809-2025 prioriterade fågelarter.docx", "A 24809-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 52652-2023</t>
+          <t>A 61035-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2030,10 +2021,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45225</v>
+        <v>45645</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2046,19 +2037,19 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.9</v>
+        <v>7.6</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2073,55 +2064,55 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Grönfläckig padda</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 52652-2023 artfynd.xlsx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 61035-2024 artfynd.xlsx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 52652-2023 karta.png", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 61035-2024 karta.png", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 52652-2023 georefererad karta.tif", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 61035-2024 georefererad karta.tif", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 52652-2023 FSC-klagomål.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 61035-2024 FSC-klagomål.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 52652-2023 FSC-klagomål mail.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 61035-2024 FSC-klagomål mail.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 52652-2023 tillsynsbegäran.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 61035-2024 tillsynsbegäran.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 52652-2023 tillsynsbegäran mail.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 61035-2024 tillsynsbegäran mail.docx", "A 61035-2024")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 18713-2024</t>
+          <t>A 14013-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2135,10 +2126,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45426</v>
+        <v>46098</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2150,8 +2141,13 @@
           <t>ESLÖV</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>4.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2163,7 +2159,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2175,10 +2171,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2187,39 +2183,43 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Gråtrut</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 18713-2024 artfynd.xlsx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14013-2026 artfynd.xlsx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 18713-2024 karta.png", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14013-2026 karta.png", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 18713-2024 georefererad karta.tif", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14013-2026 georefererad karta.tif", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 18713-2024 FSC-klagomål.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14013-2026 FSC-klagomål.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 18713-2024 FSC-klagomål mail.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14013-2026 FSC-klagomål mail.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 18713-2024 tillsynsbegäran.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14013-2026 tillsynsbegäran.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 18713-2024 tillsynsbegäran mail.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14013-2026 tillsynsbegäran mail.docx", "A 14013-2026")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 14013-2026 prioriterade fågelarter.docx", "A 14013-2026")</f>
         <v/>
       </c>
     </row>
@@ -2243,7 +2243,7 @@
         <v>44553</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>44690</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 47870-2025</t>
+          <t>A 7409-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2386,10 +2386,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45932</v>
+        <v>45705</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>6.8</v>
+        <v>1.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2445,7 +2445,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 16792-2024</t>
+          <t>A 12079-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45411</v>
+        <v>45377</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.9</v>
+        <v>6.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2518,7 +2518,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 16733-2023</t>
+          <t>A 15533-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45030</v>
+        <v>45401</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.6</v>
+        <v>7.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 28088-2025</t>
+          <t>A 36761-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2605,10 +2605,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45817</v>
+        <v>44805</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>4.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2664,7 +2664,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 5812-2022</t>
+          <t>A 11221-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2678,10 +2678,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44596</v>
+        <v>45371</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 9849-2026</t>
+          <t>A 15467-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2751,10 +2751,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46072</v>
+        <v>45747</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2810,7 +2810,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 47356-2025</t>
+          <t>A 49137-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45930</v>
+        <v>45594</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2883,7 +2883,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 14386-2026</t>
+          <t>A 25388-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2897,10 +2897,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46100</v>
+        <v>45089</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>12.4</v>
+        <v>0.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2956,7 +2956,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 15467-2025</t>
+          <t>A 32984-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2970,10 +2970,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45747</v>
+        <v>45517</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3046,7 +3046,7 @@
         <v>44958</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 35996-2025</t>
+          <t>A 16792-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45863</v>
+        <v>45411</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3175,7 +3175,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 35997-2025</t>
+          <t>A 10940-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45863</v>
+        <v>45370</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 18281-2026</t>
+          <t>A 28088-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46125</v>
+        <v>45817</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3321,7 +3321,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 7409-2025</t>
+          <t>A 9482-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3335,10 +3335,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45705</v>
+        <v>44981</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3394,7 +3394,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 9686-2023</t>
+          <t>A 47356-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3408,10 +3408,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44984</v>
+        <v>45930</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3467,7 +3467,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 7016-2025</t>
+          <t>A 25385-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3481,10 +3481,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45701</v>
+        <v>45089</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3496,13 +3496,8 @@
           <t>ESLÖV</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3545,7 +3540,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 22134-2026</t>
+          <t>A 43808-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3555,14 +3550,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46153</v>
+        <v>45571</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3575,7 +3570,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3618,7 +3613,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 24115-2022</t>
+          <t>A 35996-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3632,10 +3627,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44725</v>
+        <v>45863</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3648,7 +3643,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.4</v>
+        <v>0.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3691,7 +3686,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 18503-2026</t>
+          <t>A 35997-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3705,10 +3700,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46127</v>
+        <v>45863</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3721,7 +3716,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.9</v>
+        <v>0.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3764,7 +3759,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 10819-2026</t>
+          <t>A 7016-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3778,10 +3773,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46078</v>
+        <v>45701</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3793,8 +3788,13 @@
           <t>ESLÖV</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>4.9</v>
+        <v>2.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3837,7 +3837,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 1574-2024</t>
+          <t>A 11204-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3851,10 +3851,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45306</v>
+        <v>44992</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.6</v>
+        <v>0.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3910,7 +3910,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 25730-2026</t>
+          <t>A 22134-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3924,10 +3924,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46178</v>
+        <v>46153</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3983,7 +3983,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 26165-2026</t>
+          <t>A 25508-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46181</v>
+        <v>45089</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4056,7 +4056,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 26169-2026</t>
+          <t>A 9686-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4070,10 +4070,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46181</v>
+        <v>44984</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.5</v>
+        <v>0.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4129,7 +4129,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 26497-2026</t>
+          <t>A 18503-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4143,10 +4143,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46183</v>
+        <v>46127</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.4</v>
+        <v>4.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4202,7 +4202,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 27439-2026</t>
+          <t>A 16670-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4216,10 +4216,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46189</v>
+        <v>45754</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4275,7 +4275,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 27428-2026</t>
+          <t>A 34468-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4289,10 +4289,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46189</v>
+        <v>45139</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4348,7 +4348,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 27435-2026</t>
+          <t>A 10819-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4362,10 +4362,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46189</v>
+        <v>46078</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.9</v>
+        <v>4.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4421,7 +4421,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 25388-2023</t>
+          <t>A 1574-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4435,10 +4435,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45089</v>
+        <v>45306</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>3.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4494,7 +4494,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 12079-2024</t>
+          <t>A 47870-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45377</v>
+        <v>45932</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4567,7 +4567,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 11204-2023</t>
+          <t>A 62496-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44992</v>
+        <v>45268</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4640,7 +4640,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 9482-2023</t>
+          <t>A 25730-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4654,10 +4654,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44981</v>
+        <v>46178</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4713,7 +4713,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 15533-2024</t>
+          <t>A 26165-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4727,10 +4727,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45401</v>
+        <v>46181</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>7.5</v>
+        <v>2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4786,7 +4786,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 62496-2023</t>
+          <t>A 26169-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45268</v>
+        <v>46181</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4859,7 +4859,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 25385-2023</t>
+          <t>A 26497-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45089</v>
+        <v>46183</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4949,7 +4949,7 @@
         <v>45138</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 15357-2023</t>
+          <t>A 27428-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5019,10 +5019,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45019</v>
+        <v>46189</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5078,7 +5078,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 36761-2022</t>
+          <t>A 27439-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5092,10 +5092,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44805</v>
+        <v>46189</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>4.8</v>
+        <v>1.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5151,7 +5151,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 34468-2023</t>
+          <t>A 27435-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45139</v>
+        <v>46189</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>5.5</v>
+        <v>0.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5224,7 +5224,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 58721-2025</t>
+          <t>A 9849-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5238,10 +5238,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45986</v>
+        <v>46072</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5297,7 +5297,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 10940-2024</t>
+          <t>A 24115-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45370</v>
+        <v>44725</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>4.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5370,7 +5370,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 11221-2024</t>
+          <t>A 14386-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5384,10 +5384,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45371</v>
+        <v>46100</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.3</v>
+        <v>12.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5443,7 +5443,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 43808-2024</t>
+          <t>A 9484-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5453,14 +5453,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45571</v>
+        <v>44981</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5516,7 +5516,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 9484-2023</t>
+          <t>A 16733-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5530,10 +5530,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44981</v>
+        <v>45030</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5606,7 +5606,7 @@
         <v>45189</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 33865-2024</t>
+          <t>A 18281-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5676,10 +5676,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45520</v>
+        <v>46125</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5735,7 +5735,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 16670-2025</t>
+          <t>A 34466-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5749,10 +5749,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45754</v>
+        <v>45139</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.5</v>
+        <v>4.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5808,7 +5808,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 34466-2023</t>
+          <t>A 33865-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5822,10 +5822,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45139</v>
+        <v>45520</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>4.3</v>
+        <v>1.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5881,7 +5881,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 38173-2023</t>
+          <t>A 5812-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5895,10 +5895,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45161</v>
+        <v>44596</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5954,7 +5954,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 25508-2023</t>
+          <t>A 38173-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5968,10 +5968,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45089</v>
+        <v>45161</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6027,7 +6027,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 49137-2024</t>
+          <t>A 15357-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6041,10 +6041,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45594</v>
+        <v>45019</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6100,7 +6100,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 32984-2024</t>
+          <t>A 58721-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6114,10 +6114,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45517</v>
+        <v>45986</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>

--- a/Översikt ESLÖV.xlsx
+++ b/Översikt ESLÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45307</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45615</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44960</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>44846</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>45817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>46244</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 23773-2025</t>
+          <t>A 14395-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45793</v>
+        <v>46100</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1336,38 +1336,38 @@
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 23773-2025 artfynd.xlsx", "A 23773-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14395-2026 artfynd.xlsx", "A 14395-2026")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 23773-2025 karta.png", "A 23773-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14395-2026 karta.png", "A 14395-2026")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 23773-2025 georefererad karta.tif", "A 23773-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14395-2026 georefererad karta.tif", "A 14395-2026")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 23773-2025 FSC-klagomål.docx", "A 23773-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14395-2026 FSC-klagomål.docx", "A 14395-2026")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 23773-2025 FSC-klagomål mail.docx", "A 23773-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14395-2026 FSC-klagomål mail.docx", "A 14395-2026")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 23773-2025 tillsynsbegäran.docx", "A 23773-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14395-2026 tillsynsbegäran.docx", "A 14395-2026")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 23773-2025 tillsynsbegäran mail.docx", "A 23773-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14395-2026 tillsynsbegäran mail.docx", "A 14395-2026")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 14395-2026</t>
+          <t>A 9487-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46100</v>
+        <v>44981</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.9</v>
+        <v>1.9</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1406,13 +1406,13 @@
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1424,162 +1424,162 @@
         <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>2</v>
       </c>
       <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Älg
+Kambräken</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 9487-2023 artfynd.xlsx", "A 9487-2023")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 9487-2023 karta.png", "A 9487-2023")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 9487-2023 georefererad karta.tif", "A 9487-2023")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 9487-2023 FSC-klagomål.docx", "A 9487-2023")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 9487-2023 FSC-klagomål mail.docx", "A 9487-2023")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 9487-2023 tillsynsbegäran.docx", "A 9487-2023")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 9487-2023 tillsynsbegäran mail.docx", "A 9487-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 23773-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45793</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ESLÖV</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="n">
         <v>4</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Ask
 Kransrams</t>
         </is>
       </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14395-2026 artfynd.xlsx", "A 14395-2026")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14395-2026 karta.png", "A 14395-2026")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14395-2026 georefererad karta.tif", "A 14395-2026")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14395-2026 FSC-klagomål.docx", "A 14395-2026")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14395-2026 FSC-klagomål mail.docx", "A 14395-2026")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14395-2026 tillsynsbegäran.docx", "A 14395-2026")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14395-2026 tillsynsbegäran mail.docx", "A 14395-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 9487-2023</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>44981</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>ESLÖV</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Älg
-Kambräken</t>
-        </is>
-      </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 9487-2023 artfynd.xlsx", "A 9487-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 23773-2025 artfynd.xlsx", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 9487-2023 karta.png", "A 9487-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 23773-2025 karta.png", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 9487-2023 georefererad karta.tif", "A 9487-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 23773-2025 georefererad karta.tif", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 9487-2023 FSC-klagomål.docx", "A 9487-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 23773-2025 FSC-klagomål.docx", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 9487-2023 FSC-klagomål mail.docx", "A 9487-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 23773-2025 FSC-klagomål mail.docx", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 9487-2023 tillsynsbegäran.docx", "A 9487-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 23773-2025 tillsynsbegäran.docx", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 9487-2023 tillsynsbegäran mail.docx", "A 9487-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 23773-2025 tillsynsbegäran mail.docx", "A 23773-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 1510-2024</t>
+          <t>A 14013-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45306</v>
+        <v>46098</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1608,8 +1608,13 @@
           <t>ESLÖV</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>3.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1630,10 +1635,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1645,50 +1650,50 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Svart stork</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 1510-2024 artfynd.xlsx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14013-2026 artfynd.xlsx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 1510-2024 karta.png", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14013-2026 karta.png", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 1510-2024 georefererad karta.tif", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14013-2026 georefererad karta.tif", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 1510-2024 FSC-klagomål.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14013-2026 FSC-klagomål.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 1510-2024 FSC-klagomål mail.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14013-2026 FSC-klagomål mail.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 1510-2024 tillsynsbegäran.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14013-2026 tillsynsbegäran.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 1510-2024 tillsynsbegäran mail.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14013-2026 tillsynsbegäran mail.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 1510-2024 prioriterade fågelarter.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 14013-2026 prioriterade fågelarter.docx", "A 14013-2026")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 52652-2023</t>
+          <t>A 61035-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1702,10 +1707,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45225</v>
+        <v>45645</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1718,19 +1723,19 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.9</v>
+        <v>7.6</v>
       </c>
       <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
         <v>1</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1745,55 +1750,55 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Grönfläckig padda</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 52652-2023 artfynd.xlsx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 61035-2024 artfynd.xlsx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 52652-2023 karta.png", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 61035-2024 karta.png", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 52652-2023 georefererad karta.tif", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 61035-2024 georefererad karta.tif", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 52652-2023 FSC-klagomål.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 61035-2024 FSC-klagomål.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 52652-2023 FSC-klagomål mail.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 61035-2024 FSC-klagomål mail.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 52652-2023 tillsynsbegäran.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 61035-2024 tillsynsbegäran.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 52652-2023 tillsynsbegäran mail.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 61035-2024 tillsynsbegäran mail.docx", "A 61035-2024")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 18713-2024</t>
+          <t>A 1510-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1807,10 +1812,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45426</v>
+        <v>45306</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1823,7 +1828,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1835,22 +1840,22 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
         <v>1</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1863,42 +1868,46 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Gråtrut</t>
+          <t>Svart stork</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 18713-2024 artfynd.xlsx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 1510-2024 artfynd.xlsx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 18713-2024 karta.png", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 1510-2024 karta.png", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 18713-2024 georefererad karta.tif", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 1510-2024 georefererad karta.tif", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 18713-2024 FSC-klagomål.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 1510-2024 FSC-klagomål.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 18713-2024 FSC-klagomål mail.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 1510-2024 FSC-klagomål mail.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 18713-2024 tillsynsbegäran.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 1510-2024 tillsynsbegäran.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 18713-2024 tillsynsbegäran mail.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 1510-2024 tillsynsbegäran mail.docx", "A 1510-2024")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 1510-2024 prioriterade fågelarter.docx", "A 1510-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 24809-2025</t>
+          <t>A 52652-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1912,10 +1921,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45799</v>
+        <v>45225</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1928,7 +1937,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1940,7 +1949,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1952,10 +1961,10 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1968,46 +1977,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönfläckig padda</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 24809-2025 artfynd.xlsx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 52652-2023 artfynd.xlsx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 24809-2025 karta.png", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 52652-2023 karta.png", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 24809-2025 georefererad karta.tif", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 52652-2023 georefererad karta.tif", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 24809-2025 FSC-klagomål.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 52652-2023 FSC-klagomål.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 24809-2025 FSC-klagomål mail.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 52652-2023 FSC-klagomål mail.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 24809-2025 tillsynsbegäran.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 52652-2023 tillsynsbegäran.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 24809-2025 tillsynsbegäran mail.docx", "A 24809-2025")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 24809-2025 prioriterade fågelarter.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 52652-2023 tillsynsbegäran mail.docx", "A 52652-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 61035-2024</t>
+          <t>A 18713-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2021,10 +2026,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45645</v>
+        <v>45426</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2037,19 +2042,19 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>7.6</v>
+        <v>4.1</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2064,55 +2069,55 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Gråtrut</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 61035-2024 artfynd.xlsx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 18713-2024 artfynd.xlsx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 61035-2024 karta.png", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 18713-2024 karta.png", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 61035-2024 georefererad karta.tif", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 18713-2024 georefererad karta.tif", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 61035-2024 FSC-klagomål.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 18713-2024 FSC-klagomål.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 61035-2024 FSC-klagomål mail.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 18713-2024 FSC-klagomål mail.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 61035-2024 tillsynsbegäran.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 18713-2024 tillsynsbegäran.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 61035-2024 tillsynsbegäran mail.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 18713-2024 tillsynsbegäran mail.docx", "A 18713-2024")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 14013-2026</t>
+          <t>A 24809-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2126,10 +2131,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46098</v>
+        <v>45799</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2141,13 +2146,8 @@
           <t>ESLÖV</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>8.800000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2183,43 +2183,43 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14013-2026 artfynd.xlsx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 24809-2025 artfynd.xlsx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14013-2026 karta.png", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 24809-2025 karta.png", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14013-2026 georefererad karta.tif", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 24809-2025 georefererad karta.tif", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14013-2026 FSC-klagomål.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 24809-2025 FSC-klagomål.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14013-2026 FSC-klagomål mail.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 24809-2025 FSC-klagomål mail.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14013-2026 tillsynsbegäran.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 24809-2025 tillsynsbegäran.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14013-2026 tillsynsbegäran mail.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 24809-2025 tillsynsbegäran mail.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 14013-2026 prioriterade fågelarter.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 24809-2025 prioriterade fågelarter.docx", "A 24809-2025")</f>
         <v/>
       </c>
     </row>
@@ -2243,7 +2243,7 @@
         <v>44553</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>44690</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 7409-2025</t>
+          <t>A 16733-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2386,10 +2386,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45705</v>
+        <v>45030</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2445,7 +2445,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 12079-2024</t>
+          <t>A 5812-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45377</v>
+        <v>44596</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>6.9</v>
+        <v>0.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2518,7 +2518,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 15533-2024</t>
+          <t>A 15467-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45401</v>
+        <v>45747</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>7.5</v>
+        <v>1.4</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 36761-2022</t>
+          <t>A 5869-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2601,14 +2601,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44805</v>
+        <v>44958</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2664,7 +2664,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 11221-2024</t>
+          <t>A 7409-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2678,10 +2678,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45371</v>
+        <v>45705</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 15467-2025</t>
+          <t>A 14386-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2751,10 +2751,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45747</v>
+        <v>46100</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.4</v>
+        <v>12.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2810,7 +2810,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 49137-2024</t>
+          <t>A 9686-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45594</v>
+        <v>44984</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2883,7 +2883,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 25388-2023</t>
+          <t>A 7016-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2897,10 +2897,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45089</v>
+        <v>45701</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2912,8 +2912,13 @@
           <t>ESLÖV</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2956,7 +2961,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 32984-2024</t>
+          <t>A 47356-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2970,10 +2975,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45517</v>
+        <v>45930</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2986,7 +2991,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3029,7 +3034,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 5869-2023</t>
+          <t>A 24115-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3039,14 +3044,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44958</v>
+        <v>44725</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3059,7 +3064,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3102,7 +3107,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 16792-2024</t>
+          <t>A 35996-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3116,10 +3121,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45411</v>
+        <v>45863</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3132,7 +3137,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3175,7 +3180,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 10940-2024</t>
+          <t>A 35997-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3189,10 +3194,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45370</v>
+        <v>45863</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3205,7 +3210,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3248,7 +3253,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 28088-2025</t>
+          <t>A 18281-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3262,10 +3267,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45817</v>
+        <v>46125</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3278,7 +3283,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3321,7 +3326,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 9482-2023</t>
+          <t>A 25388-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3335,10 +3340,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44981</v>
+        <v>45089</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3351,7 +3356,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3394,7 +3399,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 47356-2025</t>
+          <t>A 12079-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3408,10 +3413,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45930</v>
+        <v>45377</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3424,7 +3429,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.6</v>
+        <v>6.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3467,7 +3472,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 25385-2023</t>
+          <t>A 11204-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3481,10 +3486,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45089</v>
+        <v>44992</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3540,7 +3545,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 43808-2024</t>
+          <t>A 47870-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3550,14 +3555,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45571</v>
+        <v>45932</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3570,7 +3575,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.5</v>
+        <v>6.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3613,7 +3618,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 35996-2025</t>
+          <t>A 9482-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3627,10 +3632,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45863</v>
+        <v>44981</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3643,7 +3648,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3686,7 +3691,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 35997-2025</t>
+          <t>A 15533-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3700,10 +3705,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45863</v>
+        <v>45401</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3716,7 +3721,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.9</v>
+        <v>7.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3759,7 +3764,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 7016-2025</t>
+          <t>A 62496-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3773,10 +3778,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45701</v>
+        <v>45268</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3788,13 +3793,8 @@
           <t>ESLÖV</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3837,7 +3837,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 11204-2023</t>
+          <t>A 25385-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3851,10 +3851,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44992</v>
+        <v>45089</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 22134-2026</t>
+          <t>A 34170-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3924,10 +3924,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46153</v>
+        <v>45138</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>5.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3983,7 +3983,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 25508-2023</t>
+          <t>A 9849-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45089</v>
+        <v>46072</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4056,7 +4056,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 9686-2023</t>
+          <t>A 15357-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4070,10 +4070,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44984</v>
+        <v>45019</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4129,7 +4129,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 18503-2026</t>
+          <t>A 36761-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4143,10 +4143,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46127</v>
+        <v>44805</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4202,7 +4202,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 16670-2025</t>
+          <t>A 22134-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4216,10 +4216,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45754</v>
+        <v>46153</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4292,7 +4292,7 @@
         <v>45139</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 10819-2026</t>
+          <t>A 18503-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4362,10 +4362,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46078</v>
+        <v>46127</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 1574-2024</t>
+          <t>A 10819-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4435,10 +4435,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45306</v>
+        <v>46078</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4494,7 +4494,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 47870-2025</t>
+          <t>A 1574-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45932</v>
+        <v>45306</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>6.8</v>
+        <v>3.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4567,7 +4567,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 62496-2023</t>
+          <t>A 25730-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45268</v>
+        <v>46178</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4640,7 +4640,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 25730-2026</t>
+          <t>A 26165-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4654,10 +4654,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4713,7 +4713,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 26165-2026</t>
+          <t>A 26169-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4730,7 +4730,7 @@
         <v>46181</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4786,7 +4786,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 26169-2026</t>
+          <t>A 26497-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46181</v>
+        <v>46183</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4859,7 +4859,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 26497-2026</t>
+          <t>A 27439-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46183</v>
+        <v>46189</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4932,7 +4932,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 34170-2023</t>
+          <t>A 27428-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4946,10 +4946,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45138</v>
+        <v>46189</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>5.8</v>
+        <v>3.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5005,7 +5005,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 27428-2026</t>
+          <t>A 27435-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5022,7 +5022,7 @@
         <v>46189</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5078,7 +5078,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 27439-2026</t>
+          <t>A 10940-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5092,10 +5092,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46189</v>
+        <v>45370</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5151,7 +5151,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 27435-2026</t>
+          <t>A 11221-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46189</v>
+        <v>45371</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5224,7 +5224,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 9849-2026</t>
+          <t>A 43808-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5234,14 +5234,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46072</v>
+        <v>45571</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5297,7 +5297,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 24115-2022</t>
+          <t>A 9484-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44725</v>
+        <v>44981</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4.4</v>
+        <v>1.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5370,7 +5370,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 14386-2026</t>
+          <t>A 44496-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5384,10 +5384,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46100</v>
+        <v>45189</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>12.4</v>
+        <v>0.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5443,7 +5443,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 9484-2023</t>
+          <t>A 33865-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5457,10 +5457,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44981</v>
+        <v>45520</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5516,7 +5516,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 16733-2023</t>
+          <t>A 16670-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5530,10 +5530,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45030</v>
+        <v>45754</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5589,7 +5589,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 44496-2023</t>
+          <t>A 34466-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5603,10 +5603,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45189</v>
+        <v>45139</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>4.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5662,7 +5662,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 18281-2026</t>
+          <t>A 38173-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5676,10 +5676,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46125</v>
+        <v>45161</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5735,7 +5735,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 34466-2023</t>
+          <t>A 25508-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5749,10 +5749,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45139</v>
+        <v>45089</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4.3</v>
+        <v>0.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5808,7 +5808,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 33865-2024</t>
+          <t>A 49137-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5822,10 +5822,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45520</v>
+        <v>45594</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5881,7 +5881,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 5812-2022</t>
+          <t>A 32984-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5895,10 +5895,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44596</v>
+        <v>45517</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5954,7 +5954,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 38173-2023</t>
+          <t>A 16792-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5968,10 +5968,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45161</v>
+        <v>45411</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6027,7 +6027,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 15357-2023</t>
+          <t>A 58721-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6041,10 +6041,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45019</v>
+        <v>45986</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6100,7 +6100,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 58721-2025</t>
+          <t>A 28088-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6114,10 +6114,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45986</v>
+        <v>45817</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>

--- a/Översikt ESLÖV.xlsx
+++ b/Översikt ESLÖV.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE70"/>
+  <dimension ref="A1:AE69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45307</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45615</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44960</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>44846</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>45817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 32950-2026</t>
+          <t>A 23773-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1164,10 +1164,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46244</v>
+        <v>45793</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1180,81 +1180,76 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>18.6</v>
+        <v>4.9</v>
       </c>
       <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
       <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
         <v>2</v>
       </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3</v>
-      </c>
       <c r="T7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika
-Svartnande kantarell
-Spillkråka</t>
+          <t>Ask
+Kransrams</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 32950-2026 artfynd.xlsx", "A 32950-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 23773-2025 artfynd.xlsx", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 32950-2026 karta.png", "A 32950-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 23773-2025 karta.png", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 32950-2026 georefererad karta.tif", "A 32950-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 23773-2025 georefererad karta.tif", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 32950-2026 FSC-klagomål.docx", "A 32950-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 23773-2025 FSC-klagomål.docx", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 32950-2026 FSC-klagomål mail.docx", "A 32950-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 23773-2025 FSC-klagomål mail.docx", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 32950-2026 tillsynsbegäran.docx", "A 32950-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 23773-2025 tillsynsbegäran.docx", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 32950-2026 tillsynsbegäran mail.docx", "A 32950-2026")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 32950-2026 prioriterade fågelarter.docx", "A 32950-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 23773-2025 tillsynsbegäran mail.docx", "A 23773-2025")</f>
         <v/>
       </c>
     </row>
@@ -1278,7 +1273,7 @@
         <v>46100</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1384,7 +1379,7 @@
         <v>44981</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1473,7 +1468,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 23773-2025</t>
+          <t>A 1510-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1487,10 +1482,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45793</v>
+        <v>45306</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1503,83 +1498,86 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
         <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
       </c>
       <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>1</v>
       </c>
-      <c r="S10" t="n">
-        <v>2</v>
-      </c>
       <c r="T10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Ask
-Kransrams</t>
+          <t>Svart stork</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 23773-2025 artfynd.xlsx", "A 23773-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 1510-2024 artfynd.xlsx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 23773-2025 karta.png", "A 23773-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 1510-2024 karta.png", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 23773-2025 georefererad karta.tif", "A 23773-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 1510-2024 georefererad karta.tif", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 23773-2025 FSC-klagomål.docx", "A 23773-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 1510-2024 FSC-klagomål.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 23773-2025 FSC-klagomål mail.docx", "A 23773-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 1510-2024 FSC-klagomål mail.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 23773-2025 tillsynsbegäran.docx", "A 23773-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 1510-2024 tillsynsbegäran.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 23773-2025 tillsynsbegäran mail.docx", "A 23773-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 1510-2024 tillsynsbegäran mail.docx", "A 1510-2024")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 1510-2024 prioriterade fågelarter.docx", "A 1510-2024")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 14013-2026</t>
+          <t>A 52652-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1593,10 +1591,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46098</v>
+        <v>45225</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1608,13 +1606,8 @@
           <t>ESLÖV</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>8.800000000000001</v>
+        <v>2.9</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1626,7 +1619,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1638,10 +1631,10 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1650,50 +1643,46 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Grönfläckig padda</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14013-2026 artfynd.xlsx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 52652-2023 artfynd.xlsx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14013-2026 karta.png", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 52652-2023 karta.png", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14013-2026 georefererad karta.tif", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 52652-2023 georefererad karta.tif", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14013-2026 FSC-klagomål.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 52652-2023 FSC-klagomål.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14013-2026 FSC-klagomål mail.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 52652-2023 FSC-klagomål mail.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14013-2026 tillsynsbegäran.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 52652-2023 tillsynsbegäran.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14013-2026 tillsynsbegäran mail.docx", "A 14013-2026")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 14013-2026 prioriterade fågelarter.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 52652-2023 tillsynsbegäran mail.docx", "A 52652-2023")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 61035-2024</t>
+          <t>A 18713-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1707,10 +1696,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45645</v>
+        <v>45426</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1723,19 +1712,19 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>7.6</v>
+        <v>4.1</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1750,55 +1739,55 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Gråtrut</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 61035-2024 artfynd.xlsx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 18713-2024 artfynd.xlsx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 61035-2024 karta.png", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 18713-2024 karta.png", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 61035-2024 georefererad karta.tif", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 18713-2024 georefererad karta.tif", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 61035-2024 FSC-klagomål.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 18713-2024 FSC-klagomål.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 61035-2024 FSC-klagomål mail.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 18713-2024 FSC-klagomål mail.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 61035-2024 tillsynsbegäran.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 18713-2024 tillsynsbegäran.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 61035-2024 tillsynsbegäran mail.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 18713-2024 tillsynsbegäran mail.docx", "A 18713-2024")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 1510-2024</t>
+          <t>A 24809-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1812,10 +1801,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45306</v>
+        <v>45799</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1828,7 +1817,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1849,10 +1838,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1868,46 +1857,46 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Svart stork</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 1510-2024 artfynd.xlsx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 24809-2025 artfynd.xlsx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 1510-2024 karta.png", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 24809-2025 karta.png", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 1510-2024 georefererad karta.tif", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 24809-2025 georefererad karta.tif", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 1510-2024 FSC-klagomål.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 24809-2025 FSC-klagomål.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 1510-2024 FSC-klagomål mail.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 24809-2025 FSC-klagomål mail.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 1510-2024 tillsynsbegäran.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 24809-2025 tillsynsbegäran.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 1510-2024 tillsynsbegäran mail.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 24809-2025 tillsynsbegäran mail.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 1510-2024 prioriterade fågelarter.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 24809-2025 prioriterade fågelarter.docx", "A 24809-2025")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 52652-2023</t>
+          <t>A 14013-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1921,10 +1910,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45225</v>
+        <v>46098</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1936,8 +1925,13 @@
           <t>ESLÖV</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>2.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1949,7 +1943,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1961,10 +1955,10 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1973,46 +1967,50 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Grönfläckig padda</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 52652-2023 artfynd.xlsx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14013-2026 artfynd.xlsx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 52652-2023 karta.png", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14013-2026 karta.png", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 52652-2023 georefererad karta.tif", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14013-2026 georefererad karta.tif", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 52652-2023 FSC-klagomål.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14013-2026 FSC-klagomål.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 52652-2023 FSC-klagomål mail.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14013-2026 FSC-klagomål mail.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 52652-2023 tillsynsbegäran.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14013-2026 tillsynsbegäran.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 52652-2023 tillsynsbegäran mail.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14013-2026 tillsynsbegäran mail.docx", "A 14013-2026")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 14013-2026 prioriterade fågelarter.docx", "A 14013-2026")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 18713-2024</t>
+          <t>A 61035-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2026,10 +2024,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45426</v>
+        <v>45645</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2042,19 +2040,19 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>4.1</v>
+        <v>7.6</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2069,55 +2067,55 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Gråtrut</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 18713-2024 artfynd.xlsx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 61035-2024 artfynd.xlsx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 18713-2024 karta.png", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 61035-2024 karta.png", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 18713-2024 georefererad karta.tif", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 61035-2024 georefererad karta.tif", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 18713-2024 FSC-klagomål.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 61035-2024 FSC-klagomål.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 18713-2024 FSC-klagomål mail.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 61035-2024 FSC-klagomål mail.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 18713-2024 tillsynsbegäran.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 61035-2024 tillsynsbegäran.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 18713-2024 tillsynsbegäran mail.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 61035-2024 tillsynsbegäran mail.docx", "A 61035-2024")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 24809-2025</t>
+          <t>A 74008-2021</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2131,10 +2129,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45799</v>
+        <v>44553</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2147,10 +2145,10 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -2177,56 +2175,20 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 24809-2025 artfynd.xlsx", "A 24809-2025")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 24809-2025 karta.png", "A 24809-2025")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 24809-2025 georefererad karta.tif", "A 24809-2025")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 24809-2025 FSC-klagomål.docx", "A 24809-2025")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 24809-2025 FSC-klagomål mail.docx", "A 24809-2025")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 24809-2025 tillsynsbegäran.docx", "A 24809-2025")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 24809-2025 tillsynsbegäran mail.docx", "A 24809-2025")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 24809-2025 prioriterade fågelarter.docx", "A 24809-2025")</f>
-        <v/>
-      </c>
+      <c r="V16" s="2" t="inlineStr"/>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 74008-2021</t>
+          <t>A 18872-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2240,10 +2202,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44553</v>
+        <v>44690</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2256,7 +2218,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2299,7 +2261,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 18872-2022</t>
+          <t>A 11221-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2313,10 +2275,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44690</v>
+        <v>45371</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2329,7 +2291,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.4</v>
+        <v>0.3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2372,7 +2334,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 16733-2023</t>
+          <t>A 44496-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2386,10 +2348,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45030</v>
+        <v>45189</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2402,7 +2364,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2445,7 +2407,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 5812-2022</t>
+          <t>A 15467-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2459,10 +2421,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44596</v>
+        <v>45747</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2475,7 +2437,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2518,7 +2480,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 15467-2025</t>
+          <t>A 25388-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2532,10 +2494,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45747</v>
+        <v>45089</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2548,7 +2510,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2591,7 +2553,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 5869-2023</t>
+          <t>A 12079-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2601,14 +2563,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44958</v>
+        <v>45377</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2621,7 +2583,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>6.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2664,7 +2626,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 7409-2025</t>
+          <t>A 34466-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2678,10 +2640,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45705</v>
+        <v>45139</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2694,7 +2656,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.5</v>
+        <v>4.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2737,7 +2699,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 14386-2026</t>
+          <t>A 15533-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2751,10 +2713,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46100</v>
+        <v>45401</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2767,7 +2729,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>12.4</v>
+        <v>7.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2810,7 +2772,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 9686-2023</t>
+          <t>A 5869-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2820,14 +2782,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44984</v>
+        <v>44958</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2840,7 +2802,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2883,7 +2845,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 7016-2025</t>
+          <t>A 10940-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2897,10 +2859,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45701</v>
+        <v>45370</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2912,13 +2874,8 @@
           <t>ESLÖV</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2961,7 +2918,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 47356-2025</t>
+          <t>A 33865-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2975,10 +2932,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45930</v>
+        <v>45520</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2991,7 +2948,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3034,7 +2991,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 24115-2022</t>
+          <t>A 5812-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3048,10 +3005,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44725</v>
+        <v>44596</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3064,7 +3021,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4.4</v>
+        <v>0.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3107,7 +3064,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 35996-2025</t>
+          <t>A 38173-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3121,10 +3078,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45863</v>
+        <v>45161</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3137,7 +3094,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3180,7 +3137,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 35997-2025</t>
+          <t>A 15357-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3194,10 +3151,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45863</v>
+        <v>45019</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3210,7 +3167,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3253,7 +3210,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 18281-2026</t>
+          <t>A 9482-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3267,10 +3224,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46125</v>
+        <v>44981</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3283,7 +3240,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3326,7 +3283,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 25388-2023</t>
+          <t>A 25385-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3343,7 +3300,7 @@
         <v>45089</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3356,7 +3313,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3399,7 +3356,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 12079-2024</t>
+          <t>A 43808-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3409,14 +3366,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45377</v>
+        <v>45571</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3429,7 +3386,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>6.9</v>
+        <v>1.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3472,7 +3429,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 11204-2023</t>
+          <t>A 49137-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3486,10 +3443,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44992</v>
+        <v>45594</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3502,7 +3459,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3545,7 +3502,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 47870-2025</t>
+          <t>A 32984-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3559,10 +3516,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45932</v>
+        <v>45517</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3575,7 +3532,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>6.8</v>
+        <v>2.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3618,7 +3575,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 9482-2023</t>
+          <t>A 47356-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3632,10 +3589,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44981</v>
+        <v>45930</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3648,7 +3605,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.7</v>
+        <v>0.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3691,7 +3648,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 15533-2024</t>
+          <t>A 7016-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3705,10 +3662,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45401</v>
+        <v>45701</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3720,8 +3677,13 @@
           <t>ESLÖV</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>7.5</v>
+        <v>2.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3764,7 +3726,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 62496-2023</t>
+          <t>A 16792-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3778,10 +3740,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45268</v>
+        <v>45411</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3794,7 +3756,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3837,7 +3799,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 25385-2023</t>
+          <t>A 11204-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3851,10 +3813,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45089</v>
+        <v>44992</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3910,7 +3872,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 34170-2023</t>
+          <t>A 28088-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3924,10 +3886,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45138</v>
+        <v>45817</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3940,7 +3902,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>5.8</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3983,7 +3945,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 9849-2026</t>
+          <t>A 25508-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3997,10 +3959,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46072</v>
+        <v>45089</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4013,7 +3975,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4056,7 +4018,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 15357-2023</t>
+          <t>A 9686-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4070,10 +4032,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45019</v>
+        <v>44984</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4086,7 +4048,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4129,7 +4091,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 36761-2022</t>
+          <t>A 35996-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4143,10 +4105,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44805</v>
+        <v>45863</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4159,7 +4121,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>4.8</v>
+        <v>0.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4202,7 +4164,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 22134-2026</t>
+          <t>A 35997-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4216,10 +4178,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46153</v>
+        <v>45863</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4232,7 +4194,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4275,7 +4237,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 34468-2023</t>
+          <t>A 16670-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4289,10 +4251,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45139</v>
+        <v>45754</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4305,7 +4267,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>5.5</v>
+        <v>1.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4348,7 +4310,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 18503-2026</t>
+          <t>A 34468-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4362,10 +4324,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46127</v>
+        <v>45139</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4378,7 +4340,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4421,7 +4383,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 10819-2026</t>
+          <t>A 7409-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4435,10 +4397,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46078</v>
+        <v>45705</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4451,7 +4413,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4.9</v>
+        <v>1.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4494,7 +4456,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 1574-2024</t>
+          <t>A 62496-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4508,10 +4470,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45306</v>
+        <v>45268</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4524,7 +4486,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4567,7 +4529,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 25730-2026</t>
+          <t>A 14386-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4581,10 +4543,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46178</v>
+        <v>46100</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4597,7 +4559,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.4</v>
+        <v>12.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4640,7 +4602,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 26165-2026</t>
+          <t>A 36761-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4654,10 +4616,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46181</v>
+        <v>44805</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4670,7 +4632,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2</v>
+        <v>4.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4713,7 +4675,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 26169-2026</t>
+          <t>A 34170-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4727,10 +4689,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46181</v>
+        <v>45138</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4743,7 +4705,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.5</v>
+        <v>5.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4786,7 +4748,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 26497-2026</t>
+          <t>A 18281-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4800,10 +4762,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46183</v>
+        <v>46125</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4816,7 +4778,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4859,7 +4821,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 27439-2026</t>
+          <t>A 24115-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4873,10 +4835,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46189</v>
+        <v>44725</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4889,7 +4851,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.6</v>
+        <v>4.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4932,7 +4894,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 27428-2026</t>
+          <t>A 47870-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4946,10 +4908,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46189</v>
+        <v>45932</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4962,7 +4924,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.4</v>
+        <v>6.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5005,7 +4967,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 27435-2026</t>
+          <t>A 9484-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5019,10 +4981,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46189</v>
+        <v>44981</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5035,7 +4997,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5078,7 +5040,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 10940-2024</t>
+          <t>A 16733-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5092,10 +5054,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45370</v>
+        <v>45030</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5108,7 +5070,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5151,7 +5113,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 11221-2024</t>
+          <t>A 9849-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5165,10 +5127,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45371</v>
+        <v>46072</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5181,7 +5143,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.3</v>
+        <v>2.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5224,7 +5186,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 43808-2024</t>
+          <t>A 22134-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5234,14 +5196,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45571</v>
+        <v>46153</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5254,7 +5216,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5297,7 +5259,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 9484-2023</t>
+          <t>A 18503-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5311,10 +5273,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44981</v>
+        <v>46127</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5327,7 +5289,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.4</v>
+        <v>4.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5370,7 +5332,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 44496-2023</t>
+          <t>A 10819-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5384,10 +5346,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45189</v>
+        <v>46078</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5400,7 +5362,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>4.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5443,7 +5405,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 33865-2024</t>
+          <t>A 1574-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5457,10 +5419,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45520</v>
+        <v>45306</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5473,7 +5435,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.3</v>
+        <v>3.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5516,7 +5478,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 16670-2025</t>
+          <t>A 25730-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5530,10 +5492,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45754</v>
+        <v>46178</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5546,7 +5508,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5589,7 +5551,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 34466-2023</t>
+          <t>A 26165-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5603,10 +5565,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45139</v>
+        <v>46181</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5619,7 +5581,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4.3</v>
+        <v>2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5662,7 +5624,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 38173-2023</t>
+          <t>A 26169-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5676,10 +5638,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45161</v>
+        <v>46181</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5692,7 +5654,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5735,7 +5697,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 25508-2023</t>
+          <t>A 26497-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5749,10 +5711,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45089</v>
+        <v>46183</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5765,7 +5727,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5808,7 +5770,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 49137-2024</t>
+          <t>A 27428-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5822,10 +5784,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45594</v>
+        <v>46189</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5838,7 +5800,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5881,7 +5843,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 32984-2024</t>
+          <t>A 27439-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5895,10 +5857,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45517</v>
+        <v>46189</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5911,7 +5873,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5954,7 +5916,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 16792-2024</t>
+          <t>A 27435-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5968,10 +5930,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45411</v>
+        <v>46189</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6024,7 +5986,7 @@
       </c>
       <c r="V68" s="2" t="inlineStr"/>
     </row>
-    <row r="69" ht="15" customHeight="1">
+    <row r="69">
       <c r="A69" t="inlineStr">
         <is>
           <t>A 58721-2025</t>
@@ -6044,7 +6006,7 @@
         <v>45986</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6096,79 +6058,6 @@
         <v>0</v>
       </c>
       <c r="V69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>A 28088-2025</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D70" s="1" t="n">
-        <v>45817</v>
-      </c>
-      <c r="E70" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>ESLÖV</t>
-        </is>
-      </c>
-      <c r="I70" t="n">
-        <v>1</v>
-      </c>
-      <c r="J70" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" t="n">
-        <v>0</v>
-      </c>
-      <c r="M70" t="n">
-        <v>0</v>
-      </c>
-      <c r="N70" t="n">
-        <v>0</v>
-      </c>
-      <c r="O70" t="n">
-        <v>0</v>
-      </c>
-      <c r="P70" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
-      <c r="R70" t="n">
-        <v>0</v>
-      </c>
-      <c r="S70" t="n">
-        <v>0</v>
-      </c>
-      <c r="T70" t="n">
-        <v>0</v>
-      </c>
-      <c r="U70" t="n">
-        <v>0</v>
-      </c>
-      <c r="V70" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ESLÖV.xlsx
+++ b/Översikt ESLÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45307</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45615</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44960</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>44846</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>45817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>45793</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>46100</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>44981</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>45306</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>45225</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>45426</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>45799</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>46098</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>45645</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>44553</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>44690</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>45371</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>45189</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>45747</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>45089</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>45377</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>45139</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>45401</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>44958</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>45370</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>45520</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>44596</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>45161</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         <v>45019</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>44981</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>45089</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>45571</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>45594</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>45517</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3592,7 +3592,7 @@
         <v>45930</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>45701</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>45411</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         <v>44992</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         <v>45817</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>45089</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         <v>44984</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>45863</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>45863</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>45754</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>45139</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>45705</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>45268</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>46100</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>44805</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>45138</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>46125</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         <v>44725</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>45932</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>44981</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         <v>45030</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>46072</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>46153</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>46127</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         <v>46078</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         <v>45306</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         <v>46178</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>46181</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>46181</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         <v>46183</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>46189</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>46189</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>46189</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         <v>45986</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>

--- a/Översikt ESLÖV.xlsx
+++ b/Översikt ESLÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45307</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45615</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44960</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>44846</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>45817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>45793</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>46100</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>44981</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>45306</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>45225</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>45426</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>45799</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>46098</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>45645</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>44553</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>44690</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>45371</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>45189</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>45747</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>45089</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>45377</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>45139</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>45401</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>44958</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>45370</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>45520</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>44596</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>45161</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         <v>45019</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>44981</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>45089</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>45571</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>45594</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>45517</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3592,7 +3592,7 @@
         <v>45930</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>45701</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>45411</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         <v>44992</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         <v>45817</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>45089</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         <v>44984</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>45863</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>45863</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>45754</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>45139</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>45705</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>45268</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>46100</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>44805</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>45138</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>46125</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         <v>44725</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>45932</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>44981</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         <v>45030</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>46072</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>46153</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>46127</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         <v>46078</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         <v>45306</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         <v>46178</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>46181</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>46181</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         <v>46183</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>46189</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>46189</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>46189</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         <v>45986</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>

--- a/Översikt ESLÖV.xlsx
+++ b/Översikt ESLÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45307</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45615</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44960</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>44846</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>45817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>45793</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>46100</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>44981</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>45306</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>45225</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>45426</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>45799</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>46098</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>45645</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>44553</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>44690</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 11221-2024</t>
+          <t>A 44496-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45371</v>
+        <v>45189</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2334,7 +2334,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 44496-2023</t>
+          <t>A 33865-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45189</v>
+        <v>45520</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 15467-2025</t>
+          <t>A 16670-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45747</v>
+        <v>45754</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 25388-2023</t>
+          <t>A 34466-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45089</v>
+        <v>45139</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.5</v>
+        <v>4.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 12079-2024</t>
+          <t>A 38173-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45377</v>
+        <v>45161</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>6.9</v>
+        <v>2.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2626,7 +2626,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 34466-2023</t>
+          <t>A 1574-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45139</v>
+        <v>45306</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2699,7 +2699,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 15533-2024</t>
+          <t>A 25730-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45401</v>
+        <v>46178</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>7.5</v>
+        <v>1.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2772,7 +2772,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 5869-2023</t>
+          <t>A 26165-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2782,14 +2782,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44958</v>
+        <v>46181</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 10940-2024</t>
+          <t>A 47356-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45370</v>
+        <v>45930</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2918,7 +2918,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 33865-2024</t>
+          <t>A 26169-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45520</v>
+        <v>46181</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2991,7 +2991,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 5812-2022</t>
+          <t>A 26497-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44596</v>
+        <v>46183</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3064,7 +3064,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 38173-2023</t>
+          <t>A 27439-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3078,10 +3078,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45161</v>
+        <v>46189</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3137,7 +3137,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 15357-2023</t>
+          <t>A 27428-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45019</v>
+        <v>46189</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3210,7 +3210,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 9482-2023</t>
+          <t>A 27435-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44981</v>
+        <v>46189</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3283,7 +3283,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 25385-2023</t>
+          <t>A 25508-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3300,7 +3300,7 @@
         <v>45089</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 43808-2024</t>
+          <t>A 35996-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3366,14 +3366,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45571</v>
+        <v>45863</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3429,7 +3429,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 49137-2024</t>
+          <t>A 35997-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45594</v>
+        <v>45863</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3502,7 +3502,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 32984-2024</t>
+          <t>A 49137-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45517</v>
+        <v>45594</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3575,7 +3575,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 47356-2025</t>
+          <t>A 32984-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45930</v>
+        <v>45517</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3648,7 +3648,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 7016-2025</t>
+          <t>A 16792-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3662,10 +3662,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45701</v>
+        <v>45411</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3677,13 +3677,8 @@
           <t>ESLÖV</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3726,7 +3721,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 16792-2024</t>
+          <t>A 28088-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3740,10 +3735,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45411</v>
+        <v>45817</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3756,7 +3751,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3799,7 +3794,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 11204-2023</t>
+          <t>A 47870-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3813,10 +3808,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44992</v>
+        <v>45932</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3829,7 +3824,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.7</v>
+        <v>6.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3872,7 +3867,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 28088-2025</t>
+          <t>A 58721-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3886,10 +3881,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45817</v>
+        <v>45986</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3902,7 +3897,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3945,7 +3940,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 25508-2023</t>
+          <t>A 9849-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3959,10 +3954,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45089</v>
+        <v>46072</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3975,7 +3970,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4018,7 +4013,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 9686-2023</t>
+          <t>A 14386-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4032,10 +4027,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44984</v>
+        <v>46100</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4048,7 +4043,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.8</v>
+        <v>12.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4091,7 +4086,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 35996-2025</t>
+          <t>A 18281-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4105,10 +4100,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45863</v>
+        <v>46125</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4164,7 +4159,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 35997-2025</t>
+          <t>A 16733-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4178,10 +4173,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45863</v>
+        <v>45030</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4194,7 +4189,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4237,7 +4232,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 16670-2025</t>
+          <t>A 5812-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4251,10 +4246,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45754</v>
+        <v>44596</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4267,7 +4262,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4310,7 +4305,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 34468-2023</t>
+          <t>A 22134-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4324,10 +4319,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45139</v>
+        <v>46153</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4340,7 +4335,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>5.5</v>
+        <v>2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4383,7 +4378,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 7409-2025</t>
+          <t>A 15467-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4397,10 +4392,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45705</v>
+        <v>45747</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4413,7 +4408,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4456,7 +4451,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 62496-2023</t>
+          <t>A 5869-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4466,14 +4461,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45268</v>
+        <v>44958</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4486,7 +4481,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4529,7 +4524,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 14386-2026</t>
+          <t>A 18503-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4543,10 +4538,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46100</v>
+        <v>46127</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4559,7 +4554,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>12.4</v>
+        <v>4.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4602,7 +4597,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 36761-2022</t>
+          <t>A 7409-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4616,10 +4611,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44805</v>
+        <v>45705</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4632,7 +4627,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>4.8</v>
+        <v>1.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4675,7 +4670,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 34170-2023</t>
+          <t>A 9686-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4689,10 +4684,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45138</v>
+        <v>44984</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4705,7 +4700,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>5.8</v>
+        <v>0.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4748,7 +4743,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 18281-2026</t>
+          <t>A 10819-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4762,10 +4757,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46125</v>
+        <v>46078</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4778,7 +4773,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.8</v>
+        <v>4.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4821,7 +4816,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 24115-2022</t>
+          <t>A 7016-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4835,10 +4830,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44725</v>
+        <v>45701</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4850,8 +4845,13 @@
           <t>ESLÖV</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4894,7 +4894,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 47870-2025</t>
+          <t>A 24115-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45932</v>
+        <v>44725</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>6.8</v>
+        <v>4.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4967,7 +4967,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 9484-2023</t>
+          <t>A 25388-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4981,10 +4981,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44981</v>
+        <v>45089</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5040,7 +5040,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 16733-2023</t>
+          <t>A 12079-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5054,10 +5054,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45030</v>
+        <v>45377</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.6</v>
+        <v>6.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5113,7 +5113,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 9849-2026</t>
+          <t>A 11204-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5127,10 +5127,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46072</v>
+        <v>44992</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5186,7 +5186,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 22134-2026</t>
+          <t>A 9482-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5200,10 +5200,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46153</v>
+        <v>44981</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5259,7 +5259,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 18503-2026</t>
+          <t>A 15533-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5273,10 +5273,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46127</v>
+        <v>45401</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4.9</v>
+        <v>7.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5332,7 +5332,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 10819-2026</t>
+          <t>A 62496-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5346,10 +5346,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46078</v>
+        <v>45268</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4.9</v>
+        <v>2.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5405,7 +5405,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 1574-2024</t>
+          <t>A 25385-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5419,10 +5419,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45306</v>
+        <v>45089</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.6</v>
+        <v>0.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5478,7 +5478,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 25730-2026</t>
+          <t>A 34170-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5492,10 +5492,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46178</v>
+        <v>45138</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.4</v>
+        <v>5.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5551,7 +5551,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 26165-2026</t>
+          <t>A 15357-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46181</v>
+        <v>45019</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5624,7 +5624,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 26169-2026</t>
+          <t>A 36761-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46181</v>
+        <v>44805</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5697,7 +5697,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 26497-2026</t>
+          <t>A 34468-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46183</v>
+        <v>45139</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.4</v>
+        <v>5.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5770,7 +5770,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 27428-2026</t>
+          <t>A 10940-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5784,10 +5784,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46189</v>
+        <v>45370</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5843,7 +5843,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 27439-2026</t>
+          <t>A 11221-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5857,10 +5857,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46189</v>
+        <v>45371</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5916,7 +5916,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 27435-2026</t>
+          <t>A 43808-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5926,14 +5926,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46189</v>
+        <v>45571</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5989,7 +5989,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 58721-2025</t>
+          <t>A 9484-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6003,10 +6003,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45986</v>
+        <v>44981</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6019,7 +6019,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>

--- a/Översikt ESLÖV.xlsx
+++ b/Översikt ESLÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45307</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45615</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44960</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>44846</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>45817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>45793</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>46100</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>44981</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 1510-2024</t>
+          <t>A 18713-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1482,10 +1482,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45306</v>
+        <v>45426</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1510,7 +1510,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1519,13 +1519,13 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1538,46 +1538,42 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Svart stork</t>
+          <t>Gråtrut</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 1510-2024 artfynd.xlsx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 18713-2024 artfynd.xlsx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 1510-2024 karta.png", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 18713-2024 karta.png", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 1510-2024 georefererad karta.tif", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 18713-2024 georefererad karta.tif", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 1510-2024 FSC-klagomål.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 18713-2024 FSC-klagomål.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 1510-2024 FSC-klagomål mail.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 18713-2024 FSC-klagomål mail.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 1510-2024 tillsynsbegäran.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 18713-2024 tillsynsbegäran.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 1510-2024 tillsynsbegäran mail.docx", "A 1510-2024")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 1510-2024 prioriterade fågelarter.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 18713-2024 tillsynsbegäran mail.docx", "A 18713-2024")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 52652-2023</t>
+          <t>A 24809-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1591,10 +1587,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45225</v>
+        <v>45799</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1607,7 +1603,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1619,7 +1615,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1631,10 +1627,10 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1647,42 +1643,46 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Grönfläckig padda</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 52652-2023 artfynd.xlsx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 24809-2025 artfynd.xlsx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 52652-2023 karta.png", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 24809-2025 karta.png", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 52652-2023 georefererad karta.tif", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 24809-2025 georefererad karta.tif", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 52652-2023 FSC-klagomål.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 24809-2025 FSC-klagomål.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 52652-2023 FSC-klagomål mail.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 24809-2025 FSC-klagomål mail.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 52652-2023 tillsynsbegäran.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 24809-2025 tillsynsbegäran.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 52652-2023 tillsynsbegäran mail.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 24809-2025 tillsynsbegäran mail.docx", "A 24809-2025")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 24809-2025 prioriterade fågelarter.docx", "A 24809-2025")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 18713-2024</t>
+          <t>A 14013-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45426</v>
+        <v>46098</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1711,8 +1711,13 @@
           <t>ESLÖV</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>4.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1724,7 +1729,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1736,10 +1741,10 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1748,46 +1753,50 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Gråtrut</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 18713-2024 artfynd.xlsx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14013-2026 artfynd.xlsx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 18713-2024 karta.png", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14013-2026 karta.png", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 18713-2024 georefererad karta.tif", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14013-2026 georefererad karta.tif", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 18713-2024 FSC-klagomål.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14013-2026 FSC-klagomål.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 18713-2024 FSC-klagomål mail.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14013-2026 FSC-klagomål mail.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 18713-2024 tillsynsbegäran.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14013-2026 tillsynsbegäran.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 18713-2024 tillsynsbegäran mail.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14013-2026 tillsynsbegäran mail.docx", "A 14013-2026")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 14013-2026 prioriterade fågelarter.docx", "A 14013-2026")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 24809-2025</t>
+          <t>A 61035-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1801,10 +1810,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45799</v>
+        <v>45645</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1817,17 +1826,17 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.4</v>
+        <v>7.6</v>
       </c>
       <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
@@ -1841,7 +1850,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1850,53 +1859,49 @@
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 24809-2025 artfynd.xlsx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 61035-2024 artfynd.xlsx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 24809-2025 karta.png", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 61035-2024 karta.png", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 24809-2025 georefererad karta.tif", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 61035-2024 georefererad karta.tif", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 24809-2025 FSC-klagomål.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 61035-2024 FSC-klagomål.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 24809-2025 FSC-klagomål mail.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 61035-2024 FSC-klagomål mail.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 24809-2025 tillsynsbegäran.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 61035-2024 tillsynsbegäran.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 24809-2025 tillsynsbegäran mail.docx", "A 24809-2025")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 24809-2025 prioriterade fågelarter.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 61035-2024 tillsynsbegäran mail.docx", "A 61035-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 14013-2026</t>
+          <t>A 1510-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1910,10 +1915,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46098</v>
+        <v>45306</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1925,13 +1930,8 @@
           <t>ESLÖV</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>8.800000000000001</v>
+        <v>3.7</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1952,10 +1952,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1967,50 +1967,50 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Svart stork</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14013-2026 artfynd.xlsx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 1510-2024 artfynd.xlsx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14013-2026 karta.png", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 1510-2024 karta.png", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14013-2026 georefererad karta.tif", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 1510-2024 georefererad karta.tif", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14013-2026 FSC-klagomål.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 1510-2024 FSC-klagomål.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14013-2026 FSC-klagomål mail.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 1510-2024 FSC-klagomål mail.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14013-2026 tillsynsbegäran.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 1510-2024 tillsynsbegäran.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14013-2026 tillsynsbegäran mail.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 1510-2024 tillsynsbegäran mail.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 14013-2026 prioriterade fågelarter.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 1510-2024 prioriterade fågelarter.docx", "A 1510-2024")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 61035-2024</t>
+          <t>A 52652-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2024,10 +2024,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45645</v>
+        <v>45225</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2040,19 +2040,19 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>7.6</v>
+        <v>2.9</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2067,48 +2067,48 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Grönfläckig padda</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 61035-2024 artfynd.xlsx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 52652-2023 artfynd.xlsx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 61035-2024 karta.png", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 52652-2023 karta.png", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 61035-2024 georefererad karta.tif", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 52652-2023 georefererad karta.tif", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 61035-2024 FSC-klagomål.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 52652-2023 FSC-klagomål.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 61035-2024 FSC-klagomål mail.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 52652-2023 FSC-klagomål mail.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 61035-2024 tillsynsbegäran.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 52652-2023 tillsynsbegäran.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 61035-2024 tillsynsbegäran mail.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 52652-2023 tillsynsbegäran mail.docx", "A 52652-2023")</f>
         <v/>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
         <v>44553</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>44690</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 44496-2023</t>
+          <t>A 12079-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45189</v>
+        <v>45377</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.5</v>
+        <v>6.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2334,7 +2334,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 33865-2024</t>
+          <t>A 15533-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45520</v>
+        <v>45401</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.3</v>
+        <v>7.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 16670-2025</t>
+          <t>A 11221-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45754</v>
+        <v>45371</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 34466-2023</t>
+          <t>A 15467-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45139</v>
+        <v>45747</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.3</v>
+        <v>1.4</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 38173-2023</t>
+          <t>A 32984-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45161</v>
+        <v>45517</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2626,7 +2626,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 1574-2024</t>
+          <t>A 5869-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2636,14 +2636,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45306</v>
+        <v>44958</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2699,7 +2699,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 25730-2026</t>
+          <t>A 47870-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46178</v>
+        <v>45932</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.4</v>
+        <v>6.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2772,7 +2772,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 26165-2026</t>
+          <t>A 16792-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46181</v>
+        <v>45411</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 47356-2025</t>
+          <t>A 9482-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45930</v>
+        <v>44981</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.6</v>
+        <v>3.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2918,7 +2918,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 26169-2026</t>
+          <t>A 25385-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46181</v>
+        <v>45089</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2991,7 +2991,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 26497-2026</t>
+          <t>A 28088-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46183</v>
+        <v>45817</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3064,7 +3064,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 27439-2026</t>
+          <t>A 43808-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3074,14 +3074,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46189</v>
+        <v>45571</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3137,7 +3137,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 27428-2026</t>
+          <t>A 47356-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46189</v>
+        <v>45930</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.4</v>
+        <v>0.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3210,7 +3210,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 27435-2026</t>
+          <t>A 35996-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46189</v>
+        <v>45863</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3283,7 +3283,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 25508-2023</t>
+          <t>A 35997-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45089</v>
+        <v>45863</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 35996-2025</t>
+          <t>A 11204-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45863</v>
+        <v>44992</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3429,7 +3429,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 35997-2025</t>
+          <t>A 25508-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45863</v>
+        <v>45089</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3502,7 +3502,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 49137-2024</t>
+          <t>A 9686-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45594</v>
+        <v>44984</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3575,7 +3575,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 32984-2024</t>
+          <t>A 9849-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45517</v>
+        <v>46072</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3648,7 +3648,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 16792-2024</t>
+          <t>A 7409-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3662,10 +3662,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45411</v>
+        <v>45705</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3721,7 +3721,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 28088-2025</t>
+          <t>A 14386-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45817</v>
+        <v>46100</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>12.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3794,7 +3794,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 47870-2025</t>
+          <t>A 36761-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45932</v>
+        <v>44805</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>6.8</v>
+        <v>4.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3867,7 +3867,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 58721-2025</t>
+          <t>A 18281-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3881,10 +3881,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45986</v>
+        <v>46125</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3940,7 +3940,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 9849-2026</t>
+          <t>A 25388-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46072</v>
+        <v>45089</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4013,7 +4013,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 14386-2026</t>
+          <t>A 10940-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46100</v>
+        <v>45370</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>12.4</v>
+        <v>0.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4086,7 +4086,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 18281-2026</t>
+          <t>A 22134-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4100,10 +4100,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46125</v>
+        <v>46153</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4159,7 +4159,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 16733-2023</t>
+          <t>A 7016-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4173,10 +4173,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45030</v>
+        <v>45701</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4188,8 +4188,13 @@
           <t>ESLÖV</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4232,7 +4237,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 5812-2022</t>
+          <t>A 18503-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4246,10 +4251,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44596</v>
+        <v>46127</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4262,7 +4267,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>4.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4305,7 +4310,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 22134-2026</t>
+          <t>A 10819-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4319,10 +4324,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46153</v>
+        <v>46078</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4335,7 +4340,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>4.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4378,7 +4383,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 15467-2025</t>
+          <t>A 1574-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4392,10 +4397,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45747</v>
+        <v>45306</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4408,7 +4413,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.4</v>
+        <v>3.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4451,7 +4456,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 5869-2023</t>
+          <t>A 25730-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4461,14 +4466,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44958</v>
+        <v>46178</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4481,7 +4486,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4524,7 +4529,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 18503-2026</t>
+          <t>A 16670-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4538,10 +4543,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46127</v>
+        <v>45754</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4554,7 +4559,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>4.9</v>
+        <v>1.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4597,7 +4602,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 7409-2025</t>
+          <t>A 34468-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4611,10 +4616,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45705</v>
+        <v>45139</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4627,7 +4632,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4670,7 +4675,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 9686-2023</t>
+          <t>A 26165-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4684,10 +4689,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44984</v>
+        <v>46181</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4700,7 +4705,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4743,7 +4748,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 10819-2026</t>
+          <t>A 26169-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4757,10 +4762,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46078</v>
+        <v>46181</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4773,7 +4778,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>4.9</v>
+        <v>3.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4816,7 +4821,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 7016-2025</t>
+          <t>A 26497-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4830,10 +4835,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45701</v>
+        <v>46183</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4845,13 +4850,8 @@
           <t>ESLÖV</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4894,7 +4894,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 24115-2022</t>
+          <t>A 27428-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44725</v>
+        <v>46189</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4967,7 +4967,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 25388-2023</t>
+          <t>A 27439-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4981,10 +4981,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45089</v>
+        <v>46189</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5040,7 +5040,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 12079-2024</t>
+          <t>A 27435-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5054,10 +5054,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45377</v>
+        <v>46189</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>6.9</v>
+        <v>0.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5113,7 +5113,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 11204-2023</t>
+          <t>A 62496-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5127,10 +5127,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44992</v>
+        <v>45268</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5186,7 +5186,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 9482-2023</t>
+          <t>A 34170-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5200,10 +5200,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44981</v>
+        <v>45138</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.7</v>
+        <v>5.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5259,7 +5259,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 15533-2024</t>
+          <t>A 24115-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5273,10 +5273,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45401</v>
+        <v>44725</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>7.5</v>
+        <v>4.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5332,7 +5332,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 62496-2023</t>
+          <t>A 9484-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5346,10 +5346,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45268</v>
+        <v>44981</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5405,7 +5405,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 25385-2023</t>
+          <t>A 16733-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5419,10 +5419,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45089</v>
+        <v>45030</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5478,7 +5478,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 34170-2023</t>
+          <t>A 44496-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5492,10 +5492,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45138</v>
+        <v>45189</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>5.8</v>
+        <v>0.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5551,7 +5551,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 15357-2023</t>
+          <t>A 34466-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45019</v>
+        <v>45139</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>4.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5624,7 +5624,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 36761-2022</t>
+          <t>A 33865-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44805</v>
+        <v>45520</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4.8</v>
+        <v>1.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5697,7 +5697,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 34468-2023</t>
+          <t>A 5812-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45139</v>
+        <v>44596</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>5.5</v>
+        <v>0.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5770,7 +5770,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 10940-2024</t>
+          <t>A 38173-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5784,10 +5784,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45370</v>
+        <v>45161</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5843,7 +5843,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 11221-2024</t>
+          <t>A 15357-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5857,10 +5857,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45371</v>
+        <v>45019</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5916,7 +5916,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 43808-2024</t>
+          <t>A 58721-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5926,14 +5926,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45571</v>
+        <v>45986</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5989,7 +5989,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 9484-2023</t>
+          <t>A 49137-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6003,10 +6003,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44981</v>
+        <v>45594</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6019,7 +6019,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>

--- a/Översikt ESLÖV.xlsx
+++ b/Översikt ESLÖV.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE69"/>
+  <dimension ref="A1:AE68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45307</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45615</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44960</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>44846</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>45817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>45793</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>46100</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>44981</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 18713-2024</t>
+          <t>A 24809-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1482,10 +1482,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45426</v>
+        <v>45799</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.1</v>
+        <v>1.4</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1510,7 +1510,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1522,10 +1522,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1538,42 +1538,46 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Gråtrut</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 18713-2024 artfynd.xlsx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 24809-2025 artfynd.xlsx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 18713-2024 karta.png", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 24809-2025 karta.png", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 18713-2024 georefererad karta.tif", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 24809-2025 georefererad karta.tif", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 18713-2024 FSC-klagomål.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 24809-2025 FSC-klagomål.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 18713-2024 FSC-klagomål mail.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 24809-2025 FSC-klagomål mail.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 18713-2024 tillsynsbegäran.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 24809-2025 tillsynsbegäran.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 18713-2024 tillsynsbegäran mail.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 24809-2025 tillsynsbegäran mail.docx", "A 24809-2025")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 24809-2025 prioriterade fågelarter.docx", "A 24809-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 24809-2025</t>
+          <t>A 14013-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1587,10 +1591,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45799</v>
+        <v>46098</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1602,8 +1606,13 @@
           <t>ESLÖV</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>1.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1639,50 +1648,50 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 24809-2025 artfynd.xlsx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14013-2026 artfynd.xlsx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 24809-2025 karta.png", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14013-2026 karta.png", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 24809-2025 georefererad karta.tif", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14013-2026 georefererad karta.tif", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 24809-2025 FSC-klagomål.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14013-2026 FSC-klagomål.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 24809-2025 FSC-klagomål mail.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14013-2026 FSC-klagomål mail.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 24809-2025 tillsynsbegäran.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14013-2026 tillsynsbegäran.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 24809-2025 tillsynsbegäran mail.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14013-2026 tillsynsbegäran mail.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 24809-2025 prioriterade fågelarter.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 14013-2026 prioriterade fågelarter.docx", "A 14013-2026")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 14013-2026</t>
+          <t>A 61035-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1696,10 +1705,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46098</v>
+        <v>45645</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1711,23 +1720,18 @@
           <t>ESLÖV</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
         <v>1</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
@@ -1741,7 +1745,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1750,53 +1754,49 @@
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14013-2026 artfynd.xlsx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 61035-2024 artfynd.xlsx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14013-2026 karta.png", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 61035-2024 karta.png", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14013-2026 georefererad karta.tif", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 61035-2024 georefererad karta.tif", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14013-2026 FSC-klagomål.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 61035-2024 FSC-klagomål.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14013-2026 FSC-klagomål mail.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 61035-2024 FSC-klagomål mail.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14013-2026 tillsynsbegäran.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 61035-2024 tillsynsbegäran.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14013-2026 tillsynsbegäran mail.docx", "A 14013-2026")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 14013-2026 prioriterade fågelarter.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 61035-2024 tillsynsbegäran mail.docx", "A 61035-2024")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 61035-2024</t>
+          <t>A 1510-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1810,10 +1810,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45645</v>
+        <v>45306</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1826,28 +1826,28 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>7.6</v>
+        <v>3.7</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
         <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
@@ -1859,49 +1859,53 @@
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Svart stork</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 61035-2024 artfynd.xlsx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 1510-2024 artfynd.xlsx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 61035-2024 karta.png", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 1510-2024 karta.png", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 61035-2024 georefererad karta.tif", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 1510-2024 georefererad karta.tif", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 61035-2024 FSC-klagomål.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 1510-2024 FSC-klagomål.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 61035-2024 FSC-klagomål mail.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 1510-2024 FSC-klagomål mail.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 61035-2024 tillsynsbegäran.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 1510-2024 tillsynsbegäran.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 61035-2024 tillsynsbegäran mail.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 1510-2024 tillsynsbegäran mail.docx", "A 1510-2024")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 1510-2024 prioriterade fågelarter.docx", "A 1510-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 1510-2024</t>
+          <t>A 52652-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1915,10 +1919,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45306</v>
+        <v>45225</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1931,7 +1935,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1943,7 +1947,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1952,13 +1956,13 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1971,46 +1975,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Svart stork</t>
+          <t>Grönfläckig padda</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 1510-2024 artfynd.xlsx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 52652-2023 artfynd.xlsx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 1510-2024 karta.png", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 52652-2023 karta.png", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 1510-2024 georefererad karta.tif", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 52652-2023 georefererad karta.tif", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 1510-2024 FSC-klagomål.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 52652-2023 FSC-klagomål.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 1510-2024 FSC-klagomål mail.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 52652-2023 FSC-klagomål mail.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 1510-2024 tillsynsbegäran.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 52652-2023 tillsynsbegäran.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 1510-2024 tillsynsbegäran mail.docx", "A 1510-2024")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 1510-2024 prioriterade fågelarter.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 52652-2023 tillsynsbegäran mail.docx", "A 52652-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 52652-2023</t>
+          <t>A 18713-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2024,10 +2024,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45225</v>
+        <v>45426</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2080,35 +2080,35 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Grönfläckig padda</t>
+          <t>Gråtrut</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 52652-2023 artfynd.xlsx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 18713-2024 artfynd.xlsx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 52652-2023 karta.png", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 18713-2024 karta.png", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 52652-2023 georefererad karta.tif", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 18713-2024 georefererad karta.tif", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 52652-2023 FSC-klagomål.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 18713-2024 FSC-klagomål.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 52652-2023 FSC-klagomål mail.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 18713-2024 FSC-klagomål mail.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 52652-2023 tillsynsbegäran.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 18713-2024 tillsynsbegäran.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 52652-2023 tillsynsbegäran mail.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 18713-2024 tillsynsbegäran mail.docx", "A 18713-2024")</f>
         <v/>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
         <v>44553</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>44690</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 12079-2024</t>
+          <t>A 16792-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45377</v>
+        <v>45411</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>6.9</v>
+        <v>0.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2334,7 +2334,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 15533-2024</t>
+          <t>A 28088-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45401</v>
+        <v>45817</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>7.5</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 11221-2024</t>
+          <t>A 25388-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45371</v>
+        <v>45089</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 15467-2025</t>
+          <t>A 12079-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45747</v>
+        <v>45377</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.4</v>
+        <v>6.9</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 32984-2024</t>
+          <t>A 47356-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45517</v>
+        <v>45930</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2626,7 +2626,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 5869-2023</t>
+          <t>A 9849-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2636,14 +2636,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44958</v>
+        <v>46072</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2699,7 +2699,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 47870-2025</t>
+          <t>A 16733-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45932</v>
+        <v>45030</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>6.8</v>
+        <v>2.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2772,7 +2772,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 16792-2024</t>
+          <t>A 11204-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45411</v>
+        <v>44992</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 9482-2023</t>
+          <t>A 35996-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44981</v>
+        <v>45863</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.7</v>
+        <v>0.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2918,7 +2918,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 25385-2023</t>
+          <t>A 35997-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45089</v>
+        <v>45863</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2991,7 +2991,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 28088-2025</t>
+          <t>A 14386-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45817</v>
+        <v>46100</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>12.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3064,7 +3064,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 43808-2024</t>
+          <t>A 5812-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3074,14 +3074,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45571</v>
+        <v>44596</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3137,7 +3137,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 47356-2025</t>
+          <t>A 18281-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45930</v>
+        <v>46125</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3210,7 +3210,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 35996-2025</t>
+          <t>A 15467-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45863</v>
+        <v>45747</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3283,7 +3283,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 35997-2025</t>
+          <t>A 5869-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3293,14 +3293,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45863</v>
+        <v>44958</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 11204-2023</t>
+          <t>A 7409-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44992</v>
+        <v>45705</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3429,7 +3429,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 25508-2023</t>
+          <t>A 9686-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45089</v>
+        <v>44984</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3502,7 +3502,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 9686-2023</t>
+          <t>A 7016-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44984</v>
+        <v>45701</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3531,8 +3531,13 @@
           <t>ESLÖV</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3575,7 +3580,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 9849-2026</t>
+          <t>A 47870-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3589,10 +3594,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46072</v>
+        <v>45932</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3605,7 +3610,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.5</v>
+        <v>6.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3648,7 +3653,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 7409-2025</t>
+          <t>A 24115-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3662,10 +3667,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45705</v>
+        <v>44725</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3678,7 +3683,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.5</v>
+        <v>4.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3721,7 +3726,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 14386-2026</t>
+          <t>A 9482-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3735,10 +3740,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46100</v>
+        <v>44981</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3751,7 +3756,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>12.4</v>
+        <v>3.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3794,7 +3799,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 36761-2022</t>
+          <t>A 15533-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3808,10 +3813,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44805</v>
+        <v>45401</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3824,7 +3829,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4.8</v>
+        <v>7.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3867,7 +3872,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 18281-2026</t>
+          <t>A 22134-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3881,10 +3886,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46125</v>
+        <v>46153</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3897,7 +3902,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3940,7 +3945,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 25388-2023</t>
+          <t>A 62496-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3954,10 +3959,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45089</v>
+        <v>45268</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3970,7 +3975,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4013,7 +4018,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 10940-2024</t>
+          <t>A 25385-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4027,10 +4032,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45370</v>
+        <v>45089</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4043,7 +4048,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4086,7 +4091,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 22134-2026</t>
+          <t>A 18503-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4100,10 +4105,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46153</v>
+        <v>46127</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4116,7 +4121,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>4.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4159,7 +4164,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 7016-2025</t>
+          <t>A 10819-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4173,10 +4178,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45701</v>
+        <v>46078</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4188,13 +4193,8 @@
           <t>ESLÖV</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>2.3</v>
+        <v>4.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4237,7 +4237,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 18503-2026</t>
+          <t>A 34170-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4251,10 +4251,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46127</v>
+        <v>45138</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4310,7 +4310,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 10819-2026</t>
+          <t>A 1574-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4324,10 +4324,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46078</v>
+        <v>45306</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>4.9</v>
+        <v>3.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4383,7 +4383,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 1574-2024</t>
+          <t>A 15357-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4397,10 +4397,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45306</v>
+        <v>45019</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4456,7 +4456,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 25730-2026</t>
+          <t>A 36761-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4470,10 +4470,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46178</v>
+        <v>44805</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4486,7 +4486,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.4</v>
+        <v>4.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4529,7 +4529,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 16670-2025</t>
+          <t>A 26165-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4543,10 +4543,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45754</v>
+        <v>46181</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4602,7 +4602,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 34468-2023</t>
+          <t>A 26169-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4616,10 +4616,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45139</v>
+        <v>46181</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4675,7 +4675,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 26165-2026</t>
+          <t>A 26497-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46181</v>
+        <v>46183</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 26169-2026</t>
+          <t>A 27439-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4762,10 +4762,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46181</v>
+        <v>46189</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4821,7 +4821,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 26497-2026</t>
+          <t>A 27428-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4835,10 +4835,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46183</v>
+        <v>46189</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4894,7 +4894,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 27428-2026</t>
+          <t>A 27435-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4911,7 +4911,7 @@
         <v>46189</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4967,7 +4967,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 27439-2026</t>
+          <t>A 34468-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4981,10 +4981,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46189</v>
+        <v>45139</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.6</v>
+        <v>5.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5040,7 +5040,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 27435-2026</t>
+          <t>A 10940-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5054,10 +5054,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46189</v>
+        <v>45370</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5113,7 +5113,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 62496-2023</t>
+          <t>A 11221-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5127,10 +5127,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45268</v>
+        <v>45371</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.6</v>
+        <v>0.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5186,7 +5186,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 34170-2023</t>
+          <t>A 43808-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5196,14 +5196,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45138</v>
+        <v>45571</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>5.8</v>
+        <v>1.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5259,7 +5259,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 24115-2022</t>
+          <t>A 9484-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5273,10 +5273,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44725</v>
+        <v>44981</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4.4</v>
+        <v>1.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5332,7 +5332,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 9484-2023</t>
+          <t>A 44496-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5346,10 +5346,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44981</v>
+        <v>45189</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5405,7 +5405,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 16733-2023</t>
+          <t>A 33865-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5419,10 +5419,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45030</v>
+        <v>45520</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5478,7 +5478,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 44496-2023</t>
+          <t>A 16670-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5492,10 +5492,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45189</v>
+        <v>45754</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5568,7 +5568,7 @@
         <v>45139</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 33865-2024</t>
+          <t>A 58721-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45520</v>
+        <v>45986</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5697,7 +5697,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 5812-2022</t>
+          <t>A 38173-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44596</v>
+        <v>45161</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5770,7 +5770,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 38173-2023</t>
+          <t>A 25508-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5784,10 +5784,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45161</v>
+        <v>45089</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.8</v>
+        <v>0.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5843,7 +5843,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 15357-2023</t>
+          <t>A 49137-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5857,10 +5857,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45019</v>
+        <v>45594</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5913,10 +5913,10 @@
       </c>
       <c r="V67" s="2" t="inlineStr"/>
     </row>
-    <row r="68" ht="15" customHeight="1">
+    <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 58721-2025</t>
+          <t>A 32984-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5930,10 +5930,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45986</v>
+        <v>45517</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5985,79 +5985,6 @@
         <v>0</v>
       </c>
       <c r="V68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>A 49137-2024</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D69" s="1" t="n">
-        <v>45594</v>
-      </c>
-      <c r="E69" s="1" t="n">
-        <v>46309</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>ESLÖV</t>
-        </is>
-      </c>
-      <c r="I69" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J69" t="n">
-        <v>0</v>
-      </c>
-      <c r="K69" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" t="n">
-        <v>0</v>
-      </c>
-      <c r="M69" t="n">
-        <v>0</v>
-      </c>
-      <c r="N69" t="n">
-        <v>0</v>
-      </c>
-      <c r="O69" t="n">
-        <v>0</v>
-      </c>
-      <c r="P69" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
-      <c r="R69" t="n">
-        <v>0</v>
-      </c>
-      <c r="S69" t="n">
-        <v>0</v>
-      </c>
-      <c r="T69" t="n">
-        <v>0</v>
-      </c>
-      <c r="U69" t="n">
-        <v>0</v>
-      </c>
-      <c r="V69" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ESLÖV.xlsx
+++ b/Översikt ESLÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45307</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45615</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44960</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>44846</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>45817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 23773-2025</t>
+          <t>A 14395-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1164,10 +1164,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45793</v>
+        <v>46100</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1225,38 +1225,38 @@
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 23773-2025 artfynd.xlsx", "A 23773-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14395-2026 artfynd.xlsx", "A 14395-2026")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 23773-2025 karta.png", "A 23773-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14395-2026 karta.png", "A 14395-2026")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 23773-2025 georefererad karta.tif", "A 23773-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14395-2026 georefererad karta.tif", "A 14395-2026")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 23773-2025 FSC-klagomål.docx", "A 23773-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14395-2026 FSC-klagomål.docx", "A 14395-2026")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 23773-2025 FSC-klagomål mail.docx", "A 23773-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14395-2026 FSC-klagomål mail.docx", "A 14395-2026")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 23773-2025 tillsynsbegäran.docx", "A 23773-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14395-2026 tillsynsbegäran.docx", "A 14395-2026")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 23773-2025 tillsynsbegäran mail.docx", "A 23773-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14395-2026 tillsynsbegäran mail.docx", "A 14395-2026")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 14395-2026</t>
+          <t>A 9487-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46100</v>
+        <v>44981</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4.9</v>
+        <v>1.9</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1295,13 +1295,13 @@
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1313,155 +1313,155 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
       </c>
       <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Älg
+Kambräken</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 9487-2023 artfynd.xlsx", "A 9487-2023")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 9487-2023 karta.png", "A 9487-2023")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 9487-2023 georefererad karta.tif", "A 9487-2023")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 9487-2023 FSC-klagomål.docx", "A 9487-2023")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 9487-2023 FSC-klagomål mail.docx", "A 9487-2023")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 9487-2023 tillsynsbegäran.docx", "A 9487-2023")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 9487-2023 tillsynsbegäran mail.docx", "A 9487-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 23773-2025</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45793</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ESLÖV</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
         <v>4</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Ask
 Kransrams</t>
         </is>
       </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14395-2026 artfynd.xlsx", "A 14395-2026")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14395-2026 karta.png", "A 14395-2026")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14395-2026 georefererad karta.tif", "A 14395-2026")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14395-2026 FSC-klagomål.docx", "A 14395-2026")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14395-2026 FSC-klagomål mail.docx", "A 14395-2026")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14395-2026 tillsynsbegäran.docx", "A 14395-2026")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14395-2026 tillsynsbegäran mail.docx", "A 14395-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 9487-2023</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>44981</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46310</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>ESLÖV</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Älg
-Kambräken</t>
-        </is>
-      </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 9487-2023 artfynd.xlsx", "A 9487-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 23773-2025 artfynd.xlsx", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 9487-2023 karta.png", "A 9487-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 23773-2025 karta.png", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 9487-2023 georefererad karta.tif", "A 9487-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 23773-2025 georefererad karta.tif", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 9487-2023 FSC-klagomål.docx", "A 9487-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 23773-2025 FSC-klagomål.docx", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 9487-2023 FSC-klagomål mail.docx", "A 9487-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 23773-2025 FSC-klagomål mail.docx", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 9487-2023 tillsynsbegäran.docx", "A 9487-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 23773-2025 tillsynsbegäran.docx", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 9487-2023 tillsynsbegäran mail.docx", "A 9487-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 23773-2025 tillsynsbegäran mail.docx", "A 23773-2025")</f>
         <v/>
       </c>
     </row>
@@ -1485,7 +1485,7 @@
         <v>45799</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>46098</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>45645</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>45306</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>45225</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>45426</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>44553</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>44690</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>45411</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 28088-2025</t>
+          <t>A 36761-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45817</v>
+        <v>44805</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>4.8</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 25388-2023</t>
+          <t>A 12079-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45089</v>
+        <v>45377</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.5</v>
+        <v>6.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 12079-2024</t>
+          <t>A 15533-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45377</v>
+        <v>45401</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 47356-2025</t>
+          <t>A 28088-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45930</v>
+        <v>45817</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2626,7 +2626,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 9849-2026</t>
+          <t>A 11221-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46072</v>
+        <v>45371</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.5</v>
+        <v>0.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2699,7 +2699,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 16733-2023</t>
+          <t>A 15467-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45030</v>
+        <v>45747</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2772,7 +2772,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 11204-2023</t>
+          <t>A 25388-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44992</v>
+        <v>45089</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 35996-2025</t>
+          <t>A 5869-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2855,14 +2855,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45863</v>
+        <v>44958</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2918,7 +2918,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 35997-2025</t>
+          <t>A 10940-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45863</v>
+        <v>45370</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2991,7 +2991,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 14386-2026</t>
+          <t>A 9482-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46100</v>
+        <v>44981</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>12.4</v>
+        <v>3.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3064,7 +3064,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 5812-2022</t>
+          <t>A 25385-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3078,10 +3078,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44596</v>
+        <v>45089</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3137,7 +3137,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 18281-2026</t>
+          <t>A 43808-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3147,14 +3147,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46125</v>
+        <v>45571</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3210,7 +3210,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 15467-2025</t>
+          <t>A 14386-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45747</v>
+        <v>46100</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.4</v>
+        <v>12.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3283,7 +3283,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 5869-2023</t>
+          <t>A 18281-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3293,14 +3293,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44958</v>
+        <v>46125</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 7409-2025</t>
+          <t>A 7016-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45705</v>
+        <v>45701</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3385,8 +3385,13 @@
           <t>ESLÖV</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3429,7 +3434,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 9686-2023</t>
+          <t>A 11204-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3443,10 +3448,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44984</v>
+        <v>44992</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3459,7 +3464,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3502,7 +3507,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 7016-2025</t>
+          <t>A 25508-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3516,10 +3521,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45701</v>
+        <v>45089</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3531,13 +3536,8 @@
           <t>ESLÖV</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>2.3</v>
+        <v>0.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3580,7 +3580,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 47870-2025</t>
+          <t>A 9686-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3594,10 +3594,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45932</v>
+        <v>44984</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>6.8</v>
+        <v>0.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3653,7 +3653,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 24115-2022</t>
+          <t>A 16670-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3667,10 +3667,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44725</v>
+        <v>45754</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.4</v>
+        <v>1.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3726,7 +3726,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 9482-2023</t>
+          <t>A 34468-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3740,10 +3740,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44981</v>
+        <v>45139</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3799,7 +3799,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 15533-2024</t>
+          <t>A 7409-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45401</v>
+        <v>45705</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>7.5</v>
+        <v>1.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3889,7 +3889,7 @@
         <v>46153</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 62496-2023</t>
+          <t>A 18503-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3959,10 +3959,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45268</v>
+        <v>46127</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.6</v>
+        <v>4.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4018,7 +4018,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 25385-2023</t>
+          <t>A 62496-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4032,10 +4032,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45089</v>
+        <v>45268</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4091,7 +4091,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 18503-2026</t>
+          <t>A 10819-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46127</v>
+        <v>46078</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 10819-2026</t>
+          <t>A 1574-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4178,10 +4178,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46078</v>
+        <v>45306</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4.9</v>
+        <v>3.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4237,7 +4237,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 34170-2023</t>
+          <t>A 47356-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4251,10 +4251,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45138</v>
+        <v>45930</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>5.8</v>
+        <v>0.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4310,7 +4310,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 1574-2024</t>
+          <t>A 34170-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4324,10 +4324,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45306</v>
+        <v>45138</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.6</v>
+        <v>5.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4383,7 +4383,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 15357-2023</t>
+          <t>A 24115-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4397,10 +4397,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45019</v>
+        <v>44725</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>4.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4456,7 +4456,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 36761-2022</t>
+          <t>A 26165-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4470,10 +4470,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44805</v>
+        <v>46181</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4486,7 +4486,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>4.8</v>
+        <v>2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4529,7 +4529,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 26165-2026</t>
+          <t>A 26169-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4546,7 +4546,7 @@
         <v>46181</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4602,7 +4602,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 26169-2026</t>
+          <t>A 26497-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4616,10 +4616,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46181</v>
+        <v>46183</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4675,7 +4675,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 26497-2026</t>
+          <t>A 27428-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46183</v>
+        <v>46189</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4765,7 +4765,7 @@
         <v>46189</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 27428-2026</t>
+          <t>A 27435-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4838,7 +4838,7 @@
         <v>46189</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4894,7 +4894,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 27435-2026</t>
+          <t>A 9484-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46189</v>
+        <v>44981</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4967,7 +4967,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 34468-2023</t>
+          <t>A 16733-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4981,10 +4981,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45139</v>
+        <v>45030</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>5.5</v>
+        <v>2.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5040,7 +5040,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 10940-2024</t>
+          <t>A 44496-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5054,10 +5054,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45370</v>
+        <v>45189</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 11221-2024</t>
+          <t>A 35996-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5127,10 +5127,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45371</v>
+        <v>45863</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5186,7 +5186,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 43808-2024</t>
+          <t>A 35997-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5196,14 +5196,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45571</v>
+        <v>45863</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5259,7 +5259,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 9484-2023</t>
+          <t>A 34466-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5273,10 +5273,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44981</v>
+        <v>45139</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.4</v>
+        <v>4.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5332,7 +5332,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 44496-2023</t>
+          <t>A 33865-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5346,10 +5346,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45189</v>
+        <v>45520</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5405,7 +5405,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 33865-2024</t>
+          <t>A 5812-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5419,10 +5419,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45520</v>
+        <v>44596</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5478,7 +5478,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 16670-2025</t>
+          <t>A 38173-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5492,10 +5492,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45754</v>
+        <v>45161</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5551,7 +5551,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 34466-2023</t>
+          <t>A 15357-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45139</v>
+        <v>45019</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4.3</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5641,7 +5641,7 @@
         <v>45986</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 38173-2023</t>
+          <t>A 49137-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45161</v>
+        <v>45594</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5770,7 +5770,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 25508-2023</t>
+          <t>A 32984-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5784,10 +5784,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45089</v>
+        <v>45517</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5843,7 +5843,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 49137-2024</t>
+          <t>A 47870-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5857,10 +5857,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45594</v>
+        <v>45932</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.4</v>
+        <v>6.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5916,7 +5916,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 32984-2024</t>
+          <t>A 9849-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5930,10 +5930,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45517</v>
+        <v>46072</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>

--- a/Översikt ESLÖV.xlsx
+++ b/Översikt ESLÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45307</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45615</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44960</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>44846</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>45817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>46100</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>44981</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>45793</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 24809-2025</t>
+          <t>A 61035-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1482,10 +1482,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45799</v>
+        <v>45645</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1498,17 +1498,17 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.4</v>
+        <v>7.6</v>
       </c>
       <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1531,46 +1531,42 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 24809-2025 artfynd.xlsx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 61035-2024 artfynd.xlsx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 24809-2025 karta.png", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 61035-2024 karta.png", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 24809-2025 georefererad karta.tif", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 61035-2024 georefererad karta.tif", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 24809-2025 FSC-klagomål.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 61035-2024 FSC-klagomål.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 24809-2025 FSC-klagomål mail.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 61035-2024 FSC-klagomål mail.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 24809-2025 tillsynsbegäran.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 61035-2024 tillsynsbegäran.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 24809-2025 tillsynsbegäran mail.docx", "A 24809-2025")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 24809-2025 prioriterade fågelarter.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 61035-2024 tillsynsbegäran mail.docx", "A 61035-2024")</f>
         <v/>
       </c>
     </row>
@@ -1594,7 +1590,7 @@
         <v>46098</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1691,7 +1687,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 61035-2024</t>
+          <t>A 1510-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1705,10 +1701,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45645</v>
+        <v>45306</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1721,28 +1717,28 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>7.6</v>
+        <v>3.7</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
         <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
@@ -1754,49 +1750,53 @@
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Svart stork</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 61035-2024 artfynd.xlsx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 1510-2024 artfynd.xlsx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 61035-2024 karta.png", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 1510-2024 karta.png", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 61035-2024 georefererad karta.tif", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 1510-2024 georefererad karta.tif", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 61035-2024 FSC-klagomål.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 1510-2024 FSC-klagomål.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 61035-2024 FSC-klagomål mail.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 1510-2024 FSC-klagomål mail.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 61035-2024 tillsynsbegäran.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 1510-2024 tillsynsbegäran.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 61035-2024 tillsynsbegäran mail.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 1510-2024 tillsynsbegäran mail.docx", "A 1510-2024")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 1510-2024 prioriterade fågelarter.docx", "A 1510-2024")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 1510-2024</t>
+          <t>A 52652-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1810,10 +1810,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45306</v>
+        <v>45225</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1838,7 +1838,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1847,13 +1847,13 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1866,46 +1866,42 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Svart stork</t>
+          <t>Grönfläckig padda</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 1510-2024 artfynd.xlsx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 52652-2023 artfynd.xlsx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 1510-2024 karta.png", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 52652-2023 karta.png", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 1510-2024 georefererad karta.tif", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 52652-2023 georefererad karta.tif", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 1510-2024 FSC-klagomål.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 52652-2023 FSC-klagomål.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 1510-2024 FSC-klagomål mail.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 52652-2023 FSC-klagomål mail.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 1510-2024 tillsynsbegäran.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 52652-2023 tillsynsbegäran.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 1510-2024 tillsynsbegäran mail.docx", "A 1510-2024")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 1510-2024 prioriterade fågelarter.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 52652-2023 tillsynsbegäran mail.docx", "A 52652-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 52652-2023</t>
+          <t>A 18713-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1919,10 +1915,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45225</v>
+        <v>45426</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1935,7 +1931,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1975,42 +1971,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Grönfläckig padda</t>
+          <t>Gråtrut</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 52652-2023 artfynd.xlsx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 18713-2024 artfynd.xlsx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 52652-2023 karta.png", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 18713-2024 karta.png", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 52652-2023 georefererad karta.tif", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 18713-2024 georefererad karta.tif", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 52652-2023 FSC-klagomål.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 18713-2024 FSC-klagomål.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 52652-2023 FSC-klagomål mail.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 18713-2024 FSC-klagomål mail.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 52652-2023 tillsynsbegäran.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 18713-2024 tillsynsbegäran.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 52652-2023 tillsynsbegäran mail.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 18713-2024 tillsynsbegäran mail.docx", "A 18713-2024")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 18713-2024</t>
+          <t>A 24809-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2024,10 +2020,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45426</v>
+        <v>45799</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2040,7 +2036,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>4.1</v>
+        <v>1.4</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2052,7 +2048,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2064,10 +2060,10 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2080,35 +2076,39 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Gråtrut</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 18713-2024 artfynd.xlsx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 24809-2025 artfynd.xlsx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 18713-2024 karta.png", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 24809-2025 karta.png", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 18713-2024 georefererad karta.tif", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 24809-2025 georefererad karta.tif", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 18713-2024 FSC-klagomål.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 24809-2025 FSC-klagomål.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 18713-2024 FSC-klagomål mail.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 24809-2025 FSC-klagomål mail.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 18713-2024 tillsynsbegäran.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 24809-2025 tillsynsbegäran.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 18713-2024 tillsynsbegäran mail.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 24809-2025 tillsynsbegäran mail.docx", "A 24809-2025")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 24809-2025 prioriterade fågelarter.docx", "A 24809-2025")</f>
         <v/>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
         <v>44553</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>44690</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 16792-2024</t>
+          <t>A 16733-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45411</v>
+        <v>45030</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2334,7 +2334,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 36761-2022</t>
+          <t>A 5812-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44805</v>
+        <v>44596</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>4.8</v>
+        <v>0.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 12079-2024</t>
+          <t>A 15467-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45377</v>
+        <v>45747</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>6.9</v>
+        <v>1.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 15533-2024</t>
+          <t>A 5869-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2490,14 +2490,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45401</v>
+        <v>44958</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>7.5</v>
+        <v>3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 28088-2025</t>
+          <t>A 7409-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45817</v>
+        <v>45705</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2626,7 +2626,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 11221-2024</t>
+          <t>A 9686-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45371</v>
+        <v>44984</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2699,7 +2699,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 15467-2025</t>
+          <t>A 7016-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45747</v>
+        <v>45701</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2728,8 +2728,13 @@
           <t>ESLÖV</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2772,7 +2777,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 25388-2023</t>
+          <t>A 24115-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2786,10 +2791,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45089</v>
+        <v>44725</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2802,7 +2807,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.5</v>
+        <v>4.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2845,7 +2850,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 5869-2023</t>
+          <t>A 47356-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2855,14 +2860,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44958</v>
+        <v>45930</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2875,7 +2880,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2918,7 +2923,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 10940-2024</t>
+          <t>A 22134-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2932,10 +2937,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45370</v>
+        <v>46153</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2948,7 +2953,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2991,7 +2996,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 9482-2023</t>
+          <t>A 25388-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3005,10 +3010,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44981</v>
+        <v>45089</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3021,7 +3026,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3064,7 +3069,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 25385-2023</t>
+          <t>A 35996-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3078,10 +3083,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45089</v>
+        <v>45863</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3094,7 +3099,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3137,7 +3142,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 43808-2024</t>
+          <t>A 35997-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3147,14 +3152,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45571</v>
+        <v>45863</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3167,7 +3172,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3210,7 +3215,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 14386-2026</t>
+          <t>A 12079-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3224,10 +3229,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46100</v>
+        <v>45377</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3240,7 +3245,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>12.4</v>
+        <v>6.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3283,7 +3288,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 18281-2026</t>
+          <t>A 18503-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3297,10 +3302,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3313,7 +3318,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.8</v>
+        <v>4.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3356,7 +3361,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 7016-2025</t>
+          <t>A 11204-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3370,10 +3375,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45701</v>
+        <v>44992</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3385,13 +3390,8 @@
           <t>ESLÖV</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3434,7 +3434,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 11204-2023</t>
+          <t>A 10819-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3448,10 +3448,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44992</v>
+        <v>46078</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.7</v>
+        <v>4.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3507,7 +3507,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 25508-2023</t>
+          <t>A 9482-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45089</v>
+        <v>44981</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.4</v>
+        <v>3.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3580,7 +3580,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 9686-2023</t>
+          <t>A 15533-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3594,10 +3594,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44984</v>
+        <v>45401</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.8</v>
+        <v>7.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3653,7 +3653,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 16670-2025</t>
+          <t>A 1574-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3667,10 +3667,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45754</v>
+        <v>45306</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3726,7 +3726,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 34468-2023</t>
+          <t>A 62496-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3740,10 +3740,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45139</v>
+        <v>45268</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>5.5</v>
+        <v>2.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3799,7 +3799,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 7409-2025</t>
+          <t>A 47870-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45705</v>
+        <v>45932</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.5</v>
+        <v>6.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3872,7 +3872,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 22134-2026</t>
+          <t>A 25385-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3886,10 +3886,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46153</v>
+        <v>45089</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3945,7 +3945,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 18503-2026</t>
+          <t>A 26165-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3959,10 +3959,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46127</v>
+        <v>46181</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>4.9</v>
+        <v>2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4018,7 +4018,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 62496-2023</t>
+          <t>A 26169-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4032,10 +4032,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45268</v>
+        <v>46181</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4091,7 +4091,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 10819-2026</t>
+          <t>A 34170-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46078</v>
+        <v>45138</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4164,7 +4164,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 1574-2024</t>
+          <t>A 26497-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4178,10 +4178,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45306</v>
+        <v>46183</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.6</v>
+        <v>1.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4237,7 +4237,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 47356-2025</t>
+          <t>A 15357-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4251,10 +4251,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45930</v>
+        <v>45019</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4310,7 +4310,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 34170-2023</t>
+          <t>A 36761-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4324,10 +4324,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45138</v>
+        <v>44805</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4383,7 +4383,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 24115-2022</t>
+          <t>A 9849-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4397,10 +4397,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44725</v>
+        <v>46072</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4456,7 +4456,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 26165-2026</t>
+          <t>A 27439-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4470,10 +4470,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46181</v>
+        <v>46189</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4486,7 +4486,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4529,7 +4529,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 26169-2026</t>
+          <t>A 27428-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4543,10 +4543,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46181</v>
+        <v>46189</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4602,7 +4602,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 26497-2026</t>
+          <t>A 27435-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4616,10 +4616,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46183</v>
+        <v>46189</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4675,7 +4675,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 27428-2026</t>
+          <t>A 34468-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46189</v>
+        <v>45139</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 27439-2026</t>
+          <t>A 14386-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4762,10 +4762,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46189</v>
+        <v>46100</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.6</v>
+        <v>12.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4821,7 +4821,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 27435-2026</t>
+          <t>A 18281-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4835,10 +4835,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46189</v>
+        <v>46125</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4894,7 +4894,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 9484-2023</t>
+          <t>A 10940-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44981</v>
+        <v>45370</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4967,7 +4967,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 16733-2023</t>
+          <t>A 11221-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4981,10 +4981,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45030</v>
+        <v>45371</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.6</v>
+        <v>0.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5040,7 +5040,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 44496-2023</t>
+          <t>A 43808-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5050,14 +5050,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45189</v>
+        <v>45571</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5113,7 +5113,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 35996-2025</t>
+          <t>A 9484-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5127,10 +5127,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45863</v>
+        <v>44981</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5186,7 +5186,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 35997-2025</t>
+          <t>A 44496-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5200,10 +5200,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45863</v>
+        <v>45189</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5259,7 +5259,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 34466-2023</t>
+          <t>A 33865-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5273,10 +5273,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45139</v>
+        <v>45520</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4.3</v>
+        <v>1.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5332,7 +5332,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 33865-2024</t>
+          <t>A 16670-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5346,10 +5346,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45520</v>
+        <v>45754</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5405,7 +5405,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 5812-2022</t>
+          <t>A 34466-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5419,10 +5419,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44596</v>
+        <v>45139</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>4.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5495,7 +5495,7 @@
         <v>45161</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 15357-2023</t>
+          <t>A 58721-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45019</v>
+        <v>45986</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5624,7 +5624,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 58721-2025</t>
+          <t>A 25508-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45986</v>
+        <v>45089</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>45594</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>45517</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 47870-2025</t>
+          <t>A 16792-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5857,10 +5857,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45932</v>
+        <v>45411</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>6.8</v>
+        <v>0.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5916,7 +5916,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 9849-2026</t>
+          <t>A 28088-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5930,10 +5930,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46072</v>
+        <v>45817</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>

--- a/Översikt ESLÖV.xlsx
+++ b/Översikt ESLÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45307</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45615</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44960</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>44846</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>45817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>46100</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>44981</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>45793</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>45645</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>46098</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>45306</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>45225</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>45426</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>45799</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>44553</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>44690</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>45030</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>44596</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>45747</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>44958</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>45705</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>44984</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>45701</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>44725</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>45930</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>46153</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>45089</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>45863</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>45863</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>45377</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>46127</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>44992</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         <v>46078</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>44981</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>45401</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         <v>45306</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>45268</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         <v>45932</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         <v>45089</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>46181</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         <v>46181</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>45138</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>46183</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>45019</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>44805</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>46072</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>46189</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>46189</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>46189</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>45139</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>46100</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         <v>46125</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>45370</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>45371</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         <v>45571</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>44981</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>45189</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>45520</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         <v>45754</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         <v>45139</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         <v>45161</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>45986</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>45089</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         <v>45594</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>45517</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>45411</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>45817</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>

--- a/Översikt ESLÖV.xlsx
+++ b/Översikt ESLÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45307</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45615</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44960</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>44846</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>45817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>46100</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>44981</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>45793</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>45645</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>46098</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>45306</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>45225</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>45426</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>45799</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>44553</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>44690</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>45030</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>44596</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>45747</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>44958</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>45705</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>44984</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>45701</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>44725</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>45930</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>46153</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>45089</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>45863</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>45863</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>45377</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>46127</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>44992</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         <v>46078</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>44981</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>45401</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         <v>45306</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>45268</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         <v>45932</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         <v>45089</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>46181</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         <v>46181</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>45138</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>46183</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>45019</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>44805</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>46072</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>46189</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>46189</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>46189</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>45139</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>46100</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         <v>46125</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>45370</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>45371</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         <v>45571</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>44981</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>45189</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>45520</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         <v>45754</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         <v>45139</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         <v>45161</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>45986</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>45089</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         <v>45594</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>45517</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>45411</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>45817</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>

--- a/Översikt ESLÖV.xlsx
+++ b/Översikt ESLÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45307</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45615</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44960</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>44846</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>45817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>46100</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>44981</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>45793</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>45645</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>46098</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>45306</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>45225</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>45426</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>45799</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>44553</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>44690</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 16733-2023</t>
+          <t>A 12079-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45030</v>
+        <v>45377</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.6</v>
+        <v>6.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2334,7 +2334,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 5812-2022</t>
+          <t>A 15533-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44596</v>
+        <v>45401</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.5</v>
+        <v>7.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 15467-2025</t>
+          <t>A 11221-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45747</v>
+        <v>45371</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.4</v>
+        <v>0.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 5869-2023</t>
+          <t>A 15467-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2490,14 +2490,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44958</v>
+        <v>45747</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 7409-2025</t>
+          <t>A 5869-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2563,14 +2563,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45705</v>
+        <v>44958</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2626,7 +2626,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 9686-2023</t>
+          <t>A 9482-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44984</v>
+        <v>44981</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2699,7 +2699,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 7016-2025</t>
+          <t>A 25385-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45701</v>
+        <v>45089</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2728,13 +2728,8 @@
           <t>ESLÖV</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2777,7 +2772,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 24115-2022</t>
+          <t>A 43808-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2787,14 +2782,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44725</v>
+        <v>45571</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2807,7 +2802,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>4.4</v>
+        <v>1.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2850,7 +2845,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 47356-2025</t>
+          <t>A 11204-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2864,10 +2859,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45930</v>
+        <v>44992</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2880,7 +2875,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2923,7 +2918,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 22134-2026</t>
+          <t>A 25508-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2937,10 +2932,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46153</v>
+        <v>45089</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2953,7 +2948,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2996,7 +2991,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 25388-2023</t>
+          <t>A 9686-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3010,10 +3005,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45089</v>
+        <v>44984</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3026,7 +3021,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3069,7 +3064,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 35996-2025</t>
+          <t>A 7409-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3083,10 +3078,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45863</v>
+        <v>45705</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3099,7 +3094,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3142,7 +3137,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 35997-2025</t>
+          <t>A 36761-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3156,10 +3151,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45863</v>
+        <v>44805</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3172,7 +3167,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.9</v>
+        <v>4.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3215,7 +3210,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 12079-2024</t>
+          <t>A 47356-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3229,10 +3224,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45377</v>
+        <v>45930</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3245,7 +3240,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>6.9</v>
+        <v>0.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3288,7 +3283,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 18503-2026</t>
+          <t>A 25388-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3302,10 +3297,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46127</v>
+        <v>45089</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3318,7 +3313,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>4.9</v>
+        <v>0.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3361,7 +3356,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 11204-2023</t>
+          <t>A 35996-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3375,10 +3370,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44992</v>
+        <v>45863</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3391,7 +3386,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3434,7 +3429,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 10819-2026</t>
+          <t>A 35997-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3448,10 +3443,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46078</v>
+        <v>45863</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3464,7 +3459,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4.9</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3507,7 +3502,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 9482-2023</t>
+          <t>A 22134-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3521,10 +3516,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44981</v>
+        <v>46153</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3537,7 +3532,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3580,7 +3575,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 15533-2024</t>
+          <t>A 10940-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3594,10 +3589,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45401</v>
+        <v>45370</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3610,7 +3605,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>7.5</v>
+        <v>0.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3653,7 +3648,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 1574-2024</t>
+          <t>A 18503-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3667,10 +3662,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45306</v>
+        <v>46127</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3683,7 +3678,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3726,7 +3721,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 62496-2023</t>
+          <t>A 10819-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3740,10 +3735,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45268</v>
+        <v>46078</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3756,7 +3751,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.6</v>
+        <v>4.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3799,7 +3794,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 47870-2025</t>
+          <t>A 1574-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3813,10 +3808,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45932</v>
+        <v>45306</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3829,7 +3824,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>6.8</v>
+        <v>3.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3872,7 +3867,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 25385-2023</t>
+          <t>A 47870-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3886,10 +3881,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45089</v>
+        <v>45932</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3902,7 +3897,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.7</v>
+        <v>6.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3945,7 +3940,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 26165-2026</t>
+          <t>A 7016-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3959,10 +3954,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46181</v>
+        <v>45701</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3974,8 +3969,13 @@
           <t>ESLÖV</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4018,7 +4018,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 26169-2026</t>
+          <t>A 26165-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4035,7 +4035,7 @@
         <v>46181</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4091,7 +4091,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 34170-2023</t>
+          <t>A 26169-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45138</v>
+        <v>46181</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>5.8</v>
+        <v>3.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
         <v>46183</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 15357-2023</t>
+          <t>A 9849-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4251,10 +4251,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45019</v>
+        <v>46072</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4310,7 +4310,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 36761-2022</t>
+          <t>A 16670-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4324,10 +4324,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44805</v>
+        <v>45754</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>4.8</v>
+        <v>1.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4383,7 +4383,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 9849-2026</t>
+          <t>A 34468-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4397,10 +4397,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46072</v>
+        <v>45139</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4456,7 +4456,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 27439-2026</t>
+          <t>A 27428-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4473,7 +4473,7 @@
         <v>46189</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4486,7 +4486,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4529,7 +4529,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 27428-2026</t>
+          <t>A 27439-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4546,7 +4546,7 @@
         <v>46189</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.4</v>
+        <v>1.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4619,7 +4619,7 @@
         <v>46189</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 34468-2023</t>
+          <t>A 14386-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45139</v>
+        <v>46100</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>5.5</v>
+        <v>12.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 14386-2026</t>
+          <t>A 62496-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4762,10 +4762,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46100</v>
+        <v>45268</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>12.4</v>
+        <v>2.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4838,7 +4838,7 @@
         <v>46125</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 10940-2024</t>
+          <t>A 34170-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45370</v>
+        <v>45138</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.5</v>
+        <v>5.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4967,7 +4967,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 11221-2024</t>
+          <t>A 24115-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4981,10 +4981,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45371</v>
+        <v>44725</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.3</v>
+        <v>4.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5040,7 +5040,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 43808-2024</t>
+          <t>A 9484-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5050,14 +5050,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45571</v>
+        <v>44981</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5113,7 +5113,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 9484-2023</t>
+          <t>A 16733-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5127,10 +5127,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44981</v>
+        <v>45030</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5203,7 +5203,7 @@
         <v>45189</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 33865-2024</t>
+          <t>A 34466-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5273,10 +5273,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45520</v>
+        <v>45139</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.3</v>
+        <v>4.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5332,7 +5332,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 16670-2025</t>
+          <t>A 33865-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5346,10 +5346,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45754</v>
+        <v>45520</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5405,7 +5405,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 34466-2023</t>
+          <t>A 5812-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5419,10 +5419,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45139</v>
+        <v>44596</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4.3</v>
+        <v>0.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5495,7 +5495,7 @@
         <v>45161</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>45986</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 25508-2023</t>
+          <t>A 15357-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45089</v>
+        <v>45019</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>45594</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>45517</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>45411</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>45817</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>

--- a/Översikt ESLÖV.xlsx
+++ b/Översikt ESLÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45307</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45615</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44960</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>44846</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>45817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 14395-2026</t>
+          <t>A 23773-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1164,10 +1164,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46100</v>
+        <v>45793</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1225,38 +1225,38 @@
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14395-2026 artfynd.xlsx", "A 14395-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 23773-2025 artfynd.xlsx", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14395-2026 karta.png", "A 14395-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 23773-2025 karta.png", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14395-2026 georefererad karta.tif", "A 14395-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 23773-2025 georefererad karta.tif", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14395-2026 FSC-klagomål.docx", "A 14395-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 23773-2025 FSC-klagomål.docx", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14395-2026 FSC-klagomål mail.docx", "A 14395-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 23773-2025 FSC-klagomål mail.docx", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14395-2026 tillsynsbegäran.docx", "A 14395-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 23773-2025 tillsynsbegäran.docx", "A 23773-2025")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14395-2026 tillsynsbegäran mail.docx", "A 14395-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 23773-2025 tillsynsbegäran mail.docx", "A 23773-2025")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 9487-2023</t>
+          <t>A 14395-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44981</v>
+        <v>46100</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.9</v>
+        <v>4.9</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1295,13 +1295,13 @@
         <v>1</v>
       </c>
       <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
         <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1313,162 +1313,162 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
       </c>
       <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Kransrams</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14395-2026 artfynd.xlsx", "A 14395-2026")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14395-2026 karta.png", "A 14395-2026")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14395-2026 georefererad karta.tif", "A 14395-2026")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14395-2026 FSC-klagomål.docx", "A 14395-2026")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14395-2026 FSC-klagomål mail.docx", "A 14395-2026")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14395-2026 tillsynsbegäran.docx", "A 14395-2026")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14395-2026 tillsynsbegäran mail.docx", "A 14395-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 9487-2023</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>44981</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ESLÖV</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
         <v>2</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Älg
 Kambräken</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 9487-2023 artfynd.xlsx", "A 9487-2023")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 9487-2023 karta.png", "A 9487-2023")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 9487-2023 georefererad karta.tif", "A 9487-2023")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 9487-2023 FSC-klagomål.docx", "A 9487-2023")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 9487-2023 FSC-klagomål mail.docx", "A 9487-2023")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 9487-2023 tillsynsbegäran.docx", "A 9487-2023")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 9487-2023 tillsynsbegäran mail.docx", "A 9487-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 23773-2025</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45793</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46315</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>ESLÖV</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>4</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Kransrams</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 23773-2025 artfynd.xlsx", "A 23773-2025")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 23773-2025 karta.png", "A 23773-2025")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 23773-2025 georefererad karta.tif", "A 23773-2025")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 23773-2025 FSC-klagomål.docx", "A 23773-2025")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 23773-2025 FSC-klagomål mail.docx", "A 23773-2025")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 23773-2025 tillsynsbegäran.docx", "A 23773-2025")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 23773-2025 tillsynsbegäran mail.docx", "A 23773-2025")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 61035-2024</t>
+          <t>A 18713-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1482,10 +1482,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45645</v>
+        <v>45426</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1498,19 +1498,19 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>7.6</v>
+        <v>4.1</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
         <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1525,55 +1525,55 @@
         <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Gråtrut</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 61035-2024 artfynd.xlsx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 18713-2024 artfynd.xlsx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 61035-2024 karta.png", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 18713-2024 karta.png", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 61035-2024 georefererad karta.tif", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 18713-2024 georefererad karta.tif", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 61035-2024 FSC-klagomål.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 18713-2024 FSC-klagomål.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 61035-2024 FSC-klagomål mail.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 18713-2024 FSC-klagomål mail.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 61035-2024 tillsynsbegäran.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 18713-2024 tillsynsbegäran.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 61035-2024 tillsynsbegäran mail.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 18713-2024 tillsynsbegäran mail.docx", "A 18713-2024")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 14013-2026</t>
+          <t>A 24809-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1587,10 +1587,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46098</v>
+        <v>45799</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1602,13 +1602,8 @@
           <t>ESLÖV</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>8.800000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1644,50 +1639,50 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14013-2026 artfynd.xlsx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 24809-2025 artfynd.xlsx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14013-2026 karta.png", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 24809-2025 karta.png", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14013-2026 georefererad karta.tif", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 24809-2025 georefererad karta.tif", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14013-2026 FSC-klagomål.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 24809-2025 FSC-klagomål.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14013-2026 FSC-klagomål mail.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 24809-2025 FSC-klagomål mail.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14013-2026 tillsynsbegäran.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 24809-2025 tillsynsbegäran.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14013-2026 tillsynsbegäran mail.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 24809-2025 tillsynsbegäran mail.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 14013-2026 prioriterade fågelarter.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 24809-2025 prioriterade fågelarter.docx", "A 24809-2025")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 1510-2024</t>
+          <t>A 14013-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1701,10 +1696,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45306</v>
+        <v>46098</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1716,8 +1711,13 @@
           <t>ESLÖV</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>3.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1738,10 +1738,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1753,50 +1753,50 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Svart stork</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 1510-2024 artfynd.xlsx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14013-2026 artfynd.xlsx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 1510-2024 karta.png", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14013-2026 karta.png", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 1510-2024 georefererad karta.tif", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14013-2026 georefererad karta.tif", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 1510-2024 FSC-klagomål.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14013-2026 FSC-klagomål.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 1510-2024 FSC-klagomål mail.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14013-2026 FSC-klagomål mail.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 1510-2024 tillsynsbegäran.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14013-2026 tillsynsbegäran.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 1510-2024 tillsynsbegäran mail.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14013-2026 tillsynsbegäran mail.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 1510-2024 prioriterade fågelarter.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 14013-2026 prioriterade fågelarter.docx", "A 14013-2026")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 52652-2023</t>
+          <t>A 61035-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1810,10 +1810,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45225</v>
+        <v>45645</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1826,19 +1826,19 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.9</v>
+        <v>7.6</v>
       </c>
       <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1853,55 +1853,55 @@
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Grönfläckig padda</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 52652-2023 artfynd.xlsx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 61035-2024 artfynd.xlsx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 52652-2023 karta.png", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 61035-2024 karta.png", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 52652-2023 georefererad karta.tif", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 61035-2024 georefererad karta.tif", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 52652-2023 FSC-klagomål.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 61035-2024 FSC-klagomål.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 52652-2023 FSC-klagomål mail.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 61035-2024 FSC-klagomål mail.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 52652-2023 tillsynsbegäran.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 61035-2024 tillsynsbegäran.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 52652-2023 tillsynsbegäran mail.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 61035-2024 tillsynsbegäran mail.docx", "A 61035-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 18713-2024</t>
+          <t>A 1510-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1915,10 +1915,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45426</v>
+        <v>45306</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1943,22 +1943,22 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
         <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1971,42 +1971,46 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Gråtrut</t>
+          <t>Svart stork</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 18713-2024 artfynd.xlsx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 1510-2024 artfynd.xlsx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 18713-2024 karta.png", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 1510-2024 karta.png", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 18713-2024 georefererad karta.tif", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 1510-2024 georefererad karta.tif", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 18713-2024 FSC-klagomål.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 1510-2024 FSC-klagomål.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 18713-2024 FSC-klagomål mail.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 1510-2024 FSC-klagomål mail.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 18713-2024 tillsynsbegäran.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 1510-2024 tillsynsbegäran.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 18713-2024 tillsynsbegäran mail.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 1510-2024 tillsynsbegäran mail.docx", "A 1510-2024")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 1510-2024 prioriterade fågelarter.docx", "A 1510-2024")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 24809-2025</t>
+          <t>A 52652-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2020,10 +2024,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45799</v>
+        <v>45225</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2036,7 +2040,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2048,7 +2052,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2060,10 +2064,10 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2076,39 +2080,35 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönfläckig padda</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 24809-2025 artfynd.xlsx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 52652-2023 artfynd.xlsx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 24809-2025 karta.png", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 52652-2023 karta.png", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 24809-2025 georefererad karta.tif", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 52652-2023 georefererad karta.tif", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 24809-2025 FSC-klagomål.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 52652-2023 FSC-klagomål.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 24809-2025 FSC-klagomål mail.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 52652-2023 FSC-klagomål mail.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 24809-2025 tillsynsbegäran.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 52652-2023 tillsynsbegäran.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 24809-2025 tillsynsbegäran mail.docx", "A 24809-2025")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 24809-2025 prioriterade fågelarter.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 52652-2023 tillsynsbegäran mail.docx", "A 52652-2023")</f>
         <v/>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
         <v>44553</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>44690</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 12079-2024</t>
+          <t>A 32984-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45377</v>
+        <v>45517</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>6.9</v>
+        <v>2.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2334,7 +2334,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 15533-2024</t>
+          <t>A 16792-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45401</v>
+        <v>45411</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>7.5</v>
+        <v>0.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 11221-2024</t>
+          <t>A 47870-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45371</v>
+        <v>45932</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.3</v>
+        <v>6.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 15467-2025</t>
+          <t>A 28088-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45747</v>
+        <v>45817</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 5869-2023</t>
+          <t>A 16733-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2563,14 +2563,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44958</v>
+        <v>45030</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2626,7 +2626,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 9482-2023</t>
+          <t>A 47356-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44981</v>
+        <v>45930</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.7</v>
+        <v>0.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2699,7 +2699,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 25385-2023</t>
+          <t>A 9849-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45089</v>
+        <v>46072</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2772,7 +2772,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 43808-2024</t>
+          <t>A 5812-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2782,14 +2782,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45571</v>
+        <v>44596</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 11204-2023</t>
+          <t>A 35996-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44992</v>
+        <v>45863</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2918,7 +2918,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 25508-2023</t>
+          <t>A 35997-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45089</v>
+        <v>45863</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2991,7 +2991,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 9686-2023</t>
+          <t>A 14386-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44984</v>
+        <v>46100</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.8</v>
+        <v>12.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3064,7 +3064,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 7409-2025</t>
+          <t>A 18281-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3078,10 +3078,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45705</v>
+        <v>46125</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3137,7 +3137,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 36761-2022</t>
+          <t>A 15467-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44805</v>
+        <v>45747</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>4.8</v>
+        <v>1.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3210,7 +3210,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 47356-2025</t>
+          <t>A 5869-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3220,14 +3220,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45930</v>
+        <v>44958</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3283,7 +3283,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 25388-2023</t>
+          <t>A 7409-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45089</v>
+        <v>45705</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 35996-2025</t>
+          <t>A 9686-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45863</v>
+        <v>44984</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 35997-2025</t>
+          <t>A 7016-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45863</v>
+        <v>45701</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3458,8 +3458,13 @@
           <t>ESLÖV</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3502,7 +3507,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 22134-2026</t>
+          <t>A 24115-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3516,10 +3521,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46153</v>
+        <v>44725</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3532,7 +3537,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2</v>
+        <v>4.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3575,7 +3580,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 10940-2024</t>
+          <t>A 25388-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3589,10 +3594,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45370</v>
+        <v>45089</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3648,7 +3653,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 18503-2026</t>
+          <t>A 22134-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3662,10 +3667,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46127</v>
+        <v>46153</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3678,7 +3683,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.9</v>
+        <v>2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3721,7 +3726,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 10819-2026</t>
+          <t>A 12079-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3735,10 +3740,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46078</v>
+        <v>45377</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3751,7 +3756,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>4.9</v>
+        <v>6.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3794,7 +3799,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 1574-2024</t>
+          <t>A 18503-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3808,10 +3813,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45306</v>
+        <v>46127</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3824,7 +3829,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3867,7 +3872,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 47870-2025</t>
+          <t>A 11204-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3881,10 +3886,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45932</v>
+        <v>44992</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3897,7 +3902,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>6.8</v>
+        <v>0.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3940,7 +3945,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 7016-2025</t>
+          <t>A 10819-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3954,10 +3959,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45701</v>
+        <v>46078</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3969,13 +3974,8 @@
           <t>ESLÖV</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>2.3</v>
+        <v>4.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4018,7 +4018,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 26165-2026</t>
+          <t>A 1574-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4032,10 +4032,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46181</v>
+        <v>45306</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4091,7 +4091,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 26169-2026</t>
+          <t>A 9482-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46181</v>
+        <v>44981</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4164,7 +4164,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 26497-2026</t>
+          <t>A 26165-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4178,10 +4178,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46183</v>
+        <v>46181</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4237,7 +4237,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 9849-2026</t>
+          <t>A 15533-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4251,10 +4251,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46072</v>
+        <v>45401</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.5</v>
+        <v>7.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4310,7 +4310,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 16670-2025</t>
+          <t>A 26169-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4324,10 +4324,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45754</v>
+        <v>46181</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4383,7 +4383,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 34468-2023</t>
+          <t>A 26497-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4397,10 +4397,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45139</v>
+        <v>46183</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>5.5</v>
+        <v>1.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4456,7 +4456,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 27428-2026</t>
+          <t>A 62496-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4470,10 +4470,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46189</v>
+        <v>45268</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4486,7 +4486,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4546,7 +4546,7 @@
         <v>46189</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 27435-2026</t>
+          <t>A 27428-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4619,7 +4619,7 @@
         <v>46189</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4675,7 +4675,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 14386-2026</t>
+          <t>A 27435-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46100</v>
+        <v>46189</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>12.4</v>
+        <v>0.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 62496-2023</t>
+          <t>A 25385-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4762,10 +4762,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45268</v>
+        <v>45089</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4821,7 +4821,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 18281-2026</t>
+          <t>A 34170-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4835,10 +4835,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46125</v>
+        <v>45138</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.8</v>
+        <v>5.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4894,7 +4894,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 34170-2023</t>
+          <t>A 15357-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45138</v>
+        <v>45019</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>5.8</v>
+        <v>1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4967,7 +4967,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 24115-2022</t>
+          <t>A 36761-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4981,10 +4981,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44725</v>
+        <v>44805</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5040,7 +5040,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 9484-2023</t>
+          <t>A 34468-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5054,10 +5054,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44981</v>
+        <v>45139</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.4</v>
+        <v>5.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5113,7 +5113,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 16733-2023</t>
+          <t>A 58721-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5127,10 +5127,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45030</v>
+        <v>45986</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5186,7 +5186,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 44496-2023</t>
+          <t>A 10940-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5200,10 +5200,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45189</v>
+        <v>45370</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 34466-2023</t>
+          <t>A 11221-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5273,10 +5273,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45139</v>
+        <v>45371</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4.3</v>
+        <v>0.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5332,7 +5332,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 33865-2024</t>
+          <t>A 43808-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5342,14 +5342,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45520</v>
+        <v>45571</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5405,7 +5405,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 5812-2022</t>
+          <t>A 9484-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5419,10 +5419,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44596</v>
+        <v>44981</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5478,7 +5478,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 38173-2023</t>
+          <t>A 44496-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5492,10 +5492,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45161</v>
+        <v>45189</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5551,7 +5551,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 58721-2025</t>
+          <t>A 33865-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45986</v>
+        <v>45520</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5624,7 +5624,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 15357-2023</t>
+          <t>A 16670-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45019</v>
+        <v>45754</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5697,7 +5697,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 49137-2024</t>
+          <t>A 34466-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45594</v>
+        <v>45139</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.4</v>
+        <v>4.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5770,7 +5770,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 32984-2024</t>
+          <t>A 38173-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5784,10 +5784,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45517</v>
+        <v>45161</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5843,7 +5843,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 16792-2024</t>
+          <t>A 25508-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5857,10 +5857,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45411</v>
+        <v>45089</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5916,7 +5916,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 28088-2025</t>
+          <t>A 49137-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5930,10 +5930,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45817</v>
+        <v>45594</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>

--- a/Översikt ESLÖV.xlsx
+++ b/Översikt ESLÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45307</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45615</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44960</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>44846</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>45817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>45793</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>46100</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>44981</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 18713-2024</t>
+          <t>A 52652-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1482,10 +1482,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45426</v>
+        <v>45225</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1538,42 +1538,42 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Gråtrut</t>
+          <t>Grönfläckig padda</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 18713-2024 artfynd.xlsx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 52652-2023 artfynd.xlsx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 18713-2024 karta.png", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 52652-2023 karta.png", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 18713-2024 georefererad karta.tif", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 52652-2023 georefererad karta.tif", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 18713-2024 FSC-klagomål.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 52652-2023 FSC-klagomål.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 18713-2024 FSC-klagomål mail.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 52652-2023 FSC-klagomål mail.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 18713-2024 tillsynsbegäran.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 52652-2023 tillsynsbegäran.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 18713-2024 tillsynsbegäran mail.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 52652-2023 tillsynsbegäran mail.docx", "A 52652-2023")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 24809-2025</t>
+          <t>A 18713-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1587,10 +1587,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45799</v>
+        <v>45426</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.4</v>
+        <v>4.1</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1615,7 +1615,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1627,10 +1627,10 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1643,46 +1643,42 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gråtrut</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 24809-2025 artfynd.xlsx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 18713-2024 artfynd.xlsx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 24809-2025 karta.png", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 18713-2024 karta.png", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 24809-2025 georefererad karta.tif", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 18713-2024 georefererad karta.tif", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 24809-2025 FSC-klagomål.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 18713-2024 FSC-klagomål.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 24809-2025 FSC-klagomål mail.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 18713-2024 FSC-klagomål mail.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 24809-2025 tillsynsbegäran.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 18713-2024 tillsynsbegäran.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 24809-2025 tillsynsbegäran mail.docx", "A 24809-2025")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 24809-2025 prioriterade fågelarter.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 18713-2024 tillsynsbegäran mail.docx", "A 18713-2024")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 14013-2026</t>
+          <t>A 24809-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1696,10 +1692,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46098</v>
+        <v>45799</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1711,13 +1707,8 @@
           <t>ESLÖV</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>8.800000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1753,50 +1744,50 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14013-2026 artfynd.xlsx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 24809-2025 artfynd.xlsx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14013-2026 karta.png", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 24809-2025 karta.png", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14013-2026 georefererad karta.tif", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 24809-2025 georefererad karta.tif", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14013-2026 FSC-klagomål.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 24809-2025 FSC-klagomål.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14013-2026 FSC-klagomål mail.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 24809-2025 FSC-klagomål mail.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14013-2026 tillsynsbegäran.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 24809-2025 tillsynsbegäran.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14013-2026 tillsynsbegäran mail.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 24809-2025 tillsynsbegäran mail.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 14013-2026 prioriterade fågelarter.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 24809-2025 prioriterade fågelarter.docx", "A 24809-2025")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 61035-2024</t>
+          <t>A 14013-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1810,10 +1801,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45645</v>
+        <v>46098</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1825,17 +1816,22 @@
           <t>ESLÖV</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1850,7 +1846,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1859,49 +1855,53 @@
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 61035-2024 artfynd.xlsx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14013-2026 artfynd.xlsx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 61035-2024 karta.png", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14013-2026 karta.png", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 61035-2024 georefererad karta.tif", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14013-2026 georefererad karta.tif", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 61035-2024 FSC-klagomål.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14013-2026 FSC-klagomål.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 61035-2024 FSC-klagomål mail.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14013-2026 FSC-klagomål mail.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 61035-2024 tillsynsbegäran.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14013-2026 tillsynsbegäran.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 61035-2024 tillsynsbegäran mail.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14013-2026 tillsynsbegäran mail.docx", "A 14013-2026")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 14013-2026 prioriterade fågelarter.docx", "A 14013-2026")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 1510-2024</t>
+          <t>A 61035-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1915,10 +1915,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45306</v>
+        <v>45645</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1931,17 +1931,17 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.7</v>
+        <v>7.6</v>
       </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
@@ -1952,7 +1952,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>1</v>
@@ -1964,53 +1964,49 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Svart stork</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 1510-2024 artfynd.xlsx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 61035-2024 artfynd.xlsx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 1510-2024 karta.png", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 61035-2024 karta.png", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 1510-2024 georefererad karta.tif", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 61035-2024 georefererad karta.tif", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 1510-2024 FSC-klagomål.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 61035-2024 FSC-klagomål.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 1510-2024 FSC-klagomål mail.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 61035-2024 FSC-klagomål mail.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 1510-2024 tillsynsbegäran.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 61035-2024 tillsynsbegäran.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 1510-2024 tillsynsbegäran mail.docx", "A 1510-2024")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 1510-2024 prioriterade fågelarter.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 61035-2024 tillsynsbegäran mail.docx", "A 61035-2024")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 52652-2023</t>
+          <t>A 1510-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2024,10 +2020,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45225</v>
+        <v>45306</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2040,7 +2036,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2052,22 +2048,22 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
         <v>1</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2080,35 +2076,39 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Grönfläckig padda</t>
+          <t>Svart stork</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 52652-2023 artfynd.xlsx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 1510-2024 artfynd.xlsx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 52652-2023 karta.png", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 1510-2024 karta.png", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 52652-2023 georefererad karta.tif", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 1510-2024 georefererad karta.tif", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 52652-2023 FSC-klagomål.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 1510-2024 FSC-klagomål.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 52652-2023 FSC-klagomål mail.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 1510-2024 FSC-klagomål mail.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 52652-2023 tillsynsbegäran.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 1510-2024 tillsynsbegäran.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 52652-2023 tillsynsbegäran mail.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 1510-2024 tillsynsbegäran mail.docx", "A 1510-2024")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 1510-2024 prioriterade fågelarter.docx", "A 1510-2024")</f>
         <v/>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
         <v>44553</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>44690</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 32984-2024</t>
+          <t>A 12079-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45517</v>
+        <v>45377</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.9</v>
+        <v>6.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2334,7 +2334,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 16792-2024</t>
+          <t>A 15533-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45411</v>
+        <v>45401</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.9</v>
+        <v>7.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 47870-2025</t>
+          <t>A 11221-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45932</v>
+        <v>45371</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>6.8</v>
+        <v>0.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 28088-2025</t>
+          <t>A 15467-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45817</v>
+        <v>45747</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 16733-2023</t>
+          <t>A 32984-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45030</v>
+        <v>45517</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2626,7 +2626,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 47356-2025</t>
+          <t>A 5869-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2636,14 +2636,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45930</v>
+        <v>44958</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2699,7 +2699,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 9849-2026</t>
+          <t>A 16792-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46072</v>
+        <v>45411</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2772,7 +2772,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 5812-2022</t>
+          <t>A 47870-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44596</v>
+        <v>45932</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.5</v>
+        <v>6.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 35996-2025</t>
+          <t>A 9482-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45863</v>
+        <v>44981</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2918,7 +2918,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 35997-2025</t>
+          <t>A 25385-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45863</v>
+        <v>45089</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2991,7 +2991,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 14386-2026</t>
+          <t>A 28088-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46100</v>
+        <v>45817</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>12.4</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3064,7 +3064,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 18281-2026</t>
+          <t>A 43808-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3074,14 +3074,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46125</v>
+        <v>45571</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3137,7 +3137,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 15467-2025</t>
+          <t>A 47356-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45747</v>
+        <v>45930</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3210,7 +3210,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 5869-2023</t>
+          <t>A 35996-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3220,14 +3220,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44958</v>
+        <v>45863</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3283,7 +3283,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 7409-2025</t>
+          <t>A 35997-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45705</v>
+        <v>45863</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 9686-2023</t>
+          <t>A 11204-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44984</v>
+        <v>44992</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3429,7 +3429,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 7016-2025</t>
+          <t>A 25508-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45701</v>
+        <v>45089</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3458,13 +3458,8 @@
           <t>ESLÖV</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>2.3</v>
+        <v>0.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3507,7 +3502,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 24115-2022</t>
+          <t>A 9686-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3521,10 +3516,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44725</v>
+        <v>44984</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3537,7 +3532,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4.4</v>
+        <v>0.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3580,7 +3575,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 25388-2023</t>
+          <t>A 7409-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3594,10 +3589,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45089</v>
+        <v>45705</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3610,7 +3605,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3653,7 +3648,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 22134-2026</t>
+          <t>A 9849-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3667,10 +3662,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46153</v>
+        <v>46072</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3683,7 +3678,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3726,7 +3721,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 12079-2024</t>
+          <t>A 36761-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3740,10 +3735,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45377</v>
+        <v>44805</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3756,7 +3751,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>6.9</v>
+        <v>4.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3799,7 +3794,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 18503-2026</t>
+          <t>A 14386-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3813,10 +3808,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46127</v>
+        <v>46100</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3829,7 +3824,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4.9</v>
+        <v>12.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3872,7 +3867,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 11204-2023</t>
+          <t>A 25388-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3886,10 +3881,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44992</v>
+        <v>45089</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3902,7 +3897,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3945,7 +3940,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 10819-2026</t>
+          <t>A 18281-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3959,10 +3954,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46078</v>
+        <v>46125</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3975,7 +3970,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>4.9</v>
+        <v>0.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4018,7 +4013,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 1574-2024</t>
+          <t>A 10940-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4032,10 +4027,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45306</v>
+        <v>45370</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4048,7 +4043,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.6</v>
+        <v>0.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4091,7 +4086,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 9482-2023</t>
+          <t>A 7016-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4105,10 +4100,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44981</v>
+        <v>45701</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4120,8 +4115,13 @@
           <t>ESLÖV</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4164,7 +4164,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 26165-2026</t>
+          <t>A 22134-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4178,10 +4178,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46181</v>
+        <v>46153</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 15533-2024</t>
+          <t>A 18503-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4251,10 +4251,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45401</v>
+        <v>46127</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>7.5</v>
+        <v>4.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4310,7 +4310,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 26169-2026</t>
+          <t>A 10819-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4324,10 +4324,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46181</v>
+        <v>46078</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4383,7 +4383,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 26497-2026</t>
+          <t>A 1574-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4397,10 +4397,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46183</v>
+        <v>45306</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.4</v>
+        <v>3.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4456,7 +4456,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 62496-2023</t>
+          <t>A 16670-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4470,10 +4470,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45268</v>
+        <v>45754</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4486,7 +4486,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4529,7 +4529,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 27439-2026</t>
+          <t>A 34468-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4543,10 +4543,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46189</v>
+        <v>45139</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.6</v>
+        <v>5.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4602,7 +4602,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 27428-2026</t>
+          <t>A 26165-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4616,10 +4616,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46189</v>
+        <v>46181</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4675,7 +4675,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 27435-2026</t>
+          <t>A 26169-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46189</v>
+        <v>46181</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 25385-2023</t>
+          <t>A 26497-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4762,10 +4762,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45089</v>
+        <v>46183</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4821,7 +4821,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 34170-2023</t>
+          <t>A 62496-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4835,10 +4835,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45138</v>
+        <v>45268</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>5.8</v>
+        <v>2.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4894,7 +4894,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 15357-2023</t>
+          <t>A 27428-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45019</v>
+        <v>46189</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4967,7 +4967,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 36761-2022</t>
+          <t>A 27439-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4981,10 +4981,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44805</v>
+        <v>46189</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4.8</v>
+        <v>1.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5040,7 +5040,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 34468-2023</t>
+          <t>A 27435-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5054,10 +5054,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45139</v>
+        <v>46189</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>5.5</v>
+        <v>0.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5113,7 +5113,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 58721-2025</t>
+          <t>A 34170-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5127,10 +5127,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45986</v>
+        <v>45138</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.2</v>
+        <v>5.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5186,7 +5186,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 10940-2024</t>
+          <t>A 24115-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5200,10 +5200,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45370</v>
+        <v>44725</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.5</v>
+        <v>4.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5259,7 +5259,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 11221-2024</t>
+          <t>A 9484-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5273,10 +5273,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45371</v>
+        <v>44981</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5332,7 +5332,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 43808-2024</t>
+          <t>A 16733-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5342,14 +5342,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45571</v>
+        <v>45030</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5405,7 +5405,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 9484-2023</t>
+          <t>A 44496-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5419,10 +5419,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44981</v>
+        <v>45189</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5478,7 +5478,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 44496-2023</t>
+          <t>A 34466-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5492,10 +5492,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45189</v>
+        <v>45139</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.5</v>
+        <v>4.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5568,7 +5568,7 @@
         <v>45520</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 16670-2025</t>
+          <t>A 5812-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45754</v>
+        <v>44596</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5697,7 +5697,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 34466-2023</t>
+          <t>A 38173-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45139</v>
+        <v>45161</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5770,7 +5770,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 38173-2023</t>
+          <t>A 58721-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5784,10 +5784,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45161</v>
+        <v>45986</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5843,7 +5843,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 25508-2023</t>
+          <t>A 15357-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5857,10 +5857,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45089</v>
+        <v>45019</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5933,7 +5933,7 @@
         <v>45594</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>

--- a/Översikt ESLÖV.xlsx
+++ b/Översikt ESLÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45307</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45615</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44960</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>44846</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>45817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 23773-2025</t>
+          <t>A 9487-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1164,10 +1164,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45793</v>
+        <v>44981</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4.9</v>
+        <v>1.9</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1207,268 +1207,268 @@
         <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>2</v>
       </c>
       <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Älg
+Kambräken</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 9487-2023 artfynd.xlsx", "A 9487-2023")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 9487-2023 karta.png", "A 9487-2023")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 9487-2023 georefererad karta.tif", "A 9487-2023")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 9487-2023 FSC-klagomål.docx", "A 9487-2023")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 9487-2023 FSC-klagomål mail.docx", "A 9487-2023")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 9487-2023 tillsynsbegäran.docx", "A 9487-2023")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 9487-2023 tillsynsbegäran mail.docx", "A 9487-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 23773-2025</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45793</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ESLÖV</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
         <v>4</v>
       </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Ask
 Kransrams</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 23773-2025 artfynd.xlsx", "A 23773-2025")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 23773-2025 karta.png", "A 23773-2025")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 23773-2025 georefererad karta.tif", "A 23773-2025")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 23773-2025 FSC-klagomål.docx", "A 23773-2025")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 23773-2025 FSC-klagomål mail.docx", "A 23773-2025")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 23773-2025 tillsynsbegäran.docx", "A 23773-2025")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 23773-2025 tillsynsbegäran mail.docx", "A 23773-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>A 14395-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
         <v>46100</v>
       </c>
-      <c r="E8" s="1" t="n">
-        <v>46317</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>ESLÖV</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
+      <c r="E9" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ESLÖV</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>4.9</v>
       </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>1</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
         <v>1</v>
       </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>1</v>
       </c>
-      <c r="R8" t="n">
+      <c r="R9" t="n">
         <v>1</v>
       </c>
-      <c r="S8" t="n">
+      <c r="S9" t="n">
         <v>2</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T9" t="n">
         <v>4</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Ask
 Kransrams</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14395-2026 artfynd.xlsx", "A 14395-2026")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14395-2026 karta.png", "A 14395-2026")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14395-2026 georefererad karta.tif", "A 14395-2026")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14395-2026 FSC-klagomål.docx", "A 14395-2026")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14395-2026 FSC-klagomål mail.docx", "A 14395-2026")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14395-2026 tillsynsbegäran.docx", "A 14395-2026")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14395-2026 tillsynsbegäran mail.docx", "A 14395-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 9487-2023</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>44981</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46317</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>ESLÖV</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Älg
-Kambräken</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 9487-2023 artfynd.xlsx", "A 9487-2023")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 9487-2023 karta.png", "A 9487-2023")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 9487-2023 georefererad karta.tif", "A 9487-2023")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 9487-2023 FSC-klagomål.docx", "A 9487-2023")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 9487-2023 FSC-klagomål mail.docx", "A 9487-2023")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 9487-2023 tillsynsbegäran.docx", "A 9487-2023")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 9487-2023 tillsynsbegäran mail.docx", "A 9487-2023")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 52652-2023</t>
+          <t>A 24809-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1482,10 +1482,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45225</v>
+        <v>45799</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1510,7 +1510,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1522,10 +1522,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1538,42 +1538,46 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Grönfläckig padda</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 52652-2023 artfynd.xlsx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 24809-2025 artfynd.xlsx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 52652-2023 karta.png", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 24809-2025 karta.png", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 52652-2023 georefererad karta.tif", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 24809-2025 georefererad karta.tif", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 52652-2023 FSC-klagomål.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 24809-2025 FSC-klagomål.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 52652-2023 FSC-klagomål mail.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 24809-2025 FSC-klagomål mail.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 52652-2023 tillsynsbegäran.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 24809-2025 tillsynsbegäran.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 52652-2023 tillsynsbegäran mail.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 24809-2025 tillsynsbegäran mail.docx", "A 24809-2025")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 24809-2025 prioriterade fågelarter.docx", "A 24809-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 18713-2024</t>
+          <t>A 61035-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1587,10 +1591,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45426</v>
+        <v>45645</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1603,19 +1607,19 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.1</v>
+        <v>7.6</v>
       </c>
       <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>1</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1630,55 +1634,55 @@
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Gråtrut</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 18713-2024 artfynd.xlsx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 61035-2024 artfynd.xlsx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 18713-2024 karta.png", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 61035-2024 karta.png", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 18713-2024 georefererad karta.tif", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 61035-2024 georefererad karta.tif", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 18713-2024 FSC-klagomål.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 61035-2024 FSC-klagomål.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 18713-2024 FSC-klagomål mail.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 61035-2024 FSC-klagomål mail.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 18713-2024 tillsynsbegäran.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 61035-2024 tillsynsbegäran.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 18713-2024 tillsynsbegäran mail.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 61035-2024 tillsynsbegäran mail.docx", "A 61035-2024")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 24809-2025</t>
+          <t>A 1510-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1692,10 +1696,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45799</v>
+        <v>45306</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1708,7 +1712,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1729,10 +1733,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1748,46 +1752,46 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svart stork</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 24809-2025 artfynd.xlsx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 1510-2024 artfynd.xlsx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 24809-2025 karta.png", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 1510-2024 karta.png", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 24809-2025 georefererad karta.tif", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 1510-2024 georefererad karta.tif", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 24809-2025 FSC-klagomål.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 1510-2024 FSC-klagomål.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 24809-2025 FSC-klagomål mail.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 1510-2024 FSC-klagomål mail.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 24809-2025 tillsynsbegäran.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 1510-2024 tillsynsbegäran.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 24809-2025 tillsynsbegäran mail.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 1510-2024 tillsynsbegäran mail.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 24809-2025 prioriterade fågelarter.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 1510-2024 prioriterade fågelarter.docx", "A 1510-2024")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 14013-2026</t>
+          <t>A 52652-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1801,10 +1805,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46098</v>
+        <v>45225</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1816,13 +1820,8 @@
           <t>ESLÖV</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>8.800000000000001</v>
+        <v>2.9</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1834,7 +1833,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1846,10 +1845,10 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1858,50 +1857,46 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Grönfläckig padda</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14013-2026 artfynd.xlsx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 52652-2023 artfynd.xlsx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14013-2026 karta.png", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 52652-2023 karta.png", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14013-2026 georefererad karta.tif", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 52652-2023 georefererad karta.tif", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14013-2026 FSC-klagomål.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 52652-2023 FSC-klagomål.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14013-2026 FSC-klagomål mail.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 52652-2023 FSC-klagomål mail.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14013-2026 tillsynsbegäran.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 52652-2023 tillsynsbegäran.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14013-2026 tillsynsbegäran mail.docx", "A 14013-2026")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 14013-2026 prioriterade fågelarter.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 52652-2023 tillsynsbegäran mail.docx", "A 52652-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 61035-2024</t>
+          <t>A 18713-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1915,10 +1910,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45645</v>
+        <v>45426</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1931,19 +1926,19 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>7.6</v>
+        <v>4.1</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
         <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1958,55 +1953,55 @@
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Gråtrut</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 61035-2024 artfynd.xlsx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 18713-2024 artfynd.xlsx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 61035-2024 karta.png", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 18713-2024 karta.png", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 61035-2024 georefererad karta.tif", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 18713-2024 georefererad karta.tif", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 61035-2024 FSC-klagomål.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 18713-2024 FSC-klagomål.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 61035-2024 FSC-klagomål mail.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 18713-2024 FSC-klagomål mail.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 61035-2024 tillsynsbegäran.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 18713-2024 tillsynsbegäran.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 61035-2024 tillsynsbegäran mail.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 18713-2024 tillsynsbegäran mail.docx", "A 18713-2024")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 1510-2024</t>
+          <t>A 14013-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2020,10 +2015,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45306</v>
+        <v>46098</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2035,8 +2030,13 @@
           <t>ESLÖV</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>3.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2057,10 +2057,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2072,43 +2072,43 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Svart stork</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 1510-2024 artfynd.xlsx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14013-2026 artfynd.xlsx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 1510-2024 karta.png", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14013-2026 karta.png", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 1510-2024 georefererad karta.tif", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14013-2026 georefererad karta.tif", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 1510-2024 FSC-klagomål.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14013-2026 FSC-klagomål.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 1510-2024 FSC-klagomål mail.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14013-2026 FSC-klagomål mail.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 1510-2024 tillsynsbegäran.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14013-2026 tillsynsbegäran.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 1510-2024 tillsynsbegäran mail.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14013-2026 tillsynsbegäran mail.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 1510-2024 prioriterade fågelarter.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 14013-2026 prioriterade fågelarter.docx", "A 14013-2026")</f>
         <v/>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
         <v>44553</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>44690</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 12079-2024</t>
+          <t>A 34170-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45377</v>
+        <v>45138</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>6.9</v>
+        <v>5.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2334,7 +2334,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 15533-2024</t>
+          <t>A 16792-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45401</v>
+        <v>45411</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>7.5</v>
+        <v>0.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 11221-2024</t>
+          <t>A 15357-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45371</v>
+        <v>45019</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 15467-2025</t>
+          <t>A 36761-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45747</v>
+        <v>44805</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.4</v>
+        <v>4.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 32984-2024</t>
+          <t>A 28088-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45517</v>
+        <v>45817</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2626,7 +2626,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 5869-2023</t>
+          <t>A 34468-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2636,14 +2636,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44958</v>
+        <v>45139</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2699,7 +2699,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 16792-2024</t>
+          <t>A 47356-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45411</v>
+        <v>45930</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2772,7 +2772,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 47870-2025</t>
+          <t>A 35996-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45932</v>
+        <v>45863</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>6.8</v>
+        <v>0.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 9482-2023</t>
+          <t>A 35997-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44981</v>
+        <v>45863</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2918,7 +2918,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 25385-2023</t>
+          <t>A 10940-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45089</v>
+        <v>45370</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2991,7 +2991,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 28088-2025</t>
+          <t>A 11221-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45817</v>
+        <v>45371</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3081,7 +3081,7 @@
         <v>45571</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 47356-2025</t>
+          <t>A 9484-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45930</v>
+        <v>44981</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3210,7 +3210,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 35996-2025</t>
+          <t>A 44496-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45863</v>
+        <v>45189</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3283,7 +3283,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 35997-2025</t>
+          <t>A 33865-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45863</v>
+        <v>45520</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 11204-2023</t>
+          <t>A 16670-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44992</v>
+        <v>45754</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3429,7 +3429,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 25508-2023</t>
+          <t>A 34466-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45089</v>
+        <v>45139</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.4</v>
+        <v>4.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3502,7 +3502,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 9686-2023</t>
+          <t>A 22134-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44984</v>
+        <v>46153</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3575,7 +3575,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 7409-2025</t>
+          <t>A 38173-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45705</v>
+        <v>45161</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3648,7 +3648,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 9849-2026</t>
+          <t>A 18503-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3662,10 +3662,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46072</v>
+        <v>46127</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.5</v>
+        <v>4.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3721,7 +3721,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 36761-2022</t>
+          <t>A 10819-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44805</v>
+        <v>46078</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3794,7 +3794,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 14386-2026</t>
+          <t>A 47870-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46100</v>
+        <v>45932</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>12.4</v>
+        <v>6.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3867,7 +3867,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 25388-2023</t>
+          <t>A 1574-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3881,10 +3881,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45089</v>
+        <v>45306</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.5</v>
+        <v>3.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3940,7 +3940,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 18281-2026</t>
+          <t>A 25508-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46125</v>
+        <v>45089</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4013,7 +4013,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 10940-2024</t>
+          <t>A 26165-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45370</v>
+        <v>46181</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4086,7 +4086,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 7016-2025</t>
+          <t>A 26169-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4100,10 +4100,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45701</v>
+        <v>46181</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4115,13 +4115,8 @@
           <t>ESLÖV</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4164,7 +4159,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 22134-2026</t>
+          <t>A 49137-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4178,10 +4173,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46153</v>
+        <v>45594</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4194,7 +4189,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4237,7 +4232,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 18503-2026</t>
+          <t>A 16733-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4251,10 +4246,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46127</v>
+        <v>45030</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4267,7 +4262,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4.9</v>
+        <v>2.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4310,7 +4305,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 10819-2026</t>
+          <t>A 26497-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4324,10 +4319,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46078</v>
+        <v>46183</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4340,7 +4335,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>4.9</v>
+        <v>1.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4383,7 +4378,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 1574-2024</t>
+          <t>A 9849-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4397,10 +4392,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45306</v>
+        <v>46072</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4413,7 +4408,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4456,7 +4451,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 16670-2025</t>
+          <t>A 27439-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4470,10 +4465,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45754</v>
+        <v>46189</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4486,7 +4481,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4529,7 +4524,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 34468-2023</t>
+          <t>A 32984-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4543,10 +4538,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45139</v>
+        <v>45517</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4559,7 +4554,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4602,7 +4597,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 26165-2026</t>
+          <t>A 27428-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4616,10 +4611,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46181</v>
+        <v>46189</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4632,7 +4627,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4675,7 +4670,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 26169-2026</t>
+          <t>A 27435-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4689,10 +4684,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46181</v>
+        <v>46189</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4705,7 +4700,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.5</v>
+        <v>0.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4748,7 +4743,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 26497-2026</t>
+          <t>A 14386-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4762,10 +4757,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46183</v>
+        <v>46100</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4778,7 +4773,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.4</v>
+        <v>12.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4821,7 +4816,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 62496-2023</t>
+          <t>A 18281-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4835,10 +4830,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45268</v>
+        <v>46125</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4851,7 +4846,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4894,7 +4889,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 27428-2026</t>
+          <t>A 5812-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4908,10 +4903,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46189</v>
+        <v>44596</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4924,7 +4919,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4967,7 +4962,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 27439-2026</t>
+          <t>A 15467-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4981,10 +4976,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46189</v>
+        <v>45747</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4997,7 +4992,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5040,7 +5035,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 27435-2026</t>
+          <t>A 5869-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5050,14 +5045,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46189</v>
+        <v>44958</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5070,7 +5065,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5113,7 +5108,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 34170-2023</t>
+          <t>A 7409-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5127,10 +5122,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45138</v>
+        <v>45705</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5143,7 +5138,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>5.8</v>
+        <v>1.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5186,7 +5181,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 24115-2022</t>
+          <t>A 9686-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5200,10 +5195,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44725</v>
+        <v>44984</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5216,7 +5211,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4.4</v>
+        <v>0.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5259,7 +5254,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 9484-2023</t>
+          <t>A 7016-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5273,10 +5268,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44981</v>
+        <v>45701</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5288,8 +5283,13 @@
           <t>ESLÖV</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5332,7 +5332,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 16733-2023</t>
+          <t>A 58721-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5346,10 +5346,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45030</v>
+        <v>45986</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5405,7 +5405,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 44496-2023</t>
+          <t>A 24115-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5419,10 +5419,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45189</v>
+        <v>44725</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>4.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5478,7 +5478,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 34466-2023</t>
+          <t>A 25388-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5492,10 +5492,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45139</v>
+        <v>45089</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4.3</v>
+        <v>0.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5551,7 +5551,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 33865-2024</t>
+          <t>A 12079-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45520</v>
+        <v>45377</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.3</v>
+        <v>6.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5624,7 +5624,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 5812-2022</t>
+          <t>A 11204-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44596</v>
+        <v>44992</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5697,7 +5697,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 38173-2023</t>
+          <t>A 9482-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45161</v>
+        <v>44981</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5770,7 +5770,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 58721-2025</t>
+          <t>A 15533-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5784,10 +5784,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45986</v>
+        <v>45401</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.2</v>
+        <v>7.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5843,7 +5843,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 15357-2023</t>
+          <t>A 62496-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5857,10 +5857,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45019</v>
+        <v>45268</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5916,7 +5916,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 49137-2024</t>
+          <t>A 25385-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5930,10 +5930,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45594</v>
+        <v>45089</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>

--- a/Översikt ESLÖV.xlsx
+++ b/Översikt ESLÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45307</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45615</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44960</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>44846</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>45817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>44981</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>45793</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>46100</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 24809-2025</t>
+          <t>A 61035-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1482,10 +1482,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45799</v>
+        <v>45645</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1498,17 +1498,17 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.4</v>
+        <v>7.6</v>
       </c>
       <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1531,53 +1531,49 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 24809-2025 artfynd.xlsx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 61035-2024 artfynd.xlsx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 24809-2025 karta.png", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 61035-2024 karta.png", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 24809-2025 georefererad karta.tif", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 61035-2024 georefererad karta.tif", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 24809-2025 FSC-klagomål.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 61035-2024 FSC-klagomål.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 24809-2025 FSC-klagomål mail.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 61035-2024 FSC-klagomål mail.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 24809-2025 tillsynsbegäran.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 61035-2024 tillsynsbegäran.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 24809-2025 tillsynsbegäran mail.docx", "A 24809-2025")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 24809-2025 prioriterade fågelarter.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 61035-2024 tillsynsbegäran mail.docx", "A 61035-2024")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 61035-2024</t>
+          <t>A 1510-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1591,10 +1587,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45645</v>
+        <v>45306</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1607,28 +1603,28 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>7.6</v>
+        <v>3.7</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
         <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
@@ -1640,49 +1636,53 @@
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Svart stork</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 61035-2024 artfynd.xlsx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 1510-2024 artfynd.xlsx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 61035-2024 karta.png", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 1510-2024 karta.png", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 61035-2024 georefererad karta.tif", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 1510-2024 georefererad karta.tif", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 61035-2024 FSC-klagomål.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 1510-2024 FSC-klagomål.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 61035-2024 FSC-klagomål mail.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 1510-2024 FSC-klagomål mail.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 61035-2024 tillsynsbegäran.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 1510-2024 tillsynsbegäran.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 61035-2024 tillsynsbegäran mail.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 1510-2024 tillsynsbegäran mail.docx", "A 1510-2024")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 1510-2024 prioriterade fågelarter.docx", "A 1510-2024")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 1510-2024</t>
+          <t>A 52652-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45306</v>
+        <v>45225</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1724,7 +1724,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1733,13 +1733,13 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1752,46 +1752,42 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Svart stork</t>
+          <t>Grönfläckig padda</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 1510-2024 artfynd.xlsx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 52652-2023 artfynd.xlsx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 1510-2024 karta.png", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 52652-2023 karta.png", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 1510-2024 georefererad karta.tif", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 52652-2023 georefererad karta.tif", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 1510-2024 FSC-klagomål.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 52652-2023 FSC-klagomål.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 1510-2024 FSC-klagomål mail.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 52652-2023 FSC-klagomål mail.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 1510-2024 tillsynsbegäran.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 52652-2023 tillsynsbegäran.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 1510-2024 tillsynsbegäran mail.docx", "A 1510-2024")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 1510-2024 prioriterade fågelarter.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 52652-2023 tillsynsbegäran mail.docx", "A 52652-2023")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 52652-2023</t>
+          <t>A 18713-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1805,10 +1801,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45225</v>
+        <v>45426</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1821,7 +1817,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1861,42 +1857,42 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Grönfläckig padda</t>
+          <t>Gråtrut</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 52652-2023 artfynd.xlsx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 18713-2024 artfynd.xlsx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 52652-2023 karta.png", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 18713-2024 karta.png", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 52652-2023 georefererad karta.tif", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 18713-2024 georefererad karta.tif", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 52652-2023 FSC-klagomål.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 18713-2024 FSC-klagomål.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 52652-2023 FSC-klagomål mail.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 18713-2024 FSC-klagomål mail.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 52652-2023 tillsynsbegäran.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 18713-2024 tillsynsbegäran.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 52652-2023 tillsynsbegäran mail.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 18713-2024 tillsynsbegäran mail.docx", "A 18713-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 18713-2024</t>
+          <t>A 24809-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1910,10 +1906,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45426</v>
+        <v>45799</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1926,7 +1922,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>4.1</v>
+        <v>1.4</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1938,7 +1934,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1950,10 +1946,10 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1966,35 +1962,39 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Gråtrut</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 18713-2024 artfynd.xlsx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 24809-2025 artfynd.xlsx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 18713-2024 karta.png", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 24809-2025 karta.png", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 18713-2024 georefererad karta.tif", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 24809-2025 georefererad karta.tif", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 18713-2024 FSC-klagomål.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 24809-2025 FSC-klagomål.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 18713-2024 FSC-klagomål mail.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 24809-2025 FSC-klagomål mail.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 18713-2024 tillsynsbegäran.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 24809-2025 tillsynsbegäran.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 18713-2024 tillsynsbegäran mail.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 24809-2025 tillsynsbegäran mail.docx", "A 24809-2025")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 24809-2025 prioriterade fågelarter.docx", "A 24809-2025")</f>
         <v/>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
         <v>46098</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>44553</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>44690</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 34170-2023</t>
+          <t>A 12079-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45138</v>
+        <v>45377</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>5.8</v>
+        <v>6.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2334,7 +2334,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 16792-2024</t>
+          <t>A 15533-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45411</v>
+        <v>45401</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.9</v>
+        <v>7.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 15357-2023</t>
+          <t>A 11221-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45019</v>
+        <v>45371</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 36761-2022</t>
+          <t>A 18503-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44805</v>
+        <v>46127</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 28088-2025</t>
+          <t>A 15467-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45817</v>
+        <v>45747</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2626,7 +2626,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 34468-2023</t>
+          <t>A 10819-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45139</v>
+        <v>46078</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2699,7 +2699,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 47356-2025</t>
+          <t>A 1574-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45930</v>
+        <v>45306</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.6</v>
+        <v>3.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2772,7 +2772,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 35996-2025</t>
+          <t>A 47356-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45863</v>
+        <v>45930</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 35997-2025</t>
+          <t>A 9484-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45863</v>
+        <v>44981</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2918,7 +2918,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 10940-2024</t>
+          <t>A 16733-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45370</v>
+        <v>45030</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2991,7 +2991,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 11221-2024</t>
+          <t>A 44496-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45371</v>
+        <v>45189</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3064,7 +3064,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 43808-2024</t>
+          <t>A 26165-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3074,14 +3074,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45571</v>
+        <v>46181</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3137,7 +3137,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 9484-2023</t>
+          <t>A 26169-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44981</v>
+        <v>46181</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3210,7 +3210,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 44496-2023</t>
+          <t>A 26497-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45189</v>
+        <v>46183</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3283,7 +3283,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 33865-2024</t>
+          <t>A 35996-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45520</v>
+        <v>45863</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 16670-2025</t>
+          <t>A 35997-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45754</v>
+        <v>45863</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3429,7 +3429,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 34466-2023</t>
+          <t>A 5869-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3439,14 +3439,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45139</v>
+        <v>44958</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3502,7 +3502,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 22134-2026</t>
+          <t>A 27428-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46153</v>
+        <v>46189</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3575,7 +3575,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 38173-2023</t>
+          <t>A 34466-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45161</v>
+        <v>45139</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.8</v>
+        <v>4.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3648,7 +3648,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 18503-2026</t>
+          <t>A 27439-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3662,10 +3662,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46127</v>
+        <v>46189</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.9</v>
+        <v>1.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3721,7 +3721,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 10819-2026</t>
+          <t>A 27435-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46078</v>
+        <v>46189</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>4.9</v>
+        <v>0.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3794,7 +3794,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 47870-2025</t>
+          <t>A 33865-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45932</v>
+        <v>45520</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>6.8</v>
+        <v>1.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3867,7 +3867,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 1574-2024</t>
+          <t>A 5812-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3881,10 +3881,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45306</v>
+        <v>44596</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.6</v>
+        <v>0.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3940,7 +3940,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 25508-2023</t>
+          <t>A 38173-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45089</v>
+        <v>45161</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4013,7 +4013,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 26165-2026</t>
+          <t>A 15357-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46181</v>
+        <v>45019</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4086,7 +4086,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 26169-2026</t>
+          <t>A 49137-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4100,10 +4100,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46181</v>
+        <v>45594</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4159,7 +4159,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 49137-2024</t>
+          <t>A 47870-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4173,10 +4173,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45594</v>
+        <v>45932</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.4</v>
+        <v>6.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4232,7 +4232,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 16733-2023</t>
+          <t>A 32984-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4246,10 +4246,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45030</v>
+        <v>45517</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4305,7 +4305,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 26497-2026</t>
+          <t>A 16792-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46183</v>
+        <v>45411</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4378,7 +4378,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 9849-2026</t>
+          <t>A 58721-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4392,10 +4392,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46072</v>
+        <v>45986</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4451,7 +4451,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 27439-2026</t>
+          <t>A 28088-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4465,10 +4465,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46189</v>
+        <v>45817</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4524,7 +4524,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 32984-2024</t>
+          <t>A 9849-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4538,10 +4538,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45517</v>
+        <v>46072</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4597,7 +4597,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 27428-2026</t>
+          <t>A 14386-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46189</v>
+        <v>46100</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.4</v>
+        <v>12.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4670,7 +4670,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 27435-2026</t>
+          <t>A 9482-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4684,10 +4684,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46189</v>
+        <v>44981</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.9</v>
+        <v>3.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4743,7 +4743,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 14386-2026</t>
+          <t>A 25385-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4757,10 +4757,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46100</v>
+        <v>45089</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>12.4</v>
+        <v>0.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4833,7 +4833,7 @@
         <v>46125</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 5812-2022</t>
+          <t>A 43808-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4899,14 +4899,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44596</v>
+        <v>45571</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4919,7 +4919,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4962,7 +4962,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 15467-2025</t>
+          <t>A 22134-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4976,10 +4976,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45747</v>
+        <v>46153</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5035,7 +5035,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 5869-2023</t>
+          <t>A 11204-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5045,14 +5045,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44958</v>
+        <v>44992</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5108,7 +5108,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 7409-2025</t>
+          <t>A 25508-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45705</v>
+        <v>45089</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5198,7 +5198,7 @@
         <v>44984</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 7016-2025</t>
+          <t>A 7409-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5268,10 +5268,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45701</v>
+        <v>45705</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5283,13 +5283,8 @@
           <t>ESLÖV</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5332,7 +5327,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 58721-2025</t>
+          <t>A 36761-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5346,10 +5341,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45986</v>
+        <v>44805</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5362,7 +5357,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.2</v>
+        <v>4.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5405,7 +5400,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 24115-2022</t>
+          <t>A 25388-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5419,10 +5414,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44725</v>
+        <v>45089</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5435,7 +5430,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4.4</v>
+        <v>0.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5478,7 +5473,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 25388-2023</t>
+          <t>A 10940-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5492,10 +5487,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45089</v>
+        <v>45370</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5551,7 +5546,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 12079-2024</t>
+          <t>A 7016-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5565,10 +5560,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45377</v>
+        <v>45701</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5580,8 +5575,13 @@
           <t>ESLÖV</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>6.9</v>
+        <v>2.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5624,7 +5624,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 11204-2023</t>
+          <t>A 16670-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44992</v>
+        <v>45754</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5697,7 +5697,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 9482-2023</t>
+          <t>A 34468-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44981</v>
+        <v>45139</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5770,7 +5770,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 15533-2024</t>
+          <t>A 62496-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5784,10 +5784,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45401</v>
+        <v>45268</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>7.5</v>
+        <v>2.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5843,7 +5843,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 62496-2023</t>
+          <t>A 34170-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5857,10 +5857,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45268</v>
+        <v>45138</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.6</v>
+        <v>5.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5916,7 +5916,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 25385-2023</t>
+          <t>A 24115-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5930,10 +5930,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45089</v>
+        <v>44725</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.7</v>
+        <v>4.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>

--- a/Översikt ESLÖV.xlsx
+++ b/Översikt ESLÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45307</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45615</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44960</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>44846</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>45817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>44981</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>45793</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>46100</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>45645</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>45306</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>45225</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>45426</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
         <v>45799</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>46098</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>44553</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>44690</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>45377</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>45401</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>45371</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>46127</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>45747</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>46078</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>45306</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>45930</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>44981</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>45030</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>45189</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>46181</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         <v>46181</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>46183</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>45863</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>45863</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>44958</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>46189</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3592,7 +3592,7 @@
         <v>45139</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>46189</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>46189</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>45520</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>44596</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>45161</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>45019</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         <v>45594</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>45932</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         <v>45517</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>45411</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>45986</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>45817</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
         <v>46072</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4614,7 +4614,7 @@
         <v>46100</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>44981</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>45089</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         <v>46125</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>45571</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
         <v>46153</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>44992</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>45089</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>44984</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>45705</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>44805</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>45089</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         <v>45370</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
         <v>45701</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>45754</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         <v>45139</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>45268</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>45138</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>44725</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>

--- a/Översikt ESLÖV.xlsx
+++ b/Översikt ESLÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45307</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45615</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44960</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>44846</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>45817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>44981</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>45793</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>46100</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>45645</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>45306</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>45225</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>45426</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
         <v>45799</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>46098</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>44553</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>44690</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>45377</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>45401</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>45371</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>46127</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>45747</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>46078</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>45306</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>45930</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>44981</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>45030</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>45189</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>46181</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         <v>46181</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>46183</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>45863</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>45863</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>44958</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>46189</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3592,7 +3592,7 @@
         <v>45139</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>46189</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>46189</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>45520</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>44596</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>45161</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>45019</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         <v>45594</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>45932</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         <v>45517</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>45411</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>45986</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>45817</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
         <v>46072</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4614,7 +4614,7 @@
         <v>46100</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>44981</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>45089</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         <v>46125</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>45571</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
         <v>46153</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>44992</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>45089</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>44984</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>45705</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>44805</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>45089</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         <v>45370</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
         <v>45701</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>45754</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         <v>45139</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>45268</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>45138</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>44725</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>

--- a/Översikt ESLÖV.xlsx
+++ b/Översikt ESLÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45307</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45615</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44960</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>44846</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>45817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 9487-2023</t>
+          <t>A 23773-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1164,10 +1164,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44981</v>
+        <v>45793</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.9</v>
+        <v>4.9</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
         <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1207,268 +1207,268 @@
         <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>2</v>
       </c>
       <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Kransrams</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 23773-2025 artfynd.xlsx", "A 23773-2025")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 23773-2025 karta.png", "A 23773-2025")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 23773-2025 georefererad karta.tif", "A 23773-2025")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 23773-2025 FSC-klagomål.docx", "A 23773-2025")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 23773-2025 FSC-klagomål mail.docx", "A 23773-2025")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 23773-2025 tillsynsbegäran.docx", "A 23773-2025")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 23773-2025 tillsynsbegäran mail.docx", "A 23773-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 14395-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>46100</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ESLÖV</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
         <v>2</v>
       </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Kransrams</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14395-2026 artfynd.xlsx", "A 14395-2026")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14395-2026 karta.png", "A 14395-2026")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14395-2026 georefererad karta.tif", "A 14395-2026")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14395-2026 FSC-klagomål.docx", "A 14395-2026")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14395-2026 FSC-klagomål mail.docx", "A 14395-2026")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14395-2026 tillsynsbegäran.docx", "A 14395-2026")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14395-2026 tillsynsbegäran mail.docx", "A 14395-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 9487-2023</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>44981</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ESLÖV</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Älg
 Kambräken</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 9487-2023 artfynd.xlsx", "A 9487-2023")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 9487-2023 karta.png", "A 9487-2023")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 9487-2023 georefererad karta.tif", "A 9487-2023")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 9487-2023 FSC-klagomål.docx", "A 9487-2023")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 9487-2023 FSC-klagomål mail.docx", "A 9487-2023")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 9487-2023 tillsynsbegäran.docx", "A 9487-2023")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 9487-2023 tillsynsbegäran mail.docx", "A 9487-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 23773-2025</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45793</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46321</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>ESLÖV</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>4</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Kransrams</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 23773-2025 artfynd.xlsx", "A 23773-2025")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 23773-2025 karta.png", "A 23773-2025")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 23773-2025 georefererad karta.tif", "A 23773-2025")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 23773-2025 FSC-klagomål.docx", "A 23773-2025")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 23773-2025 FSC-klagomål mail.docx", "A 23773-2025")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 23773-2025 tillsynsbegäran.docx", "A 23773-2025")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 23773-2025 tillsynsbegäran mail.docx", "A 23773-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 14395-2026</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>46100</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46321</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>ESLÖV</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>4</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Kransrams</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14395-2026 artfynd.xlsx", "A 14395-2026")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14395-2026 karta.png", "A 14395-2026")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14395-2026 georefererad karta.tif", "A 14395-2026")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14395-2026 FSC-klagomål.docx", "A 14395-2026")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14395-2026 FSC-klagomål mail.docx", "A 14395-2026")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14395-2026 tillsynsbegäran.docx", "A 14395-2026")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14395-2026 tillsynsbegäran mail.docx", "A 14395-2026")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 61035-2024</t>
+          <t>A 1510-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1482,10 +1482,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45645</v>
+        <v>45306</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1498,28 +1498,28 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>7.6</v>
+        <v>3.7</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
         <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
@@ -1531,49 +1531,53 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Svart stork</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 61035-2024 artfynd.xlsx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 1510-2024 artfynd.xlsx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 61035-2024 karta.png", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 1510-2024 karta.png", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 61035-2024 georefererad karta.tif", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 1510-2024 georefererad karta.tif", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 61035-2024 FSC-klagomål.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 1510-2024 FSC-klagomål.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 61035-2024 FSC-klagomål mail.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 1510-2024 FSC-klagomål mail.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 61035-2024 tillsynsbegäran.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 1510-2024 tillsynsbegäran.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 61035-2024 tillsynsbegäran mail.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 1510-2024 tillsynsbegäran mail.docx", "A 1510-2024")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 1510-2024 prioriterade fågelarter.docx", "A 1510-2024")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 1510-2024</t>
+          <t>A 52652-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1587,10 +1591,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45306</v>
+        <v>45225</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1603,7 +1607,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1615,7 +1619,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1624,13 +1628,13 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1643,46 +1647,42 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Svart stork</t>
+          <t>Grönfläckig padda</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 1510-2024 artfynd.xlsx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 52652-2023 artfynd.xlsx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 1510-2024 karta.png", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 52652-2023 karta.png", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 1510-2024 georefererad karta.tif", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 52652-2023 georefererad karta.tif", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 1510-2024 FSC-klagomål.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 52652-2023 FSC-klagomål.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 1510-2024 FSC-klagomål mail.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 52652-2023 FSC-klagomål mail.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 1510-2024 tillsynsbegäran.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 52652-2023 tillsynsbegäran.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 1510-2024 tillsynsbegäran mail.docx", "A 1510-2024")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 1510-2024 prioriterade fågelarter.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 52652-2023 tillsynsbegäran mail.docx", "A 52652-2023")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 52652-2023</t>
+          <t>A 18713-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45225</v>
+        <v>45426</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1752,42 +1752,42 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Grönfläckig padda</t>
+          <t>Gråtrut</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 52652-2023 artfynd.xlsx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 18713-2024 artfynd.xlsx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 52652-2023 karta.png", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 18713-2024 karta.png", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 52652-2023 georefererad karta.tif", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 18713-2024 georefererad karta.tif", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 52652-2023 FSC-klagomål.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 18713-2024 FSC-klagomål.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 52652-2023 FSC-klagomål mail.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 18713-2024 FSC-klagomål mail.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 52652-2023 tillsynsbegäran.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 18713-2024 tillsynsbegäran.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 52652-2023 tillsynsbegäran mail.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 18713-2024 tillsynsbegäran mail.docx", "A 18713-2024")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 18713-2024</t>
+          <t>A 24809-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1801,10 +1801,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45426</v>
+        <v>45799</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>4.1</v>
+        <v>1.4</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1829,7 +1829,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1841,10 +1841,10 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1857,42 +1857,46 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Gråtrut</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 18713-2024 artfynd.xlsx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 24809-2025 artfynd.xlsx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 18713-2024 karta.png", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 24809-2025 karta.png", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 18713-2024 georefererad karta.tif", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 24809-2025 georefererad karta.tif", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 18713-2024 FSC-klagomål.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 24809-2025 FSC-klagomål.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 18713-2024 FSC-klagomål mail.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 24809-2025 FSC-klagomål mail.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 18713-2024 tillsynsbegäran.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 24809-2025 tillsynsbegäran.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 18713-2024 tillsynsbegäran mail.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 24809-2025 tillsynsbegäran mail.docx", "A 24809-2025")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 24809-2025 prioriterade fågelarter.docx", "A 24809-2025")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 24809-2025</t>
+          <t>A 14013-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1906,10 +1910,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45799</v>
+        <v>46098</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1921,8 +1925,13 @@
           <t>ESLÖV</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>1.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1958,50 +1967,50 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 24809-2025 artfynd.xlsx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14013-2026 artfynd.xlsx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 24809-2025 karta.png", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14013-2026 karta.png", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 24809-2025 georefererad karta.tif", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14013-2026 georefererad karta.tif", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 24809-2025 FSC-klagomål.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14013-2026 FSC-klagomål.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 24809-2025 FSC-klagomål mail.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14013-2026 FSC-klagomål mail.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 24809-2025 tillsynsbegäran.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14013-2026 tillsynsbegäran.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 24809-2025 tillsynsbegäran mail.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14013-2026 tillsynsbegäran mail.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 24809-2025 prioriterade fågelarter.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 14013-2026 prioriterade fågelarter.docx", "A 14013-2026")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 14013-2026</t>
+          <t>A 61035-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2015,10 +2024,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46098</v>
+        <v>45645</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2030,23 +2039,18 @@
           <t>ESLÖV</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
@@ -2060,7 +2064,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2069,46 +2073,42 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14013-2026 artfynd.xlsx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 61035-2024 artfynd.xlsx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14013-2026 karta.png", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 61035-2024 karta.png", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14013-2026 georefererad karta.tif", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 61035-2024 georefererad karta.tif", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14013-2026 FSC-klagomål.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 61035-2024 FSC-klagomål.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14013-2026 FSC-klagomål mail.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 61035-2024 FSC-klagomål mail.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14013-2026 tillsynsbegäran.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 61035-2024 tillsynsbegäran.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14013-2026 tillsynsbegäran mail.docx", "A 14013-2026")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 14013-2026 prioriterade fågelarter.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 61035-2024 tillsynsbegäran mail.docx", "A 61035-2024")</f>
         <v/>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
         <v>44553</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>44690</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 12079-2024</t>
+          <t>A 44496-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45377</v>
+        <v>45189</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>6.9</v>
+        <v>0.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2334,7 +2334,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 15533-2024</t>
+          <t>A 33865-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45401</v>
+        <v>45520</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>7.5</v>
+        <v>1.3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 11221-2024</t>
+          <t>A 16670-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45371</v>
+        <v>45754</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 18503-2026</t>
+          <t>A 34466-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46127</v>
+        <v>45139</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 15467-2025</t>
+          <t>A 38173-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45747</v>
+        <v>45161</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2626,7 +2626,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 10819-2026</t>
+          <t>A 47356-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46078</v>
+        <v>45930</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4.9</v>
+        <v>0.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2699,7 +2699,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 1574-2024</t>
+          <t>A 27439-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45306</v>
+        <v>46189</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.6</v>
+        <v>1.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2772,7 +2772,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 47356-2025</t>
+          <t>A 25508-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45930</v>
+        <v>45089</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 9484-2023</t>
+          <t>A 27428-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44981</v>
+        <v>46189</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2918,7 +2918,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 16733-2023</t>
+          <t>A 27435-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45030</v>
+        <v>46189</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2991,7 +2991,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 44496-2023</t>
+          <t>A 35996-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45189</v>
+        <v>45863</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3064,7 +3064,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 26165-2026</t>
+          <t>A 35997-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3078,10 +3078,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46181</v>
+        <v>45863</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3137,7 +3137,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 26169-2026</t>
+          <t>A 49137-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46181</v>
+        <v>45594</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3210,7 +3210,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 26497-2026</t>
+          <t>A 32984-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46183</v>
+        <v>45517</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3283,7 +3283,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 35996-2025</t>
+          <t>A 16733-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45863</v>
+        <v>45030</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 35997-2025</t>
+          <t>A 16792-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45863</v>
+        <v>45411</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 5869-2023</t>
+          <t>A 28088-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3439,14 +3439,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44958</v>
+        <v>45817</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3502,7 +3502,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 27428-2026</t>
+          <t>A 5812-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46189</v>
+        <v>44596</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3575,7 +3575,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 34466-2023</t>
+          <t>A 47870-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45139</v>
+        <v>45932</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3648,7 +3648,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 27439-2026</t>
+          <t>A 15467-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3662,10 +3662,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46189</v>
+        <v>45747</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3721,7 +3721,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 27435-2026</t>
+          <t>A 5869-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3731,14 +3731,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46189</v>
+        <v>44958</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3794,7 +3794,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 33865-2024</t>
+          <t>A 7409-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45520</v>
+        <v>45705</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3867,7 +3867,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 5812-2022</t>
+          <t>A 9686-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3881,10 +3881,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44596</v>
+        <v>44984</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3940,7 +3940,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 38173-2023</t>
+          <t>A 7016-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45161</v>
+        <v>45701</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3969,8 +3969,13 @@
           <t>ESLÖV</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4013,7 +4018,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 15357-2023</t>
+          <t>A 24115-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4027,10 +4032,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45019</v>
+        <v>44725</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4043,7 +4048,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>4.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4086,7 +4091,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 49137-2024</t>
+          <t>A 14386-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4100,10 +4105,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45594</v>
+        <v>46100</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4116,7 +4121,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.4</v>
+        <v>12.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4159,7 +4164,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 47870-2025</t>
+          <t>A 25388-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4173,10 +4178,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45932</v>
+        <v>45089</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4189,7 +4194,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>6.8</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4232,7 +4237,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 32984-2024</t>
+          <t>A 12079-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4246,10 +4251,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45517</v>
+        <v>45377</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4262,7 +4267,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.9</v>
+        <v>6.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4305,7 +4310,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 16792-2024</t>
+          <t>A 18281-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4319,10 +4324,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45411</v>
+        <v>46125</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4335,7 +4340,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4378,7 +4383,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 58721-2025</t>
+          <t>A 11204-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4392,10 +4397,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45986</v>
+        <v>44992</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4408,7 +4413,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4451,7 +4456,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 28088-2025</t>
+          <t>A 9482-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4465,10 +4470,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45817</v>
+        <v>44981</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4481,7 +4486,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4524,7 +4529,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 9849-2026</t>
+          <t>A 15533-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4538,10 +4543,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46072</v>
+        <v>45401</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4554,7 +4559,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.5</v>
+        <v>7.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4597,7 +4602,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 14386-2026</t>
+          <t>A 62496-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4611,10 +4616,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46100</v>
+        <v>45268</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4627,7 +4632,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>12.4</v>
+        <v>2.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4670,7 +4675,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 9482-2023</t>
+          <t>A 25385-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4684,10 +4689,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44981</v>
+        <v>45089</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4700,7 +4705,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4743,7 +4748,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 25385-2023</t>
+          <t>A 58721-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4757,10 +4762,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45089</v>
+        <v>45986</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4773,7 +4778,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4816,7 +4821,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 18281-2026</t>
+          <t>A 34170-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4830,10 +4835,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46125</v>
+        <v>45138</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4846,7 +4851,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.8</v>
+        <v>5.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4889,7 +4894,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 43808-2024</t>
+          <t>A 22134-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4899,14 +4904,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45571</v>
+        <v>46153</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4919,7 +4924,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4962,7 +4967,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 22134-2026</t>
+          <t>A 15357-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4976,10 +4981,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46153</v>
+        <v>45019</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4992,7 +4997,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5035,7 +5040,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 11204-2023</t>
+          <t>A 36761-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5049,10 +5054,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44992</v>
+        <v>44805</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5065,7 +5070,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.7</v>
+        <v>4.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5108,7 +5113,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 25508-2023</t>
+          <t>A 18503-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5122,10 +5127,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45089</v>
+        <v>46127</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5138,7 +5143,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.4</v>
+        <v>4.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5181,7 +5186,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 9686-2023</t>
+          <t>A 10819-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5195,10 +5200,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44984</v>
+        <v>46078</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5211,7 +5216,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.8</v>
+        <v>4.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5254,7 +5259,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 7409-2025</t>
+          <t>A 34468-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5268,10 +5273,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45705</v>
+        <v>45139</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5284,7 +5289,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5327,7 +5332,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 36761-2022</t>
+          <t>A 1574-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5341,10 +5346,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44805</v>
+        <v>45306</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5357,7 +5362,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5400,7 +5405,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 25388-2023</t>
+          <t>A 26165-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5414,10 +5419,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45089</v>
+        <v>46181</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5430,7 +5435,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5473,7 +5478,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 10940-2024</t>
+          <t>A 26169-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5487,10 +5492,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45370</v>
+        <v>46181</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5503,7 +5508,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5546,7 +5551,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 7016-2025</t>
+          <t>A 26497-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5560,10 +5565,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45701</v>
+        <v>46183</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5575,13 +5580,8 @@
           <t>ESLÖV</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5624,7 +5624,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 16670-2025</t>
+          <t>A 10940-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45754</v>
+        <v>45370</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5697,7 +5697,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 34468-2023</t>
+          <t>A 11221-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45139</v>
+        <v>45371</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>5.5</v>
+        <v>0.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5770,7 +5770,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 62496-2023</t>
+          <t>A 43808-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5780,14 +5780,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45268</v>
+        <v>45571</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5843,7 +5843,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 34170-2023</t>
+          <t>A 9484-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5857,10 +5857,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45138</v>
+        <v>44981</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>5.8</v>
+        <v>1.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5916,7 +5916,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 24115-2022</t>
+          <t>A 9849-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5930,10 +5930,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44725</v>
+        <v>46072</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>

--- a/Översikt ESLÖV.xlsx
+++ b/Översikt ESLÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45307</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45615</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44960</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>44846</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>45817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>45793</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>46100</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>44981</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>45306</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>45225</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>45426</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>45799</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>46098</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>45645</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>44553</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>44690</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 44496-2023</t>
+          <t>A 33865-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45189</v>
+        <v>45520</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2334,7 +2334,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 33865-2024</t>
+          <t>A 11204-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45520</v>
+        <v>44992</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 16670-2025</t>
+          <t>A 25508-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45754</v>
+        <v>45089</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 34466-2023</t>
+          <t>A 5812-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45139</v>
+        <v>44596</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.3</v>
+        <v>0.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 38173-2023</t>
+          <t>A 9686-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45161</v>
+        <v>44984</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2626,7 +2626,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 47356-2025</t>
+          <t>A 12079-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45930</v>
+        <v>45377</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.6</v>
+        <v>6.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2699,7 +2699,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 27439-2026</t>
+          <t>A 15533-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46189</v>
+        <v>45401</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.6</v>
+        <v>7.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2772,7 +2772,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 25508-2023</t>
+          <t>A 38173-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45089</v>
+        <v>45161</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 27428-2026</t>
+          <t>A 11221-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46189</v>
+        <v>45371</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.4</v>
+        <v>0.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2918,7 +2918,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 27435-2026</t>
+          <t>A 15467-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46189</v>
+        <v>45747</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2991,7 +2991,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 35996-2025</t>
+          <t>A 15357-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45863</v>
+        <v>45019</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3064,7 +3064,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 35997-2025</t>
+          <t>A 7409-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3078,10 +3078,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45863</v>
+        <v>45705</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3137,7 +3137,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 49137-2024</t>
+          <t>A 5869-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3147,14 +3147,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45594</v>
+        <v>44958</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3210,7 +3210,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 32984-2024</t>
+          <t>A 36761-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45517</v>
+        <v>44805</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.9</v>
+        <v>4.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3283,7 +3283,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 16733-2023</t>
+          <t>A 25388-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45030</v>
+        <v>45089</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 16792-2024</t>
+          <t>A 9482-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45411</v>
+        <v>44981</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.9</v>
+        <v>3.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3429,7 +3429,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 28088-2025</t>
+          <t>A 47356-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45817</v>
+        <v>45930</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3502,7 +3502,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 5812-2022</t>
+          <t>A 25385-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44596</v>
+        <v>45089</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3575,7 +3575,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 47870-2025</t>
+          <t>A 43808-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3585,14 +3585,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45932</v>
+        <v>45571</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>6.8</v>
+        <v>1.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3648,7 +3648,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 15467-2025</t>
+          <t>A 10940-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3662,10 +3662,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45747</v>
+        <v>45370</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3721,7 +3721,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 5869-2023</t>
+          <t>A 35996-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3731,14 +3731,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44958</v>
+        <v>45863</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3794,7 +3794,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 7409-2025</t>
+          <t>A 35997-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45705</v>
+        <v>45863</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3867,7 +3867,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 9686-2023</t>
+          <t>A 49137-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3881,10 +3881,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44984</v>
+        <v>45594</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3957,7 +3957,7 @@
         <v>45701</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 24115-2022</t>
+          <t>A 47870-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4032,10 +4032,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44725</v>
+        <v>45932</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4091,7 +4091,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 14386-2026</t>
+          <t>A 32984-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46100</v>
+        <v>45517</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>12.4</v>
+        <v>2.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4164,7 +4164,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 25388-2023</t>
+          <t>A 16670-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4178,10 +4178,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45089</v>
+        <v>45754</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4237,7 +4237,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 12079-2024</t>
+          <t>A 34468-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4251,10 +4251,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45377</v>
+        <v>45139</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>6.9</v>
+        <v>5.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4310,7 +4310,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 18281-2026</t>
+          <t>A 16792-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4324,10 +4324,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46125</v>
+        <v>45411</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4383,7 +4383,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 11204-2023</t>
+          <t>A 62496-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4397,10 +4397,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44992</v>
+        <v>45268</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4456,7 +4456,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 9482-2023</t>
+          <t>A 14386-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4470,10 +4470,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44981</v>
+        <v>46100</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4486,7 +4486,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.7</v>
+        <v>12.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4529,7 +4529,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 15533-2024</t>
+          <t>A 58721-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4543,10 +4543,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45401</v>
+        <v>45986</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>7.5</v>
+        <v>2.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4602,7 +4602,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 62496-2023</t>
+          <t>A 34170-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4616,10 +4616,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45268</v>
+        <v>45138</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.6</v>
+        <v>5.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4675,7 +4675,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 25385-2023</t>
+          <t>A 24115-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45089</v>
+        <v>44725</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.7</v>
+        <v>4.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 58721-2025</t>
+          <t>A 18281-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4762,10 +4762,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45986</v>
+        <v>46125</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4821,7 +4821,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 34170-2023</t>
+          <t>A 28088-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4835,10 +4835,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45138</v>
+        <v>45817</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>5.8</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4894,7 +4894,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 22134-2026</t>
+          <t>A 9484-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46153</v>
+        <v>44981</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4967,7 +4967,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 15357-2023</t>
+          <t>A 16733-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4981,10 +4981,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45019</v>
+        <v>45030</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5040,7 +5040,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 36761-2022</t>
+          <t>A 44496-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5054,10 +5054,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44805</v>
+        <v>45189</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>4.8</v>
+        <v>0.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5113,7 +5113,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 18503-2026</t>
+          <t>A 34466-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5127,10 +5127,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46127</v>
+        <v>45139</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5186,7 +5186,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 10819-2026</t>
+          <t>A 22134-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5200,10 +5200,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46078</v>
+        <v>46153</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4.9</v>
+        <v>2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5259,7 +5259,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 34468-2023</t>
+          <t>A 9849-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5273,10 +5273,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45139</v>
+        <v>46072</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5332,7 +5332,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 1574-2024</t>
+          <t>A 18503-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5346,10 +5346,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45306</v>
+        <v>46127</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5405,7 +5405,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 26165-2026</t>
+          <t>A 10819-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5419,10 +5419,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46181</v>
+        <v>46078</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2</v>
+        <v>4.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5478,7 +5478,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 26169-2026</t>
+          <t>A 1574-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5492,10 +5492,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46181</v>
+        <v>45306</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5551,7 +5551,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 26497-2026</t>
+          <t>A 26165-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46183</v>
+        <v>46181</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5624,7 +5624,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 10940-2024</t>
+          <t>A 26169-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45370</v>
+        <v>46181</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5697,7 +5697,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 11221-2024</t>
+          <t>A 26497-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45371</v>
+        <v>46183</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5770,7 +5770,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 43808-2024</t>
+          <t>A 27428-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5780,14 +5780,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45571</v>
+        <v>46189</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5843,7 +5843,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 9484-2023</t>
+          <t>A 27439-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5857,10 +5857,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44981</v>
+        <v>46189</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5916,7 +5916,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 9849-2026</t>
+          <t>A 27435-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5930,10 +5930,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46072</v>
+        <v>46189</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>

--- a/Översikt ESLÖV.xlsx
+++ b/Översikt ESLÖV.xlsx
@@ -601,7 +601,7 @@
         <v>45307</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45615</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44960</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>44846</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>45817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>45793</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 14395-2026</t>
+          <t>A 9487-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46100</v>
+        <v>44981</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4.9</v>
+        <v>1.9</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1295,13 +1295,13 @@
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1313,162 +1313,162 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
       </c>
       <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Älg
+Kambräken</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 9487-2023 artfynd.xlsx", "A 9487-2023")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 9487-2023 karta.png", "A 9487-2023")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 9487-2023 georefererad karta.tif", "A 9487-2023")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 9487-2023 FSC-klagomål.docx", "A 9487-2023")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 9487-2023 FSC-klagomål mail.docx", "A 9487-2023")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 9487-2023 tillsynsbegäran.docx", "A 9487-2023")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 9487-2023 tillsynsbegäran mail.docx", "A 9487-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 14395-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>46100</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ESLÖV</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
         <v>4</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Ask
 Kransrams</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14395-2026 artfynd.xlsx", "A 14395-2026")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14395-2026 karta.png", "A 14395-2026")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14395-2026 georefererad karta.tif", "A 14395-2026")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14395-2026 FSC-klagomål.docx", "A 14395-2026")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14395-2026 FSC-klagomål mail.docx", "A 14395-2026")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14395-2026 tillsynsbegäran.docx", "A 14395-2026")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14395-2026 tillsynsbegäran mail.docx", "A 14395-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 9487-2023</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>44981</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46323</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>ESLÖV</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Älg
-Kambräken</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 9487-2023 artfynd.xlsx", "A 9487-2023")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 9487-2023 karta.png", "A 9487-2023")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 9487-2023 georefererad karta.tif", "A 9487-2023")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 9487-2023 FSC-klagomål.docx", "A 9487-2023")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 9487-2023 FSC-klagomål mail.docx", "A 9487-2023")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 9487-2023 tillsynsbegäran.docx", "A 9487-2023")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 9487-2023 tillsynsbegäran mail.docx", "A 9487-2023")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 1510-2024</t>
+          <t>A 24809-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1482,10 +1482,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45306</v>
+        <v>45799</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1519,10 +1519,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1538,46 +1538,46 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Svart stork</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 1510-2024 artfynd.xlsx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 24809-2025 artfynd.xlsx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 1510-2024 karta.png", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 24809-2025 karta.png", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 1510-2024 georefererad karta.tif", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 24809-2025 georefererad karta.tif", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 1510-2024 FSC-klagomål.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 24809-2025 FSC-klagomål.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 1510-2024 FSC-klagomål mail.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 24809-2025 FSC-klagomål mail.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 1510-2024 tillsynsbegäran.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 24809-2025 tillsynsbegäran.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 1510-2024 tillsynsbegäran mail.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 24809-2025 tillsynsbegäran mail.docx", "A 24809-2025")</f>
         <v/>
       </c>
       <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 1510-2024 prioriterade fågelarter.docx", "A 1510-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 24809-2025 prioriterade fågelarter.docx", "A 24809-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 52652-2023</t>
+          <t>A 61035-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45225</v>
+        <v>45645</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1607,19 +1607,19 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.9</v>
+        <v>7.6</v>
       </c>
       <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>1</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1634,55 +1634,55 @@
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Grönfläckig padda</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 52652-2023 artfynd.xlsx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 61035-2024 artfynd.xlsx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 52652-2023 karta.png", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 61035-2024 karta.png", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 52652-2023 georefererad karta.tif", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 61035-2024 georefererad karta.tif", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 52652-2023 FSC-klagomål.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 61035-2024 FSC-klagomål.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 52652-2023 FSC-klagomål mail.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 61035-2024 FSC-klagomål mail.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 52652-2023 tillsynsbegäran.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 61035-2024 tillsynsbegäran.docx", "A 61035-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 52652-2023 tillsynsbegäran mail.docx", "A 52652-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 61035-2024 tillsynsbegäran mail.docx", "A 61035-2024")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 18713-2024</t>
+          <t>A 14013-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45426</v>
+        <v>46098</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1711,8 +1711,13 @@
           <t>ESLÖV</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>4.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1724,7 +1729,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1736,10 +1741,10 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1748,46 +1753,50 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Gråtrut</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 18713-2024 artfynd.xlsx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14013-2026 artfynd.xlsx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 18713-2024 karta.png", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14013-2026 karta.png", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 18713-2024 georefererad karta.tif", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14013-2026 georefererad karta.tif", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 18713-2024 FSC-klagomål.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14013-2026 FSC-klagomål.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 18713-2024 FSC-klagomål mail.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14013-2026 FSC-klagomål mail.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 18713-2024 tillsynsbegäran.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14013-2026 tillsynsbegäran.docx", "A 14013-2026")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 18713-2024 tillsynsbegäran mail.docx", "A 18713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14013-2026 tillsynsbegäran mail.docx", "A 14013-2026")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 14013-2026 prioriterade fågelarter.docx", "A 14013-2026")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 24809-2025</t>
+          <t>A 1510-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1801,10 +1810,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45799</v>
+        <v>45306</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1817,7 +1826,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1838,10 +1847,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1857,46 +1866,46 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svart stork</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 24809-2025 artfynd.xlsx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 1510-2024 artfynd.xlsx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 24809-2025 karta.png", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 1510-2024 karta.png", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 24809-2025 georefererad karta.tif", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 1510-2024 georefererad karta.tif", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 24809-2025 FSC-klagomål.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 1510-2024 FSC-klagomål.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 24809-2025 FSC-klagomål mail.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 1510-2024 FSC-klagomål mail.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 24809-2025 tillsynsbegäran.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 1510-2024 tillsynsbegäran.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 24809-2025 tillsynsbegäran mail.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 1510-2024 tillsynsbegäran mail.docx", "A 1510-2024")</f>
         <v/>
       </c>
       <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 24809-2025 prioriterade fågelarter.docx", "A 24809-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 1510-2024 prioriterade fågelarter.docx", "A 1510-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 14013-2026</t>
+          <t>A 52652-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1910,10 +1919,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46098</v>
+        <v>45225</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1925,13 +1934,8 @@
           <t>ESLÖV</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>8.800000000000001</v>
+        <v>2.9</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1943,7 +1947,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1955,10 +1959,10 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1967,50 +1971,46 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Grönfläckig padda</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 14013-2026 artfynd.xlsx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 52652-2023 artfynd.xlsx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 14013-2026 karta.png", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 52652-2023 karta.png", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 14013-2026 georefererad karta.tif", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 52652-2023 georefererad karta.tif", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 14013-2026 FSC-klagomål.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 52652-2023 FSC-klagomål.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 14013-2026 FSC-klagomål mail.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 52652-2023 FSC-klagomål mail.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 14013-2026 tillsynsbegäran.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 52652-2023 tillsynsbegäran.docx", "A 52652-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 14013-2026 tillsynsbegäran mail.docx", "A 14013-2026")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/fåglar/A 14013-2026 prioriterade fågelarter.docx", "A 14013-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 52652-2023 tillsynsbegäran mail.docx", "A 52652-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 61035-2024</t>
+          <t>A 18713-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2024,10 +2024,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45645</v>
+        <v>45426</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2040,19 +2040,19 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>7.6</v>
+        <v>4.1</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2067,48 +2067,48 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Gråtrut</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 61035-2024 artfynd.xlsx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/artfynd/A 18713-2024 artfynd.xlsx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 61035-2024 karta.png", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor/A 18713-2024 karta.png", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 61035-2024 georefererad karta.tif", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/kartor_geotiff/A 18713-2024 georefererad karta.tif", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 61035-2024 FSC-klagomål.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomål/A 18713-2024 FSC-klagomål.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 61035-2024 FSC-klagomål mail.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/klagomålsmail/A 18713-2024 FSC-klagomål mail.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 61035-2024 tillsynsbegäran.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsyn/A 18713-2024 tillsynsbegäran.docx", "A 18713-2024")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 61035-2024 tillsynsbegäran mail.docx", "A 61035-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1285/tillsynsmail/A 18713-2024 tillsynsbegäran mail.docx", "A 18713-2024")</f>
         <v/>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
         <v>44553</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>44690</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 33865-2024</t>
+          <t>A 9482-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45520</v>
+        <v>44981</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.3</v>
+        <v>3.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2334,7 +2334,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 11204-2023</t>
+          <t>A 15533-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44992</v>
+        <v>45401</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.7</v>
+        <v>7.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 25508-2023</t>
+          <t>A 16792-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45089</v>
+        <v>45411</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 5812-2022</t>
+          <t>A 62496-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44596</v>
+        <v>45268</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 9686-2023</t>
+          <t>A 25385-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44984</v>
+        <v>45089</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2626,7 +2626,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 12079-2024</t>
+          <t>A 28088-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45377</v>
+        <v>45817</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>6.9</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2699,7 +2699,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 15533-2024</t>
+          <t>A 34170-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45401</v>
+        <v>45138</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>7.5</v>
+        <v>5.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2772,7 +2772,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 38173-2023</t>
+          <t>A 15357-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45161</v>
+        <v>45019</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 11221-2024</t>
+          <t>A 36761-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45371</v>
+        <v>44805</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.3</v>
+        <v>4.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2918,7 +2918,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 15467-2025</t>
+          <t>A 47356-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45747</v>
+        <v>45930</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
     